--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76824D6D-2E39-4373-B6B4-1311D570A5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FCB2543-A0DC-404A-8BBA-96D9EABAE62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="475">
   <si>
     <t>Time</t>
   </si>
@@ -62,39 +62,333 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/03/2026 5:14:46 PM</t>
+  </si>
+  <si>
+    <t>22970</t>
+  </si>
+  <si>
+    <t>MEYERS, DAVID</t>
+  </si>
+  <si>
+    <t>Air Temperature, Local</t>
+  </si>
+  <si>
+    <t>OTR</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>I 70, Lakewood, CO, 80410</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f8d-abd6-5146-8bb1-64bec70d67ff</t>
+  </si>
+  <si>
+    <t>06/03/2026 3:43:38 PM</t>
+  </si>
+  <si>
+    <t>24910</t>
+  </si>
+  <si>
+    <t>BROUSSEAU, SALLY</t>
+  </si>
+  <si>
+    <t>Air Temperature, OTR</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanya Smith </t>
+  </si>
+  <si>
+    <t>US Highway 287, Washburn, TX</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f3a-39c4-5099-b36c-20f6bb3436bb</t>
+  </si>
+  <si>
+    <t>06/03/2026 5:35:42 AM</t>
+  </si>
+  <si>
+    <t>24688</t>
+  </si>
+  <si>
+    <t>WADE,ADAM</t>
+  </si>
+  <si>
+    <t>Tuskegee Airmen Memorial Highway, Denver, CO, 80238</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458d0d-a730-5e11-9d43-47e13c31e947</t>
+  </si>
+  <si>
+    <t>06/02/2026 1:11:41 PM</t>
+  </si>
+  <si>
+    <t>23470</t>
+  </si>
+  <si>
+    <t>JELTOV, VLADIMIR K.</t>
+  </si>
+  <si>
+    <t>OTR, Safety Pro Test</t>
+  </si>
+  <si>
+    <t>Barstow and Mojave Freeway, 20.0 mi SE Fort Irwin, San Bernardino County, CA</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458988-c24f-5239-8b2f-6ed4002c3d47</t>
+  </si>
+  <si>
+    <t>06/01/2026 1:21:17 PM</t>
+  </si>
+  <si>
+    <t>24632</t>
+  </si>
+  <si>
+    <t>EMERY.SHANE</t>
+  </si>
+  <si>
+    <t>Purple Heart Trail, Williams, AZ</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445846b-2f9b-504c-a5e2-746dc3eb184b</t>
+  </si>
+  <si>
+    <t>06/01/2026 1:03:09 PM</t>
+  </si>
+  <si>
+    <t>I 70, Wheeler Junction, CO</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445845a-93f3-5a28-8c8f-4d792daac76a</t>
+  </si>
+  <si>
+    <t>06/01/2026 8:29:16 AM</t>
+  </si>
+  <si>
+    <t>24677</t>
+  </si>
+  <si>
+    <t>WALLACE, ANDREW</t>
+  </si>
+  <si>
+    <t>Truman/Eisenhower Presidential Highway, 12.3 mi SE Manhattan, Riley County, KS</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445835f-d7b4-5879-807e-486a45440275</t>
+  </si>
+  <si>
+    <t>05/31/2026 12:04:28 PM</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, 83.4 mi N Lamar, Kit Carson County, CO</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457efe-7fb9-5272-9be1-1033b1429e83</t>
+  </si>
+  <si>
+    <t>05/30/2026 11:04:14 AM</t>
+  </si>
+  <si>
+    <t>24679</t>
+  </si>
+  <si>
+    <t>GERVACIO, ARNOLD</t>
+  </si>
+  <si>
+    <t>Las Vegas Freeway, 14.4 mi WSW Moapa Valley, Clark County, NV</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544579a0-ffd5-53f5-ad38-1bb699bee121</t>
+  </si>
+  <si>
+    <t>05/29/2026 4:52:36 PM</t>
+  </si>
+  <si>
+    <t>I 70, 6.4 mi NNW Evergreen, Jefferson County, CO</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544575b9-92fc-55ef-a898-fa27588be6bb</t>
+  </si>
+  <si>
+    <t>05/29/2026 11:37:37 AM</t>
+  </si>
+  <si>
+    <t>Las Vegas Freeway, 17.2 mi NE Sunrise Manor, Clark County, NV</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457499-31c1-5502-bd12-77ecc94be916</t>
+  </si>
+  <si>
+    <t>05/28/2026 12:12:12 PM</t>
+  </si>
+  <si>
+    <t>Construction, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 215, Riverside, CA, 93507</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456f92-7fde-51e0-88a7-c63bcd50ad87</t>
+  </si>
+  <si>
+    <t>05/27/2026 4:38:39 PM</t>
+  </si>
+  <si>
+    <t>23471</t>
+  </si>
+  <si>
+    <t>TREVIZO, ESTABAN I.</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, Commerce City, CO, 80266</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b60-14f9-5a48-9d21-698da447b93c</t>
+  </si>
+  <si>
+    <t>05/27/2026 11:08:19 AM</t>
+  </si>
+  <si>
+    <t>Las Vegas Freeway, North Las Vegas, NV, 89165</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a31-a5a8-5e7e-b93a-9a5ca0fa096a</t>
+  </si>
+  <si>
+    <t>05/26/2026 3:34:06 PM</t>
+  </si>
+  <si>
+    <t>I 70, Silt, CO, 81652</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544565fe-a10f-5965-a302-83a8e3584b11</t>
+  </si>
+  <si>
+    <t>05/26/2026 3:20:19 PM</t>
+  </si>
+  <si>
+    <t>22003</t>
+  </si>
+  <si>
+    <t>ACKERMAN, JASON B.</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Riverside Freeway, Anaheim, CA, 92817</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544565f2-020f-5dd3-a972-2e172d1dd4b2</t>
+  </si>
+  <si>
+    <t>05/25/2026 5:35:28 PM</t>
+  </si>
+  <si>
+    <t>Needles Freeway, 19.9 mi NW Lake Havasu City, San Bernardino County, CA, 92363</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456147-62b9-5147-8973-5d0101640dd4</t>
+  </si>
+  <si>
+    <t>05/25/2026 11:15:21 AM</t>
+  </si>
+  <si>
+    <t>Veterans Memorial Highway, 15.6 mi SSW Santa Clara, Mohave County, AZ</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455feb-5f71-5eba-be9e-a36e01923dc2</t>
+  </si>
+  <si>
+    <t>05/24/2026 9:35:31 AM</t>
+  </si>
+  <si>
+    <t>4490 I 70;US 6, Georgetown, CO, 80452</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455a69-9c9f-597a-a394-68472b8c2b7f</t>
+  </si>
+  <si>
+    <t>05/22/2026 3:18:28 PM</t>
+  </si>
+  <si>
+    <t>24911</t>
+  </si>
+  <si>
+    <t>GARCIA, FRANCISCO</t>
+  </si>
+  <si>
+    <t>Gerald R. Ford Memorial Highway, Gypsum, CO, 81637</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455156-dfad-56b2-9565-910122a51df4</t>
+  </si>
+  <si>
     <t>05/21/2026 1:03:45 PM</t>
   </si>
   <si>
-    <t>24632</t>
-  </si>
-  <si>
-    <t>EMERY.SHANE</t>
-  </si>
-  <si>
-    <t>OTR</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
     <t>Kansas Turnpike, 1.9 mi NE Lawrence, Douglas County, KS, 66044:66046</t>
   </si>
   <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454bb5-2fc4-5f6a-b062-ed0090cd46cf</t>
   </si>
   <si>
@@ -113,18 +407,6 @@
     <t>05/20/2026 12:22:51 PM</t>
   </si>
   <si>
-    <t>24677</t>
-  </si>
-  <si>
-    <t>WALLACE, ANDREW</t>
-  </si>
-  <si>
-    <t>Air Temperature, OTR</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>Ronald Reagan Memorial Tollway, Rochelle, IL, 61068</t>
   </si>
   <si>
@@ -149,12 +431,6 @@
     <t>05/19/2026 4:15:44 PM</t>
   </si>
   <si>
-    <t>24688</t>
-  </si>
-  <si>
-    <t>WADE,ADAM</t>
-  </si>
-  <si>
     <t>I 35, Civil Bend, MO, 64689</t>
   </si>
   <si>
@@ -164,18 +440,6 @@
     <t>05/19/2026 1:29:17 PM</t>
   </si>
   <si>
-    <t>23470</t>
-  </si>
-  <si>
-    <t>JELTOV, VLADIMIR K.</t>
-  </si>
-  <si>
-    <t>OTR, Safety Pro Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanya Smith </t>
-  </si>
-  <si>
     <t>I 15, Parowan, UT, 87620</t>
   </si>
   <si>
@@ -188,9 +452,6 @@
     <t>I 70;US 6, Frisco, CO, 80443</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453d61-015a-5d73-ac9b-53f98002fc26</t>
   </si>
   <si>
@@ -200,9 +461,6 @@
     <t>Purple Heart Trail, Flagstaff, AZ</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453c73-853c-5119-8b53-27f347efb4ef</t>
   </si>
   <si>
@@ -227,18 +485,9 @@
     <t>05/15/2026 4:10:22 PM</t>
   </si>
   <si>
-    <t>23471</t>
-  </si>
-  <si>
-    <t>TREVIZO, ESTABAN I.</t>
-  </si>
-  <si>
     <t>I 25, Colorado Springs, CO, 80906</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452d79-df18-50bb-b4e3-cb346e3190f8</t>
   </si>
   <si>
@@ -272,18 +521,9 @@
     <t>05/14/2026 12:37:30 PM</t>
   </si>
   <si>
-    <t>24679</t>
-  </si>
-  <si>
-    <t>GERVACIO, ARNOLD</t>
-  </si>
-  <si>
     <t>I 10, 7.9 mi W Benson, Cochise County, AZ</t>
   </si>
   <si>
-    <t>66</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452790-a126-5449-9239-ef6570957a47</t>
   </si>
   <si>
@@ -371,9 +611,6 @@
     <t>I 10, Loma Linda, CA, 92408-3539</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fabb-9539-57e9-8686-c4f946e17ab4</t>
   </si>
   <si>
@@ -404,9 +641,6 @@
     <t>05/04/2026 4:03:39 PM</t>
   </si>
   <si>
-    <t>I 70, Silt, CO, 81652</t>
-  </si>
-  <si>
     <t>73</t>
   </si>
   <si>
@@ -425,9 +659,6 @@
     <t>I 40, 17.5 mi WSW Gallup, McKinley County, NM, 86308</t>
   </si>
   <si>
-    <t>68</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f3ae-8ef0-529b-ab32-2f61959df938</t>
   </si>
   <si>
@@ -470,9 +701,6 @@
     <t>04/29/2026 12:03:52 PM</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>I 29;US 71, 12.1 mi WNW Smithville, Platte County, MO, 64439</t>
   </si>
   <si>
@@ -503,9 +731,6 @@
     <t>1702 I 25, 4.4 mi ESE Erie, City and County of Broomfield, CO, 80516</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d92b-5897-570f-952f-7d2bd666df23</t>
   </si>
   <si>
@@ -557,9 +782,6 @@
     <t>04/27/2026 1:48:35 PM</t>
   </si>
   <si>
-    <t>Gerald R. Ford Memorial Highway, Gypsum, CO, 81637</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d045-9983-5475-9ca4-258c86e3f735</t>
   </si>
   <si>
@@ -587,12 +809,6 @@
     <t>04/25/2026 1:09:23 PM</t>
   </si>
   <si>
-    <t>24911</t>
-  </si>
-  <si>
-    <t>GARCIA, FRANCISCO</t>
-  </si>
-  <si>
     <t>I 70, 76.0 mi SSE Brush, Kit Carson County, CO</t>
   </si>
   <si>
@@ -626,9 +842,6 @@
     <t>04/23/2026 2:30:37 PM</t>
   </si>
   <si>
-    <t>Construction, Moderate Traffic</t>
-  </si>
-  <si>
     <t>I 15, 9.4 mi SW Cedar City, Iron County, UT, 84742</t>
   </si>
   <si>
@@ -674,9 +887,6 @@
     <t>Needles Freeway, 53.5 mi NE Twentynine Palms, San Bernardino County, CA</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ad06-38a7-50b3-b5c5-69248d4d182e</t>
   </si>
   <si>
@@ -719,15 +929,6 @@
     <t>04/17/2026 12:36:30 PM</t>
   </si>
   <si>
-    <t>22970</t>
-  </si>
-  <si>
-    <t>MEYERS, DAVID</t>
-  </si>
-  <si>
-    <t>Air Temperature, Local</t>
-  </si>
-  <si>
     <t>Harsh Brake, Defensive Driving</t>
   </si>
   <si>
@@ -764,9 +965,6 @@
     <t>Veterans Memorial Highway, St. George, UT</t>
   </si>
   <si>
-    <t>74</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445948b-d4e5-570d-a292-d7620cbbd82b</t>
   </si>
   <si>
@@ -839,9 +1037,6 @@
     <t>04/07/2026 2:58:08 PM</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>5822 Palmer Park Boulevard, Cimarron Hills, CO, 80915</t>
   </si>
   <si>
@@ -971,12 +1166,6 @@
     <t>03/27/2026 9:14:50 AM</t>
   </si>
   <si>
-    <t>22003</t>
-  </si>
-  <si>
-    <t>ACKERMAN, JASON B.</t>
-  </si>
-  <si>
     <t>I 70;US 6, 11.3 mi NE Clifton, Mesa County, CO</t>
   </si>
   <si>
@@ -1251,303 +1440,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d3a3-4362-5968-b3cb-e1586f94d629</t>
-  </si>
-  <si>
-    <t>03/07/2026 4:30:09 PM</t>
-  </si>
-  <si>
-    <t>I 80, 4.6 mi ESE Kearney, Buffalo County, NE, 68848</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ca6c-1e52-519a-b22e-5f240ae372b9</t>
-  </si>
-  <si>
-    <t>03/07/2026 4:04:20 PM</t>
-  </si>
-  <si>
-    <t>I 25, 15.0 mi W Eldorado at Santa Fe, Santa Fe County, NM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ca54-7e81-52e1-b0e7-6c0d0d56bad3</t>
-  </si>
-  <si>
-    <t>03/06/2026 11:55:39 PM</t>
-  </si>
-  <si>
-    <t>NEWSON, THOMAS</t>
-  </si>
-  <si>
-    <t>Rolling Stop</t>
-  </si>
-  <si>
-    <t>Watkins Drive, Riverside, CA, 92507</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c6dd-a34e-52b8-9baa-7575f1e6c81a</t>
-  </si>
-  <si>
-    <t>03/06/2026 6:38:34 PM</t>
-  </si>
-  <si>
-    <t>23468</t>
-  </si>
-  <si>
-    <t>IVANOV, ALEXANDER G.</t>
-  </si>
-  <si>
-    <t>Doctor James E. and Representative Mina M. Hibdon Memorial Highway, Norman, OK</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c5bb-54c4-54e5-8ce6-ebfc5354f6c9</t>
-  </si>
-  <si>
-    <t>03/06/2026 2:30:07 PM</t>
-  </si>
-  <si>
-    <t>Snowy Road, Light Traffic, Snowing</t>
-  </si>
-  <si>
-    <t>I 25, Fountain, CO, 8017</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c4d7-e032-5cb7-bc2b-16f78c7de037</t>
-  </si>
-  <si>
-    <t>03/05/2026 6:25:05 PM</t>
-  </si>
-  <si>
-    <t>I 76, Zuni, CO, 80221</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c088-a2c6-5752-85a1-b166d56a7a14</t>
-  </si>
-  <si>
-    <t>03/05/2026 6:05:37 PM</t>
-  </si>
-  <si>
-    <t>I 70, 46.1 mi E The Pinery, Elbert County, CO, 80264</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c076-ce71-5371-b59b-3ce66fb6681f</t>
-  </si>
-  <si>
-    <t>03/03/2026 6:34:50 PM</t>
-  </si>
-  <si>
-    <t>Helen Cole Memorial Highway, Moore, OK, 73160</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b644-d411-5d41-b556-0e23fe4ebca6</t>
-  </si>
-  <si>
-    <t>03/03/2026 3:02:55 PM</t>
-  </si>
-  <si>
-    <t>I 40, 17.5 mi ESE Grants, Cibola County, NM, 87034</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b582-d2bc-5fec-94bc-db8b944d5b34</t>
-  </si>
-  <si>
-    <t>03/03/2026 1:56:17 PM</t>
-  </si>
-  <si>
-    <t>Lane Departure</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b545-d27f-5d89-aaba-e445d3d7f145</t>
-  </si>
-  <si>
-    <t>03/02/2026 10:09:13 AM</t>
-  </si>
-  <si>
-    <t>Harsh Turn</t>
-  </si>
-  <si>
-    <t>West Richey Road, 5.3 mi NNW Aldine, Harris County, TX, 77090</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445af4f-9281-5896-8c88-d3a8d1f4ef7c</t>
-  </si>
-  <si>
-    <t>02/27/2026 11:33:20 PM</t>
-  </si>
-  <si>
-    <t>Foothill Freeway, Pasadena, CA, 91101:91106</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a2bc-af38-5c31-a0f6-106bf4266d7a</t>
-  </si>
-  <si>
-    <t>02/26/2026 7:35:26 PM</t>
-  </si>
-  <si>
-    <t>I 25, Frederick, CO, 80504-3546</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459cbc-870c-562b-a50a-b65469142f5c</t>
-  </si>
-  <si>
-    <t>02/26/2026 4:54:28 PM</t>
-  </si>
-  <si>
-    <t>I 15, Beaver, UT</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459c29-27c4-5339-9be6-068c07424405</t>
-  </si>
-  <si>
-    <t>02/25/2026 4:44:31 PM</t>
-  </si>
-  <si>
-    <t>24690</t>
-  </si>
-  <si>
-    <t>MOORE, ROYCE</t>
-  </si>
-  <si>
-    <t>2438 KS 128, 36.1 mi W Concordia, Mitchell County, KS, 67446</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544596f9-aeee-550d-98c9-3d7df961c2b8</t>
-  </si>
-  <si>
-    <t>02/25/2026 3:47:08 PM</t>
-  </si>
-  <si>
-    <t>San Gabriel River Freeway, Irwindale, CA, 91010</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544596c5-255e-500e-b8d9-1e0571e56d36</t>
-  </si>
-  <si>
-    <t>02/25/2026 12:19:32 PM</t>
-  </si>
-  <si>
-    <t>I 40, Milan, NM, 87021</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459607-16bf-5519-93bd-8f62f2829d60</t>
-  </si>
-  <si>
-    <t>02/25/2026 9:45:30 AM</t>
-  </si>
-  <si>
-    <t>Katy Freeway, Katy, TX, 77493</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445957a-0df2-5da8-8942-f5e12a9c00ec</t>
-  </si>
-  <si>
-    <t>02/25/2026 8:09:44 AM</t>
-  </si>
-  <si>
-    <t>Ronald Reagan Memorial Tollway, Nachusa, IL, 61006</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459522-638a-5ffe-8729-cf7214a2ad70</t>
-  </si>
-  <si>
-    <t>02/24/2026 6:56:38 PM</t>
-  </si>
-  <si>
-    <t>Purple Heart Trail, 24.8 mi NNE Lake Havasu City, Mohave County, AZ</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445924c-458d-5a08-92d6-7b5cfe873ad6</t>
-  </si>
-  <si>
-    <t>02/24/2026 5:30:30 PM</t>
-  </si>
-  <si>
-    <t>San Bernardino Freeway, Colton, CA, 92324</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544591fd-6a53-5704-8a2f-379626db5a93</t>
-  </si>
-  <si>
-    <t>02/24/2026 3:37:56 PM</t>
-  </si>
-  <si>
-    <t>Ontario Freeway, 6.3 mi NW Muscoy, San Bernardino County, CA, 92407</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459196-5de8-52e6-8de8-b57dc16bb640</t>
-  </si>
-  <si>
-    <t>02/24/2026 1:50:41 PM</t>
-  </si>
-  <si>
-    <t>Purple Heart Trail, Winslow, AZ, 86047-4122</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459134-2bf1-56d0-922d-2088c7b5a7d9</t>
-  </si>
-  <si>
-    <t>02/24/2026 1:01:57 PM</t>
-  </si>
-  <si>
-    <t>Mojave Freeway, Beacon Station, CA</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459107-8fa2-50c3-9924-b52dc9b3915e</t>
-  </si>
-  <si>
-    <t>02/24/2026 9:23:33 AM</t>
-  </si>
-  <si>
-    <t>World War I Veterans Memorial Highway, 6.2 mi NW Pauls Valley, Garvin County, OK, 73074</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445903f-9c8e-5789-919d-9cd92c4023b0</t>
-  </si>
-  <si>
-    <t>02/24/2026 9:08:25 AM</t>
-  </si>
-  <si>
-    <t>World War I Veterans Memorial Highway, Purcell, OK, 73080</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459031-c122-5003-9970-d51ddef5d4f1</t>
-  </si>
-  <si>
-    <t>02/24/2026 9:06:45 AM</t>
-  </si>
-  <si>
-    <t>Veterans Memorial Highway, Washington, UT, 84690</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459030-3a89-59d5-99d4-d9844a7e869a</t>
-  </si>
-  <si>
-    <t>02/24/2026 8:05:10 AM</t>
-  </si>
-  <si>
-    <t>Shannon Miller Parkway, Edmond, OK, 73129</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458ff7-d760-5225-b518-cdab524ff532</t>
   </si>
 </sst>
 </file>
@@ -1924,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1988,418 +1880,418 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K7" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="L10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
         <v>44</v>
@@ -2408,1259 +2300,1259 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="L11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K16" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K17" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="O17" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K18" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J19" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K19" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="L19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O19" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K20" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="L20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I21" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J21" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K21" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I22" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K22" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="L22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O22" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I23" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="K23" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="L23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="K24" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K25" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="L25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="J27" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K27" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="L27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K28" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K29" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="L29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K30" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="L30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H31" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K31" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H32" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K32" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="L32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" t="s">
         <v>159</v>
       </c>
-      <c r="D33" t="s">
+      <c r="K33" t="s">
         <v>160</v>
       </c>
-      <c r="E33" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" t="s">
-        <v>52</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="L33" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" t="s">
+        <v>26</v>
+      </c>
+      <c r="O33" t="s">
         <v>161</v>
-      </c>
-      <c r="K33" t="s">
-        <v>162</v>
-      </c>
-      <c r="L33" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" t="s">
-        <v>25</v>
-      </c>
-      <c r="N33" t="s">
-        <v>25</v>
-      </c>
-      <c r="O33" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" t="s">
         <v>164</v>
       </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
+        <v>66</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" t="s">
         <v>165</v>
       </c>
-      <c r="H34" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
+        <v>109</v>
+      </c>
+      <c r="L34" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" t="s">
+        <v>26</v>
+      </c>
+      <c r="O34" t="s">
         <v>166</v>
-      </c>
-      <c r="K34" t="s">
-        <v>57</v>
-      </c>
-      <c r="L34" t="s">
-        <v>25</v>
-      </c>
-      <c r="M34" t="s">
-        <v>25</v>
-      </c>
-      <c r="N34" t="s">
-        <v>25</v>
-      </c>
-      <c r="O34" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>167</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" t="s">
+        <v>66</v>
+      </c>
+      <c r="I35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" t="s">
         <v>168</v>
       </c>
-      <c r="B35" t="s">
-        <v>139</v>
-      </c>
-      <c r="C35" t="s">
-        <v>140</v>
-      </c>
-      <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="K35" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" t="s">
+        <v>26</v>
+      </c>
+      <c r="O35" t="s">
         <v>169</v>
-      </c>
-      <c r="H35" t="s">
-        <v>151</v>
-      </c>
-      <c r="I35" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" t="s">
-        <v>170</v>
-      </c>
-      <c r="K35" t="s">
-        <v>37</v>
-      </c>
-      <c r="L35" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" t="s">
-        <v>25</v>
-      </c>
-      <c r="N35" t="s">
-        <v>25</v>
-      </c>
-      <c r="O35" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" t="s">
+        <v>66</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" t="s">
+        <v>171</v>
+      </c>
+      <c r="K36" t="s">
         <v>172</v>
       </c>
-      <c r="B36" t="s">
-        <v>158</v>
-      </c>
-      <c r="C36" t="s">
-        <v>159</v>
-      </c>
-      <c r="D36" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" t="s">
-        <v>18</v>
-      </c>
-      <c r="F36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" t="s">
-        <v>151</v>
-      </c>
-      <c r="I36" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="L36" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>26</v>
+      </c>
+      <c r="O36" t="s">
         <v>173</v>
-      </c>
-      <c r="K36" t="s">
-        <v>174</v>
-      </c>
-      <c r="L36" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" t="s">
-        <v>25</v>
-      </c>
-      <c r="N36" t="s">
-        <v>25</v>
-      </c>
-      <c r="O36" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" t="s">
+        <v>175</v>
+      </c>
+      <c r="C37" t="s">
         <v>176</v>
       </c>
-      <c r="B37" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" t="s">
-        <v>50</v>
-      </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H37" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J37" t="s">
         <v>177</v>
       </c>
       <c r="K37" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O37" t="s">
         <v>178</v>
@@ -3671,43 +3563,43 @@
         <v>179</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>163</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H38" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J38" t="s">
         <v>180</v>
       </c>
       <c r="K38" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="L38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O38" t="s">
         <v>181</v>
@@ -3718,513 +3610,513 @@
         <v>182</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" t="s">
+        <v>66</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" t="s">
         <v>183</v>
       </c>
-      <c r="H39" t="s">
-        <v>151</v>
-      </c>
-      <c r="I39" t="s">
-        <v>22</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" t="s">
+        <v>26</v>
+      </c>
+      <c r="O39" t="s">
         <v>184</v>
-      </c>
-      <c r="K39" t="s">
-        <v>162</v>
-      </c>
-      <c r="L39" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" t="s">
-        <v>25</v>
-      </c>
-      <c r="N39" t="s">
-        <v>25</v>
-      </c>
-      <c r="O39" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" t="s">
         <v>186</v>
       </c>
-      <c r="B40" t="s">
-        <v>106</v>
-      </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H40" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K40" t="s">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="L40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
-        <v>190</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" t="s">
+        <v>66</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" t="s">
         <v>191</v>
       </c>
-      <c r="D41" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" t="s">
-        <v>19</v>
-      </c>
-      <c r="G41" t="s">
-        <v>35</v>
-      </c>
-      <c r="H41" t="s">
-        <v>151</v>
-      </c>
-      <c r="I41" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
+        <v>135</v>
+      </c>
+      <c r="L41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" t="s">
+        <v>26</v>
+      </c>
+      <c r="O41" t="s">
         <v>192</v>
-      </c>
-      <c r="K41" t="s">
-        <v>136</v>
-      </c>
-      <c r="L41" t="s">
-        <v>25</v>
-      </c>
-      <c r="M41" t="s">
-        <v>25</v>
-      </c>
-      <c r="N41" t="s">
-        <v>25</v>
-      </c>
-      <c r="O41" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>193</v>
+      </c>
+      <c r="B42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" t="s">
+        <v>32</v>
+      </c>
+      <c r="H42" t="s">
+        <v>66</v>
+      </c>
+      <c r="I42" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" t="s">
         <v>194</v>
       </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" t="s">
-        <v>18</v>
-      </c>
-      <c r="F42" t="s">
-        <v>19</v>
-      </c>
-      <c r="G42" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" t="s">
-        <v>151</v>
-      </c>
-      <c r="I42" t="s">
-        <v>22</v>
-      </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
+        <v>127</v>
+      </c>
+      <c r="L42" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" t="s">
+        <v>26</v>
+      </c>
+      <c r="O42" t="s">
         <v>195</v>
-      </c>
-      <c r="K42" t="s">
-        <v>92</v>
-      </c>
-      <c r="L42" t="s">
-        <v>25</v>
-      </c>
-      <c r="M42" t="s">
-        <v>25</v>
-      </c>
-      <c r="N42" t="s">
-        <v>25</v>
-      </c>
-      <c r="O42" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>196</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" t="s">
+        <v>66</v>
+      </c>
+      <c r="I43" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" t="s">
         <v>197</v>
       </c>
-      <c r="B43" t="s">
+      <c r="K43" t="s">
+        <v>41</v>
+      </c>
+      <c r="L43" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" t="s">
+        <v>26</v>
+      </c>
+      <c r="O43" t="s">
         <v>198</v>
-      </c>
-      <c r="C43" t="s">
-        <v>199</v>
-      </c>
-      <c r="D43" t="s">
-        <v>34</v>
-      </c>
-      <c r="E43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" t="s">
-        <v>19</v>
-      </c>
-      <c r="G43" t="s">
-        <v>35</v>
-      </c>
-      <c r="H43" t="s">
-        <v>151</v>
-      </c>
-      <c r="I43" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" t="s">
-        <v>200</v>
-      </c>
-      <c r="K43" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43" t="s">
-        <v>25</v>
-      </c>
-      <c r="M43" t="s">
-        <v>25</v>
-      </c>
-      <c r="N43" t="s">
-        <v>25</v>
-      </c>
-      <c r="O43" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>199</v>
+      </c>
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" t="s">
+        <v>200</v>
+      </c>
+      <c r="H44" t="s">
+        <v>66</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" t="s">
+        <v>201</v>
+      </c>
+      <c r="K44" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" t="s">
+        <v>26</v>
+      </c>
+      <c r="O44" t="s">
         <v>202</v>
-      </c>
-      <c r="B44" t="s">
-        <v>133</v>
-      </c>
-      <c r="C44" t="s">
-        <v>134</v>
-      </c>
-      <c r="D44" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" t="s">
-        <v>203</v>
-      </c>
-      <c r="H44" t="s">
-        <v>151</v>
-      </c>
-      <c r="I44" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" t="s">
-        <v>204</v>
-      </c>
-      <c r="K44" t="s">
-        <v>136</v>
-      </c>
-      <c r="L44" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" t="s">
-        <v>25</v>
-      </c>
-      <c r="N44" t="s">
-        <v>25</v>
-      </c>
-      <c r="O44" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>203</v>
+      </c>
+      <c r="B45" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>32</v>
+      </c>
+      <c r="H45" t="s">
+        <v>66</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" t="s">
+        <v>204</v>
+      </c>
+      <c r="K45" t="s">
+        <v>205</v>
+      </c>
+      <c r="L45" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" t="s">
+        <v>26</v>
+      </c>
+      <c r="O45" t="s">
         <v>206</v>
-      </c>
-      <c r="B45" t="s">
-        <v>207</v>
-      </c>
-      <c r="C45" t="s">
-        <v>208</v>
-      </c>
-      <c r="D45" t="s">
-        <v>160</v>
-      </c>
-      <c r="E45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" t="s">
-        <v>35</v>
-      </c>
-      <c r="H45" t="s">
-        <v>151</v>
-      </c>
-      <c r="I45" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" t="s">
-        <v>209</v>
-      </c>
-      <c r="K45" t="s">
-        <v>61</v>
-      </c>
-      <c r="L45" t="s">
-        <v>25</v>
-      </c>
-      <c r="M45" t="s">
-        <v>25</v>
-      </c>
-      <c r="N45" t="s">
-        <v>25</v>
-      </c>
-      <c r="O45" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H46" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J46" t="s">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="L46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O46" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>210</v>
+      </c>
+      <c r="B47" t="s">
+        <v>211</v>
+      </c>
+      <c r="C47" t="s">
+        <v>212</v>
+      </c>
+      <c r="D47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" t="s">
+        <v>66</v>
+      </c>
+      <c r="I47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" t="s">
+        <v>213</v>
+      </c>
+      <c r="K47" t="s">
+        <v>35</v>
+      </c>
+      <c r="L47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" t="s">
+        <v>26</v>
+      </c>
+      <c r="O47" t="s">
         <v>214</v>
-      </c>
-      <c r="B47" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47" t="s">
-        <v>51</v>
-      </c>
-      <c r="E47" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" t="s">
-        <v>19</v>
-      </c>
-      <c r="G47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" t="s">
-        <v>151</v>
-      </c>
-      <c r="I47" t="s">
-        <v>22</v>
-      </c>
-      <c r="J47" t="s">
-        <v>215</v>
-      </c>
-      <c r="K47" t="s">
-        <v>88</v>
-      </c>
-      <c r="L47" t="s">
-        <v>25</v>
-      </c>
-      <c r="M47" t="s">
-        <v>25</v>
-      </c>
-      <c r="N47" t="s">
-        <v>25</v>
-      </c>
-      <c r="O47" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>215</v>
+      </c>
+      <c r="B48" t="s">
+        <v>216</v>
+      </c>
+      <c r="C48" t="s">
         <v>217</v>
       </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="s">
-        <v>17</v>
-      </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H48" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I48" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J48" t="s">
         <v>218</v>
       </c>
       <c r="K48" t="s">
+        <v>109</v>
+      </c>
+      <c r="L48" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" t="s">
+        <v>26</v>
+      </c>
+      <c r="O48" t="s">
         <v>219</v>
-      </c>
-      <c r="L48" t="s">
-        <v>25</v>
-      </c>
-      <c r="M48" t="s">
-        <v>25</v>
-      </c>
-      <c r="N48" t="s">
-        <v>25</v>
-      </c>
-      <c r="O48" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>220</v>
+      </c>
+      <c r="B49" t="s">
+        <v>216</v>
+      </c>
+      <c r="C49" t="s">
+        <v>217</v>
+      </c>
+      <c r="D49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" t="s">
+        <v>66</v>
+      </c>
+      <c r="I49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" t="s">
         <v>221</v>
       </c>
-      <c r="B49" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" t="s">
-        <v>18</v>
-      </c>
-      <c r="F49" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" t="s">
-        <v>35</v>
-      </c>
-      <c r="H49" t="s">
-        <v>151</v>
-      </c>
-      <c r="I49" t="s">
-        <v>22</v>
-      </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>222</v>
       </c>
-      <c r="K49" t="s">
-        <v>130</v>
-      </c>
       <c r="L49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O49" t="s">
         <v>223</v>
@@ -4235,43 +4127,43 @@
         <v>224</v>
       </c>
       <c r="B50" t="s">
-        <v>133</v>
+        <v>186</v>
       </c>
       <c r="C50" t="s">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H50" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I50" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J50" t="s">
         <v>225</v>
       </c>
       <c r="K50" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O50" t="s">
         <v>226</v>
@@ -4282,43 +4174,43 @@
         <v>227</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="C51" t="s">
-        <v>71</v>
+        <v>187</v>
       </c>
       <c r="D51" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H51" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J51" t="s">
         <v>228</v>
       </c>
       <c r="K51" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O51" t="s">
         <v>229</v>
@@ -4329,43 +4221,43 @@
         <v>230</v>
       </c>
       <c r="B52" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C52" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D52" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H52" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I52" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J52" t="s">
         <v>231</v>
       </c>
       <c r="K52" t="s">
-        <v>88</v>
+        <v>222</v>
       </c>
       <c r="L52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O52" t="s">
         <v>232</v>
@@ -4385,2862 +4277,2862 @@
         <v>236</v>
       </c>
       <c r="E53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" t="s">
+        <v>66</v>
+      </c>
+      <c r="I53" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" t="s">
         <v>237</v>
       </c>
-      <c r="G53" t="s">
+      <c r="K53" t="s">
+        <v>25</v>
+      </c>
+      <c r="L53" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" t="s">
+        <v>26</v>
+      </c>
+      <c r="O53" t="s">
         <v>238</v>
-      </c>
-      <c r="H53" t="s">
-        <v>151</v>
-      </c>
-      <c r="I53" t="s">
-        <v>22</v>
-      </c>
-      <c r="J53" t="s">
-        <v>239</v>
-      </c>
-      <c r="K53" t="s">
-        <v>240</v>
-      </c>
-      <c r="L53" t="s">
-        <v>25</v>
-      </c>
-      <c r="M53" t="s">
-        <v>25</v>
-      </c>
-      <c r="N53" t="s">
-        <v>241</v>
-      </c>
-      <c r="O53" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>163</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="H54" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I54" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J54" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K54" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O54" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55" t="s">
+        <v>216</v>
+      </c>
+      <c r="C55" t="s">
+        <v>217</v>
+      </c>
+      <c r="D55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" t="s">
+        <v>244</v>
+      </c>
+      <c r="H55" t="s">
+        <v>66</v>
+      </c>
+      <c r="I55" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" t="s">
+        <v>245</v>
+      </c>
+      <c r="K55" t="s">
+        <v>131</v>
+      </c>
+      <c r="L55" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" t="s">
+        <v>26</v>
+      </c>
+      <c r="O55" t="s">
         <v>246</v>
-      </c>
-      <c r="B55" t="s">
-        <v>49</v>
-      </c>
-      <c r="C55" t="s">
-        <v>50</v>
-      </c>
-      <c r="D55" t="s">
-        <v>51</v>
-      </c>
-      <c r="E55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F55" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" t="s">
-        <v>247</v>
-      </c>
-      <c r="H55" t="s">
-        <v>151</v>
-      </c>
-      <c r="I55" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" t="s">
-        <v>248</v>
-      </c>
-      <c r="K55" t="s">
-        <v>249</v>
-      </c>
-      <c r="L55" t="s">
-        <v>25</v>
-      </c>
-      <c r="M55" t="s">
-        <v>25</v>
-      </c>
-      <c r="N55" t="s">
-        <v>25</v>
-      </c>
-      <c r="O55" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B56" t="s">
-        <v>139</v>
+        <v>234</v>
       </c>
       <c r="C56" t="s">
-        <v>140</v>
+        <v>235</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H56" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I56" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J56" t="s">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="K56" t="s">
-        <v>37</v>
+        <v>249</v>
       </c>
       <c r="L56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O56" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>251</v>
+      </c>
+      <c r="B57" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" t="s">
+        <v>46</v>
+      </c>
+      <c r="E57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>32</v>
+      </c>
+      <c r="H57" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" t="s">
+        <v>252</v>
+      </c>
+      <c r="K57" t="s">
+        <v>57</v>
+      </c>
+      <c r="L57" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" t="s">
+        <v>26</v>
+      </c>
+      <c r="O57" t="s">
         <v>253</v>
-      </c>
-      <c r="B57" t="s">
-        <v>85</v>
-      </c>
-      <c r="C57" t="s">
-        <v>86</v>
-      </c>
-      <c r="D57" t="s">
-        <v>34</v>
-      </c>
-      <c r="E57" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" t="s">
-        <v>19</v>
-      </c>
-      <c r="G57" t="s">
-        <v>35</v>
-      </c>
-      <c r="H57" t="s">
-        <v>151</v>
-      </c>
-      <c r="I57" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" t="s">
-        <v>254</v>
-      </c>
-      <c r="K57" t="s">
-        <v>136</v>
-      </c>
-      <c r="L57" t="s">
-        <v>25</v>
-      </c>
-      <c r="M57" t="s">
-        <v>25</v>
-      </c>
-      <c r="N57" t="s">
-        <v>25</v>
-      </c>
-      <c r="O57" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="C58" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="D58" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H58" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J58" t="s">
-        <v>257</v>
+        <v>120</v>
       </c>
       <c r="K58" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="L58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O58" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>256</v>
+      </c>
+      <c r="B59" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" t="s">
+        <v>88</v>
+      </c>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" t="s">
+        <v>257</v>
+      </c>
+      <c r="H59" t="s">
+        <v>66</v>
+      </c>
+      <c r="I59" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" t="s">
+        <v>258</v>
+      </c>
+      <c r="K59" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" t="s">
+        <v>26</v>
+      </c>
+      <c r="O59" t="s">
         <v>259</v>
-      </c>
-      <c r="B59" t="s">
-        <v>49</v>
-      </c>
-      <c r="C59" t="s">
-        <v>50</v>
-      </c>
-      <c r="D59" t="s">
-        <v>51</v>
-      </c>
-      <c r="E59" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" t="s">
-        <v>81</v>
-      </c>
-      <c r="H59" t="s">
-        <v>151</v>
-      </c>
-      <c r="I59" t="s">
-        <v>22</v>
-      </c>
-      <c r="J59" t="s">
-        <v>260</v>
-      </c>
-      <c r="K59" t="s">
-        <v>130</v>
-      </c>
-      <c r="L59" t="s">
-        <v>25</v>
-      </c>
-      <c r="M59" t="s">
-        <v>25</v>
-      </c>
-      <c r="N59" t="s">
-        <v>25</v>
-      </c>
-      <c r="O59" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>260</v>
+      </c>
+      <c r="B60" t="s">
+        <v>186</v>
+      </c>
+      <c r="C60" t="s">
+        <v>187</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" t="s">
+        <v>66</v>
+      </c>
+      <c r="I60" t="s">
+        <v>23</v>
+      </c>
+      <c r="J60" t="s">
+        <v>261</v>
+      </c>
+      <c r="K60" t="s">
+        <v>131</v>
+      </c>
+      <c r="L60" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" t="s">
+        <v>26</v>
+      </c>
+      <c r="O60" t="s">
         <v>262</v>
-      </c>
-      <c r="B60" t="s">
-        <v>263</v>
-      </c>
-      <c r="C60" t="s">
-        <v>264</v>
-      </c>
-      <c r="D60" t="s">
-        <v>34</v>
-      </c>
-      <c r="E60" t="s">
-        <v>18</v>
-      </c>
-      <c r="F60" t="s">
-        <v>19</v>
-      </c>
-      <c r="G60" t="s">
-        <v>20</v>
-      </c>
-      <c r="H60" t="s">
-        <v>151</v>
-      </c>
-      <c r="I60" t="s">
-        <v>22</v>
-      </c>
-      <c r="J60" t="s">
-        <v>265</v>
-      </c>
-      <c r="K60" t="s">
-        <v>41</v>
-      </c>
-      <c r="L60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M60" t="s">
-        <v>25</v>
-      </c>
-      <c r="N60" t="s">
-        <v>25</v>
-      </c>
-      <c r="O60" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G61" t="s">
+        <v>32</v>
+      </c>
+      <c r="H61" t="s">
+        <v>66</v>
+      </c>
+      <c r="I61" t="s">
+        <v>23</v>
+      </c>
+      <c r="J61" t="s">
+        <v>264</v>
+      </c>
+      <c r="K61" t="s">
         <v>35</v>
       </c>
-      <c r="H61" t="s">
-        <v>151</v>
-      </c>
-      <c r="I61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" t="s">
-        <v>268</v>
-      </c>
-      <c r="K61" t="s">
-        <v>219</v>
-      </c>
       <c r="L61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O61" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B62" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H62" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I62" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J62" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K62" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="L62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O62" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>269</v>
+      </c>
+      <c r="B63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C63" t="s">
+        <v>271</v>
+      </c>
+      <c r="D63" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F63" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63" t="s">
+        <v>66</v>
+      </c>
+      <c r="I63" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" t="s">
+        <v>272</v>
+      </c>
+      <c r="K63" t="s">
+        <v>63</v>
+      </c>
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" t="s">
+        <v>26</v>
+      </c>
+      <c r="O63" t="s">
         <v>273</v>
-      </c>
-      <c r="B63" t="s">
-        <v>207</v>
-      </c>
-      <c r="C63" t="s">
-        <v>208</v>
-      </c>
-      <c r="D63" t="s">
-        <v>160</v>
-      </c>
-      <c r="E63" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" t="s">
-        <v>274</v>
-      </c>
-      <c r="G63" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" t="s">
-        <v>151</v>
-      </c>
-      <c r="I63" t="s">
-        <v>22</v>
-      </c>
-      <c r="J63" t="s">
-        <v>275</v>
-      </c>
-      <c r="K63" t="s">
-        <v>276</v>
-      </c>
-      <c r="L63" t="s">
-        <v>25</v>
-      </c>
-      <c r="M63" t="s">
-        <v>25</v>
-      </c>
-      <c r="N63" t="s">
-        <v>277</v>
-      </c>
-      <c r="O63" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>211</v>
       </c>
       <c r="C64" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G64" t="s">
+        <v>83</v>
+      </c>
+      <c r="H64" t="s">
+        <v>66</v>
+      </c>
+      <c r="I64" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" t="s">
+        <v>275</v>
+      </c>
+      <c r="K64" t="s">
         <v>35</v>
       </c>
-      <c r="H64" t="s">
-        <v>151</v>
-      </c>
-      <c r="I64" t="s">
-        <v>22</v>
-      </c>
-      <c r="J64" t="s">
-        <v>257</v>
-      </c>
-      <c r="K64" t="s">
-        <v>29</v>
-      </c>
       <c r="L64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O64" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>277</v>
+      </c>
+      <c r="B65" t="s">
+        <v>278</v>
+      </c>
+      <c r="C65" t="s">
+        <v>279</v>
+      </c>
+      <c r="D65" t="s">
+        <v>236</v>
+      </c>
+      <c r="E65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65" t="s">
+        <v>66</v>
+      </c>
+      <c r="I65" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" t="s">
+        <v>280</v>
+      </c>
+      <c r="K65" t="s">
+        <v>93</v>
+      </c>
+      <c r="L65" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" t="s">
+        <v>26</v>
+      </c>
+      <c r="O65" t="s">
         <v>281</v>
-      </c>
-      <c r="B65" t="s">
-        <v>49</v>
-      </c>
-      <c r="C65" t="s">
-        <v>50</v>
-      </c>
-      <c r="D65" t="s">
-        <v>51</v>
-      </c>
-      <c r="E65" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" t="s">
-        <v>35</v>
-      </c>
-      <c r="H65" t="s">
-        <v>151</v>
-      </c>
-      <c r="I65" t="s">
-        <v>22</v>
-      </c>
-      <c r="J65" t="s">
-        <v>282</v>
-      </c>
-      <c r="K65" t="s">
-        <v>88</v>
-      </c>
-      <c r="L65" t="s">
-        <v>25</v>
-      </c>
-      <c r="M65" t="s">
-        <v>25</v>
-      </c>
-      <c r="N65" t="s">
-        <v>25</v>
-      </c>
-      <c r="O65" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>282</v>
+      </c>
+      <c r="B66" t="s">
+        <v>211</v>
+      </c>
+      <c r="C66" t="s">
+        <v>212</v>
+      </c>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F66" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" t="s">
+        <v>66</v>
+      </c>
+      <c r="I66" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" t="s">
+        <v>283</v>
+      </c>
+      <c r="K66" t="s">
+        <v>25</v>
+      </c>
+      <c r="L66" t="s">
+        <v>26</v>
+      </c>
+      <c r="M66" t="s">
+        <v>26</v>
+      </c>
+      <c r="N66" t="s">
+        <v>26</v>
+      </c>
+      <c r="O66" t="s">
         <v>284</v>
-      </c>
-      <c r="B66" t="s">
-        <v>285</v>
-      </c>
-      <c r="C66" t="s">
-        <v>286</v>
-      </c>
-      <c r="D66" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66" t="s">
-        <v>18</v>
-      </c>
-      <c r="F66" t="s">
-        <v>19</v>
-      </c>
-      <c r="G66" t="s">
-        <v>203</v>
-      </c>
-      <c r="H66" t="s">
-        <v>151</v>
-      </c>
-      <c r="I66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J66" t="s">
-        <v>287</v>
-      </c>
-      <c r="K66" t="s">
-        <v>61</v>
-      </c>
-      <c r="L66" t="s">
-        <v>25</v>
-      </c>
-      <c r="M66" t="s">
-        <v>25</v>
-      </c>
-      <c r="N66" t="s">
-        <v>25</v>
-      </c>
-      <c r="O66" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="C67" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="D67" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E67" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H67" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J67" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K67" t="s">
         <v>57</v>
       </c>
       <c r="L67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O67" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B68" t="s">
-        <v>293</v>
+        <v>51</v>
       </c>
       <c r="C68" t="s">
-        <v>294</v>
+        <v>52</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H68" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J68" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="K68" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="L68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O68" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D69" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G69" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H69" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I69" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J69" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="K69" t="s">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="L69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O69" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>211</v>
       </c>
       <c r="C70" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="D70" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E70" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H70" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I70" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J70" t="s">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="K70" t="s">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="L70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O70" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="D71" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E71" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H71" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I71" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J71" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="K71" t="s">
-        <v>304</v>
+        <v>97</v>
       </c>
       <c r="L71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O71" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B72" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="C72" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G72" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H72" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I72" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J72" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="K72" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="L72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O72" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>303</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" t="s">
+        <v>304</v>
+      </c>
+      <c r="G73" t="s">
+        <v>305</v>
+      </c>
+      <c r="H73" t="s">
+        <v>66</v>
+      </c>
+      <c r="I73" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" t="s">
+        <v>306</v>
+      </c>
+      <c r="K73" t="s">
+        <v>307</v>
+      </c>
+      <c r="L73" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" t="s">
+        <v>308</v>
+      </c>
+      <c r="O73" t="s">
         <v>309</v>
-      </c>
-      <c r="B73" t="s">
-        <v>49</v>
-      </c>
-      <c r="C73" t="s">
-        <v>50</v>
-      </c>
-      <c r="D73" t="s">
-        <v>51</v>
-      </c>
-      <c r="E73" t="s">
-        <v>18</v>
-      </c>
-      <c r="F73" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" t="s">
-        <v>20</v>
-      </c>
-      <c r="H73" t="s">
-        <v>151</v>
-      </c>
-      <c r="I73" t="s">
-        <v>22</v>
-      </c>
-      <c r="J73" t="s">
-        <v>310</v>
-      </c>
-      <c r="K73" t="s">
-        <v>88</v>
-      </c>
-      <c r="L73" t="s">
-        <v>25</v>
-      </c>
-      <c r="M73" t="s">
-        <v>25</v>
-      </c>
-      <c r="N73" t="s">
-        <v>25</v>
-      </c>
-      <c r="O73" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>310</v>
+      </c>
+      <c r="B74" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" t="s">
+        <v>45</v>
+      </c>
+      <c r="D74" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" t="s">
+        <v>66</v>
+      </c>
+      <c r="I74" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" t="s">
+        <v>311</v>
+      </c>
+      <c r="K74" t="s">
+        <v>57</v>
+      </c>
+      <c r="L74" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" t="s">
+        <v>26</v>
+      </c>
+      <c r="O74" t="s">
         <v>312</v>
-      </c>
-      <c r="B74" t="s">
-        <v>85</v>
-      </c>
-      <c r="C74" t="s">
-        <v>86</v>
-      </c>
-      <c r="D74" t="s">
-        <v>34</v>
-      </c>
-      <c r="E74" t="s">
-        <v>18</v>
-      </c>
-      <c r="F74" t="s">
-        <v>274</v>
-      </c>
-      <c r="G74" t="s">
-        <v>313</v>
-      </c>
-      <c r="H74" t="s">
-        <v>151</v>
-      </c>
-      <c r="I74" t="s">
-        <v>22</v>
-      </c>
-      <c r="J74" t="s">
-        <v>314</v>
-      </c>
-      <c r="K74" t="s">
-        <v>276</v>
-      </c>
-      <c r="L74" t="s">
-        <v>25</v>
-      </c>
-      <c r="M74" t="s">
-        <v>25</v>
-      </c>
-      <c r="N74" t="s">
-        <v>315</v>
-      </c>
-      <c r="O74" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B75" t="s">
-        <v>318</v>
+        <v>44</v>
       </c>
       <c r="C75" t="s">
-        <v>319</v>
+        <v>45</v>
       </c>
       <c r="D75" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E75" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="H75" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I75" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J75" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="K75" t="s">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="L75" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M75" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N75" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O75" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="C76" t="s">
-        <v>50</v>
+        <v>217</v>
       </c>
       <c r="D76" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E76" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>203</v>
+        <v>32</v>
       </c>
       <c r="H76" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J76" t="s">
-        <v>323</v>
+        <v>245</v>
       </c>
       <c r="K76" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="L76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O76" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="C77" t="s">
-        <v>208</v>
+        <v>72</v>
       </c>
       <c r="D77" t="s">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="E77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G77" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" t="s">
+        <v>66</v>
+      </c>
+      <c r="I77" t="s">
+        <v>23</v>
+      </c>
+      <c r="J77" t="s">
+        <v>320</v>
+      </c>
+      <c r="K77" t="s">
         <v>35</v>
       </c>
-      <c r="H77" t="s">
-        <v>151</v>
-      </c>
-      <c r="I77" t="s">
-        <v>22</v>
-      </c>
-      <c r="J77" t="s">
-        <v>326</v>
-      </c>
-      <c r="K77" t="s">
-        <v>162</v>
-      </c>
       <c r="L77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O77" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B78" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="C78" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E78" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H78" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I78" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J78" t="s">
-        <v>225</v>
+        <v>323</v>
       </c>
       <c r="K78" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="L78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O78" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B79" t="s">
-        <v>331</v>
+        <v>44</v>
       </c>
       <c r="C79" t="s">
-        <v>332</v>
+        <v>45</v>
       </c>
       <c r="D79" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E79" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H79" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I79" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J79" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K79" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="L79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O79" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B80" t="s">
-        <v>198</v>
+        <v>329</v>
       </c>
       <c r="C80" t="s">
-        <v>199</v>
+        <v>330</v>
       </c>
       <c r="D80" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E80" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H80" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="K80" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L80" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M80" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N80" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O80" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B81" t="s">
-        <v>339</v>
+        <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="D81" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="E81" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>274</v>
+        <v>20</v>
       </c>
       <c r="G81" t="s">
-        <v>340</v>
+        <v>32</v>
       </c>
       <c r="H81" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I81" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J81" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="K81" t="s">
-        <v>342</v>
+        <v>74</v>
       </c>
       <c r="L81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N81" t="s">
-        <v>343</v>
+        <v>26</v>
       </c>
       <c r="O81" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B82" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C82" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D82" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E82" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H82" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I82" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="K82" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="L82" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M82" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N82" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O82" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B83" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="C83" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="D83" t="s">
         <v>236</v>
       </c>
       <c r="E83" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="G83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H83" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J83" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="K83" t="s">
-        <v>219</v>
+        <v>341</v>
       </c>
       <c r="L83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N83" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="O83" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B84" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="D84" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E84" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F84" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>203</v>
+        <v>32</v>
       </c>
       <c r="H84" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I84" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J84" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="K84" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="L84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O84" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D85" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F85" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H85" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I85" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J85" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="K85" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="L85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O85" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B86" t="s">
-        <v>49</v>
+        <v>350</v>
       </c>
       <c r="C86" t="s">
-        <v>50</v>
+        <v>351</v>
       </c>
       <c r="D86" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="H86" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I86" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J86" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="K86" t="s">
-        <v>358</v>
+        <v>93</v>
       </c>
       <c r="L86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O86" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B87" t="s">
-        <v>361</v>
+        <v>216</v>
       </c>
       <c r="C87" t="s">
-        <v>362</v>
+        <v>217</v>
       </c>
       <c r="D87" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E87" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F87" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="H87" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I87" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J87" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="K87" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L87" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M87" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N87" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O87" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B88" t="s">
-        <v>85</v>
+        <v>358</v>
       </c>
       <c r="C88" t="s">
-        <v>86</v>
+        <v>359</v>
       </c>
       <c r="D88" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H88" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I88" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J88" t="s">
-        <v>257</v>
+        <v>360</v>
       </c>
       <c r="K88" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="L88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O88" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B89" t="s">
-        <v>318</v>
+        <v>51</v>
       </c>
       <c r="C89" t="s">
-        <v>319</v>
+        <v>52</v>
       </c>
       <c r="D89" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E89" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H89" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I89" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J89" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="K89" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="L89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O89" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B90" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C90" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D90" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G90" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="H90" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J90" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K90" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L90" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M90" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N90" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O90" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B91" t="s">
-        <v>234</v>
+        <v>44</v>
       </c>
       <c r="C91" t="s">
-        <v>235</v>
+        <v>45</v>
       </c>
       <c r="D91" t="s">
-        <v>236</v>
+        <v>46</v>
       </c>
       <c r="E91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G91" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H91" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I91" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J91" t="s">
-        <v>326</v>
+        <v>368</v>
       </c>
       <c r="K91" t="s">
-        <v>162</v>
+        <v>369</v>
       </c>
       <c r="L91" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M91" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N91" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O91" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B92" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C92" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D92" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="E92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G92" t="s">
-        <v>203</v>
+        <v>32</v>
       </c>
       <c r="H92" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I92" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J92" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="K92" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L92" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M92" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N92" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O92" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E93" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="G93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H93" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I93" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J93" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K93" t="s">
-        <v>380</v>
+        <v>57</v>
       </c>
       <c r="L93" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M93" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N93" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O93" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B94" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D94" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="G94" t="s">
-        <v>35</v>
+        <v>378</v>
       </c>
       <c r="H94" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I94" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J94" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="K94" t="s">
-        <v>145</v>
+        <v>341</v>
       </c>
       <c r="L94" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M94" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N94" t="s">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="O94" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B95" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D95" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G95" t="s">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="H95" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I95" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J95" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="K95" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="L95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O95" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B96" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C96" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E96" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F96" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G96" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="H96" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I96" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J96" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="K96" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="L96" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M96" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N96" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O96" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B97" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="C97" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="D97" t="s">
         <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G97" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H97" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I97" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J97" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K97" t="s">
-        <v>219</v>
+        <v>25</v>
       </c>
       <c r="L97" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M97" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N97" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O97" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>216</v>
       </c>
       <c r="C98" t="s">
-        <v>45</v>
+        <v>217</v>
       </c>
       <c r="D98" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G98" t="s">
-        <v>395</v>
+        <v>32</v>
       </c>
       <c r="H98" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I98" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J98" t="s">
-        <v>396</v>
+        <v>295</v>
       </c>
       <c r="K98" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="L98" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M98" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N98" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O98" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>394</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>395</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E99" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F99" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="H99" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J99" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="K99" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="L99" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M99" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N99" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O99" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B100" t="s">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="C100" t="s">
-        <v>208</v>
+        <v>271</v>
       </c>
       <c r="D100" t="s">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G100" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H100" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I100" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J100" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="K100" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="L100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O100" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>401</v>
+      </c>
+      <c r="B101" t="s">
+        <v>402</v>
+      </c>
+      <c r="C101" t="s">
+        <v>235</v>
+      </c>
+      <c r="D101" t="s">
+        <v>236</v>
+      </c>
+      <c r="E101" t="s">
+        <v>236</v>
+      </c>
+      <c r="F101" t="s">
+        <v>102</v>
+      </c>
+      <c r="G101" t="s">
+        <v>403</v>
+      </c>
+      <c r="H101" t="s">
+        <v>66</v>
+      </c>
+      <c r="I101" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" t="s">
         <v>404</v>
       </c>
-      <c r="B101" t="s">
-        <v>49</v>
-      </c>
-      <c r="C101" t="s">
-        <v>50</v>
-      </c>
-      <c r="D101" t="s">
-        <v>51</v>
-      </c>
-      <c r="E101" t="s">
-        <v>18</v>
-      </c>
-      <c r="F101" t="s">
-        <v>19</v>
-      </c>
-      <c r="G101" t="s">
-        <v>35</v>
-      </c>
-      <c r="H101" t="s">
-        <v>151</v>
-      </c>
-      <c r="I101" t="s">
-        <v>22</v>
-      </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>405</v>
       </c>
-      <c r="K101" t="s">
-        <v>41</v>
-      </c>
       <c r="L101" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M101" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N101" t="s">
-        <v>25</v>
+        <v>406</v>
       </c>
       <c r="O101" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B102" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C102" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D102" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E102" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G102" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H102" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I102" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J102" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K102" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="L102" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M102" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N102" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O102" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B103" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="C103" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H103" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I103" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J103" t="s">
-        <v>336</v>
+        <v>389</v>
       </c>
       <c r="K103" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="L103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O103" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B104" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="C104" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="D104" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E104" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G104" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="H104" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I104" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J104" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K104" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="L104" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M104" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N104" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O104" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B105" t="s">
-        <v>361</v>
+        <v>51</v>
       </c>
       <c r="C105" t="s">
-        <v>362</v>
+        <v>52</v>
       </c>
       <c r="D105" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E105" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F105" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G105" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H105" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I105" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J105" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K105" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L105" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M105" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N105" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O105" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B106" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C106" t="s">
-        <v>419</v>
+        <v>45</v>
       </c>
       <c r="D106" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E106" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F106" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" t="s">
+        <v>32</v>
+      </c>
+      <c r="H106" t="s">
+        <v>66</v>
+      </c>
+      <c r="I106" t="s">
+        <v>23</v>
+      </c>
+      <c r="J106" t="s">
         <v>420</v>
       </c>
-      <c r="G106" t="s">
-        <v>165</v>
-      </c>
-      <c r="H106" t="s">
-        <v>151</v>
-      </c>
-      <c r="I106" t="s">
-        <v>22</v>
-      </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>421</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" t="s">
+        <v>26</v>
+      </c>
+      <c r="M106" t="s">
+        <v>26</v>
+      </c>
+      <c r="N106" t="s">
+        <v>26</v>
+      </c>
+      <c r="O106" t="s">
         <v>422</v>
-      </c>
-      <c r="L106" t="s">
-        <v>25</v>
-      </c>
-      <c r="M106" t="s">
-        <v>25</v>
-      </c>
-      <c r="N106" t="s">
-        <v>25</v>
-      </c>
-      <c r="O106" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>423</v>
+      </c>
+      <c r="B107" t="s">
         <v>424</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>425</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" t="s">
+        <v>164</v>
+      </c>
+      <c r="H107" t="s">
+        <v>66</v>
+      </c>
+      <c r="I107" t="s">
+        <v>23</v>
+      </c>
+      <c r="J107" t="s">
         <v>426</v>
       </c>
-      <c r="D107" t="s">
-        <v>18</v>
-      </c>
-      <c r="E107" t="s">
-        <v>18</v>
-      </c>
-      <c r="F107" t="s">
-        <v>19</v>
-      </c>
-      <c r="G107" t="s">
-        <v>35</v>
-      </c>
-      <c r="H107" t="s">
-        <v>151</v>
-      </c>
-      <c r="I107" t="s">
-        <v>22</v>
-      </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
+        <v>172</v>
+      </c>
+      <c r="L107" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" t="s">
+        <v>26</v>
+      </c>
+      <c r="N107" t="s">
+        <v>26</v>
+      </c>
+      <c r="O107" t="s">
         <v>427</v>
-      </c>
-      <c r="K107" t="s">
-        <v>61</v>
-      </c>
-      <c r="L107" t="s">
-        <v>25</v>
-      </c>
-      <c r="M107" t="s">
-        <v>25</v>
-      </c>
-      <c r="N107" t="s">
-        <v>25</v>
-      </c>
-      <c r="O107" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>428</v>
+      </c>
+      <c r="B108" t="s">
+        <v>71</v>
+      </c>
+      <c r="C108" t="s">
+        <v>72</v>
+      </c>
+      <c r="D108" t="s">
+        <v>31</v>
+      </c>
+      <c r="E108" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" t="s">
+        <v>20</v>
+      </c>
+      <c r="G108" t="s">
+        <v>32</v>
+      </c>
+      <c r="H108" t="s">
+        <v>66</v>
+      </c>
+      <c r="I108" t="s">
+        <v>23</v>
+      </c>
+      <c r="J108" t="s">
+        <v>323</v>
+      </c>
+      <c r="K108" t="s">
+        <v>172</v>
+      </c>
+      <c r="L108" t="s">
+        <v>26</v>
+      </c>
+      <c r="M108" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" t="s">
+        <v>26</v>
+      </c>
+      <c r="O108" t="s">
         <v>429</v>
-      </c>
-      <c r="B108" t="s">
-        <v>293</v>
-      </c>
-      <c r="C108" t="s">
-        <v>294</v>
-      </c>
-      <c r="D108" t="s">
-        <v>18</v>
-      </c>
-      <c r="E108" t="s">
-        <v>18</v>
-      </c>
-      <c r="F108" t="s">
-        <v>19</v>
-      </c>
-      <c r="G108" t="s">
-        <v>430</v>
-      </c>
-      <c r="H108" t="s">
-        <v>151</v>
-      </c>
-      <c r="I108" t="s">
-        <v>22</v>
-      </c>
-      <c r="J108" t="s">
-        <v>431</v>
-      </c>
-      <c r="K108" t="s">
-        <v>37</v>
-      </c>
-      <c r="L108" t="s">
-        <v>25</v>
-      </c>
-      <c r="M108" t="s">
-        <v>25</v>
-      </c>
-      <c r="N108" t="s">
-        <v>25</v>
-      </c>
-      <c r="O108" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B109" t="s">
-        <v>234</v>
+        <v>100</v>
       </c>
       <c r="C109" t="s">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="D109" t="s">
-        <v>236</v>
+        <v>31</v>
       </c>
       <c r="E109" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F109" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G109" t="s">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="H109" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I109" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J109" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="K109" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="L109" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M109" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N109" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O109" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B110" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C110" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D110" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E110" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F110" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G110" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="H110" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I110" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J110" t="s">
-        <v>437</v>
+        <v>252</v>
       </c>
       <c r="K110" t="s">
-        <v>438</v>
+        <v>127</v>
       </c>
       <c r="L110" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M110" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N110" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O110" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B111" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C111" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="D111" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="E111" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F111" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="H111" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I111" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J111" t="s">
-        <v>441</v>
+        <v>389</v>
       </c>
       <c r="K111" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="L111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O111" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B112" t="s">
-        <v>85</v>
+        <v>278</v>
       </c>
       <c r="C112" t="s">
-        <v>86</v>
+        <v>279</v>
       </c>
       <c r="D112" t="s">
-        <v>34</v>
+        <v>236</v>
       </c>
       <c r="E112" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F112" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G112" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="H112" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I112" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J112" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="K112" t="s">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="L112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O112" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B113" t="s">
-        <v>318</v>
+        <v>51</v>
       </c>
       <c r="C113" t="s">
-        <v>319</v>
+        <v>52</v>
       </c>
       <c r="D113" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E113" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="G113" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H113" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I113" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J113" t="s">
-        <v>323</v>
+        <v>442</v>
       </c>
       <c r="K113" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="L113" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M113" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N113" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O113" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B114" t="s">
         <v>44</v>
@@ -7249,327 +7141,327 @@
         <v>45</v>
       </c>
       <c r="D114" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E114" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F114" t="s">
-        <v>451</v>
+        <v>20</v>
       </c>
       <c r="G114" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H114" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I114" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J114" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="K114" t="s">
-        <v>453</v>
+        <v>222</v>
       </c>
       <c r="L114" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M114" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N114" t="s">
-        <v>277</v>
+        <v>26</v>
       </c>
       <c r="O114" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B115" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D115" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E115" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="H115" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I115" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J115" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="K115" t="s">
-        <v>41</v>
+        <v>205</v>
       </c>
       <c r="L115" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M115" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N115" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O115" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="B116" t="s">
-        <v>234</v>
+        <v>44</v>
       </c>
       <c r="C116" t="s">
-        <v>235</v>
+        <v>45</v>
       </c>
       <c r="D116" t="s">
-        <v>236</v>
+        <v>46</v>
       </c>
       <c r="E116" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F116" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G116" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H116" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I116" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J116" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="K116" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L116" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M116" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N116" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O116" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B117" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C117" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="E117" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H117" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I117" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J117" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="K117" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="L117" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M117" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N117" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O117" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="B118" t="s">
-        <v>465</v>
+        <v>38</v>
       </c>
       <c r="C118" t="s">
-        <v>466</v>
+        <v>39</v>
       </c>
       <c r="D118" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E118" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>274</v>
+        <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>35</v>
+        <v>458</v>
       </c>
       <c r="H118" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I118" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J118" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="K118" t="s">
-        <v>468</v>
+        <v>93</v>
       </c>
       <c r="L118" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M118" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N118" t="s">
-        <v>469</v>
+        <v>26</v>
       </c>
       <c r="O118" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B119" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="D119" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E119" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F119" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G119" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H119" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I119" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J119" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="K119" t="s">
-        <v>358</v>
+        <v>93</v>
       </c>
       <c r="L119" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M119" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N119" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O119" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>278</v>
       </c>
       <c r="C120" t="s">
-        <v>17</v>
+        <v>279</v>
       </c>
       <c r="D120" t="s">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="E120" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F120" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G120" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H120" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I120" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J120" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K120" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L120" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M120" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N120" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O120" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B121" t="s">
         <v>44</v>
@@ -7578,510 +7470,134 @@
         <v>45</v>
       </c>
       <c r="D121" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E121" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F121" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G121" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H121" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I121" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J121" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="K121" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="L121" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M121" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N121" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O121" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="B122" t="s">
+        <v>44</v>
+      </c>
+      <c r="C122" t="s">
+        <v>45</v>
+      </c>
+      <c r="D122" t="s">
+        <v>46</v>
+      </c>
+      <c r="E122" t="s">
+        <v>19</v>
+      </c>
+      <c r="F122" t="s">
+        <v>20</v>
+      </c>
+      <c r="G122" t="s">
         <v>32</v>
       </c>
-      <c r="C122" t="s">
-        <v>33</v>
-      </c>
-      <c r="D122" t="s">
-        <v>34</v>
-      </c>
-      <c r="E122" t="s">
-        <v>25</v>
-      </c>
-      <c r="F122" t="s">
-        <v>19</v>
-      </c>
-      <c r="G122" t="s">
-        <v>35</v>
-      </c>
       <c r="H122" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I122" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J122" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="K122" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O122" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B123" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="C123" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="D123" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E123" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F123" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G123" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H123" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="I123" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J123" t="s">
-        <v>484</v>
+        <v>399</v>
       </c>
       <c r="K123" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="L123" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M123" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N123" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O123" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>486</v>
-      </c>
-      <c r="B124" t="s">
-        <v>49</v>
-      </c>
-      <c r="C124" t="s">
-        <v>50</v>
-      </c>
-      <c r="D124" t="s">
-        <v>51</v>
-      </c>
-      <c r="E124" t="s">
-        <v>18</v>
-      </c>
-      <c r="F124" t="s">
-        <v>19</v>
-      </c>
-      <c r="G124" t="s">
-        <v>20</v>
-      </c>
-      <c r="H124" t="s">
-        <v>151</v>
-      </c>
-      <c r="I124" t="s">
-        <v>22</v>
-      </c>
-      <c r="J124" t="s">
-        <v>487</v>
-      </c>
-      <c r="K124" t="s">
-        <v>488</v>
-      </c>
-      <c r="L124" t="s">
-        <v>25</v>
-      </c>
-      <c r="M124" t="s">
-        <v>25</v>
-      </c>
-      <c r="N124" t="s">
-        <v>25</v>
-      </c>
-      <c r="O124" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>490</v>
-      </c>
-      <c r="B125" t="s">
-        <v>49</v>
-      </c>
-      <c r="C125" t="s">
-        <v>50</v>
-      </c>
-      <c r="D125" t="s">
-        <v>51</v>
-      </c>
-      <c r="E125" t="s">
-        <v>18</v>
-      </c>
-      <c r="F125" t="s">
-        <v>19</v>
-      </c>
-      <c r="G125" t="s">
-        <v>20</v>
-      </c>
-      <c r="H125" t="s">
-        <v>151</v>
-      </c>
-      <c r="I125" t="s">
-        <v>22</v>
-      </c>
-      <c r="J125" t="s">
-        <v>491</v>
-      </c>
-      <c r="K125" t="s">
-        <v>61</v>
-      </c>
-      <c r="L125" t="s">
-        <v>25</v>
-      </c>
-      <c r="M125" t="s">
-        <v>25</v>
-      </c>
-      <c r="N125" t="s">
-        <v>25</v>
-      </c>
-      <c r="O125" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>493</v>
-      </c>
-      <c r="B126" t="s">
-        <v>106</v>
-      </c>
-      <c r="C126" t="s">
-        <v>107</v>
-      </c>
-      <c r="D126" t="s">
-        <v>18</v>
-      </c>
-      <c r="E126" t="s">
-        <v>18</v>
-      </c>
-      <c r="F126" t="s">
-        <v>19</v>
-      </c>
-      <c r="G126" t="s">
-        <v>35</v>
-      </c>
-      <c r="H126" t="s">
-        <v>151</v>
-      </c>
-      <c r="I126" t="s">
-        <v>22</v>
-      </c>
-      <c r="J126" t="s">
-        <v>494</v>
-      </c>
-      <c r="K126" t="s">
-        <v>37</v>
-      </c>
-      <c r="L126" t="s">
-        <v>25</v>
-      </c>
-      <c r="M126" t="s">
-        <v>25</v>
-      </c>
-      <c r="N126" t="s">
-        <v>25</v>
-      </c>
-      <c r="O126" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>496</v>
-      </c>
-      <c r="B127" t="s">
-        <v>49</v>
-      </c>
-      <c r="C127" t="s">
-        <v>50</v>
-      </c>
-      <c r="D127" t="s">
-        <v>51</v>
-      </c>
-      <c r="E127" t="s">
-        <v>18</v>
-      </c>
-      <c r="F127" t="s">
-        <v>19</v>
-      </c>
-      <c r="G127" t="s">
-        <v>35</v>
-      </c>
-      <c r="H127" t="s">
-        <v>151</v>
-      </c>
-      <c r="I127" t="s">
-        <v>22</v>
-      </c>
-      <c r="J127" t="s">
-        <v>497</v>
-      </c>
-      <c r="K127" t="s">
-        <v>88</v>
-      </c>
-      <c r="L127" t="s">
-        <v>25</v>
-      </c>
-      <c r="M127" t="s">
-        <v>25</v>
-      </c>
-      <c r="N127" t="s">
-        <v>25</v>
-      </c>
-      <c r="O127" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>499</v>
-      </c>
-      <c r="B128" t="s">
-        <v>44</v>
-      </c>
-      <c r="C128" t="s">
-        <v>45</v>
-      </c>
-      <c r="D128" t="s">
-        <v>34</v>
-      </c>
-      <c r="E128" t="s">
-        <v>18</v>
-      </c>
-      <c r="F128" t="s">
-        <v>19</v>
-      </c>
-      <c r="G128" t="s">
-        <v>35</v>
-      </c>
-      <c r="H128" t="s">
-        <v>151</v>
-      </c>
-      <c r="I128" t="s">
-        <v>22</v>
-      </c>
-      <c r="J128" t="s">
-        <v>500</v>
-      </c>
-      <c r="K128" t="s">
-        <v>37</v>
-      </c>
-      <c r="L128" t="s">
-        <v>25</v>
-      </c>
-      <c r="M128" t="s">
-        <v>25</v>
-      </c>
-      <c r="N128" t="s">
-        <v>25</v>
-      </c>
-      <c r="O128" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>502</v>
-      </c>
-      <c r="B129" t="s">
-        <v>44</v>
-      </c>
-      <c r="C129" t="s">
-        <v>45</v>
-      </c>
-      <c r="D129" t="s">
-        <v>34</v>
-      </c>
-      <c r="E129" t="s">
-        <v>18</v>
-      </c>
-      <c r="F129" t="s">
-        <v>19</v>
-      </c>
-      <c r="G129" t="s">
-        <v>20</v>
-      </c>
-      <c r="H129" t="s">
-        <v>151</v>
-      </c>
-      <c r="I129" t="s">
-        <v>22</v>
-      </c>
-      <c r="J129" t="s">
-        <v>503</v>
-      </c>
-      <c r="K129" t="s">
-        <v>88</v>
-      </c>
-      <c r="L129" t="s">
-        <v>25</v>
-      </c>
-      <c r="M129" t="s">
-        <v>25</v>
-      </c>
-      <c r="N129" t="s">
-        <v>25</v>
-      </c>
-      <c r="O129" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>505</v>
-      </c>
-      <c r="B130" t="s">
-        <v>49</v>
-      </c>
-      <c r="C130" t="s">
-        <v>50</v>
-      </c>
-      <c r="D130" t="s">
-        <v>51</v>
-      </c>
-      <c r="E130" t="s">
-        <v>18</v>
-      </c>
-      <c r="F130" t="s">
-        <v>19</v>
-      </c>
-      <c r="G130" t="s">
-        <v>35</v>
-      </c>
-      <c r="H130" t="s">
-        <v>151</v>
-      </c>
-      <c r="I130" t="s">
-        <v>22</v>
-      </c>
-      <c r="J130" t="s">
-        <v>506</v>
-      </c>
-      <c r="K130" t="s">
-        <v>37</v>
-      </c>
-      <c r="L130" t="s">
-        <v>25</v>
-      </c>
-      <c r="M130" t="s">
-        <v>25</v>
-      </c>
-      <c r="N130" t="s">
-        <v>25</v>
-      </c>
-      <c r="O130" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>508</v>
-      </c>
-      <c r="B131" t="s">
-        <v>44</v>
-      </c>
-      <c r="C131" t="s">
-        <v>45</v>
-      </c>
-      <c r="D131" t="s">
-        <v>34</v>
-      </c>
-      <c r="E131" t="s">
-        <v>18</v>
-      </c>
-      <c r="F131" t="s">
-        <v>19</v>
-      </c>
-      <c r="G131" t="s">
-        <v>20</v>
-      </c>
-      <c r="H131" t="s">
-        <v>151</v>
-      </c>
-      <c r="I131" t="s">
-        <v>22</v>
-      </c>
-      <c r="J131" t="s">
-        <v>509</v>
-      </c>
-      <c r="K131" t="s">
-        <v>88</v>
-      </c>
-      <c r="L131" t="s">
-        <v>25</v>
-      </c>
-      <c r="M131" t="s">
-        <v>25</v>
-      </c>
-      <c r="N131" t="s">
-        <v>25</v>
-      </c>
-      <c r="O131" t="s">
-        <v>510</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CAC2F16-6F20-47E0-8391-D28992B80E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4BBA11F-F5B9-4E5B-9101-F4E524FD4A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21930" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="485">
   <si>
     <t>Time</t>
   </si>
@@ -62,42 +62,201 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/18/2026 12:45:10 PM</t>
+  </si>
+  <si>
+    <t>23470</t>
+  </si>
+  <si>
+    <t>JELTOV, VLADIMIR K.</t>
+  </si>
+  <si>
+    <t>OTR, Safety Pro Test</t>
+  </si>
+  <si>
+    <t>OTR</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanya Smith </t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, 44.6 mi E The Pinery, Elbert County, CO</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dbd6-3af7-524c-87f3-6e56bdb0f8b4</t>
+  </si>
+  <si>
+    <t>06/18/2026 11:35:17 AM</t>
+  </si>
+  <si>
+    <t>24632</t>
+  </si>
+  <si>
+    <t>EMERY.SHANE</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>KS 156, 30.5 mi NE Great Bend, Ellsworth County, KS</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445db96-3efe-5994-964b-1a1194aab183</t>
+  </si>
+  <si>
+    <t>06/17/2026 3:18:01 PM</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 40, Los Pinos, NM</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d73b-cd21-58a1-a5c5-b4a294014f75</t>
+  </si>
+  <si>
+    <t>06/17/2026 1:24:24 PM</t>
+  </si>
+  <si>
+    <t>24630</t>
+  </si>
+  <si>
+    <t>MAGEE LONDON, TRESSEL</t>
+  </si>
+  <si>
+    <t>Air Temperature, OTR</t>
+  </si>
+  <si>
+    <t>Purple Heart Trail, 20.7 mi ENE Holbrook, Apache County, AZ</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d6d3-c962-50ff-9b41-3d746ff61c92</t>
+  </si>
+  <si>
+    <t>06/17/2026 9:51:05 AM</t>
+  </si>
+  <si>
+    <t>North Collins Freeway, Howe, TX, 75459</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d610-7f77-5f72-81b1-c4694de011c7</t>
+  </si>
+  <si>
+    <t>06/14/2026 12:51:39 PM</t>
+  </si>
+  <si>
+    <t>24688</t>
+  </si>
+  <si>
+    <t>WADE,ADAM</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>Gerald R. Ford Memorial Highway, Dotsero, CO</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c742-bb80-57f3-bbb2-56768c9b226e</t>
+  </si>
+  <si>
+    <t>06/13/2026 12:37:03 PM</t>
+  </si>
+  <si>
+    <t>23473</t>
+  </si>
+  <si>
+    <t>WELCH, GREGORY</t>
+  </si>
+  <si>
+    <t>I 80, 7.1 mi SW Seward, Seward County, NE, 68364</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c20f-014b-5409-87c5-e43d0cc0efd9</t>
+  </si>
+  <si>
+    <t>06/12/2026 6:47:19 PM</t>
+  </si>
+  <si>
+    <t>22970</t>
+  </si>
+  <si>
+    <t>MEYERS, DAVID</t>
+  </si>
+  <si>
+    <t>Air Temperature, Local</t>
+  </si>
+  <si>
+    <t>I 70, Wheat Ridge, CO, 80033</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445be3b-9f80-5fd9-a6cf-dbf18fac6d9d</t>
+  </si>
+  <si>
+    <t>06/12/2026 2:22:37 PM</t>
+  </si>
+  <si>
+    <t>Heartland Expressway, Hazeltine Heights, CO, 80640</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bd49-499d-5743-adbe-6302dd74cc86</t>
+  </si>
+  <si>
+    <t>06/12/2026 10:50:38 AM</t>
+  </si>
+  <si>
+    <t>I 70, Dumont, CO, 80436</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc87-36b4-5f55-82c0-3ec307c4646f</t>
+  </si>
+  <si>
     <t>06/11/2026 5:29:52 PM</t>
   </si>
   <si>
-    <t>24688</t>
-  </si>
-  <si>
-    <t>WADE,ADAM</t>
-  </si>
-  <si>
-    <t>Air Temperature, OTR</t>
-  </si>
-  <si>
-    <t>OTR</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
     <t>Truman/Eisenhower Presidential Highway, 7.0 mi ENE Abilene, Dickinson County, KS, 67431</t>
   </si>
   <si>
     <t>64</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b8ce-5cde-5f34-8fd0-70906359417e</t>
   </si>
   <si>
@@ -119,21 +278,9 @@
     <t>06/11/2026 10:57:37 AM</t>
   </si>
   <si>
-    <t>23470</t>
-  </si>
-  <si>
-    <t>JELTOV, VLADIMIR K.</t>
-  </si>
-  <si>
-    <t>OTR, Safety Pro Test</t>
-  </si>
-  <si>
     <t>Las Vegas Freeway, Moapa, NV</t>
   </si>
   <si>
-    <t>73</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b767-3eca-56ce-bec5-a899a8fc9176</t>
   </si>
   <si>
@@ -155,21 +302,9 @@
     <t>06/10/2026 2:34:29 PM</t>
   </si>
   <si>
-    <t>23473</t>
-  </si>
-  <si>
-    <t>WELCH, GREGORY</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>I 80, 4.4 mi SSE Lexington, Dawson County, NE</t>
   </si>
   <si>
-    <t>68</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b307-6f9f-5d8d-b567-89a04243da8c</t>
   </si>
   <si>
@@ -185,9 +320,6 @@
     <t>Purple Heart Trail, 22.1 mi NW Zuni Pueblo, Apache County, AZ</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b20a-6a3c-5987-953d-06052c8a1179</t>
   </si>
   <si>
@@ -260,15 +392,6 @@
     <t>06/08/2026 10:24:03 AM</t>
   </si>
   <si>
-    <t>22970</t>
-  </si>
-  <si>
-    <t>MEYERS, DAVID</t>
-  </si>
-  <si>
-    <t>Air Temperature, Local</t>
-  </si>
-  <si>
     <t>Heartland Expressway, Brighton, CO</t>
   </si>
   <si>
@@ -278,12 +401,6 @@
     <t>06/08/2026 6:36:45 AM</t>
   </si>
   <si>
-    <t>24632</t>
-  </si>
-  <si>
-    <t>EMERY.SHANE</t>
-  </si>
-  <si>
     <t>I 40, McCartys, NM</t>
   </si>
   <si>
@@ -323,9 +440,6 @@
     <t>I 70, Lakewood, CO, 80410</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f8d-abd6-5146-8bb1-64bec70d67ff</t>
   </si>
   <si>
@@ -476,9 +590,6 @@
     <t>I 70, Silt, CO, 81652</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544565fe-a10f-5965-a302-83a8e3584b11</t>
   </si>
   <si>
@@ -506,9 +617,6 @@
     <t>Needles Freeway, 19.9 mi NW Lake Havasu City, San Bernardino County, CA, 92363</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456147-62b9-5147-8973-5d0101640dd4</t>
   </si>
   <si>
@@ -560,9 +668,6 @@
     <t>I 40, 12.9 mi ESE Grants, Cibola County, NM, 87034</t>
   </si>
   <si>
-    <t>71</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454678-8fe2-5166-907f-e0171d3ee957</t>
   </si>
   <si>
@@ -953,12 +1058,6 @@
     <t>04/23/2026 3:01:20 PM</t>
   </si>
   <si>
-    <t>24630</t>
-  </si>
-  <si>
-    <t>MAGEE LONDON, TRESSEL</t>
-  </si>
-  <si>
     <t>I 80, 7.2 mi S Grand Island, Hamilton County, NE, 68832</t>
   </si>
   <si>
@@ -1371,144 +1470,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c2a-0dbb-5556-8bd1-1742efd68c0e</t>
-  </si>
-  <si>
-    <t>03/22/2026 2:17:45 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544516fb-5ca2-571f-b101-2cc8046f5a47</t>
-  </si>
-  <si>
-    <t>03/21/2026 2:27:39 PM</t>
-  </si>
-  <si>
-    <t>I 435, Shawnee, KS, 66217-9321</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544511de-11f0-5452-8206-95afe1871223</t>
-  </si>
-  <si>
-    <t>03/20/2026 11:58:36 AM</t>
-  </si>
-  <si>
-    <t>I 70, 45.3 mi E The Pinery, Elbert County, CO, 80264</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450c2f-4060-5e48-a407-9065ec66af5b</t>
-  </si>
-  <si>
-    <t>03/20/2026 9:44:31 AM</t>
-  </si>
-  <si>
-    <t>I 70;US 40, 28.9 mi WNW Hays, Trego County, KS, 67672</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450bb4-7e54-53c8-a154-3ec5c89a51e4</t>
-  </si>
-  <si>
-    <t>03/19/2026 8:15:37 PM</t>
-  </si>
-  <si>
-    <t>23465</t>
-  </si>
-  <si>
-    <t>TORRES, VIVIAN</t>
-  </si>
-  <si>
-    <t>I 80, 44.4 mi E Sidney, Deuel County, NE, 69122</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544508cf-ed96-51d5-972b-5534390edfbc</t>
-  </si>
-  <si>
-    <t>03/19/2026 6:14:32 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450861-11e8-5d09-a81d-bdf61f8fc8bb</t>
-  </si>
-  <si>
-    <t>03/19/2026 3:58:45 PM</t>
-  </si>
-  <si>
-    <t>Mojave Freeway, 30.2 mi E Fort Irwin, San Bernardino County, CA</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544507e4-c0a3-5c0a-875a-f29b7d8a578f</t>
-  </si>
-  <si>
-    <t>03/18/2026 5:18:14 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450307-2c54-5922-bc07-5c8127fa8afa</t>
-  </si>
-  <si>
-    <t>03/18/2026 1:50:01 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450248-8a3c-5c93-96c3-7c25b3ea7ab3</t>
-  </si>
-  <si>
-    <t>03/17/2026 5:10:26 PM</t>
-  </si>
-  <si>
-    <t>I 270, Commerce City, CO, 80216-8470</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fdd9-a96d-5b16-ba6a-d13ec8f22300</t>
-  </si>
-  <si>
-    <t>03/17/2026 2:50:46 PM</t>
-  </si>
-  <si>
-    <t>Forward Collision Warning</t>
-  </si>
-  <si>
-    <t>Barstow and Mojave Freeway (Heavy Traffic Route), 9.0 mi NW Muscoy, San Bernardino County, CA</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fd59-cd17-5b1e-96f0-ecd52d9ca617</t>
-  </si>
-  <si>
-    <t>03/17/2026 2:08:56 PM</t>
-  </si>
-  <si>
-    <t>Mojave Freeway, 40.9 mi E Fort Irwin, San Bernardino County, CA</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fd33-7ea2-593c-bc80-3292e8564a1b</t>
-  </si>
-  <si>
-    <t>03/17/2026 12:47:12 PM</t>
-  </si>
-  <si>
-    <t>CA 57, Glendora, CA, 91740-4507</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fce8-ab6b-5d8d-8a47-e5ac356c0409</t>
-  </si>
-  <si>
-    <t>03/16/2026 4:57:00 PM</t>
-  </si>
-  <si>
-    <t>I 70, 6.9 mi ENE Clifton, Mesa County, CO, 81526</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f8a7-02d9-56dd-919e-e46a5ec5ebb3</t>
-  </si>
-  <si>
-    <t>03/16/2026 4:24:56 PM</t>
-  </si>
-  <si>
-    <t>I 70, Lakewood, CO, 80401-4015</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f889-a46d-52d3-a704-9c67740b5bef</t>
   </si>
 </sst>
 </file>
@@ -1885,7 +1846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1993,7 +1954,7 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -2008,13 +1969,13 @@
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -2026,36 +1987,36 @@
         <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
         <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
         <v>37</v>
@@ -2081,34 +2042,34 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
         <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>41</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -2120,21 +2081,21 @@
         <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -2143,7 +2104,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -2152,51 +2113,51 @@
         <v>23</v>
       </c>
       <c r="J6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" t="s">
         <v>49</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" t="s">
         <v>50</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
         <v>52</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>53</v>
       </c>
-      <c r="C7" t="s">
-        <v>54</v>
-      </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J7" t="s">
         <v>55</v>
@@ -2228,7 +2189,7 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -2237,66 +2198,66 @@
         <v>20</v>
       </c>
       <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" t="s">
         <v>61</v>
       </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" t="s">
         <v>62</v>
-      </c>
-      <c r="K8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
         <v>64</v>
       </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
         <v>36</v>
       </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>48</v>
-      </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -2308,42 +2269,42 @@
         <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J10" t="s">
         <v>71</v>
       </c>
       <c r="K10" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -2363,13 +2324,13 @@
         <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -2381,16 +2342,16 @@
         <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L11" t="s">
         <v>26</v>
@@ -2402,68 +2363,68 @@
         <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" t="s">
         <v>80</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" t="s">
-        <v>84</v>
-      </c>
-      <c r="K12" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -2472,19 +2433,19 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J13" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="K13" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L13" t="s">
         <v>26</v>
@@ -2496,18 +2457,18 @@
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -2519,19 +2480,19 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L14" t="s">
         <v>26</v>
@@ -2543,21 +2504,21 @@
         <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -2566,19 +2527,19 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J15" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
@@ -2590,21 +2551,21 @@
         <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -2616,16 +2577,16 @@
         <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I16" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J16" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
@@ -2637,42 +2598,42 @@
         <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K17" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="L17" t="s">
         <v>26</v>
@@ -2684,68 +2645,68 @@
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" t="s">
+        <v>106</v>
+      </c>
+      <c r="K18" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" t="s">
+        <v>26</v>
+      </c>
+      <c r="O18" t="s">
         <v>107</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" t="s">
-        <v>108</v>
-      </c>
-      <c r="K18" t="s">
-        <v>109</v>
-      </c>
-      <c r="L18" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" t="s">
-        <v>26</v>
-      </c>
-      <c r="N18" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -2757,16 +2718,16 @@
         <v>21</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K19" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="L19" t="s">
         <v>26</v>
@@ -2778,42 +2739,42 @@
         <v>26</v>
       </c>
       <c r="O19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s">
         <v>114</v>
       </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
       <c r="D20" t="s">
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
         <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J20" t="s">
         <v>115</v>
       </c>
       <c r="K20" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
@@ -2833,34 +2794,34 @@
         <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
         <v>36</v>
       </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" t="s">
-        <v>21</v>
-      </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J21" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K21" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
@@ -2872,42 +2833,42 @@
         <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K22" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
@@ -2919,42 +2880,42 @@
         <v>26</v>
       </c>
       <c r="O22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
         <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -2966,21 +2927,21 @@
         <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -2989,19 +2950,19 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K24" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -3013,42 +2974,42 @@
         <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" t="s">
         <v>36</v>
       </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" t="s">
-        <v>48</v>
-      </c>
       <c r="H25" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K25" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -3060,21 +3021,21 @@
         <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
@@ -3083,19 +3044,19 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J26" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K26" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
@@ -3107,21 +3068,21 @@
         <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -3130,19 +3091,19 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="H27" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J27" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K27" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
@@ -3154,21 +3115,21 @@
         <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -3177,19 +3138,19 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H28" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="L28" t="s">
         <v>26</v>
@@ -3201,42 +3162,42 @@
         <v>26</v>
       </c>
       <c r="O28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
         <v>36</v>
       </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" t="s">
-        <v>48</v>
-      </c>
       <c r="H29" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K29" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="L29" t="s">
         <v>26</v>
@@ -3248,21 +3209,21 @@
         <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -3274,16 +3235,16 @@
         <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K30" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="L30" t="s">
         <v>26</v>
@@ -3303,10 +3264,10 @@
         <v>155</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -3315,116 +3276,116 @@
         <v>19</v>
       </c>
       <c r="F31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" t="s">
+        <v>54</v>
+      </c>
+      <c r="I31" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" t="s">
         <v>156</v>
       </c>
-      <c r="G31" t="s">
-        <v>61</v>
-      </c>
-      <c r="H31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
+        <v>129</v>
+      </c>
+      <c r="L31" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" t="s">
+        <v>26</v>
+      </c>
+      <c r="O31" t="s">
         <v>157</v>
-      </c>
-      <c r="K31" t="s">
-        <v>158</v>
-      </c>
-      <c r="L31" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" t="s">
-        <v>159</v>
-      </c>
-      <c r="O31" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" t="s">
+        <v>54</v>
+      </c>
+      <c r="I32" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" t="s">
         <v>161</v>
       </c>
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" t="s">
-        <v>48</v>
-      </c>
-      <c r="H32" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" t="s">
-        <v>23</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>162</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" t="s">
+        <v>26</v>
+      </c>
+      <c r="O32" t="s">
         <v>163</v>
-      </c>
-      <c r="L32" t="s">
-        <v>26</v>
-      </c>
-      <c r="M32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O32" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" t="s">
+        <v>54</v>
+      </c>
+      <c r="I33" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" t="s">
         <v>165</v>
       </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" t="s">
-        <v>48</v>
-      </c>
-      <c r="H33" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>166</v>
-      </c>
-      <c r="K33" t="s">
-        <v>163</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
@@ -3444,13 +3405,13 @@
         <v>168</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -3459,19 +3420,19 @@
         <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H34" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J34" t="s">
         <v>169</v>
       </c>
       <c r="K34" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L34" t="s">
         <v>26</v>
@@ -3491,10 +3452,10 @@
         <v>171</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -3506,19 +3467,19 @@
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H35" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K35" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="L35" t="s">
         <v>26</v>
@@ -3530,21 +3491,21 @@
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -3556,16 +3517,16 @@
         <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K36" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="L36" t="s">
         <v>26</v>
@@ -3577,136 +3538,136 @@
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" t="s">
+        <v>105</v>
+      </c>
+      <c r="H37" t="s">
+        <v>54</v>
+      </c>
+      <c r="I37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" t="s">
+        <v>178</v>
+      </c>
+      <c r="K37" t="s">
+        <v>110</v>
+      </c>
+      <c r="L37" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" t="s">
+        <v>26</v>
+      </c>
+      <c r="O37" t="s">
         <v>179</v>
-      </c>
-      <c r="B37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" t="s">
-        <v>21</v>
-      </c>
-      <c r="H37" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" t="s">
-        <v>180</v>
-      </c>
-      <c r="K37" t="s">
-        <v>181</v>
-      </c>
-      <c r="L37" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>180</v>
+      </c>
+      <c r="B38" t="s">
+        <v>181</v>
+      </c>
+      <c r="C38" t="s">
+        <v>182</v>
+      </c>
+      <c r="D38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" t="s">
+        <v>54</v>
+      </c>
+      <c r="I38" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" t="s">
         <v>183</v>
       </c>
-      <c r="B38" t="s">
-        <v>121</v>
-      </c>
-      <c r="C38" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" t="s">
-        <v>26</v>
-      </c>
-      <c r="F38" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" t="s">
-        <v>23</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" t="s">
         <v>184</v>
-      </c>
-      <c r="K38" t="s">
-        <v>56</v>
-      </c>
-      <c r="L38" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>185</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" t="s">
+        <v>54</v>
+      </c>
+      <c r="I39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" t="s">
         <v>186</v>
       </c>
-      <c r="B39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H39" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>187</v>
-      </c>
-      <c r="K39" t="s">
-        <v>25</v>
       </c>
       <c r="L39" t="s">
         <v>26</v>
@@ -3741,19 +3702,19 @@
         <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H40" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J40" t="s">
         <v>190</v>
       </c>
       <c r="K40" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="L40" t="s">
         <v>26</v>
@@ -3773,34 +3734,34 @@
         <v>192</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="G41" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="H41" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J41" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K41" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="L41" t="s">
         <v>26</v>
@@ -3809,24 +3770,24 @@
         <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="O41" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -3835,19 +3796,19 @@
         <v>20</v>
       </c>
       <c r="G42" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H42" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J42" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K42" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="L42" t="s">
         <v>26</v>
@@ -3859,21 +3820,21 @@
         <v>26</v>
       </c>
       <c r="O42" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -3885,16 +3846,16 @@
         <v>21</v>
       </c>
       <c r="H43" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I43" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J43" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K43" t="s">
-        <v>149</v>
+        <v>38</v>
       </c>
       <c r="L43" t="s">
         <v>26</v>
@@ -3906,24 +3867,24 @@
         <v>26</v>
       </c>
       <c r="O43" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
         <v>20</v>
@@ -3932,16 +3893,16 @@
         <v>21</v>
       </c>
       <c r="H44" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J44" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K44" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="L44" t="s">
         <v>26</v>
@@ -3953,21 +3914,21 @@
         <v>26</v>
       </c>
       <c r="O44" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>208</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
@@ -3976,19 +3937,19 @@
         <v>20</v>
       </c>
       <c r="G45" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H45" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I45" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J45" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K45" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L45" t="s">
         <v>26</v>
@@ -4000,21 +3961,21 @@
         <v>26</v>
       </c>
       <c r="O45" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
@@ -4023,19 +3984,19 @@
         <v>20</v>
       </c>
       <c r="G46" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H46" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I46" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="K46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L46" t="s">
         <v>26</v>
@@ -4047,21 +4008,21 @@
         <v>26</v>
       </c>
       <c r="O46" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
@@ -4070,19 +4031,19 @@
         <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H47" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I47" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J47" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="K47" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="L47" t="s">
         <v>26</v>
@@ -4094,42 +4055,42 @@
         <v>26</v>
       </c>
       <c r="O47" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F48" t="s">
         <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>215</v>
+        <v>21</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J48" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K48" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="L48" t="s">
         <v>26</v>
@@ -4141,21 +4102,21 @@
         <v>26</v>
       </c>
       <c r="O48" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
@@ -4164,19 +4125,19 @@
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H49" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I49" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J49" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K49" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L49" t="s">
         <v>26</v>
@@ -4188,21 +4149,21 @@
         <v>26</v>
       </c>
       <c r="O49" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
@@ -4214,16 +4175,16 @@
         <v>21</v>
       </c>
       <c r="H50" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I50" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J50" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K50" t="s">
-        <v>223</v>
+        <v>68</v>
       </c>
       <c r="L50" t="s">
         <v>26</v>
@@ -4235,42 +4196,42 @@
         <v>26</v>
       </c>
       <c r="O50" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
         <v>20</v>
       </c>
       <c r="G51" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H51" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I51" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J51" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K51" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="L51" t="s">
         <v>26</v>
@@ -4282,21 +4243,21 @@
         <v>26</v>
       </c>
       <c r="O51" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
@@ -4305,19 +4266,19 @@
         <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H52" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I52" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J52" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K52" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="L52" t="s">
         <v>26</v>
@@ -4329,42 +4290,42 @@
         <v>26</v>
       </c>
       <c r="O52" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D53" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" t="s">
         <v>36</v>
       </c>
-      <c r="E53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" t="s">
-        <v>21</v>
-      </c>
       <c r="H53" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I53" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J53" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K53" t="s">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="L53" t="s">
         <v>26</v>
@@ -4376,42 +4337,42 @@
         <v>26</v>
       </c>
       <c r="O53" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>159</v>
       </c>
       <c r="C54" t="s">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="D54" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F54" t="s">
         <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H54" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I54" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J54" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K54" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="L54" t="s">
         <v>26</v>
@@ -4423,21 +4384,21 @@
         <v>26</v>
       </c>
       <c r="O54" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B55" t="s">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
@@ -4446,19 +4407,19 @@
         <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H55" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I55" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J55" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K55" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L55" t="s">
         <v>26</v>
@@ -4470,42 +4431,42 @@
         <v>26</v>
       </c>
       <c r="O55" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="C56" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="D56" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" t="s">
         <v>36</v>
       </c>
-      <c r="E56" t="s">
-        <v>19</v>
-      </c>
-      <c r="F56" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" t="s">
-        <v>48</v>
-      </c>
       <c r="H56" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I56" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J56" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K56" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="L56" t="s">
         <v>26</v>
@@ -4517,42 +4478,42 @@
         <v>26</v>
       </c>
       <c r="O56" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="C57" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="D57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
         <v>36</v>
       </c>
-      <c r="E57" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" t="s">
-        <v>21</v>
-      </c>
       <c r="H57" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I57" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J57" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K57" t="s">
-        <v>109</v>
+        <v>247</v>
       </c>
       <c r="L57" t="s">
         <v>26</v>
@@ -4564,21 +4525,21 @@
         <v>26</v>
       </c>
       <c r="O57" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
@@ -4587,19 +4548,19 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H58" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I58" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J58" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K58" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="L58" t="s">
         <v>26</v>
@@ -4611,21 +4572,21 @@
         <v>26</v>
       </c>
       <c r="O58" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
@@ -4634,19 +4595,19 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H59" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I59" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J59" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="K59" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="L59" t="s">
         <v>26</v>
@@ -4658,42 +4619,42 @@
         <v>26</v>
       </c>
       <c r="O59" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="C60" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" t="s">
         <v>36</v>
       </c>
-      <c r="E60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" t="s">
-        <v>20</v>
-      </c>
-      <c r="G60" t="s">
-        <v>48</v>
-      </c>
       <c r="H60" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I60" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J60" t="s">
-        <v>152</v>
+        <v>257</v>
       </c>
       <c r="K60" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="L60" t="s">
         <v>26</v>
@@ -4705,18 +4666,18 @@
         <v>26</v>
       </c>
       <c r="O60" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="D61" t="s">
         <v>19</v>
@@ -4728,19 +4689,19 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H61" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I61" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J61" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K61" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="L61" t="s">
         <v>26</v>
@@ -4752,18 +4713,18 @@
         <v>26</v>
       </c>
       <c r="O61" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>118</v>
       </c>
       <c r="C62" t="s">
-        <v>260</v>
+        <v>30</v>
       </c>
       <c r="D62" t="s">
         <v>19</v>
@@ -4778,16 +4739,16 @@
         <v>21</v>
       </c>
       <c r="H62" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I62" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J62" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K62" t="s">
-        <v>163</v>
+        <v>38</v>
       </c>
       <c r="L62" t="s">
         <v>26</v>
@@ -4799,21 +4760,21 @@
         <v>26</v>
       </c>
       <c r="O62" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B63" t="s">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>260</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
@@ -4822,19 +4783,19 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H63" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I63" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J63" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K63" t="s">
-        <v>265</v>
+        <v>129</v>
       </c>
       <c r="L63" t="s">
         <v>26</v>
@@ -4846,18 +4807,18 @@
         <v>26</v>
       </c>
       <c r="O63" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B64" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -4869,19 +4830,19 @@
         <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H64" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I64" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J64" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K64" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="L64" t="s">
         <v>26</v>
@@ -4893,21 +4854,21 @@
         <v>26</v>
       </c>
       <c r="O64" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B65" t="s">
-        <v>46</v>
+        <v>181</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="D65" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
@@ -4919,16 +4880,16 @@
         <v>21</v>
       </c>
       <c r="H65" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I65" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J65" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K65" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="L65" t="s">
         <v>26</v>
@@ -4940,12 +4901,12 @@
         <v>26</v>
       </c>
       <c r="O65" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B66" t="s">
         <v>16</v>
@@ -4966,16 +4927,16 @@
         <v>21</v>
       </c>
       <c r="H66" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I66" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J66" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K66" t="s">
-        <v>265</v>
+        <v>56</v>
       </c>
       <c r="L66" t="s">
         <v>26</v>
@@ -4987,21 +4948,21 @@
         <v>26</v>
       </c>
       <c r="O66" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B67" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>278</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
@@ -5010,19 +4971,19 @@
         <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H67" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I67" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J67" t="s">
         <v>279</v>
       </c>
       <c r="K67" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="L67" t="s">
         <v>26</v>
@@ -5042,13 +5003,13 @@
         <v>281</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C68" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
@@ -5060,16 +5021,16 @@
         <v>282</v>
       </c>
       <c r="H68" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I68" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J68" t="s">
         <v>283</v>
       </c>
       <c r="K68" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -5089,13 +5050,13 @@
         <v>285</v>
       </c>
       <c r="B69" t="s">
-        <v>259</v>
+        <v>118</v>
       </c>
       <c r="C69" t="s">
-        <v>260</v>
+        <v>26</v>
       </c>
       <c r="D69" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
@@ -5104,113 +5065,113 @@
         <v>20</v>
       </c>
       <c r="G69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" t="s">
+        <v>54</v>
+      </c>
+      <c r="I69" t="s">
+        <v>31</v>
+      </c>
+      <c r="J69" t="s">
         <v>286</v>
       </c>
-      <c r="H69" t="s">
-        <v>22</v>
-      </c>
-      <c r="I69" t="s">
-        <v>23</v>
-      </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
+        <v>122</v>
+      </c>
+      <c r="L69" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" t="s">
+        <v>26</v>
+      </c>
+      <c r="O69" t="s">
         <v>287</v>
-      </c>
-      <c r="K69" t="s">
-        <v>56</v>
-      </c>
-      <c r="L69" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" t="s">
-        <v>26</v>
-      </c>
-      <c r="O69" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>288</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" t="s">
+        <v>54</v>
+      </c>
+      <c r="I70" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" t="s">
+        <v>190</v>
+      </c>
+      <c r="K70" t="s">
+        <v>75</v>
+      </c>
+      <c r="L70" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" t="s">
+        <v>26</v>
+      </c>
+      <c r="O70" t="s">
         <v>289</v>
-      </c>
-      <c r="B70" t="s">
-        <v>277</v>
-      </c>
-      <c r="C70" t="s">
-        <v>278</v>
-      </c>
-      <c r="D70" t="s">
-        <v>76</v>
-      </c>
-      <c r="E70" t="s">
-        <v>19</v>
-      </c>
-      <c r="F70" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" t="s">
-        <v>48</v>
-      </c>
-      <c r="H70" t="s">
-        <v>22</v>
-      </c>
-      <c r="I70" t="s">
-        <v>23</v>
-      </c>
-      <c r="J70" t="s">
-        <v>290</v>
-      </c>
-      <c r="K70" t="s">
-        <v>291</v>
-      </c>
-      <c r="L70" t="s">
-        <v>26</v>
-      </c>
-      <c r="M70" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" t="s">
-        <v>26</v>
-      </c>
-      <c r="O70" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="C71" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="D71" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F71" t="s">
         <v>20</v>
       </c>
       <c r="G71" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H71" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I71" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J71" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="K71" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="L71" t="s">
         <v>26</v>
@@ -5222,42 +5183,42 @@
         <v>26</v>
       </c>
       <c r="O71" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>293</v>
+      </c>
+      <c r="B72" t="s">
+        <v>294</v>
+      </c>
+      <c r="C72" t="s">
+        <v>295</v>
+      </c>
+      <c r="D72" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" t="s">
+        <v>36</v>
+      </c>
+      <c r="H72" t="s">
+        <v>54</v>
+      </c>
+      <c r="I72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J72" t="s">
         <v>296</v>
       </c>
-      <c r="B72" t="s">
-        <v>34</v>
-      </c>
-      <c r="C72" t="s">
-        <v>35</v>
-      </c>
-      <c r="D72" t="s">
-        <v>36</v>
-      </c>
-      <c r="E72" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" t="s">
-        <v>20</v>
-      </c>
-      <c r="G72" t="s">
-        <v>48</v>
-      </c>
-      <c r="H72" t="s">
-        <v>22</v>
-      </c>
-      <c r="I72" t="s">
-        <v>23</v>
-      </c>
-      <c r="J72" t="s">
-        <v>174</v>
-      </c>
       <c r="K72" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="L72" t="s">
         <v>26</v>
@@ -5277,13 +5238,13 @@
         <v>298</v>
       </c>
       <c r="B73" t="s">
-        <v>143</v>
+        <v>294</v>
       </c>
       <c r="C73" t="s">
-        <v>144</v>
+        <v>295</v>
       </c>
       <c r="D73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
@@ -5292,19 +5253,19 @@
         <v>20</v>
       </c>
       <c r="G73" t="s">
+        <v>36</v>
+      </c>
+      <c r="H73" t="s">
+        <v>54</v>
+      </c>
+      <c r="I73" t="s">
+        <v>31</v>
+      </c>
+      <c r="J73" t="s">
         <v>299</v>
       </c>
-      <c r="H73" t="s">
-        <v>22</v>
-      </c>
-      <c r="I73" t="s">
-        <v>23</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>300</v>
-      </c>
-      <c r="K73" t="s">
-        <v>102</v>
       </c>
       <c r="L73" t="s">
         <v>26</v>
@@ -5324,10 +5285,10 @@
         <v>302</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C74" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D74" t="s">
         <v>19</v>
@@ -5342,16 +5303,16 @@
         <v>21</v>
       </c>
       <c r="H74" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I74" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J74" t="s">
         <v>303</v>
       </c>
       <c r="K74" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="L74" t="s">
         <v>26</v>
@@ -5371,13 +5332,13 @@
         <v>305</v>
       </c>
       <c r="B75" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="C75" t="s">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="D75" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
@@ -5386,19 +5347,19 @@
         <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H75" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I75" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J75" t="s">
         <v>306</v>
       </c>
       <c r="K75" t="s">
-        <v>50</v>
+        <v>162</v>
       </c>
       <c r="L75" t="s">
         <v>26</v>
@@ -5418,13 +5379,13 @@
         <v>308</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D76" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
@@ -5433,19 +5394,19 @@
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H76" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I76" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J76" t="s">
         <v>309</v>
       </c>
       <c r="K76" t="s">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="L76" t="s">
         <v>26</v>
@@ -5471,28 +5432,28 @@
         <v>313</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="E77" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
         <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H77" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I77" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J77" t="s">
         <v>314</v>
       </c>
       <c r="K77" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="L77" t="s">
         <v>26</v>
@@ -5512,34 +5473,34 @@
         <v>316</v>
       </c>
       <c r="B78" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="C78" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E78" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F78" t="s">
         <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>61</v>
+        <v>317</v>
       </c>
       <c r="H78" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I78" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J78" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K78" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L78" t="s">
         <v>26</v>
@@ -5551,21 +5512,21 @@
         <v>26</v>
       </c>
       <c r="O78" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B79" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="C79" t="s">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="D79" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
@@ -5574,19 +5535,19 @@
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>48</v>
+        <v>321</v>
       </c>
       <c r="H79" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I79" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J79" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K79" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="L79" t="s">
         <v>26</v>
@@ -5598,24 +5559,24 @@
         <v>26</v>
       </c>
       <c r="O79" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B80" t="s">
-        <v>69</v>
+        <v>312</v>
       </c>
       <c r="C80" t="s">
-        <v>70</v>
+        <v>313</v>
       </c>
       <c r="D80" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="E80" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F80" t="s">
         <v>20</v>
@@ -5624,16 +5585,16 @@
         <v>21</v>
       </c>
       <c r="H80" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I80" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J80" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K80" t="s">
-        <v>102</v>
+        <v>326</v>
       </c>
       <c r="L80" t="s">
         <v>26</v>
@@ -5645,21 +5606,21 @@
         <v>26</v>
       </c>
       <c r="O80" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C81" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
@@ -5671,16 +5632,16 @@
         <v>21</v>
       </c>
       <c r="H81" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I81" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J81" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K81" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="L81" t="s">
         <v>26</v>
@@ -5692,21 +5653,21 @@
         <v>26</v>
       </c>
       <c r="O81" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="C82" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
         <v>19</v>
@@ -5718,16 +5679,16 @@
         <v>21</v>
       </c>
       <c r="H82" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I82" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J82" t="s">
-        <v>330</v>
+        <v>210</v>
       </c>
       <c r="K82" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="L82" t="s">
         <v>26</v>
@@ -5739,21 +5700,21 @@
         <v>26</v>
       </c>
       <c r="O82" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
@@ -5762,19 +5723,19 @@
         <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>48</v>
+        <v>334</v>
       </c>
       <c r="H83" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I83" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J83" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K83" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L83" t="s">
         <v>26</v>
@@ -5786,42 +5747,42 @@
         <v>26</v>
       </c>
       <c r="O83" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B84" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C84" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D84" t="s">
         <v>19</v>
       </c>
       <c r="E84" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F84" t="s">
         <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H84" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I84" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J84" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K84" t="s">
-        <v>153</v>
+        <v>68</v>
       </c>
       <c r="L84" t="s">
         <v>26</v>
@@ -5833,21 +5794,21 @@
         <v>26</v>
       </c>
       <c r="O84" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B85" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="C85" t="s">
-        <v>144</v>
+        <v>209</v>
       </c>
       <c r="D85" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E85" t="s">
         <v>19</v>
@@ -5859,16 +5820,16 @@
         <v>21</v>
       </c>
       <c r="H85" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I85" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J85" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K85" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
@@ -5880,21 +5841,21 @@
         <v>26</v>
       </c>
       <c r="O85" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
@@ -5903,19 +5864,19 @@
         <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H86" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I86" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J86" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K86" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="L86" t="s">
         <v>26</v>
@@ -5927,206 +5888,206 @@
         <v>26</v>
       </c>
       <c r="O86" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B87" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="C87" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="D87" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F87" t="s">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="H87" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I87" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J87" t="s">
         <v>347</v>
       </c>
       <c r="K87" t="s">
+        <v>162</v>
+      </c>
+      <c r="L87" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" t="s">
+        <v>26</v>
+      </c>
+      <c r="O87" t="s">
         <v>348</v>
-      </c>
-      <c r="L87" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" t="s">
-        <v>349</v>
-      </c>
-      <c r="O87" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>349</v>
+      </c>
+      <c r="B88" t="s">
+        <v>113</v>
+      </c>
+      <c r="C88" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F88" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" t="s">
+        <v>105</v>
+      </c>
+      <c r="H88" t="s">
+        <v>54</v>
+      </c>
+      <c r="I88" t="s">
+        <v>31</v>
+      </c>
+      <c r="J88" t="s">
+        <v>350</v>
+      </c>
+      <c r="K88" t="s">
+        <v>49</v>
+      </c>
+      <c r="L88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" t="s">
+        <v>26</v>
+      </c>
+      <c r="N88" t="s">
+        <v>26</v>
+      </c>
+      <c r="O88" t="s">
         <v>351</v>
-      </c>
-      <c r="B88" t="s">
-        <v>34</v>
-      </c>
-      <c r="C88" t="s">
-        <v>35</v>
-      </c>
-      <c r="D88" t="s">
-        <v>36</v>
-      </c>
-      <c r="E88" t="s">
-        <v>19</v>
-      </c>
-      <c r="F88" t="s">
-        <v>20</v>
-      </c>
-      <c r="G88" t="s">
-        <v>48</v>
-      </c>
-      <c r="H88" t="s">
-        <v>22</v>
-      </c>
-      <c r="I88" t="s">
-        <v>23</v>
-      </c>
-      <c r="J88" t="s">
-        <v>352</v>
-      </c>
-      <c r="K88" t="s">
-        <v>90</v>
-      </c>
-      <c r="L88" t="s">
-        <v>26</v>
-      </c>
-      <c r="M88" t="s">
-        <v>26</v>
-      </c>
-      <c r="N88" t="s">
-        <v>26</v>
-      </c>
-      <c r="O88" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>352</v>
+      </c>
+      <c r="B89" t="s">
+        <v>353</v>
+      </c>
+      <c r="C89" t="s">
+        <v>119</v>
+      </c>
+      <c r="D89" t="s">
+        <v>120</v>
+      </c>
+      <c r="E89" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" t="s">
+        <v>20</v>
+      </c>
+      <c r="G89" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" t="s">
+        <v>54</v>
+      </c>
+      <c r="I89" t="s">
+        <v>31</v>
+      </c>
+      <c r="J89" t="s">
         <v>354</v>
       </c>
-      <c r="B89" t="s">
-        <v>34</v>
-      </c>
-      <c r="C89" t="s">
-        <v>35</v>
-      </c>
-      <c r="D89" t="s">
-        <v>36</v>
-      </c>
-      <c r="E89" t="s">
-        <v>19</v>
-      </c>
-      <c r="F89" t="s">
-        <v>20</v>
-      </c>
-      <c r="G89" t="s">
+      <c r="K89" t="s">
+        <v>187</v>
+      </c>
+      <c r="L89" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" t="s">
+        <v>26</v>
+      </c>
+      <c r="O89" t="s">
         <v>355</v>
-      </c>
-      <c r="H89" t="s">
-        <v>22</v>
-      </c>
-      <c r="I89" t="s">
-        <v>23</v>
-      </c>
-      <c r="J89" t="s">
-        <v>356</v>
-      </c>
-      <c r="K89" t="s">
-        <v>128</v>
-      </c>
-      <c r="L89" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" t="s">
-        <v>26</v>
-      </c>
-      <c r="O89" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>356</v>
+      </c>
+      <c r="B90" t="s">
+        <v>113</v>
+      </c>
+      <c r="C90" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" t="s">
+        <v>26</v>
+      </c>
+      <c r="F90" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" t="s">
+        <v>36</v>
+      </c>
+      <c r="H90" t="s">
+        <v>54</v>
+      </c>
+      <c r="I90" t="s">
+        <v>31</v>
+      </c>
+      <c r="J90" t="s">
+        <v>357</v>
+      </c>
+      <c r="K90" t="s">
+        <v>33</v>
+      </c>
+      <c r="L90" t="s">
+        <v>26</v>
+      </c>
+      <c r="M90" t="s">
+        <v>26</v>
+      </c>
+      <c r="N90" t="s">
+        <v>26</v>
+      </c>
+      <c r="O90" t="s">
         <v>358</v>
-      </c>
-      <c r="B90" t="s">
-        <v>259</v>
-      </c>
-      <c r="C90" t="s">
-        <v>260</v>
-      </c>
-      <c r="D90" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" t="s">
-        <v>19</v>
-      </c>
-      <c r="F90" t="s">
-        <v>20</v>
-      </c>
-      <c r="G90" t="s">
-        <v>48</v>
-      </c>
-      <c r="H90" t="s">
-        <v>22</v>
-      </c>
-      <c r="I90" t="s">
-        <v>23</v>
-      </c>
-      <c r="J90" t="s">
-        <v>287</v>
-      </c>
-      <c r="K90" t="s">
-        <v>56</v>
-      </c>
-      <c r="L90" t="s">
-        <v>26</v>
-      </c>
-      <c r="M90" t="s">
-        <v>26</v>
-      </c>
-      <c r="N90" t="s">
-        <v>26</v>
-      </c>
-      <c r="O90" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B91" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -6138,207 +6099,207 @@
         <v>20</v>
       </c>
       <c r="G91" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H91" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I91" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J91" t="s">
+        <v>360</v>
+      </c>
+      <c r="K91" t="s">
+        <v>129</v>
+      </c>
+      <c r="L91" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" t="s">
+        <v>26</v>
+      </c>
+      <c r="O91" t="s">
         <v>361</v>
-      </c>
-      <c r="K91" t="s">
-        <v>50</v>
-      </c>
-      <c r="L91" t="s">
-        <v>26</v>
-      </c>
-      <c r="M91" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" t="s">
-        <v>26</v>
-      </c>
-      <c r="O91" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>362</v>
+      </c>
+      <c r="B92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" t="s">
+        <v>30</v>
+      </c>
+      <c r="D92" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" t="s">
+        <v>36</v>
+      </c>
+      <c r="H92" t="s">
+        <v>54</v>
+      </c>
+      <c r="I92" t="s">
+        <v>31</v>
+      </c>
+      <c r="J92" t="s">
         <v>363</v>
       </c>
-      <c r="B92" t="s">
-        <v>172</v>
-      </c>
-      <c r="C92" t="s">
-        <v>173</v>
-      </c>
-      <c r="D92" t="s">
-        <v>18</v>
-      </c>
-      <c r="E92" t="s">
-        <v>19</v>
-      </c>
-      <c r="F92" t="s">
-        <v>20</v>
-      </c>
-      <c r="G92" t="s">
-        <v>48</v>
-      </c>
-      <c r="H92" t="s">
-        <v>22</v>
-      </c>
-      <c r="I92" t="s">
-        <v>23</v>
-      </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M92" t="s">
+        <v>26</v>
+      </c>
+      <c r="N92" t="s">
+        <v>26</v>
+      </c>
+      <c r="O92" t="s">
         <v>364</v>
-      </c>
-      <c r="K92" t="s">
-        <v>66</v>
-      </c>
-      <c r="L92" t="s">
-        <v>26</v>
-      </c>
-      <c r="M92" t="s">
-        <v>26</v>
-      </c>
-      <c r="N92" t="s">
-        <v>26</v>
-      </c>
-      <c r="O92" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>365</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F93" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" t="s">
+        <v>21</v>
+      </c>
+      <c r="H93" t="s">
+        <v>54</v>
+      </c>
+      <c r="I93" t="s">
+        <v>31</v>
+      </c>
+      <c r="J93" t="s">
         <v>366</v>
       </c>
-      <c r="B93" t="s">
-        <v>34</v>
-      </c>
-      <c r="C93" t="s">
-        <v>35</v>
-      </c>
-      <c r="D93" t="s">
-        <v>36</v>
-      </c>
-      <c r="E93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F93" t="s">
-        <v>20</v>
-      </c>
-      <c r="G93" t="s">
-        <v>215</v>
-      </c>
-      <c r="H93" t="s">
-        <v>22</v>
-      </c>
-      <c r="I93" t="s">
-        <v>23</v>
-      </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
+        <v>75</v>
+      </c>
+      <c r="L93" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" t="s">
+        <v>26</v>
+      </c>
+      <c r="N93" t="s">
+        <v>26</v>
+      </c>
+      <c r="O93" t="s">
         <v>367</v>
-      </c>
-      <c r="K93" t="s">
-        <v>38</v>
-      </c>
-      <c r="L93" t="s">
-        <v>26</v>
-      </c>
-      <c r="M93" t="s">
-        <v>26</v>
-      </c>
-      <c r="N93" t="s">
-        <v>26</v>
-      </c>
-      <c r="O93" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>368</v>
+      </c>
+      <c r="B94" t="s">
+        <v>113</v>
+      </c>
+      <c r="C94" t="s">
+        <v>114</v>
+      </c>
+      <c r="D94" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" t="s">
+        <v>26</v>
+      </c>
+      <c r="F94" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" t="s">
+        <v>36</v>
+      </c>
+      <c r="H94" t="s">
+        <v>54</v>
+      </c>
+      <c r="I94" t="s">
+        <v>31</v>
+      </c>
+      <c r="J94" t="s">
         <v>369</v>
       </c>
-      <c r="B94" t="s">
+      <c r="K94" t="s">
+        <v>45</v>
+      </c>
+      <c r="L94" t="s">
+        <v>26</v>
+      </c>
+      <c r="M94" t="s">
+        <v>26</v>
+      </c>
+      <c r="N94" t="s">
+        <v>26</v>
+      </c>
+      <c r="O94" t="s">
         <v>370</v>
-      </c>
-      <c r="C94" t="s">
-        <v>371</v>
-      </c>
-      <c r="D94" t="s">
-        <v>18</v>
-      </c>
-      <c r="E94" t="s">
-        <v>19</v>
-      </c>
-      <c r="F94" t="s">
-        <v>20</v>
-      </c>
-      <c r="G94" t="s">
-        <v>21</v>
-      </c>
-      <c r="H94" t="s">
-        <v>22</v>
-      </c>
-      <c r="I94" t="s">
-        <v>23</v>
-      </c>
-      <c r="J94" t="s">
-        <v>372</v>
-      </c>
-      <c r="K94" t="s">
-        <v>25</v>
-      </c>
-      <c r="L94" t="s">
-        <v>26</v>
-      </c>
-      <c r="M94" t="s">
-        <v>26</v>
-      </c>
-      <c r="N94" t="s">
-        <v>26</v>
-      </c>
-      <c r="O94" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="C95" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="D95" t="s">
+        <v>43</v>
+      </c>
+      <c r="E95" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" t="s">
         <v>36</v>
       </c>
-      <c r="E95" t="s">
-        <v>19</v>
-      </c>
-      <c r="F95" t="s">
-        <v>20</v>
-      </c>
-      <c r="G95" t="s">
-        <v>48</v>
-      </c>
       <c r="H95" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I95" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J95" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="K95" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -6350,21 +6311,21 @@
         <v>26</v>
       </c>
       <c r="O95" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C96" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D96" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E96" t="s">
         <v>19</v>
@@ -6376,16 +6337,16 @@
         <v>21</v>
       </c>
       <c r="H96" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I96" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J96" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="K96" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="L96" t="s">
         <v>26</v>
@@ -6397,89 +6358,89 @@
         <v>26</v>
       </c>
       <c r="O96" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>377</v>
+      </c>
+      <c r="B97" t="s">
+        <v>64</v>
+      </c>
+      <c r="C97" t="s">
+        <v>65</v>
+      </c>
+      <c r="D97" t="s">
+        <v>66</v>
+      </c>
+      <c r="E97" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" t="s">
+        <v>378</v>
+      </c>
+      <c r="G97" t="s">
+        <v>379</v>
+      </c>
+      <c r="H97" t="s">
+        <v>54</v>
+      </c>
+      <c r="I97" t="s">
+        <v>31</v>
+      </c>
+      <c r="J97" t="s">
         <v>380</v>
       </c>
-      <c r="B97" t="s">
-        <v>320</v>
-      </c>
-      <c r="C97" t="s">
-        <v>75</v>
-      </c>
-      <c r="D97" t="s">
-        <v>76</v>
-      </c>
-      <c r="E97" t="s">
-        <v>19</v>
-      </c>
-      <c r="F97" t="s">
-        <v>156</v>
-      </c>
-      <c r="G97" t="s">
-        <v>21</v>
-      </c>
-      <c r="H97" t="s">
-        <v>22</v>
-      </c>
-      <c r="I97" t="s">
-        <v>23</v>
-      </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>381</v>
       </c>
-      <c r="K97" t="s">
+      <c r="L97" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" t="s">
         <v>382</v>
       </c>
-      <c r="L97" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" t="s">
-        <v>26</v>
-      </c>
-      <c r="N97" t="s">
+      <c r="O97" t="s">
         <v>383</v>
-      </c>
-      <c r="O97" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>384</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" t="s">
+        <v>21</v>
+      </c>
+      <c r="H98" t="s">
+        <v>54</v>
+      </c>
+      <c r="I98" t="s">
+        <v>31</v>
+      </c>
+      <c r="J98" t="s">
         <v>385</v>
       </c>
-      <c r="B98" t="s">
-        <v>34</v>
-      </c>
-      <c r="C98" t="s">
-        <v>35</v>
-      </c>
-      <c r="D98" t="s">
-        <v>36</v>
-      </c>
-      <c r="E98" t="s">
-        <v>19</v>
-      </c>
-      <c r="F98" t="s">
-        <v>20</v>
-      </c>
-      <c r="G98" t="s">
-        <v>48</v>
-      </c>
-      <c r="H98" t="s">
-        <v>22</v>
-      </c>
-      <c r="I98" t="s">
-        <v>23</v>
-      </c>
-      <c r="J98" t="s">
-        <v>364</v>
-      </c>
       <c r="K98" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="L98" t="s">
         <v>26</v>
@@ -6499,13 +6460,13 @@
         <v>387</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C99" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
@@ -6514,19 +6475,19 @@
         <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>48</v>
+        <v>388</v>
       </c>
       <c r="H99" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I99" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J99" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K99" t="s">
-        <v>90</v>
+        <v>166</v>
       </c>
       <c r="L99" t="s">
         <v>26</v>
@@ -6538,68 +6499,68 @@
         <v>26</v>
       </c>
       <c r="O99" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>294</v>
       </c>
       <c r="C100" t="s">
+        <v>295</v>
+      </c>
+      <c r="D100" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" t="s">
+        <v>21</v>
+      </c>
+      <c r="H100" t="s">
+        <v>54</v>
+      </c>
+      <c r="I100" t="s">
+        <v>31</v>
+      </c>
+      <c r="J100" t="s">
+        <v>322</v>
+      </c>
+      <c r="K100" t="s">
+        <v>68</v>
+      </c>
+      <c r="L100" t="s">
+        <v>26</v>
+      </c>
+      <c r="M100" t="s">
+        <v>26</v>
+      </c>
+      <c r="N100" t="s">
+        <v>26</v>
+      </c>
+      <c r="O100" t="s">
         <v>392</v>
-      </c>
-      <c r="D100" t="s">
-        <v>19</v>
-      </c>
-      <c r="E100" t="s">
-        <v>19</v>
-      </c>
-      <c r="F100" t="s">
-        <v>20</v>
-      </c>
-      <c r="G100" t="s">
-        <v>61</v>
-      </c>
-      <c r="H100" t="s">
-        <v>22</v>
-      </c>
-      <c r="I100" t="s">
-        <v>23</v>
-      </c>
-      <c r="J100" t="s">
-        <v>393</v>
-      </c>
-      <c r="K100" t="s">
-        <v>149</v>
-      </c>
-      <c r="L100" t="s">
-        <v>26</v>
-      </c>
-      <c r="M100" t="s">
-        <v>26</v>
-      </c>
-      <c r="N100" t="s">
-        <v>26</v>
-      </c>
-      <c r="O100" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B101" t="s">
-        <v>259</v>
+        <v>103</v>
       </c>
       <c r="C101" t="s">
-        <v>260</v>
+        <v>104</v>
       </c>
       <c r="D101" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
@@ -6611,16 +6572,16 @@
         <v>21</v>
       </c>
       <c r="H101" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I101" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J101" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="K101" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="L101" t="s">
         <v>26</v>
@@ -6632,21 +6593,21 @@
         <v>26</v>
       </c>
       <c r="O101" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B102" t="s">
-        <v>399</v>
+        <v>208</v>
       </c>
       <c r="C102" t="s">
-        <v>400</v>
+        <v>209</v>
       </c>
       <c r="D102" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
@@ -6658,16 +6619,16 @@
         <v>21</v>
       </c>
       <c r="H102" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I102" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J102" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K102" t="s">
-        <v>223</v>
+        <v>110</v>
       </c>
       <c r="L102" t="s">
         <v>26</v>
@@ -6679,21 +6640,21 @@
         <v>26</v>
       </c>
       <c r="O102" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B103" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="C103" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E103" t="s">
         <v>19</v>
@@ -6702,19 +6663,19 @@
         <v>20</v>
       </c>
       <c r="G103" t="s">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="H103" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I103" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J103" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="K103" t="s">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="L103" t="s">
         <v>26</v>
@@ -6726,68 +6687,68 @@
         <v>26</v>
       </c>
       <c r="O103" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>402</v>
+      </c>
+      <c r="B104" t="s">
+        <v>403</v>
+      </c>
+      <c r="C104" t="s">
+        <v>404</v>
+      </c>
+      <c r="D104" t="s">
+        <v>43</v>
+      </c>
+      <c r="E104" t="s">
+        <v>19</v>
+      </c>
+      <c r="F104" t="s">
+        <v>20</v>
+      </c>
+      <c r="G104" t="s">
+        <v>36</v>
+      </c>
+      <c r="H104" t="s">
+        <v>54</v>
+      </c>
+      <c r="I104" t="s">
+        <v>31</v>
+      </c>
+      <c r="J104" t="s">
+        <v>405</v>
+      </c>
+      <c r="K104" t="s">
+        <v>79</v>
+      </c>
+      <c r="L104" t="s">
+        <v>26</v>
+      </c>
+      <c r="M104" t="s">
+        <v>26</v>
+      </c>
+      <c r="N104" t="s">
+        <v>26</v>
+      </c>
+      <c r="O104" t="s">
         <v>406</v>
-      </c>
-      <c r="B104" t="s">
-        <v>34</v>
-      </c>
-      <c r="C104" t="s">
-        <v>35</v>
-      </c>
-      <c r="D104" t="s">
-        <v>36</v>
-      </c>
-      <c r="E104" t="s">
-        <v>19</v>
-      </c>
-      <c r="F104" t="s">
-        <v>20</v>
-      </c>
-      <c r="G104" t="s">
-        <v>21</v>
-      </c>
-      <c r="H104" t="s">
-        <v>22</v>
-      </c>
-      <c r="I104" t="s">
-        <v>23</v>
-      </c>
-      <c r="J104" t="s">
-        <v>287</v>
-      </c>
-      <c r="K104" t="s">
-        <v>102</v>
-      </c>
-      <c r="L104" t="s">
-        <v>26</v>
-      </c>
-      <c r="M104" t="s">
-        <v>26</v>
-      </c>
-      <c r="N104" t="s">
-        <v>26</v>
-      </c>
-      <c r="O104" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D105" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E105" t="s">
         <v>19</v>
@@ -6799,119 +6760,119 @@
         <v>21</v>
       </c>
       <c r="H105" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I105" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J105" t="s">
+        <v>408</v>
+      </c>
+      <c r="K105" t="s">
+        <v>110</v>
+      </c>
+      <c r="L105" t="s">
+        <v>26</v>
+      </c>
+      <c r="M105" t="s">
+        <v>26</v>
+      </c>
+      <c r="N105" t="s">
+        <v>26</v>
+      </c>
+      <c r="O105" t="s">
         <v>409</v>
-      </c>
-      <c r="K105" t="s">
-        <v>410</v>
-      </c>
-      <c r="L105" t="s">
-        <v>26</v>
-      </c>
-      <c r="M105" t="s">
-        <v>26</v>
-      </c>
-      <c r="N105" t="s">
-        <v>26</v>
-      </c>
-      <c r="O105" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>410</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" t="s">
+        <v>36</v>
+      </c>
+      <c r="H106" t="s">
+        <v>54</v>
+      </c>
+      <c r="I106" t="s">
+        <v>31</v>
+      </c>
+      <c r="J106" t="s">
+        <v>411</v>
+      </c>
+      <c r="K106" t="s">
+        <v>129</v>
+      </c>
+      <c r="L106" t="s">
+        <v>26</v>
+      </c>
+      <c r="M106" t="s">
+        <v>26</v>
+      </c>
+      <c r="N106" t="s">
+        <v>26</v>
+      </c>
+      <c r="O106" t="s">
         <v>412</v>
-      </c>
-      <c r="B106" t="s">
-        <v>259</v>
-      </c>
-      <c r="C106" t="s">
-        <v>260</v>
-      </c>
-      <c r="D106" t="s">
-        <v>19</v>
-      </c>
-      <c r="E106" t="s">
-        <v>19</v>
-      </c>
-      <c r="F106" t="s">
-        <v>20</v>
-      </c>
-      <c r="G106" t="s">
-        <v>48</v>
-      </c>
-      <c r="H106" t="s">
-        <v>22</v>
-      </c>
-      <c r="I106" t="s">
-        <v>23</v>
-      </c>
-      <c r="J106" t="s">
-        <v>413</v>
-      </c>
-      <c r="K106" t="s">
-        <v>223</v>
-      </c>
-      <c r="L106" t="s">
-        <v>26</v>
-      </c>
-      <c r="M106" t="s">
-        <v>26</v>
-      </c>
-      <c r="N106" t="s">
-        <v>26</v>
-      </c>
-      <c r="O106" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>413</v>
+      </c>
+      <c r="B107" t="s">
+        <v>353</v>
+      </c>
+      <c r="C107" t="s">
+        <v>119</v>
+      </c>
+      <c r="D107" t="s">
+        <v>120</v>
+      </c>
+      <c r="E107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" t="s">
+        <v>193</v>
+      </c>
+      <c r="G107" t="s">
+        <v>36</v>
+      </c>
+      <c r="H107" t="s">
+        <v>54</v>
+      </c>
+      <c r="I107" t="s">
+        <v>31</v>
+      </c>
+      <c r="J107" t="s">
+        <v>414</v>
+      </c>
+      <c r="K107" t="s">
         <v>415</v>
       </c>
-      <c r="B107" t="s">
-        <v>34</v>
-      </c>
-      <c r="C107" t="s">
-        <v>35</v>
-      </c>
-      <c r="D107" t="s">
-        <v>36</v>
-      </c>
-      <c r="E107" t="s">
-        <v>19</v>
-      </c>
-      <c r="F107" t="s">
-        <v>20</v>
-      </c>
-      <c r="G107" t="s">
-        <v>21</v>
-      </c>
-      <c r="H107" t="s">
-        <v>22</v>
-      </c>
-      <c r="I107" t="s">
-        <v>23</v>
-      </c>
-      <c r="J107" t="s">
+      <c r="L107" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" t="s">
+        <v>26</v>
+      </c>
+      <c r="N107" t="s">
         <v>416</v>
-      </c>
-      <c r="K107" t="s">
-        <v>90</v>
-      </c>
-      <c r="L107" t="s">
-        <v>26</v>
-      </c>
-      <c r="M107" t="s">
-        <v>26</v>
-      </c>
-      <c r="N107" t="s">
-        <v>26</v>
       </c>
       <c r="O107" t="s">
         <v>417</v>
@@ -6922,10 +6883,10 @@
         <v>418</v>
       </c>
       <c r="B108" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C108" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D108" t="s">
         <v>18</v>
@@ -6934,45 +6895,45 @@
         <v>19</v>
       </c>
       <c r="F108" t="s">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="G108" t="s">
+        <v>21</v>
+      </c>
+      <c r="H108" t="s">
+        <v>54</v>
+      </c>
+      <c r="I108" t="s">
+        <v>31</v>
+      </c>
+      <c r="J108" t="s">
+        <v>397</v>
+      </c>
+      <c r="K108" t="s">
+        <v>56</v>
+      </c>
+      <c r="L108" t="s">
+        <v>26</v>
+      </c>
+      <c r="M108" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" t="s">
+        <v>26</v>
+      </c>
+      <c r="O108" t="s">
         <v>419</v>
-      </c>
-      <c r="H108" t="s">
-        <v>22</v>
-      </c>
-      <c r="I108" t="s">
-        <v>23</v>
-      </c>
-      <c r="J108" t="s">
-        <v>420</v>
-      </c>
-      <c r="K108" t="s">
-        <v>382</v>
-      </c>
-      <c r="L108" t="s">
-        <v>26</v>
-      </c>
-      <c r="M108" t="s">
-        <v>26</v>
-      </c>
-      <c r="N108" t="s">
-        <v>421</v>
-      </c>
-      <c r="O108" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B109" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="C109" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
         <v>18</v>
@@ -6987,16 +6948,16 @@
         <v>21</v>
       </c>
       <c r="H109" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I109" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J109" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="K109" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L109" t="s">
         <v>26</v>
@@ -7008,112 +6969,112 @@
         <v>26</v>
       </c>
       <c r="O109" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>423</v>
+      </c>
+      <c r="B110" t="s">
+        <v>424</v>
+      </c>
+      <c r="C110" t="s">
+        <v>425</v>
+      </c>
+      <c r="D110" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" t="s">
+        <v>20</v>
+      </c>
+      <c r="G110" t="s">
+        <v>105</v>
+      </c>
+      <c r="H110" t="s">
+        <v>54</v>
+      </c>
+      <c r="I110" t="s">
+        <v>31</v>
+      </c>
+      <c r="J110" t="s">
         <v>426</v>
       </c>
-      <c r="B110" t="s">
-        <v>34</v>
-      </c>
-      <c r="C110" t="s">
-        <v>35</v>
-      </c>
-      <c r="D110" t="s">
-        <v>36</v>
-      </c>
-      <c r="E110" t="s">
-        <v>19</v>
-      </c>
-      <c r="F110" t="s">
-        <v>20</v>
-      </c>
-      <c r="G110" t="s">
-        <v>61</v>
-      </c>
-      <c r="H110" t="s">
-        <v>22</v>
-      </c>
-      <c r="I110" t="s">
-        <v>23</v>
-      </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
+        <v>187</v>
+      </c>
+      <c r="L110" t="s">
+        <v>26</v>
+      </c>
+      <c r="M110" t="s">
+        <v>26</v>
+      </c>
+      <c r="N110" t="s">
+        <v>26</v>
+      </c>
+      <c r="O110" t="s">
         <v>427</v>
-      </c>
-      <c r="K110" t="s">
-        <v>212</v>
-      </c>
-      <c r="L110" t="s">
-        <v>26</v>
-      </c>
-      <c r="M110" t="s">
-        <v>26</v>
-      </c>
-      <c r="N110" t="s">
-        <v>26</v>
-      </c>
-      <c r="O110" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>428</v>
+      </c>
+      <c r="B111" t="s">
+        <v>294</v>
+      </c>
+      <c r="C111" t="s">
+        <v>295</v>
+      </c>
+      <c r="D111" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" t="s">
+        <v>20</v>
+      </c>
+      <c r="G111" t="s">
+        <v>36</v>
+      </c>
+      <c r="H111" t="s">
+        <v>54</v>
+      </c>
+      <c r="I111" t="s">
+        <v>31</v>
+      </c>
+      <c r="J111" t="s">
         <v>429</v>
       </c>
-      <c r="B111" t="s">
-        <v>320</v>
-      </c>
-      <c r="C111" t="s">
-        <v>75</v>
-      </c>
-      <c r="D111" t="s">
-        <v>76</v>
-      </c>
-      <c r="E111" t="s">
-        <v>19</v>
-      </c>
-      <c r="F111" t="s">
-        <v>20</v>
-      </c>
-      <c r="G111" t="s">
-        <v>48</v>
-      </c>
-      <c r="H111" t="s">
-        <v>22</v>
-      </c>
-      <c r="I111" t="s">
-        <v>23</v>
-      </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
+        <v>45</v>
+      </c>
+      <c r="L111" t="s">
+        <v>26</v>
+      </c>
+      <c r="M111" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" t="s">
+        <v>26</v>
+      </c>
+      <c r="O111" t="s">
         <v>430</v>
-      </c>
-      <c r="K111" t="s">
-        <v>102</v>
-      </c>
-      <c r="L111" t="s">
-        <v>26</v>
-      </c>
-      <c r="M111" t="s">
-        <v>26</v>
-      </c>
-      <c r="N111" t="s">
-        <v>26</v>
-      </c>
-      <c r="O111" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>431</v>
+      </c>
+      <c r="B112" t="s">
         <v>432</v>
       </c>
-      <c r="B112" t="s">
-        <v>259</v>
-      </c>
       <c r="C112" t="s">
-        <v>260</v>
+        <v>433</v>
       </c>
       <c r="D112" t="s">
         <v>19</v>
@@ -7125,19 +7086,19 @@
         <v>20</v>
       </c>
       <c r="G112" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H112" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I112" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J112" t="s">
-        <v>336</v>
+        <v>434</v>
       </c>
       <c r="K112" t="s">
-        <v>56</v>
+        <v>258</v>
       </c>
       <c r="L112" t="s">
         <v>26</v>
@@ -7149,42 +7110,42 @@
         <v>26</v>
       </c>
       <c r="O112" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B113" t="s">
-        <v>435</v>
+        <v>29</v>
       </c>
       <c r="C113" t="s">
-        <v>436</v>
+        <v>30</v>
       </c>
       <c r="D113" t="s">
         <v>19</v>
       </c>
       <c r="E113" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F113" t="s">
         <v>20</v>
       </c>
       <c r="G113" t="s">
-        <v>282</v>
+        <v>36</v>
       </c>
       <c r="H113" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I113" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J113" t="s">
         <v>437</v>
       </c>
       <c r="K113" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="L113" t="s">
         <v>26</v>
@@ -7204,107 +7165,107 @@
         <v>439</v>
       </c>
       <c r="B114" t="s">
-        <v>312</v>
+        <v>16</v>
       </c>
       <c r="C114" t="s">
-        <v>313</v>
+        <v>17</v>
       </c>
       <c r="D114" t="s">
         <v>18</v>
       </c>
       <c r="E114" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F114" t="s">
         <v>20</v>
       </c>
       <c r="G114" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H114" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I114" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J114" t="s">
+        <v>322</v>
+      </c>
+      <c r="K114" t="s">
+        <v>33</v>
+      </c>
+      <c r="L114" t="s">
+        <v>26</v>
+      </c>
+      <c r="M114" t="s">
+        <v>26</v>
+      </c>
+      <c r="N114" t="s">
+        <v>26</v>
+      </c>
+      <c r="O114" t="s">
         <v>440</v>
-      </c>
-      <c r="K114" t="s">
-        <v>50</v>
-      </c>
-      <c r="L114" t="s">
-        <v>26</v>
-      </c>
-      <c r="M114" t="s">
-        <v>26</v>
-      </c>
-      <c r="N114" t="s">
-        <v>26</v>
-      </c>
-      <c r="O114" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>441</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" t="s">
+        <v>18</v>
+      </c>
+      <c r="E115" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115" t="s">
+        <v>20</v>
+      </c>
+      <c r="G115" t="s">
+        <v>36</v>
+      </c>
+      <c r="H115" t="s">
+        <v>54</v>
+      </c>
+      <c r="I115" t="s">
+        <v>31</v>
+      </c>
+      <c r="J115" t="s">
         <v>442</v>
       </c>
-      <c r="B115" t="s">
+      <c r="K115" t="s">
         <v>443</v>
       </c>
-      <c r="C115" t="s">
-        <v>278</v>
-      </c>
-      <c r="D115" t="s">
-        <v>76</v>
-      </c>
-      <c r="E115" t="s">
-        <v>76</v>
-      </c>
-      <c r="F115" t="s">
-        <v>156</v>
-      </c>
-      <c r="G115" t="s">
+      <c r="L115" t="s">
+        <v>26</v>
+      </c>
+      <c r="M115" t="s">
+        <v>26</v>
+      </c>
+      <c r="N115" t="s">
+        <v>26</v>
+      </c>
+      <c r="O115" t="s">
         <v>444</v>
-      </c>
-      <c r="H115" t="s">
-        <v>22</v>
-      </c>
-      <c r="I115" t="s">
-        <v>23</v>
-      </c>
-      <c r="J115" t="s">
-        <v>445</v>
-      </c>
-      <c r="K115" t="s">
-        <v>446</v>
-      </c>
-      <c r="L115" t="s">
-        <v>26</v>
-      </c>
-      <c r="M115" t="s">
-        <v>26</v>
-      </c>
-      <c r="N115" t="s">
-        <v>447</v>
-      </c>
-      <c r="O115" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B116" t="s">
-        <v>34</v>
+        <v>294</v>
       </c>
       <c r="C116" t="s">
-        <v>35</v>
+        <v>295</v>
       </c>
       <c r="D116" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E116" t="s">
         <v>19</v>
@@ -7316,16 +7277,16 @@
         <v>21</v>
       </c>
       <c r="H116" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I116" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J116" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="K116" t="s">
-        <v>25</v>
+        <v>258</v>
       </c>
       <c r="L116" t="s">
         <v>26</v>
@@ -7337,21 +7298,21 @@
         <v>26</v>
       </c>
       <c r="O116" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B117" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="C117" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="E117" t="s">
         <v>19</v>
@@ -7360,19 +7321,19 @@
         <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H117" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I117" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J117" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="K117" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="L117" t="s">
         <v>26</v>
@@ -7384,209 +7345,209 @@
         <v>26</v>
       </c>
       <c r="O117" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>451</v>
+      </c>
+      <c r="B118" t="s">
+        <v>103</v>
+      </c>
+      <c r="C118" t="s">
+        <v>104</v>
+      </c>
+      <c r="D118" t="s">
+        <v>43</v>
+      </c>
+      <c r="E118" t="s">
+        <v>19</v>
+      </c>
+      <c r="F118" t="s">
+        <v>193</v>
+      </c>
+      <c r="G118" t="s">
+        <v>452</v>
+      </c>
+      <c r="H118" t="s">
+        <v>54</v>
+      </c>
+      <c r="I118" t="s">
+        <v>31</v>
+      </c>
+      <c r="J118" t="s">
+        <v>453</v>
+      </c>
+      <c r="K118" t="s">
+        <v>415</v>
+      </c>
+      <c r="L118" t="s">
+        <v>26</v>
+      </c>
+      <c r="M118" t="s">
+        <v>26</v>
+      </c>
+      <c r="N118" t="s">
         <v>454</v>
       </c>
-      <c r="B118" t="s">
-        <v>46</v>
-      </c>
-      <c r="C118" t="s">
-        <v>47</v>
-      </c>
-      <c r="D118" t="s">
-        <v>19</v>
-      </c>
-      <c r="E118" t="s">
-        <v>19</v>
-      </c>
-      <c r="F118" t="s">
-        <v>20</v>
-      </c>
-      <c r="G118" t="s">
-        <v>61</v>
-      </c>
-      <c r="H118" t="s">
-        <v>22</v>
-      </c>
-      <c r="I118" t="s">
-        <v>23</v>
-      </c>
-      <c r="J118" t="s">
+      <c r="O118" t="s">
         <v>455</v>
-      </c>
-      <c r="K118" t="s">
-        <v>102</v>
-      </c>
-      <c r="L118" t="s">
-        <v>26</v>
-      </c>
-      <c r="M118" t="s">
-        <v>26</v>
-      </c>
-      <c r="N118" t="s">
-        <v>26</v>
-      </c>
-      <c r="O118" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>456</v>
+      </c>
+      <c r="B119" t="s">
+        <v>132</v>
+      </c>
+      <c r="C119" t="s">
+        <v>133</v>
+      </c>
+      <c r="D119" t="s">
+        <v>43</v>
+      </c>
+      <c r="E119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119" t="s">
+        <v>20</v>
+      </c>
+      <c r="G119" t="s">
+        <v>36</v>
+      </c>
+      <c r="H119" t="s">
+        <v>54</v>
+      </c>
+      <c r="I119" t="s">
+        <v>31</v>
+      </c>
+      <c r="J119" t="s">
         <v>457</v>
       </c>
-      <c r="B119" t="s">
-        <v>87</v>
-      </c>
-      <c r="C119" t="s">
-        <v>88</v>
-      </c>
-      <c r="D119" t="s">
-        <v>19</v>
-      </c>
-      <c r="E119" t="s">
-        <v>19</v>
-      </c>
-      <c r="F119" t="s">
-        <v>20</v>
-      </c>
-      <c r="G119" t="s">
-        <v>21</v>
-      </c>
-      <c r="H119" t="s">
-        <v>22</v>
-      </c>
-      <c r="I119" t="s">
-        <v>23</v>
-      </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
+        <v>33</v>
+      </c>
+      <c r="L119" t="s">
+        <v>26</v>
+      </c>
+      <c r="M119" t="s">
+        <v>26</v>
+      </c>
+      <c r="N119" t="s">
+        <v>26</v>
+      </c>
+      <c r="O119" t="s">
         <v>458</v>
-      </c>
-      <c r="K119" t="s">
-        <v>25</v>
-      </c>
-      <c r="L119" t="s">
-        <v>26</v>
-      </c>
-      <c r="M119" t="s">
-        <v>26</v>
-      </c>
-      <c r="N119" t="s">
-        <v>26</v>
-      </c>
-      <c r="O119" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>459</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" t="s">
+        <v>18</v>
+      </c>
+      <c r="E120" t="s">
+        <v>19</v>
+      </c>
+      <c r="F120" t="s">
+        <v>20</v>
+      </c>
+      <c r="G120" t="s">
+        <v>105</v>
+      </c>
+      <c r="H120" t="s">
+        <v>54</v>
+      </c>
+      <c r="I120" t="s">
+        <v>31</v>
+      </c>
+      <c r="J120" t="s">
         <v>460</v>
       </c>
-      <c r="B120" t="s">
-        <v>34</v>
-      </c>
-      <c r="C120" t="s">
-        <v>35</v>
-      </c>
-      <c r="D120" t="s">
-        <v>36</v>
-      </c>
-      <c r="E120" t="s">
-        <v>19</v>
-      </c>
-      <c r="F120" t="s">
-        <v>20</v>
-      </c>
-      <c r="G120" t="s">
-        <v>48</v>
-      </c>
-      <c r="H120" t="s">
-        <v>22</v>
-      </c>
-      <c r="I120" t="s">
-        <v>23</v>
-      </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
+        <v>247</v>
+      </c>
+      <c r="L120" t="s">
+        <v>26</v>
+      </c>
+      <c r="M120" t="s">
+        <v>26</v>
+      </c>
+      <c r="N120" t="s">
+        <v>26</v>
+      </c>
+      <c r="O120" t="s">
         <v>461</v>
-      </c>
-      <c r="K120" t="s">
-        <v>462</v>
-      </c>
-      <c r="L120" t="s">
-        <v>26</v>
-      </c>
-      <c r="M120" t="s">
-        <v>26</v>
-      </c>
-      <c r="N120" t="s">
-        <v>26</v>
-      </c>
-      <c r="O120" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>462</v>
+      </c>
+      <c r="B121" t="s">
+        <v>353</v>
+      </c>
+      <c r="C121" t="s">
+        <v>119</v>
+      </c>
+      <c r="D121" t="s">
+        <v>120</v>
+      </c>
+      <c r="E121" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" t="s">
+        <v>20</v>
+      </c>
+      <c r="G121" t="s">
+        <v>21</v>
+      </c>
+      <c r="H121" t="s">
+        <v>54</v>
+      </c>
+      <c r="I121" t="s">
+        <v>31</v>
+      </c>
+      <c r="J121" t="s">
+        <v>463</v>
+      </c>
+      <c r="K121" t="s">
+        <v>33</v>
+      </c>
+      <c r="L121" t="s">
+        <v>26</v>
+      </c>
+      <c r="M121" t="s">
+        <v>26</v>
+      </c>
+      <c r="N121" t="s">
+        <v>26</v>
+      </c>
+      <c r="O121" t="s">
         <v>464</v>
-      </c>
-      <c r="B121" t="s">
-        <v>465</v>
-      </c>
-      <c r="C121" t="s">
-        <v>466</v>
-      </c>
-      <c r="D121" t="s">
-        <v>18</v>
-      </c>
-      <c r="E121" t="s">
-        <v>19</v>
-      </c>
-      <c r="F121" t="s">
-        <v>20</v>
-      </c>
-      <c r="G121" t="s">
-        <v>215</v>
-      </c>
-      <c r="H121" t="s">
-        <v>22</v>
-      </c>
-      <c r="I121" t="s">
-        <v>23</v>
-      </c>
-      <c r="J121" t="s">
-        <v>467</v>
-      </c>
-      <c r="K121" t="s">
-        <v>223</v>
-      </c>
-      <c r="L121" t="s">
-        <v>26</v>
-      </c>
-      <c r="M121" t="s">
-        <v>26</v>
-      </c>
-      <c r="N121" t="s">
-        <v>26</v>
-      </c>
-      <c r="O121" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B122" t="s">
-        <v>59</v>
+        <v>294</v>
       </c>
       <c r="C122" t="s">
-        <v>60</v>
+        <v>295</v>
       </c>
       <c r="D122" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E122" t="s">
         <v>19</v>
@@ -7595,19 +7556,19 @@
         <v>20</v>
       </c>
       <c r="G122" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H122" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I122" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J122" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K122" t="s">
-        <v>223</v>
+        <v>68</v>
       </c>
       <c r="L122" t="s">
         <v>26</v>
@@ -7619,136 +7580,136 @@
         <v>26</v>
       </c>
       <c r="O122" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>467</v>
+      </c>
+      <c r="B123" t="s">
+        <v>468</v>
+      </c>
+      <c r="C123" t="s">
+        <v>469</v>
+      </c>
+      <c r="D123" t="s">
+        <v>19</v>
+      </c>
+      <c r="E123" t="s">
+        <v>26</v>
+      </c>
+      <c r="F123" t="s">
+        <v>20</v>
+      </c>
+      <c r="G123" t="s">
+        <v>317</v>
+      </c>
+      <c r="H123" t="s">
+        <v>54</v>
+      </c>
+      <c r="I123" t="s">
+        <v>31</v>
+      </c>
+      <c r="J123" t="s">
+        <v>470</v>
+      </c>
+      <c r="K123" t="s">
+        <v>110</v>
+      </c>
+      <c r="L123" t="s">
+        <v>26</v>
+      </c>
+      <c r="M123" t="s">
+        <v>26</v>
+      </c>
+      <c r="N123" t="s">
+        <v>26</v>
+      </c>
+      <c r="O123" t="s">
         <v>471</v>
-      </c>
-      <c r="B123" t="s">
-        <v>93</v>
-      </c>
-      <c r="C123" t="s">
-        <v>94</v>
-      </c>
-      <c r="D123" t="s">
-        <v>18</v>
-      </c>
-      <c r="E123" t="s">
-        <v>19</v>
-      </c>
-      <c r="F123" t="s">
-        <v>20</v>
-      </c>
-      <c r="G123" t="s">
-        <v>21</v>
-      </c>
-      <c r="H123" t="s">
-        <v>22</v>
-      </c>
-      <c r="I123" t="s">
-        <v>23</v>
-      </c>
-      <c r="J123" t="s">
-        <v>472</v>
-      </c>
-      <c r="K123" t="s">
-        <v>149</v>
-      </c>
-      <c r="L123" t="s">
-        <v>26</v>
-      </c>
-      <c r="M123" t="s">
-        <v>26</v>
-      </c>
-      <c r="N123" t="s">
-        <v>26</v>
-      </c>
-      <c r="O123" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>472</v>
+      </c>
+      <c r="B124" t="s">
+        <v>41</v>
+      </c>
+      <c r="C124" t="s">
+        <v>42</v>
+      </c>
+      <c r="D124" t="s">
+        <v>43</v>
+      </c>
+      <c r="E124" t="s">
+        <v>26</v>
+      </c>
+      <c r="F124" t="s">
+        <v>20</v>
+      </c>
+      <c r="G124" t="s">
+        <v>21</v>
+      </c>
+      <c r="H124" t="s">
+        <v>54</v>
+      </c>
+      <c r="I124" t="s">
+        <v>31</v>
+      </c>
+      <c r="J124" t="s">
+        <v>473</v>
+      </c>
+      <c r="K124" t="s">
+        <v>49</v>
+      </c>
+      <c r="L124" t="s">
+        <v>26</v>
+      </c>
+      <c r="M124" t="s">
+        <v>26</v>
+      </c>
+      <c r="N124" t="s">
+        <v>26</v>
+      </c>
+      <c r="O124" t="s">
         <v>474</v>
-      </c>
-      <c r="B124" t="s">
-        <v>34</v>
-      </c>
-      <c r="C124" t="s">
-        <v>35</v>
-      </c>
-      <c r="D124" t="s">
-        <v>36</v>
-      </c>
-      <c r="E124" t="s">
-        <v>19</v>
-      </c>
-      <c r="F124" t="s">
-        <v>20</v>
-      </c>
-      <c r="G124" t="s">
-        <v>61</v>
-      </c>
-      <c r="H124" t="s">
-        <v>22</v>
-      </c>
-      <c r="I124" t="s">
-        <v>23</v>
-      </c>
-      <c r="J124" t="s">
-        <v>294</v>
-      </c>
-      <c r="K124" t="s">
-        <v>181</v>
-      </c>
-      <c r="L124" t="s">
-        <v>26</v>
-      </c>
-      <c r="M124" t="s">
-        <v>26</v>
-      </c>
-      <c r="N124" t="s">
-        <v>26</v>
-      </c>
-      <c r="O124" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>475</v>
+      </c>
+      <c r="B125" t="s">
         <v>476</v>
       </c>
-      <c r="B125" t="s">
-        <v>81</v>
-      </c>
       <c r="C125" t="s">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="D125" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="E125" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="F125" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="G125" t="s">
-        <v>21</v>
+        <v>477</v>
       </c>
       <c r="H125" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I125" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J125" t="s">
-        <v>430</v>
+        <v>478</v>
       </c>
       <c r="K125" t="s">
-        <v>102</v>
+        <v>479</v>
       </c>
       <c r="L125" t="s">
         <v>26</v>
@@ -7757,24 +7718,24 @@
         <v>26</v>
       </c>
       <c r="N125" t="s">
-        <v>26</v>
+        <v>480</v>
       </c>
       <c r="O125" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B126" t="s">
-        <v>320</v>
+        <v>16</v>
       </c>
       <c r="C126" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="D126" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
@@ -7783,19 +7744,19 @@
         <v>20</v>
       </c>
       <c r="G126" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="H126" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I126" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J126" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="K126" t="s">
-        <v>291</v>
+        <v>79</v>
       </c>
       <c r="L126" t="s">
         <v>26</v>
@@ -7807,242 +7768,7 @@
         <v>26</v>
       </c>
       <c r="O126" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>481</v>
-      </c>
-      <c r="B127" t="s">
-        <v>87</v>
-      </c>
-      <c r="C127" t="s">
-        <v>88</v>
-      </c>
-      <c r="D127" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127" t="s">
-        <v>19</v>
-      </c>
-      <c r="F127" t="s">
-        <v>482</v>
-      </c>
-      <c r="G127" t="s">
-        <v>21</v>
-      </c>
-      <c r="H127" t="s">
-        <v>22</v>
-      </c>
-      <c r="I127" t="s">
-        <v>23</v>
-      </c>
-      <c r="J127" t="s">
-        <v>483</v>
-      </c>
-      <c r="K127" t="s">
         <v>484</v>
-      </c>
-      <c r="L127" t="s">
-        <v>26</v>
-      </c>
-      <c r="M127" t="s">
-        <v>26</v>
-      </c>
-      <c r="N127" t="s">
-        <v>26</v>
-      </c>
-      <c r="O127" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>486</v>
-      </c>
-      <c r="B128" t="s">
-        <v>34</v>
-      </c>
-      <c r="C128" t="s">
-        <v>35</v>
-      </c>
-      <c r="D128" t="s">
-        <v>36</v>
-      </c>
-      <c r="E128" t="s">
-        <v>19</v>
-      </c>
-      <c r="F128" t="s">
-        <v>20</v>
-      </c>
-      <c r="G128" t="s">
-        <v>48</v>
-      </c>
-      <c r="H128" t="s">
-        <v>22</v>
-      </c>
-      <c r="I128" t="s">
-        <v>23</v>
-      </c>
-      <c r="J128" t="s">
-        <v>487</v>
-      </c>
-      <c r="K128" t="s">
-        <v>265</v>
-      </c>
-      <c r="L128" t="s">
-        <v>26</v>
-      </c>
-      <c r="M128" t="s">
-        <v>26</v>
-      </c>
-      <c r="N128" t="s">
-        <v>26</v>
-      </c>
-      <c r="O128" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>489</v>
-      </c>
-      <c r="B129" t="s">
-        <v>59</v>
-      </c>
-      <c r="C129" t="s">
-        <v>60</v>
-      </c>
-      <c r="D129" t="s">
-        <v>18</v>
-      </c>
-      <c r="E129" t="s">
-        <v>19</v>
-      </c>
-      <c r="F129" t="s">
-        <v>20</v>
-      </c>
-      <c r="G129" t="s">
-        <v>286</v>
-      </c>
-      <c r="H129" t="s">
-        <v>22</v>
-      </c>
-      <c r="I129" t="s">
-        <v>23</v>
-      </c>
-      <c r="J129" t="s">
-        <v>490</v>
-      </c>
-      <c r="K129" t="s">
-        <v>78</v>
-      </c>
-      <c r="L129" t="s">
-        <v>26</v>
-      </c>
-      <c r="M129" t="s">
-        <v>26</v>
-      </c>
-      <c r="N129" t="s">
-        <v>26</v>
-      </c>
-      <c r="O129" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>492</v>
-      </c>
-      <c r="B130" t="s">
-        <v>34</v>
-      </c>
-      <c r="C130" t="s">
-        <v>35</v>
-      </c>
-      <c r="D130" t="s">
-        <v>36</v>
-      </c>
-      <c r="E130" t="s">
-        <v>19</v>
-      </c>
-      <c r="F130" t="s">
-        <v>20</v>
-      </c>
-      <c r="G130" t="s">
-        <v>48</v>
-      </c>
-      <c r="H130" t="s">
-        <v>22</v>
-      </c>
-      <c r="I130" t="s">
-        <v>23</v>
-      </c>
-      <c r="J130" t="s">
-        <v>493</v>
-      </c>
-      <c r="K130" t="s">
-        <v>109</v>
-      </c>
-      <c r="L130" t="s">
-        <v>26</v>
-      </c>
-      <c r="M130" t="s">
-        <v>26</v>
-      </c>
-      <c r="N130" t="s">
-        <v>26</v>
-      </c>
-      <c r="O130" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>495</v>
-      </c>
-      <c r="B131" t="s">
-        <v>81</v>
-      </c>
-      <c r="C131" t="s">
-        <v>82</v>
-      </c>
-      <c r="D131" t="s">
-        <v>83</v>
-      </c>
-      <c r="E131" t="s">
-        <v>19</v>
-      </c>
-      <c r="F131" t="s">
-        <v>20</v>
-      </c>
-      <c r="G131" t="s">
-        <v>21</v>
-      </c>
-      <c r="H131" t="s">
-        <v>22</v>
-      </c>
-      <c r="I131" t="s">
-        <v>23</v>
-      </c>
-      <c r="J131" t="s">
-        <v>496</v>
-      </c>
-      <c r="K131" t="s">
-        <v>66</v>
-      </c>
-      <c r="L131" t="s">
-        <v>26</v>
-      </c>
-      <c r="M131" t="s">
-        <v>26</v>
-      </c>
-      <c r="N131" t="s">
-        <v>26</v>
-      </c>
-      <c r="O131" t="s">
-        <v>497</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4BBA11F-F5B9-4E5B-9101-F4E524FD4A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB812E8-4C63-458C-B500-64456F0360D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="498">
   <si>
     <t>Time</t>
   </si>
@@ -62,72 +62,321 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/25/2026 11:22:39 PM</t>
+  </si>
+  <si>
+    <t>23470</t>
+  </si>
+  <si>
+    <t>JELTOV, VLADIMIR K.</t>
+  </si>
+  <si>
+    <t>OTR, Safety Pro Test</t>
+  </si>
+  <si>
+    <t>OTR</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Congested, Night</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanya Smith </t>
+  </si>
+  <si>
+    <t>Barstow and Mojave Freeway, Hesperia, CA, 92344</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445022a-627d-5d91-bc76-f4fb85e1b796</t>
+  </si>
+  <si>
+    <t>06/25/2026 1:38:37 PM</t>
+  </si>
+  <si>
+    <t>24632</t>
+  </si>
+  <si>
+    <t>EMERY.SHANE</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>I 70, 13.5 mi SE Vail, Summit County, CO</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450013-ad6a-5d83-a658-ae2aa66529ba</t>
+  </si>
+  <si>
+    <t>06/25/2026 11:29:51 AM</t>
+  </si>
+  <si>
+    <t>22975</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, Dacono, CO, 80514</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff9d-cbdd-5880-a2e5-2df47c0ccd42</t>
+  </si>
+  <si>
+    <t>06/24/2026 5:10:48 PM</t>
+  </si>
+  <si>
+    <t>Veterans Memorial Highway, Washington, UT, 84780</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbaf-956b-5521-86c8-e1ad024b6b32</t>
+  </si>
+  <si>
+    <t>06/24/2026 4:03:42 PM</t>
+  </si>
+  <si>
+    <t>24907</t>
+  </si>
+  <si>
+    <t>WELCH, GREGORY</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Kansas Turnpike, 2.9 mi NW Bonner Springs, Leavenworth County, KS</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fb72-2783-52f2-abb8-751588740a55</t>
+  </si>
+  <si>
+    <t>06/24/2026 5:11:55 AM</t>
+  </si>
+  <si>
+    <t>22024</t>
+  </si>
+  <si>
+    <t>KENNEDY LINNETTE</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, Commerce City, CO, 80266</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f91d-6d8c-56fe-ae71-2bda4a20d15b</t>
+  </si>
+  <si>
+    <t>06/23/2026 5:11:29 PM</t>
+  </si>
+  <si>
+    <t>24630</t>
+  </si>
+  <si>
+    <t>MAGEE LONDON, TRESSEL</t>
+  </si>
+  <si>
+    <t>Air Temperature, OTR</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>US 287;US 385;CR 26, 53.0 mi S Lamar, Baca County, CO</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f689-d886-5060-a059-d716ac401798</t>
+  </si>
+  <si>
+    <t>06/22/2026 4:29:35 PM</t>
+  </si>
+  <si>
+    <t>22970</t>
+  </si>
+  <si>
+    <t>MEYERS, DAVID</t>
+  </si>
+  <si>
+    <t>Air Temperature, Local</t>
+  </si>
+  <si>
+    <t>Construction, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 70, Lakewood, CO, 80410</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f13d-20f8-5ec3-8c9c-422c511a22a2</t>
+  </si>
+  <si>
+    <t>06/22/2026 1:33:02 PM</t>
+  </si>
+  <si>
+    <t>24685</t>
+  </si>
+  <si>
+    <t>CLARK, KC</t>
+  </si>
+  <si>
+    <t>Ronald Reagan Memorial Tollway, Malta Township, IL, 60113</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f09b-7c59-5088-b251-90ee7e4b87f2</t>
+  </si>
+  <si>
+    <t>06/22/2026 12:51:06 PM</t>
+  </si>
+  <si>
+    <t>24677</t>
+  </si>
+  <si>
+    <t>WALLACE, ANDREW</t>
+  </si>
+  <si>
+    <t>Kansas Turnpike, 10.7 mi S Wellington, Sumner County, KS</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f075-1a4c-515b-a225-207386df00d7</t>
+  </si>
+  <si>
+    <t>06/21/2026 2:38:22 PM</t>
+  </si>
+  <si>
+    <t>I 80, Gretna, NE</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ebb0-f15e-5d59-b9a9-f35c7dd40f0e</t>
+  </si>
+  <si>
+    <t>06/21/2026 1:24:01 PM</t>
+  </si>
+  <si>
+    <t>I 80, Knox, NE</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445eb6c-e148-53dd-8c1e-72d7d77a9ed7</t>
+  </si>
+  <si>
+    <t>06/20/2026 12:26:55 PM</t>
+  </si>
+  <si>
+    <t>23467</t>
+  </si>
+  <si>
+    <t>KREUTZER, DON</t>
+  </si>
+  <si>
+    <t>I 35W, Alvarado, TX, 76007</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e612-3bdb-5540-a91a-7a681ddd407e</t>
+  </si>
+  <si>
+    <t>06/19/2026 6:06:53 PM</t>
+  </si>
+  <si>
+    <t>World War I Veterans Memorial Highway, Ardmore, OK, 73401</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e223-1f6b-51c2-9f70-aa656bc9b47b</t>
+  </si>
+  <si>
+    <t>06/19/2026 5:32:27 PM</t>
+  </si>
+  <si>
+    <t>24690</t>
+  </si>
+  <si>
+    <t>MOORE, ROYCE</t>
+  </si>
+  <si>
+    <t>Wet Road, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 80, Hartford Township, IA</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e203-9a5a-5c9b-90ec-204789b29201</t>
+  </si>
+  <si>
+    <t>06/19/2026 10:12:30 AM</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, Erie, CO, 80514</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e070-d0ae-5996-bafd-079887fbd3c9</t>
+  </si>
+  <si>
     <t>06/18/2026 12:45:10 PM</t>
   </si>
   <si>
-    <t>23470</t>
-  </si>
-  <si>
-    <t>JELTOV, VLADIMIR K.</t>
-  </si>
-  <si>
-    <t>OTR, Safety Pro Test</t>
-  </si>
-  <si>
-    <t>OTR</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanya Smith </t>
-  </si>
-  <si>
     <t>Dwight D. Eisenhower Highway, 44.6 mi E The Pinery, Elbert County, CO</t>
   </si>
   <si>
     <t>76</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dbd6-3af7-524c-87f3-6e56bdb0f8b4</t>
   </si>
   <si>
     <t>06/18/2026 11:35:17 AM</t>
   </si>
   <si>
-    <t>24632</t>
-  </si>
-  <si>
-    <t>EMERY.SHANE</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
     <t>KS 156, 30.5 mi NE Great Bend, Ellsworth County, KS</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445db96-3efe-5994-964b-1a1194aab183</t>
   </si>
   <si>
     <t>06/17/2026 3:18:01 PM</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>I 40, Los Pinos, NM</t>
   </si>
   <si>
@@ -140,21 +389,9 @@
     <t>06/17/2026 1:24:24 PM</t>
   </si>
   <si>
-    <t>24630</t>
-  </si>
-  <si>
-    <t>MAGEE LONDON, TRESSEL</t>
-  </si>
-  <si>
-    <t>Air Temperature, OTR</t>
-  </si>
-  <si>
     <t>Purple Heart Trail, 20.7 mi ENE Holbrook, Apache County, AZ</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d6d3-c962-50ff-9b41-3d746ff61c92</t>
   </si>
   <si>
@@ -164,9 +401,6 @@
     <t>North Collins Freeway, Howe, TX, 75459</t>
   </si>
   <si>
-    <t>68</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d610-7f77-5f72-81b1-c4694de011c7</t>
   </si>
   <si>
@@ -179,9 +413,6 @@
     <t>WADE,ADAM</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>Gerald R. Ford Memorial Highway, Dotsero, CO</t>
   </si>
   <si>
@@ -197,9 +428,6 @@
     <t>23473</t>
   </si>
   <si>
-    <t>WELCH, GREGORY</t>
-  </si>
-  <si>
     <t>I 80, 7.1 mi SW Seward, Seward County, NE, 68364</t>
   </si>
   <si>
@@ -209,21 +437,9 @@
     <t>06/12/2026 6:47:19 PM</t>
   </si>
   <si>
-    <t>22970</t>
-  </si>
-  <si>
-    <t>MEYERS, DAVID</t>
-  </si>
-  <si>
-    <t>Air Temperature, Local</t>
-  </si>
-  <si>
     <t>I 70, Wheat Ridge, CO, 80033</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445be3b-9f80-5fd9-a6cf-dbf18fac6d9d</t>
   </si>
   <si>
@@ -290,9 +506,6 @@
     <t>Construction, Congested</t>
   </si>
   <si>
-    <t>Barstow and Mojave Freeway, Hesperia, CA, 92344</t>
-  </si>
-  <si>
     <t>59</t>
   </si>
   <si>
@@ -332,9 +545,6 @@
     <t>GERVACIO, ARNOLD</t>
   </si>
   <si>
-    <t>Construction, Moderate Traffic</t>
-  </si>
-  <si>
     <t>Dwight D. Eisenhower Highway, Green River, WY, 82935</t>
   </si>
   <si>
@@ -347,9 +557,6 @@
     <t>Barstow and Mojave Freeway, 11.2 mi SW Barstow Heights, San Bernardino County, CA</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ae74-984f-5ea2-b3cb-4dcbc89dece1</t>
   </si>
   <si>
@@ -371,21 +578,12 @@
     <t>06/09/2026 6:09:33 AM</t>
   </si>
   <si>
-    <t>22975</t>
-  </si>
-  <si>
     <t>ROBERT REVELES</t>
   </si>
   <si>
-    <t>Local</t>
-  </si>
-  <si>
     <t>Tuskegee Airmen Memorial Highway, Aurora, CO, 80249</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ac12-c9e2-538b-b316-68bf086b39de</t>
   </si>
   <si>
@@ -404,9 +602,6 @@
     <t>I 40, McCartys, NM</t>
   </si>
   <si>
-    <t>66</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a705-5620-5e1a-94db-d10e3064fa7f</t>
   </si>
   <si>
@@ -437,9 +632,6 @@
     <t>06/03/2026 5:14:46 PM</t>
   </si>
   <si>
-    <t>I 70, Lakewood, CO, 80410</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f8d-abd6-5146-8bb1-64bec70d67ff</t>
   </si>
   <si>
@@ -494,12 +686,6 @@
     <t>06/01/2026 8:29:16 AM</t>
   </si>
   <si>
-    <t>24677</t>
-  </si>
-  <si>
-    <t>WALLACE, ANDREW</t>
-  </si>
-  <si>
     <t>Truman/Eisenhower Presidential Highway, 12.3 mi SE Manhattan, Riley County, KS</t>
   </si>
   <si>
@@ -566,9 +752,6 @@
     <t>TREVIZO, ESTABAN I.</t>
   </si>
   <si>
-    <t>Dwight D. Eisenhower Highway, Commerce City, CO, 80266</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b60-14f9-5a48-9d21-698da447b93c</t>
   </si>
   <si>
@@ -578,9 +761,6 @@
     <t>Las Vegas Freeway, North Las Vegas, NV, 89165</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a31-a5a8-5e7e-b93a-9a5ca0fa096a</t>
   </si>
   <si>
@@ -758,9 +938,6 @@
     <t>I 25, Lone Tree, CO, 80124-5644</t>
   </si>
   <si>
-    <t>53</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452d3f-b507-5257-8f90-7e0209dca3e8</t>
   </si>
   <si>
@@ -791,9 +968,6 @@
     <t>I 40, Vegas Junction, NM, 87070</t>
   </si>
   <si>
-    <t>67</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445234b-a412-5bb6-a4f4-fbe4e6a7330d</t>
   </si>
   <si>
@@ -899,12 +1073,6 @@
     <t>05/01/2026 3:30:32 PM</t>
   </si>
   <si>
-    <t>24685</t>
-  </si>
-  <si>
-    <t>CLARK, KC</t>
-  </si>
-  <si>
     <t>I 76;US 6, Brighton, CO, 80603</t>
   </si>
   <si>
@@ -968,9 +1136,6 @@
     <t>04/29/2026 6:20:37 AM</t>
   </si>
   <si>
-    <t>Light Traffic, Night</t>
-  </si>
-  <si>
     <t>Purple Heart Trail, 32.6 mi NNW Paulden, Yavapai County, AZ</t>
   </si>
   <si>
@@ -1328,9 +1493,6 @@
     <t>03/31/2026 4:36:02 PM</t>
   </si>
   <si>
-    <t>Veterans Memorial Highway, Washington, UT, 84780</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544545d3-332d-5368-acbf-6beb79fd8923</t>
   </si>
   <si>
@@ -1346,130 +1508,7 @@
     <t>Gerald R. Ford Memorial Highway, Avon, CO, 81620</t>
   </si>
   <si>
-    <t>75</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445400b-b984-5d9d-b2ad-a3a3ef2eecdc</t>
-  </si>
-  <si>
-    <t>03/28/2026 3:20:55 PM</t>
-  </si>
-  <si>
-    <t>Las Vegas Freeway, Mesquite, NV, 89024</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445361b-58d7-510c-83f5-f5ab184278b4</t>
-  </si>
-  <si>
-    <t>03/27/2026 7:29:13 PM</t>
-  </si>
-  <si>
-    <t>498 Edwards Access Road, Edwards, CO, 81632</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544531d8-4fea-5926-ad2c-a2b9b9368c70</t>
-  </si>
-  <si>
-    <t>03/27/2026 6:38:42 PM</t>
-  </si>
-  <si>
-    <t>Pedestrians, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>Etiwanda Avenue, Jurupa Valley, CA</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544531aa-1337-5f4f-b001-640c1979d3e6</t>
-  </si>
-  <si>
-    <t>03/27/2026 9:14:50 AM</t>
-  </si>
-  <si>
-    <t>I 70;US 6, 11.3 mi NE Clifton, Mesa County, CO</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452fa5-d696-53f6-90ad-32f8d17afd3e</t>
-  </si>
-  <si>
-    <t>03/26/2026 4:44:27 PM</t>
-  </si>
-  <si>
-    <t>Barstow Freeway, San Bernardino, CA, 92405</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c1b-1b9a-509f-92a4-5fc598652a52</t>
-  </si>
-  <si>
-    <t>03/25/2026 2:38:40 PM</t>
-  </si>
-  <si>
-    <t>I 270, Commerce City, CO, 80266</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452681-9861-5659-8e8c-349c3a1d9fb7</t>
-  </si>
-  <si>
-    <t>03/25/2026 2:10:49 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452668-1902-5191-8c0d-346d000904a0</t>
-  </si>
-  <si>
-    <t>03/24/2026 9:53:50 PM</t>
-  </si>
-  <si>
-    <t>22025</t>
-  </si>
-  <si>
-    <t>KAM KIM</t>
-  </si>
-  <si>
-    <t>I 40, Grants, NM, 87020</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544522e9-a277-587c-8c52-114416d99251</t>
-  </si>
-  <si>
-    <t>03/24/2026 5:09:20 PM</t>
-  </si>
-  <si>
-    <t>Barstow and Mojave Freeway (Heavy Traffic Route), Barstow, CA, 92347</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544521e5-2d8d-5c65-9c3e-d391a5c18002</t>
-  </si>
-  <si>
-    <t>03/24/2026 2:17:11 PM</t>
-  </si>
-  <si>
-    <t>2113</t>
-  </si>
-  <si>
-    <t>Pedestrians, Light Traffic</t>
-  </si>
-  <si>
-    <t>Northfield Boulevard, Denver, CO, 80238</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452147-925b-50a6-a890-65880ea5d677</t>
-  </si>
-  <si>
-    <t>03/23/2026 2:26:51 PM</t>
-  </si>
-  <si>
-    <t>Mojave Freeway, 20.5 mi S Fort Irwin, San Bernardino County, CA</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c2a-0dbb-5556-8bd1-1742efd68c0e</t>
   </si>
 </sst>
 </file>
@@ -1846,7 +1885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1963,19 +2002,19 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -1987,21 +2026,21 @@
         <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -2010,19 +2049,19 @@
         <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -2034,68 +2073,68 @@
         <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" t="s">
         <v>44</v>
-      </c>
-      <c r="K5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
         <v>47</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -2104,19 +2143,19 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -2128,21 +2167,21 @@
         <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -2151,19 +2190,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -2175,42 +2214,42 @@
         <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="L8" t="s">
         <v>26</v>
@@ -2222,21 +2261,21 @@
         <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -2245,19 +2284,19 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="H9" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -2269,18 +2308,18 @@
         <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
@@ -2292,19 +2331,19 @@
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -2316,42 +2355,42 @@
         <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
         <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L11" t="s">
         <v>26</v>
@@ -2363,21 +2402,21 @@
         <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
         <v>77</v>
       </c>
-      <c r="B12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" t="s">
-        <v>53</v>
-      </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -2386,16 +2425,16 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H12" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s">
         <v>79</v>
@@ -2410,21 +2449,21 @@
         <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -2433,19 +2472,19 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="L13" t="s">
         <v>26</v>
@@ -2457,21 +2496,21 @@
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -2480,19 +2519,19 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="L14" t="s">
         <v>26</v>
@@ -2504,42 +2543,42 @@
         <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K15" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
@@ -2551,18 +2590,18 @@
         <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
@@ -2574,19 +2613,19 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="H16" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="K16" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
@@ -2598,42 +2637,42 @@
         <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H17" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K17" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L17" t="s">
         <v>26</v>
@@ -2645,21 +2684,21 @@
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -2668,19 +2707,19 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="H18" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="K18" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="L18" t="s">
         <v>26</v>
@@ -2692,21 +2731,21 @@
         <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -2715,19 +2754,19 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H19" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K19" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="L19" t="s">
         <v>26</v>
@@ -2739,42 +2778,42 @@
         <v>26</v>
       </c>
       <c r="O19" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
         <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H20" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K20" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
@@ -2786,42 +2825,42 @@
         <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K21" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
@@ -2833,21 +2872,21 @@
         <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -2856,19 +2895,19 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H22" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J22" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K22" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
@@ -2880,21 +2919,21 @@
         <v>26</v>
       </c>
       <c r="O22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -2903,19 +2942,19 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K23" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -2927,21 +2966,21 @@
         <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -2950,19 +2989,19 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H24" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K24" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -2974,21 +3013,21 @@
         <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
@@ -2997,19 +3036,19 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K25" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -3021,21 +3060,21 @@
         <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
@@ -3044,19 +3083,19 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H26" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
@@ -3068,21 +3107,21 @@
         <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -3091,19 +3130,19 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H27" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K27" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
@@ -3115,21 +3154,21 @@
         <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -3138,19 +3177,19 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J28" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K28" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L28" t="s">
         <v>26</v>
@@ -3162,21 +3201,21 @@
         <v>26</v>
       </c>
       <c r="O28" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
@@ -3185,19 +3224,19 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J29" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="K29" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="L29" t="s">
         <v>26</v>
@@ -3209,21 +3248,21 @@
         <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -3232,19 +3271,19 @@
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H30" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="K30" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="L30" t="s">
         <v>26</v>
@@ -3256,12 +3295,12 @@
         <v>26</v>
       </c>
       <c r="O30" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B31" t="s">
         <v>16</v>
@@ -3279,19 +3318,19 @@
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="H31" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>156</v>
+        <v>24</v>
       </c>
       <c r="K31" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="L31" t="s">
         <v>26</v>
@@ -3303,42 +3342,42 @@
         <v>26</v>
       </c>
       <c r="O31" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>160</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H32" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J32" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="K32" t="s">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="L32" t="s">
         <v>26</v>
@@ -3350,21 +3389,21 @@
         <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C33" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
@@ -3373,19 +3412,19 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H33" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="K33" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
@@ -3397,21 +3436,21 @@
         <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -3420,19 +3459,19 @@
         <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="H34" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J34" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="K34" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="L34" t="s">
         <v>26</v>
@@ -3444,12 +3483,12 @@
         <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
@@ -3467,19 +3506,19 @@
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J35" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="K35" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="L35" t="s">
         <v>26</v>
@@ -3491,42 +3530,42 @@
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="C36" t="s">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
         <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H36" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J36" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="K36" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="L36" t="s">
         <v>26</v>
@@ -3538,21 +3577,21 @@
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -3561,19 +3600,19 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="H37" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J37" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="K37" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="L37" t="s">
         <v>26</v>
@@ -3585,21 +3624,21 @@
         <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s">
-        <v>181</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>182</v>
+        <v>69</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -3608,19 +3647,19 @@
         <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J38" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="L38" t="s">
         <v>26</v>
@@ -3632,21 +3671,21 @@
         <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -3655,19 +3694,19 @@
         <v>20</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H39" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J39" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K39" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="L39" t="s">
         <v>26</v>
@@ -3679,21 +3718,21 @@
         <v>26</v>
       </c>
       <c r="O39" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>198</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -3702,19 +3741,19 @@
         <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H40" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J40" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K40" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="L40" t="s">
         <v>26</v>
@@ -3726,42 +3765,42 @@
         <v>26</v>
       </c>
       <c r="O40" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="G41" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J41" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="K41" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="L41" t="s">
         <v>26</v>
@@ -3770,24 +3809,24 @@
         <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>196</v>
+        <v>26</v>
       </c>
       <c r="O41" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -3796,19 +3835,19 @@
         <v>20</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H42" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J42" t="s">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="K42" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="L42" t="s">
         <v>26</v>
@@ -3820,21 +3859,21 @@
         <v>26</v>
       </c>
       <c r="O42" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -3843,19 +3882,19 @@
         <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H43" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J43" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K43" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="L43" t="s">
         <v>26</v>
@@ -3867,21 +3906,21 @@
         <v>26</v>
       </c>
       <c r="O43" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D44" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
@@ -3890,19 +3929,19 @@
         <v>20</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J44" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K44" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="L44" t="s">
         <v>26</v>
@@ -3914,21 +3953,21 @@
         <v>26</v>
       </c>
       <c r="O44" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>209</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
@@ -3937,19 +3976,19 @@
         <v>20</v>
       </c>
       <c r="G45" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H45" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J45" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K45" t="s">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="L45" t="s">
         <v>26</v>
@@ -3961,12 +4000,12 @@
         <v>26</v>
       </c>
       <c r="O45" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B46" t="s">
         <v>29</v>
@@ -3984,19 +4023,19 @@
         <v>20</v>
       </c>
       <c r="G46" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H46" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J46" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K46" t="s">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="L46" t="s">
         <v>26</v>
@@ -4008,21 +4047,21 @@
         <v>26</v>
       </c>
       <c r="O46" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
@@ -4031,19 +4070,19 @@
         <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H47" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I47" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J47" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K47" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="L47" t="s">
         <v>26</v>
@@ -4055,21 +4094,21 @@
         <v>26</v>
       </c>
       <c r="O47" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="C48" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E48" t="s">
         <v>26</v>
@@ -4078,19 +4117,19 @@
         <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H48" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J48" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K48" t="s">
-        <v>68</v>
+        <v>224</v>
       </c>
       <c r="L48" t="s">
         <v>26</v>
@@ -4102,42 +4141,42 @@
         <v>26</v>
       </c>
       <c r="O48" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F49" t="s">
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H49" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J49" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K49" t="s">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="L49" t="s">
         <v>26</v>
@@ -4149,21 +4188,21 @@
         <v>26</v>
       </c>
       <c r="O49" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="D50" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
@@ -4172,19 +4211,19 @@
         <v>20</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H50" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J50" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K50" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L50" t="s">
         <v>26</v>
@@ -4196,12 +4235,12 @@
         <v>26</v>
       </c>
       <c r="O50" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
@@ -4219,19 +4258,19 @@
         <v>20</v>
       </c>
       <c r="G51" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H51" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J51" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="K51" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="L51" t="s">
         <v>26</v>
@@ -4243,21 +4282,21 @@
         <v>26</v>
       </c>
       <c r="O51" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
@@ -4266,19 +4305,19 @@
         <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H52" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J52" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="K52" t="s">
-        <v>45</v>
+        <v>224</v>
       </c>
       <c r="L52" t="s">
         <v>26</v>
@@ -4290,21 +4329,21 @@
         <v>26</v>
       </c>
       <c r="O52" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
@@ -4313,19 +4352,19 @@
         <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="H53" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J53" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K53" t="s">
-        <v>187</v>
+        <v>65</v>
       </c>
       <c r="L53" t="s">
         <v>26</v>
@@ -4337,42 +4376,42 @@
         <v>26</v>
       </c>
       <c r="O53" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B54" t="s">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="C54" t="s">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E54" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
         <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J54" t="s">
-        <v>237</v>
+        <v>57</v>
       </c>
       <c r="K54" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L54" t="s">
         <v>26</v>
@@ -4384,43 +4423,43 @@
         <v>26</v>
       </c>
       <c r="O54" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" t="s">
+        <v>48</v>
+      </c>
+      <c r="H55" t="s">
+        <v>63</v>
+      </c>
+      <c r="I55" t="s">
+        <v>32</v>
+      </c>
+      <c r="J55" t="s">
+        <v>247</v>
+      </c>
+      <c r="K55" t="s">
         <v>43</v>
       </c>
-      <c r="E55" t="s">
-        <v>19</v>
-      </c>
-      <c r="F55" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" t="s">
-        <v>54</v>
-      </c>
-      <c r="I55" t="s">
-        <v>31</v>
-      </c>
-      <c r="J55" t="s">
-        <v>240</v>
-      </c>
-      <c r="K55" t="s">
-        <v>79</v>
-      </c>
       <c r="L55" t="s">
         <v>26</v>
       </c>
@@ -4431,21 +4470,21 @@
         <v>26</v>
       </c>
       <c r="O55" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B56" t="s">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>182</v>
+        <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
@@ -4454,19 +4493,19 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H56" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J56" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="K56" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="L56" t="s">
         <v>26</v>
@@ -4478,42 +4517,42 @@
         <v>26</v>
       </c>
       <c r="O56" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B57" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C57" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="D57" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>253</v>
       </c>
       <c r="G57" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="H57" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I57" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J57" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="K57" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="L57" t="s">
         <v>26</v>
@@ -4522,18 +4561,18 @@
         <v>26</v>
       </c>
       <c r="N57" t="s">
-        <v>26</v>
+        <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B58" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
         <v>30</v>
@@ -4548,19 +4587,19 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="H58" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J58" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="K58" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="L58" t="s">
         <v>26</v>
@@ -4572,21 +4611,21 @@
         <v>26</v>
       </c>
       <c r="O58" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B59" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="D59" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
@@ -4595,19 +4634,19 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H59" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J59" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="K59" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="L59" t="s">
         <v>26</v>
@@ -4619,21 +4658,21 @@
         <v>26</v>
       </c>
       <c r="O59" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
@@ -4642,19 +4681,19 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H60" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J60" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="K60" t="s">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="L60" t="s">
         <v>26</v>
@@ -4666,42 +4705,42 @@
         <v>26</v>
       </c>
       <c r="O60" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>269</v>
       </c>
       <c r="D61" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E61" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F61" t="s">
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H61" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J61" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="K61" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L61" t="s">
         <v>26</v>
@@ -4713,15 +4752,15 @@
         <v>26</v>
       </c>
       <c r="O61" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
         <v>30</v>
@@ -4736,19 +4775,19 @@
         <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I62" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J62" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="K62" t="s">
-        <v>38</v>
+        <v>224</v>
       </c>
       <c r="L62" t="s">
         <v>26</v>
@@ -4760,21 +4799,21 @@
         <v>26</v>
       </c>
       <c r="O62" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
@@ -4783,19 +4822,19 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J63" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="K63" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L63" t="s">
         <v>26</v>
@@ -4807,42 +4846,42 @@
         <v>26</v>
       </c>
       <c r="O63" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C64" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D64" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F64" t="s">
         <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H64" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I64" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J64" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="K64" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L64" t="s">
         <v>26</v>
@@ -4854,21 +4893,21 @@
         <v>26</v>
       </c>
       <c r="O64" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B65" t="s">
-        <v>181</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="D65" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
@@ -4877,19 +4916,19 @@
         <v>20</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H65" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J65" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="K65" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="L65" t="s">
         <v>26</v>
@@ -4901,21 +4940,21 @@
         <v>26</v>
       </c>
       <c r="O65" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="D66" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
@@ -4924,19 +4963,19 @@
         <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H66" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J66" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="K66" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="L66" t="s">
         <v>26</v>
@@ -4948,12 +4987,12 @@
         <v>26</v>
       </c>
       <c r="O66" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B67" t="s">
         <v>16</v>
@@ -4971,19 +5010,19 @@
         <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H67" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I67" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J67" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="K67" t="s">
-        <v>147</v>
+        <v>224</v>
       </c>
       <c r="L67" t="s">
         <v>26</v>
@@ -4995,21 +5034,21 @@
         <v>26</v>
       </c>
       <c r="O67" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B68" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C68" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
@@ -5018,19 +5057,19 @@
         <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>282</v>
+        <v>48</v>
       </c>
       <c r="H68" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I68" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J68" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="K68" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -5042,21 +5081,21 @@
         <v>26</v>
       </c>
       <c r="O68" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B69" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="C69" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D69" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
@@ -5065,19 +5104,19 @@
         <v>20</v>
       </c>
       <c r="G69" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H69" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J69" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="K69" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="L69" t="s">
         <v>26</v>
@@ -5089,42 +5128,42 @@
         <v>26</v>
       </c>
       <c r="O69" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F70" t="s">
         <v>20</v>
       </c>
       <c r="G70" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H70" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J70" t="s">
-        <v>190</v>
+        <v>297</v>
       </c>
       <c r="K70" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L70" t="s">
         <v>26</v>
@@ -5136,42 +5175,42 @@
         <v>26</v>
       </c>
       <c r="O70" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B71" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D71" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E71" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F71" t="s">
         <v>20</v>
       </c>
       <c r="G71" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H71" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I71" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J71" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="K71" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="L71" t="s">
         <v>26</v>
@@ -5183,21 +5222,21 @@
         <v>26</v>
       </c>
       <c r="O71" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B72" t="s">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="C72" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="D72" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E72" t="s">
         <v>19</v>
@@ -5206,19 +5245,19 @@
         <v>20</v>
       </c>
       <c r="G72" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H72" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I72" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J72" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="K72" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="L72" t="s">
         <v>26</v>
@@ -5230,21 +5269,21 @@
         <v>26</v>
       </c>
       <c r="O72" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B73" t="s">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="C73" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="D73" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
@@ -5253,19 +5292,19 @@
         <v>20</v>
       </c>
       <c r="G73" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H73" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J73" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="K73" t="s">
-        <v>300</v>
+        <v>39</v>
       </c>
       <c r="L73" t="s">
         <v>26</v>
@@ -5277,18 +5316,18 @@
         <v>26</v>
       </c>
       <c r="O73" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B74" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C74" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D74" t="s">
         <v>19</v>
@@ -5300,19 +5339,19 @@
         <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>21</v>
+        <v>309</v>
       </c>
       <c r="H74" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J74" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="K74" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="L74" t="s">
         <v>26</v>
@@ -5324,21 +5363,21 @@
         <v>26</v>
       </c>
       <c r="O74" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B75" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="C75" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="D75" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
@@ -5347,19 +5386,19 @@
         <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H75" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J75" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="K75" t="s">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="L75" t="s">
         <v>26</v>
@@ -5371,21 +5410,21 @@
         <v>26</v>
       </c>
       <c r="O75" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B76" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C76" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D76" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
@@ -5394,19 +5433,19 @@
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H76" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I76" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J76" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="K76" t="s">
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="L76" t="s">
         <v>26</v>
@@ -5418,42 +5457,42 @@
         <v>26</v>
       </c>
       <c r="O76" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B77" t="s">
-        <v>312</v>
+        <v>169</v>
       </c>
       <c r="C77" t="s">
-        <v>313</v>
+        <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F77" t="s">
         <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H77" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I77" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J77" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K77" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="L77" t="s">
         <v>26</v>
@@ -5465,21 +5504,21 @@
         <v>26</v>
       </c>
       <c r="O77" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B78" t="s">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="C78" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D78" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
@@ -5488,19 +5527,19 @@
         <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>317</v>
+        <v>48</v>
       </c>
       <c r="H78" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I78" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J78" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="K78" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="L78" t="s">
         <v>26</v>
@@ -5512,21 +5551,21 @@
         <v>26</v>
       </c>
       <c r="O78" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B79" t="s">
-        <v>294</v>
+        <v>16</v>
       </c>
       <c r="C79" t="s">
-        <v>295</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
@@ -5535,19 +5574,19 @@
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>321</v>
+        <v>31</v>
       </c>
       <c r="H79" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I79" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J79" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K79" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="L79" t="s">
         <v>26</v>
@@ -5559,21 +5598,21 @@
         <v>26</v>
       </c>
       <c r="O79" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B80" t="s">
-        <v>312</v>
+        <v>136</v>
       </c>
       <c r="C80" t="s">
-        <v>313</v>
+        <v>47</v>
       </c>
       <c r="D80" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="E80" t="s">
         <v>19</v>
@@ -5582,19 +5621,19 @@
         <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H80" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J80" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K80" t="s">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="L80" t="s">
         <v>26</v>
@@ -5606,21 +5645,21 @@
         <v>26</v>
       </c>
       <c r="O80" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>244</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
@@ -5629,19 +5668,19 @@
         <v>20</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H81" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I81" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J81" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K81" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="L81" t="s">
         <v>26</v>
@@ -5653,12 +5692,12 @@
         <v>26</v>
       </c>
       <c r="O81" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B82" t="s">
         <v>16</v>
@@ -5676,19 +5715,19 @@
         <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H82" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J82" t="s">
-        <v>210</v>
+        <v>334</v>
       </c>
       <c r="K82" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L82" t="s">
         <v>26</v>
@@ -5700,21 +5739,21 @@
         <v>26</v>
       </c>
       <c r="O82" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B83" t="s">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>182</v>
+        <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
@@ -5723,19 +5762,19 @@
         <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>334</v>
+        <v>31</v>
       </c>
       <c r="H83" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I83" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J83" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K83" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="L83" t="s">
         <v>26</v>
@@ -5747,21 +5786,21 @@
         <v>26</v>
       </c>
       <c r="O83" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B84" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="C84" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="D84" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E84" t="s">
         <v>19</v>
@@ -5770,19 +5809,19 @@
         <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>36</v>
+        <v>340</v>
       </c>
       <c r="H84" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I84" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J84" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K84" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="L84" t="s">
         <v>26</v>
@@ -5794,21 +5833,21 @@
         <v>26</v>
       </c>
       <c r="O84" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B85" t="s">
-        <v>208</v>
+        <v>37</v>
       </c>
       <c r="C85" t="s">
-        <v>209</v>
+        <v>26</v>
       </c>
       <c r="D85" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E85" t="s">
         <v>19</v>
@@ -5817,19 +5856,19 @@
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H85" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I85" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J85" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K85" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
@@ -5841,21 +5880,21 @@
         <v>26</v>
       </c>
       <c r="O85" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C86" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
@@ -5864,19 +5903,19 @@
         <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H86" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I86" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J86" t="s">
-        <v>344</v>
+        <v>250</v>
       </c>
       <c r="K86" t="s">
-        <v>258</v>
+        <v>147</v>
       </c>
       <c r="L86" t="s">
         <v>26</v>
@@ -5888,21 +5927,21 @@
         <v>26</v>
       </c>
       <c r="O86" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B87" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="C87" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="D87" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E87" t="s">
         <v>26</v>
@@ -5911,19 +5950,19 @@
         <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H87" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I87" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J87" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K87" t="s">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="L87" t="s">
         <v>26</v>
@@ -5935,42 +5974,42 @@
         <v>26</v>
       </c>
       <c r="O87" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B88" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="C88" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D88" t="s">
         <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F88" t="s">
         <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="H88" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I88" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K88" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="L88" t="s">
         <v>26</v>
@@ -5982,21 +6021,21 @@
         <v>26</v>
       </c>
       <c r="O88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B89" t="s">
-        <v>353</v>
+        <v>76</v>
       </c>
       <c r="C89" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="D89" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="E89" t="s">
         <v>19</v>
@@ -6005,19 +6044,19 @@
         <v>20</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H89" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I89" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J89" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K89" t="s">
-        <v>187</v>
+        <v>356</v>
       </c>
       <c r="L89" t="s">
         <v>26</v>
@@ -6029,42 +6068,42 @@
         <v>26</v>
       </c>
       <c r="O89" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B90" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C90" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="D90" t="s">
         <v>19</v>
       </c>
       <c r="E90" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F90" t="s">
         <v>20</v>
       </c>
       <c r="G90" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H90" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I90" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J90" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K90" t="s">
-        <v>33</v>
+        <v>224</v>
       </c>
       <c r="L90" t="s">
         <v>26</v>
@@ -6076,21 +6115,21 @@
         <v>26</v>
       </c>
       <c r="O90" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="C91" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
@@ -6099,19 +6138,19 @@
         <v>20</v>
       </c>
       <c r="G91" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H91" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I91" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J91" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K91" t="s">
-        <v>129</v>
+        <v>224</v>
       </c>
       <c r="L91" t="s">
         <v>26</v>
@@ -6123,21 +6162,21 @@
         <v>26</v>
       </c>
       <c r="O91" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="C92" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="D92" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E92" t="s">
         <v>19</v>
@@ -6146,19 +6185,19 @@
         <v>20</v>
       </c>
       <c r="G92" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H92" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I92" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J92" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K92" t="s">
-        <v>110</v>
+        <v>356</v>
       </c>
       <c r="L92" t="s">
         <v>26</v>
@@ -6170,21 +6209,21 @@
         <v>26</v>
       </c>
       <c r="O92" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>368</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>369</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
@@ -6193,19 +6232,19 @@
         <v>20</v>
       </c>
       <c r="G93" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H93" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I93" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J93" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="K93" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L93" t="s">
         <v>26</v>
@@ -6217,42 +6256,42 @@
         <v>26</v>
       </c>
       <c r="O93" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B94" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="D94" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E94" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F94" t="s">
         <v>20</v>
       </c>
       <c r="G94" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="H94" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J94" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="K94" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="L94" t="s">
         <v>26</v>
@@ -6264,21 +6303,21 @@
         <v>26</v>
       </c>
       <c r="O94" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B95" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="D95" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
@@ -6287,19 +6326,19 @@
         <v>20</v>
       </c>
       <c r="G95" t="s">
-        <v>36</v>
+        <v>376</v>
       </c>
       <c r="H95" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I95" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J95" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="K95" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -6311,21 +6350,21 @@
         <v>26</v>
       </c>
       <c r="O95" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B96" t="s">
-        <v>52</v>
+        <v>368</v>
       </c>
       <c r="C96" t="s">
-        <v>53</v>
+        <v>369</v>
       </c>
       <c r="D96" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E96" t="s">
         <v>19</v>
@@ -6334,19 +6373,19 @@
         <v>20</v>
       </c>
       <c r="G96" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H96" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J96" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="K96" t="s">
-        <v>129</v>
+        <v>381</v>
       </c>
       <c r="L96" t="s">
         <v>26</v>
@@ -6358,42 +6397,42 @@
         <v>26</v>
       </c>
       <c r="O96" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B97" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C97" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E97" t="s">
         <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="G97" t="s">
-        <v>379</v>
+        <v>48</v>
       </c>
       <c r="H97" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I97" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J97" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="K97" t="s">
-        <v>381</v>
+        <v>97</v>
       </c>
       <c r="L97" t="s">
         <v>26</v>
@@ -6402,15 +6441,15 @@
         <v>26</v>
       </c>
       <c r="N97" t="s">
-        <v>382</v>
+        <v>26</v>
       </c>
       <c r="O97" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B98" t="s">
         <v>16</v>
@@ -6428,19 +6467,19 @@
         <v>20</v>
       </c>
       <c r="G98" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H98" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I98" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J98" t="s">
-        <v>385</v>
+        <v>270</v>
       </c>
       <c r="K98" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="L98" t="s">
         <v>26</v>
@@ -6452,21 +6491,21 @@
         <v>26</v>
       </c>
       <c r="O98" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>244</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
@@ -6475,19 +6514,19 @@
         <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H99" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I99" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J99" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K99" t="s">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="L99" t="s">
         <v>26</v>
@@ -6499,18 +6538,18 @@
         <v>26</v>
       </c>
       <c r="O99" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B100" t="s">
-        <v>294</v>
+        <v>136</v>
       </c>
       <c r="C100" t="s">
-        <v>295</v>
+        <v>47</v>
       </c>
       <c r="D100" t="s">
         <v>19</v>
@@ -6522,19 +6561,19 @@
         <v>20</v>
       </c>
       <c r="G100" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H100" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J100" t="s">
-        <v>322</v>
+        <v>393</v>
       </c>
       <c r="K100" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L100" t="s">
         <v>26</v>
@@ -6546,21 +6585,21 @@
         <v>26</v>
       </c>
       <c r="O100" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B101" t="s">
-        <v>103</v>
+        <v>268</v>
       </c>
       <c r="C101" t="s">
-        <v>104</v>
+        <v>269</v>
       </c>
       <c r="D101" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
@@ -6569,19 +6608,19 @@
         <v>20</v>
       </c>
       <c r="G101" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H101" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J101" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K101" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="L101" t="s">
         <v>26</v>
@@ -6593,21 +6632,21 @@
         <v>26</v>
       </c>
       <c r="O101" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B102" t="s">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="C102" t="s">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="D102" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
@@ -6616,19 +6655,19 @@
         <v>20</v>
       </c>
       <c r="G102" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H102" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I102" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J102" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K102" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="L102" t="s">
         <v>26</v>
@@ -6640,42 +6679,42 @@
         <v>26</v>
       </c>
       <c r="O102" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B103" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C103" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D103" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E103" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F103" t="s">
         <v>20</v>
       </c>
       <c r="G103" t="s">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="H103" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I103" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J103" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K103" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="L103" t="s">
         <v>26</v>
@@ -6687,42 +6726,42 @@
         <v>26</v>
       </c>
       <c r="O103" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B104" t="s">
-        <v>403</v>
+        <v>182</v>
       </c>
       <c r="C104" t="s">
-        <v>404</v>
+        <v>183</v>
       </c>
       <c r="D104" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E104" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F104" t="s">
         <v>20</v>
       </c>
       <c r="G104" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="H104" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J104" t="s">
         <v>405</v>
       </c>
       <c r="K104" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L104" t="s">
         <v>26</v>
@@ -6742,13 +6781,13 @@
         <v>407</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>408</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>187</v>
       </c>
       <c r="D105" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="E105" t="s">
         <v>19</v>
@@ -6757,19 +6796,19 @@
         <v>20</v>
       </c>
       <c r="G105" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H105" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I105" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J105" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K105" t="s">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="L105" t="s">
         <v>26</v>
@@ -6781,42 +6820,42 @@
         <v>26</v>
       </c>
       <c r="O105" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B106" t="s">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="D106" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E106" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F106" t="s">
         <v>20</v>
       </c>
       <c r="G106" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H106" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I106" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J106" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K106" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="L106" t="s">
         <v>26</v>
@@ -6828,42 +6867,42 @@
         <v>26</v>
       </c>
       <c r="O106" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B107" t="s">
-        <v>353</v>
+        <v>16</v>
       </c>
       <c r="C107" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="D107" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="E107" t="s">
         <v>19</v>
       </c>
       <c r="F107" t="s">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="G107" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H107" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I107" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J107" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K107" t="s">
-        <v>415</v>
+        <v>97</v>
       </c>
       <c r="L107" t="s">
         <v>26</v>
@@ -6872,45 +6911,45 @@
         <v>26</v>
       </c>
       <c r="N107" t="s">
+        <v>26</v>
+      </c>
+      <c r="O107" t="s">
         <v>416</v>
-      </c>
-      <c r="O107" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>417</v>
+      </c>
+      <c r="B108" t="s">
+        <v>29</v>
+      </c>
+      <c r="C108" t="s">
+        <v>30</v>
+      </c>
+      <c r="D108" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" t="s">
+        <v>20</v>
+      </c>
+      <c r="G108" t="s">
+        <v>31</v>
+      </c>
+      <c r="H108" t="s">
+        <v>63</v>
+      </c>
+      <c r="I108" t="s">
+        <v>32</v>
+      </c>
+      <c r="J108" t="s">
         <v>418</v>
       </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="s">
-        <v>17</v>
-      </c>
-      <c r="D108" t="s">
-        <v>18</v>
-      </c>
-      <c r="E108" t="s">
-        <v>19</v>
-      </c>
-      <c r="F108" t="s">
-        <v>20</v>
-      </c>
-      <c r="G108" t="s">
-        <v>21</v>
-      </c>
-      <c r="H108" t="s">
-        <v>54</v>
-      </c>
-      <c r="I108" t="s">
-        <v>31</v>
-      </c>
-      <c r="J108" t="s">
-        <v>397</v>
-      </c>
       <c r="K108" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L108" t="s">
         <v>26</v>
@@ -6945,19 +6984,19 @@
         <v>20</v>
       </c>
       <c r="G109" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H109" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I109" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J109" t="s">
         <v>421</v>
       </c>
       <c r="K109" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="L109" t="s">
         <v>26</v>
@@ -6977,184 +7016,184 @@
         <v>423</v>
       </c>
       <c r="B110" t="s">
+        <v>182</v>
+      </c>
+      <c r="C110" t="s">
+        <v>183</v>
+      </c>
+      <c r="D110" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" t="s">
+        <v>26</v>
+      </c>
+      <c r="F110" t="s">
+        <v>20</v>
+      </c>
+      <c r="G110" t="s">
+        <v>31</v>
+      </c>
+      <c r="H110" t="s">
+        <v>63</v>
+      </c>
+      <c r="I110" t="s">
+        <v>32</v>
+      </c>
+      <c r="J110" t="s">
         <v>424</v>
       </c>
-      <c r="C110" t="s">
+      <c r="K110" t="s">
+        <v>101</v>
+      </c>
+      <c r="L110" t="s">
+        <v>26</v>
+      </c>
+      <c r="M110" t="s">
+        <v>26</v>
+      </c>
+      <c r="N110" t="s">
+        <v>26</v>
+      </c>
+      <c r="O110" t="s">
         <v>425</v>
-      </c>
-      <c r="D110" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" t="s">
-        <v>19</v>
-      </c>
-      <c r="F110" t="s">
-        <v>20</v>
-      </c>
-      <c r="G110" t="s">
-        <v>105</v>
-      </c>
-      <c r="H110" t="s">
-        <v>54</v>
-      </c>
-      <c r="I110" t="s">
-        <v>31</v>
-      </c>
-      <c r="J110" t="s">
-        <v>426</v>
-      </c>
-      <c r="K110" t="s">
-        <v>187</v>
-      </c>
-      <c r="L110" t="s">
-        <v>26</v>
-      </c>
-      <c r="M110" t="s">
-        <v>26</v>
-      </c>
-      <c r="N110" t="s">
-        <v>26</v>
-      </c>
-      <c r="O110" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>426</v>
+      </c>
+      <c r="B111" t="s">
+        <v>243</v>
+      </c>
+      <c r="C111" t="s">
+        <v>244</v>
+      </c>
+      <c r="D111" t="s">
+        <v>62</v>
+      </c>
+      <c r="E111" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" t="s">
+        <v>20</v>
+      </c>
+      <c r="G111" t="s">
+        <v>31</v>
+      </c>
+      <c r="H111" t="s">
+        <v>63</v>
+      </c>
+      <c r="I111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J111" t="s">
+        <v>427</v>
+      </c>
+      <c r="K111" t="s">
+        <v>101</v>
+      </c>
+      <c r="L111" t="s">
+        <v>26</v>
+      </c>
+      <c r="M111" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" t="s">
+        <v>26</v>
+      </c>
+      <c r="O111" t="s">
         <v>428</v>
-      </c>
-      <c r="B111" t="s">
-        <v>294</v>
-      </c>
-      <c r="C111" t="s">
-        <v>295</v>
-      </c>
-      <c r="D111" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" t="s">
-        <v>19</v>
-      </c>
-      <c r="F111" t="s">
-        <v>20</v>
-      </c>
-      <c r="G111" t="s">
-        <v>36</v>
-      </c>
-      <c r="H111" t="s">
-        <v>54</v>
-      </c>
-      <c r="I111" t="s">
-        <v>31</v>
-      </c>
-      <c r="J111" t="s">
-        <v>429</v>
-      </c>
-      <c r="K111" t="s">
-        <v>45</v>
-      </c>
-      <c r="L111" t="s">
-        <v>26</v>
-      </c>
-      <c r="M111" t="s">
-        <v>26</v>
-      </c>
-      <c r="N111" t="s">
-        <v>26</v>
-      </c>
-      <c r="O111" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>429</v>
+      </c>
+      <c r="B112" t="s">
+        <v>130</v>
+      </c>
+      <c r="C112" t="s">
+        <v>131</v>
+      </c>
+      <c r="D112" t="s">
+        <v>62</v>
+      </c>
+      <c r="E112" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" t="s">
+        <v>20</v>
+      </c>
+      <c r="G112" t="s">
+        <v>48</v>
+      </c>
+      <c r="H112" t="s">
+        <v>63</v>
+      </c>
+      <c r="I112" t="s">
+        <v>32</v>
+      </c>
+      <c r="J112" t="s">
+        <v>430</v>
+      </c>
+      <c r="K112" t="s">
+        <v>97</v>
+      </c>
+      <c r="L112" t="s">
+        <v>26</v>
+      </c>
+      <c r="M112" t="s">
+        <v>26</v>
+      </c>
+      <c r="N112" t="s">
+        <v>26</v>
+      </c>
+      <c r="O112" t="s">
         <v>431</v>
-      </c>
-      <c r="B112" t="s">
-        <v>432</v>
-      </c>
-      <c r="C112" t="s">
-        <v>433</v>
-      </c>
-      <c r="D112" t="s">
-        <v>19</v>
-      </c>
-      <c r="E112" t="s">
-        <v>19</v>
-      </c>
-      <c r="F112" t="s">
-        <v>20</v>
-      </c>
-      <c r="G112" t="s">
-        <v>36</v>
-      </c>
-      <c r="H112" t="s">
-        <v>54</v>
-      </c>
-      <c r="I112" t="s">
-        <v>31</v>
-      </c>
-      <c r="J112" t="s">
-        <v>434</v>
-      </c>
-      <c r="K112" t="s">
-        <v>258</v>
-      </c>
-      <c r="L112" t="s">
-        <v>26</v>
-      </c>
-      <c r="M112" t="s">
-        <v>26</v>
-      </c>
-      <c r="N112" t="s">
-        <v>26</v>
-      </c>
-      <c r="O112" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>432</v>
+      </c>
+      <c r="B113" t="s">
+        <v>68</v>
+      </c>
+      <c r="C113" t="s">
+        <v>69</v>
+      </c>
+      <c r="D113" t="s">
+        <v>70</v>
+      </c>
+      <c r="E113" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" t="s">
+        <v>433</v>
+      </c>
+      <c r="G113" t="s">
+        <v>434</v>
+      </c>
+      <c r="H113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I113" t="s">
+        <v>32</v>
+      </c>
+      <c r="J113" t="s">
+        <v>435</v>
+      </c>
+      <c r="K113" t="s">
         <v>436</v>
       </c>
-      <c r="B113" t="s">
-        <v>29</v>
-      </c>
-      <c r="C113" t="s">
-        <v>30</v>
-      </c>
-      <c r="D113" t="s">
-        <v>19</v>
-      </c>
-      <c r="E113" t="s">
-        <v>19</v>
-      </c>
-      <c r="F113" t="s">
-        <v>20</v>
-      </c>
-      <c r="G113" t="s">
-        <v>36</v>
-      </c>
-      <c r="H113" t="s">
-        <v>54</v>
-      </c>
-      <c r="I113" t="s">
-        <v>31</v>
-      </c>
-      <c r="J113" t="s">
+      <c r="L113" t="s">
+        <v>26</v>
+      </c>
+      <c r="M113" t="s">
+        <v>26</v>
+      </c>
+      <c r="N113" t="s">
         <v>437</v>
-      </c>
-      <c r="K113" t="s">
-        <v>45</v>
-      </c>
-      <c r="L113" t="s">
-        <v>26</v>
-      </c>
-      <c r="M113" t="s">
-        <v>26</v>
-      </c>
-      <c r="N113" t="s">
-        <v>26</v>
       </c>
       <c r="O113" t="s">
         <v>438</v>
@@ -7180,19 +7219,19 @@
         <v>20</v>
       </c>
       <c r="G114" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H114" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J114" t="s">
-        <v>322</v>
+        <v>440</v>
       </c>
       <c r="K114" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="L114" t="s">
         <v>26</v>
@@ -7204,12 +7243,12 @@
         <v>26</v>
       </c>
       <c r="O114" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B115" t="s">
         <v>16</v>
@@ -7227,19 +7266,19 @@
         <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>36</v>
+        <v>443</v>
       </c>
       <c r="H115" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I115" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J115" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K115" t="s">
-        <v>443</v>
+        <v>228</v>
       </c>
       <c r="L115" t="s">
         <v>26</v>
@@ -7251,18 +7290,18 @@
         <v>26</v>
       </c>
       <c r="O115" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B116" t="s">
-        <v>294</v>
+        <v>76</v>
       </c>
       <c r="C116" t="s">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="D116" t="s">
         <v>19</v>
@@ -7274,19 +7313,19 @@
         <v>20</v>
       </c>
       <c r="G116" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H116" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I116" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J116" t="s">
-        <v>446</v>
+        <v>377</v>
       </c>
       <c r="K116" t="s">
-        <v>258</v>
+        <v>79</v>
       </c>
       <c r="L116" t="s">
         <v>26</v>
@@ -7306,13 +7345,13 @@
         <v>448</v>
       </c>
       <c r="B117" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="C117" t="s">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="D117" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E117" t="s">
         <v>19</v>
@@ -7321,19 +7360,19 @@
         <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H117" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I117" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J117" t="s">
         <v>449</v>
       </c>
       <c r="K117" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="L117" t="s">
         <v>26</v>
@@ -7353,107 +7392,107 @@
         <v>451</v>
       </c>
       <c r="B118" t="s">
-        <v>103</v>
+        <v>268</v>
       </c>
       <c r="C118" t="s">
-        <v>104</v>
+        <v>269</v>
       </c>
       <c r="D118" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E118" t="s">
         <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="G118" t="s">
+        <v>48</v>
+      </c>
+      <c r="H118" t="s">
+        <v>63</v>
+      </c>
+      <c r="I118" t="s">
+        <v>32</v>
+      </c>
+      <c r="J118" t="s">
         <v>452</v>
       </c>
-      <c r="H118" t="s">
-        <v>54</v>
-      </c>
-      <c r="I118" t="s">
-        <v>31</v>
-      </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
+        <v>65</v>
+      </c>
+      <c r="L118" t="s">
+        <v>26</v>
+      </c>
+      <c r="M118" t="s">
+        <v>26</v>
+      </c>
+      <c r="N118" t="s">
+        <v>26</v>
+      </c>
+      <c r="O118" t="s">
         <v>453</v>
-      </c>
-      <c r="K118" t="s">
-        <v>415</v>
-      </c>
-      <c r="L118" t="s">
-        <v>26</v>
-      </c>
-      <c r="M118" t="s">
-        <v>26</v>
-      </c>
-      <c r="N118" t="s">
-        <v>454</v>
-      </c>
-      <c r="O118" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>454</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" t="s">
+        <v>18</v>
+      </c>
+      <c r="E119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119" t="s">
+        <v>20</v>
+      </c>
+      <c r="G119" t="s">
+        <v>309</v>
+      </c>
+      <c r="H119" t="s">
+        <v>63</v>
+      </c>
+      <c r="I119" t="s">
+        <v>32</v>
+      </c>
+      <c r="J119" t="s">
+        <v>455</v>
+      </c>
+      <c r="K119" t="s">
+        <v>147</v>
+      </c>
+      <c r="L119" t="s">
+        <v>26</v>
+      </c>
+      <c r="M119" t="s">
+        <v>26</v>
+      </c>
+      <c r="N119" t="s">
+        <v>26</v>
+      </c>
+      <c r="O119" t="s">
         <v>456</v>
-      </c>
-      <c r="B119" t="s">
-        <v>132</v>
-      </c>
-      <c r="C119" t="s">
-        <v>133</v>
-      </c>
-      <c r="D119" t="s">
-        <v>43</v>
-      </c>
-      <c r="E119" t="s">
-        <v>19</v>
-      </c>
-      <c r="F119" t="s">
-        <v>20</v>
-      </c>
-      <c r="G119" t="s">
-        <v>36</v>
-      </c>
-      <c r="H119" t="s">
-        <v>54</v>
-      </c>
-      <c r="I119" t="s">
-        <v>31</v>
-      </c>
-      <c r="J119" t="s">
-        <v>457</v>
-      </c>
-      <c r="K119" t="s">
-        <v>33</v>
-      </c>
-      <c r="L119" t="s">
-        <v>26</v>
-      </c>
-      <c r="M119" t="s">
-        <v>26</v>
-      </c>
-      <c r="N119" t="s">
-        <v>26</v>
-      </c>
-      <c r="O119" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>457</v>
+      </c>
+      <c r="B120" t="s">
+        <v>458</v>
+      </c>
+      <c r="C120" t="s">
         <v>459</v>
       </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="s">
-        <v>17</v>
-      </c>
       <c r="D120" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E120" t="s">
         <v>19</v>
@@ -7462,19 +7501,19 @@
         <v>20</v>
       </c>
       <c r="G120" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="H120" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I120" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J120" t="s">
         <v>460</v>
       </c>
       <c r="K120" t="s">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="L120" t="s">
         <v>26</v>
@@ -7494,13 +7533,13 @@
         <v>462</v>
       </c>
       <c r="B121" t="s">
-        <v>353</v>
+        <v>16</v>
       </c>
       <c r="C121" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="D121" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
@@ -7509,19 +7548,19 @@
         <v>20</v>
       </c>
       <c r="G121" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H121" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I121" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J121" t="s">
         <v>463</v>
       </c>
       <c r="K121" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="L121" t="s">
         <v>26</v>
@@ -7541,13 +7580,13 @@
         <v>465</v>
       </c>
       <c r="B122" t="s">
-        <v>294</v>
+        <v>16</v>
       </c>
       <c r="C122" t="s">
-        <v>295</v>
+        <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E122" t="s">
         <v>19</v>
@@ -7556,19 +7595,19 @@
         <v>20</v>
       </c>
       <c r="G122" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H122" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J122" t="s">
-        <v>369</v>
+        <v>466</v>
       </c>
       <c r="K122" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="L122" t="s">
         <v>26</v>
@@ -7580,43 +7619,43 @@
         <v>26</v>
       </c>
       <c r="O122" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B123" t="s">
-        <v>468</v>
+        <v>408</v>
       </c>
       <c r="C123" t="s">
+        <v>187</v>
+      </c>
+      <c r="D123" t="s">
+        <v>55</v>
+      </c>
+      <c r="E123" t="s">
+        <v>19</v>
+      </c>
+      <c r="F123" t="s">
+        <v>253</v>
+      </c>
+      <c r="G123" t="s">
+        <v>31</v>
+      </c>
+      <c r="H123" t="s">
+        <v>63</v>
+      </c>
+      <c r="I123" t="s">
+        <v>32</v>
+      </c>
+      <c r="J123" t="s">
         <v>469</v>
       </c>
-      <c r="D123" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123" t="s">
-        <v>26</v>
-      </c>
-      <c r="F123" t="s">
-        <v>20</v>
-      </c>
-      <c r="G123" t="s">
-        <v>317</v>
-      </c>
-      <c r="H123" t="s">
-        <v>54</v>
-      </c>
-      <c r="I123" t="s">
-        <v>31</v>
-      </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>470</v>
       </c>
-      <c r="K123" t="s">
-        <v>110</v>
-      </c>
       <c r="L123" t="s">
         <v>26</v>
       </c>
@@ -7624,45 +7663,45 @@
         <v>26</v>
       </c>
       <c r="N123" t="s">
-        <v>26</v>
+        <v>471</v>
       </c>
       <c r="O123" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B124" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C124" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D124" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E124" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F124" t="s">
         <v>20</v>
       </c>
       <c r="G124" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H124" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I124" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J124" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="K124" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="L124" t="s">
         <v>26</v>
@@ -7682,93 +7721,328 @@
         <v>475</v>
       </c>
       <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" t="s">
+        <v>18</v>
+      </c>
+      <c r="E125" t="s">
+        <v>19</v>
+      </c>
+      <c r="F125" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" t="s">
+        <v>48</v>
+      </c>
+      <c r="H125" t="s">
+        <v>63</v>
+      </c>
+      <c r="I125" t="s">
+        <v>32</v>
+      </c>
+      <c r="J125" t="s">
         <v>476</v>
       </c>
-      <c r="C125" t="s">
-        <v>313</v>
-      </c>
-      <c r="D125" t="s">
-        <v>120</v>
-      </c>
-      <c r="E125" t="s">
-        <v>120</v>
-      </c>
-      <c r="F125" t="s">
-        <v>193</v>
-      </c>
-      <c r="G125" t="s">
+      <c r="K125" t="s">
+        <v>97</v>
+      </c>
+      <c r="L125" t="s">
+        <v>26</v>
+      </c>
+      <c r="M125" t="s">
+        <v>26</v>
+      </c>
+      <c r="N125" t="s">
+        <v>26</v>
+      </c>
+      <c r="O125" t="s">
         <v>477</v>
-      </c>
-      <c r="H125" t="s">
-        <v>54</v>
-      </c>
-      <c r="I125" t="s">
-        <v>31</v>
-      </c>
-      <c r="J125" t="s">
-        <v>478</v>
-      </c>
-      <c r="K125" t="s">
-        <v>479</v>
-      </c>
-      <c r="L125" t="s">
-        <v>26</v>
-      </c>
-      <c r="M125" t="s">
-        <v>26</v>
-      </c>
-      <c r="N125" t="s">
-        <v>480</v>
-      </c>
-      <c r="O125" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>478</v>
+      </c>
+      <c r="B126" t="s">
+        <v>479</v>
+      </c>
+      <c r="C126" t="s">
+        <v>480</v>
+      </c>
+      <c r="D126" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" t="s">
+        <v>71</v>
+      </c>
+      <c r="H126" t="s">
+        <v>63</v>
+      </c>
+      <c r="I126" t="s">
+        <v>32</v>
+      </c>
+      <c r="J126" t="s">
+        <v>481</v>
+      </c>
+      <c r="K126" t="s">
+        <v>43</v>
+      </c>
+      <c r="L126" t="s">
+        <v>26</v>
+      </c>
+      <c r="M126" t="s">
+        <v>26</v>
+      </c>
+      <c r="N126" t="s">
+        <v>26</v>
+      </c>
+      <c r="O126" t="s">
         <v>482</v>
       </c>
-      <c r="B126" t="s">
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>483</v>
+      </c>
+      <c r="B127" t="s">
+        <v>76</v>
+      </c>
+      <c r="C127" t="s">
+        <v>77</v>
+      </c>
+      <c r="D127" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" t="s">
+        <v>19</v>
+      </c>
+      <c r="F127" t="s">
+        <v>20</v>
+      </c>
+      <c r="G127" t="s">
+        <v>31</v>
+      </c>
+      <c r="H127" t="s">
+        <v>63</v>
+      </c>
+      <c r="I127" t="s">
+        <v>32</v>
+      </c>
+      <c r="J127" t="s">
+        <v>484</v>
+      </c>
+      <c r="K127" t="s">
+        <v>101</v>
+      </c>
+      <c r="L127" t="s">
+        <v>26</v>
+      </c>
+      <c r="M127" t="s">
+        <v>26</v>
+      </c>
+      <c r="N127" t="s">
+        <v>26</v>
+      </c>
+      <c r="O127" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>486</v>
+      </c>
+      <c r="B128" t="s">
+        <v>487</v>
+      </c>
+      <c r="C128" t="s">
+        <v>488</v>
+      </c>
+      <c r="D128" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" t="s">
+        <v>19</v>
+      </c>
+      <c r="F128" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" t="s">
+        <v>31</v>
+      </c>
+      <c r="H128" t="s">
+        <v>63</v>
+      </c>
+      <c r="I128" t="s">
+        <v>32</v>
+      </c>
+      <c r="J128" t="s">
+        <v>489</v>
+      </c>
+      <c r="K128" t="s">
+        <v>34</v>
+      </c>
+      <c r="L128" t="s">
+        <v>26</v>
+      </c>
+      <c r="M128" t="s">
+        <v>26</v>
+      </c>
+      <c r="N128" t="s">
+        <v>26</v>
+      </c>
+      <c r="O128" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>491</v>
+      </c>
+      <c r="B129" t="s">
+        <v>29</v>
+      </c>
+      <c r="C129" t="s">
+        <v>30</v>
+      </c>
+      <c r="D129" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" t="s">
+        <v>19</v>
+      </c>
+      <c r="F129" t="s">
+        <v>20</v>
+      </c>
+      <c r="G129" t="s">
+        <v>31</v>
+      </c>
+      <c r="H129" t="s">
+        <v>63</v>
+      </c>
+      <c r="I129" t="s">
+        <v>32</v>
+      </c>
+      <c r="J129" t="s">
+        <v>42</v>
+      </c>
+      <c r="K129" t="s">
+        <v>101</v>
+      </c>
+      <c r="L129" t="s">
+        <v>26</v>
+      </c>
+      <c r="M129" t="s">
+        <v>26</v>
+      </c>
+      <c r="N129" t="s">
+        <v>26</v>
+      </c>
+      <c r="O129" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>493</v>
+      </c>
+      <c r="B130" t="s">
         <v>16</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C130" t="s">
         <v>17</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D130" t="s">
         <v>18</v>
       </c>
-      <c r="E126" t="s">
-        <v>19</v>
-      </c>
-      <c r="F126" t="s">
-        <v>20</v>
-      </c>
-      <c r="G126" t="s">
-        <v>36</v>
-      </c>
-      <c r="H126" t="s">
-        <v>54</v>
-      </c>
-      <c r="I126" t="s">
+      <c r="E130" t="s">
+        <v>19</v>
+      </c>
+      <c r="F130" t="s">
+        <v>20</v>
+      </c>
+      <c r="G130" t="s">
         <v>31</v>
       </c>
-      <c r="J126" t="s">
-        <v>483</v>
-      </c>
-      <c r="K126" t="s">
-        <v>79</v>
-      </c>
-      <c r="L126" t="s">
-        <v>26</v>
-      </c>
-      <c r="M126" t="s">
-        <v>26</v>
-      </c>
-      <c r="N126" t="s">
-        <v>26</v>
-      </c>
-      <c r="O126" t="s">
-        <v>484</v>
+      <c r="H130" t="s">
+        <v>63</v>
+      </c>
+      <c r="I130" t="s">
+        <v>32</v>
+      </c>
+      <c r="J130" t="s">
+        <v>377</v>
+      </c>
+      <c r="K130" t="s">
+        <v>73</v>
+      </c>
+      <c r="L130" t="s">
+        <v>26</v>
+      </c>
+      <c r="M130" t="s">
+        <v>26</v>
+      </c>
+      <c r="N130" t="s">
+        <v>26</v>
+      </c>
+      <c r="O130" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>495</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" t="s">
+        <v>18</v>
+      </c>
+      <c r="E131" t="s">
+        <v>19</v>
+      </c>
+      <c r="F131" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" t="s">
+        <v>31</v>
+      </c>
+      <c r="H131" t="s">
+        <v>63</v>
+      </c>
+      <c r="I131" t="s">
+        <v>32</v>
+      </c>
+      <c r="J131" t="s">
+        <v>496</v>
+      </c>
+      <c r="K131" t="s">
+        <v>50</v>
+      </c>
+      <c r="L131" t="s">
+        <v>26</v>
+      </c>
+      <c r="M131" t="s">
+        <v>26</v>
+      </c>
+      <c r="N131" t="s">
+        <v>26</v>
+      </c>
+      <c r="O131" t="s">
+        <v>497</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BE132C4-5936-4085-AF9D-394BDCC839B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99F7B820-0492-487E-903B-9295C36E08F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="522">
   <si>
     <t>Time</t>
   </si>
@@ -62,7 +62,85 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>07/02/2026 12:41:50 PM</t>
+    <t>07/09/2026 9:54:42 AM</t>
+  </si>
+  <si>
+    <t>22996</t>
+  </si>
+  <si>
+    <t>FOFANA, MAMADOU</t>
+  </si>
+  <si>
+    <t>OTR</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Pearl Harbor Memorial Highway, 14.5 mi WSW Las Cruces, Doña Ana County, NM</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454796-a48a-508d-b3bf-cc18834d612c</t>
+  </si>
+  <si>
+    <t>07/09/2026 8:49:26 AM</t>
+  </si>
+  <si>
+    <t>23466</t>
+  </si>
+  <si>
+    <t>NUNEZ, WALLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanya Smith </t>
+  </si>
+  <si>
+    <t>Veterans Memorial Highway, 12.8 mi SSW Santa Clara, Mohave County, AZ</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445475a-e24a-5a99-826a-6dae8f1afedc</t>
+  </si>
+  <si>
+    <t>07/07/2026 4:35:06 PM</t>
+  </si>
+  <si>
+    <t>22970</t>
+  </si>
+  <si>
+    <t>MEYERS, DAVID</t>
+  </si>
+  <si>
+    <t>Air Temperature, Local</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, Aurora, CO, 80249</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453eb8-7e69-5014-bdb1-0ed5f2065eef</t>
+  </si>
+  <si>
+    <t>07/06/2026 5:07:40 PM</t>
   </si>
   <si>
     <t>24632</t>
@@ -71,19 +149,133 @@
     <t>EMERY.SHANE</t>
   </si>
   <si>
-    <t>OTR</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Mark</t>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>Needles Freeway, 48.5 mi WSW Bullhead City, San Bernardino County, CA</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544539af-f461-5213-aa21-f2664e51af29</t>
+  </si>
+  <si>
+    <t>07/06/2026 3:04:58 PM</t>
+  </si>
+  <si>
+    <t>24685</t>
+  </si>
+  <si>
+    <t>CLARK, KC</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>I 80, 11.7 mi W Princeton, Bureau County, IL, 61379</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445393f-9c90-50e3-b895-54e342a4ed28</t>
+  </si>
+  <si>
+    <t>07/06/2026 11:54:43 AM</t>
+  </si>
+  <si>
+    <t>24907</t>
+  </si>
+  <si>
+    <t>WELCH, GREGORY</t>
+  </si>
+  <si>
+    <t>World War I Veterans Memorial Highway, Springer, OK, 73458</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453891-6f8a-5395-8201-f189bc3d1a3e</t>
+  </si>
+  <si>
+    <t>07/05/2026 5:34:14 PM</t>
+  </si>
+  <si>
+    <t>24634</t>
+  </si>
+  <si>
+    <t>KELLY GNEITING</t>
+  </si>
+  <si>
+    <t>Purple Heart Trail, Williams, AZ</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544534a1-eabf-5ac5-aafe-d8a722491db1</t>
+  </si>
+  <si>
+    <t>07/05/2026 9:38:36 AM</t>
+  </si>
+  <si>
+    <t>24682</t>
+  </si>
+  <si>
+    <t>FOUNTAIN, RODNEY</t>
+  </si>
+  <si>
+    <t>Air Temperature, OTR</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Construction, Congested</t>
+  </si>
+  <si>
+    <t>Hubbell Avenue, Altoona, IA, 50009</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544532ee-749c-538e-8a7f-06680e19ed37</t>
+  </si>
+  <si>
+    <t>07/03/2026 12:10:42 PM</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, Del Camino, CO, 80542</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445292d-0052-54c8-87db-4a5b25b78cdd</t>
+  </si>
+  <si>
+    <t>07/03/2026 10:57:21 AM</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>I 35, Sanger, TX, 76266</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544528e9-d84f-5e24-ad4d-484ac97b8507</t>
+  </si>
+  <si>
+    <t>07/02/2026 11:41:50 AM</t>
   </si>
   <si>
     <t>Kansas Turnpike, Kanwaka Township, KS, 66050</t>
@@ -92,22 +284,10 @@
     <t>69</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523ec-334c-59c8-a435-37794192dcb9</t>
   </si>
   <si>
-    <t>06/30/2026 3:08:17 PM</t>
-  </si>
-  <si>
-    <t>24685</t>
-  </si>
-  <si>
-    <t>CLARK, KC</t>
-  </si>
-  <si>
-    <t>Coached</t>
+    <t>06/30/2026 2:08:17 PM</t>
   </si>
   <si>
     <t>I 80, Atkinson, IL, 61235</t>
@@ -119,7 +299,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451a25-8fb7-5efa-ac37-9c7b24307909</t>
   </si>
   <si>
-    <t>06/29/2026 5:02:30 PM</t>
+    <t>06/29/2026 4:02:30 PM</t>
   </si>
   <si>
     <t>I 80, 9.9 mi E Kearney, Buffalo County, NE</t>
@@ -128,16 +308,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451567-c803-56db-afc8-aa1c5ff3ce4d</t>
   </si>
   <si>
-    <t>06/29/2026 4:46:11 PM</t>
-  </si>
-  <si>
-    <t>22970</t>
-  </si>
-  <si>
-    <t>MEYERS, DAVID</t>
-  </si>
-  <si>
-    <t>Air Temperature, Local</t>
+    <t>06/29/2026 3:46:11 PM</t>
   </si>
   <si>
     <t>I 70, Wheat Ridge, CO, 80033</t>
@@ -149,25 +320,16 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451558-d5df-54c5-8319-aa414ec15dac</t>
   </si>
   <si>
-    <t>06/27/2026 11:52:56 AM</t>
-  </si>
-  <si>
-    <t>24907</t>
-  </si>
-  <si>
-    <t>WELCH, GREGORY</t>
+    <t>06/27/2026 10:52:56 AM</t>
   </si>
   <si>
     <t>I 80, Bear Creek Township, IA, 50157</t>
   </si>
   <si>
-    <t>72</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544509ff-a5f8-55a2-a14f-40bf1544bdb5</t>
   </si>
   <si>
-    <t>06/27/2026 11:42:51 AM</t>
+    <t>06/27/2026 10:42:51 AM</t>
   </si>
   <si>
     <t>23470</t>
@@ -179,28 +341,22 @@
     <t>OTR, Safety Pro Test</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>Gerald R. Ford Memorial Highway, Vail, CO, 81657</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544509f6-6a21-5547-9e61-cc365dd360f8</t>
   </si>
   <si>
-    <t>06/26/2026 2:42:28 PM</t>
+    <t>06/26/2026 1:42:28 PM</t>
   </si>
   <si>
     <t>Tuskegee Airmen Memorial Highway, Aurora, CO, 80249</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450574-7e46-54fd-89a6-eee01ccfa2db</t>
   </si>
   <si>
-    <t>06/26/2026 2:10:46 PM</t>
+    <t>06/26/2026 1:10:46 PM</t>
   </si>
   <si>
     <t>Ronald Reagan Highway, Monument, CO, 80132</t>
@@ -209,7 +365,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450557-7a36-5c2e-a107-fb21f46f8087</t>
   </si>
   <si>
-    <t>06/26/2026 1:33:31 PM</t>
+    <t>06/26/2026 12:33:31 PM</t>
   </si>
   <si>
     <t>24680</t>
@@ -221,13 +377,10 @@
     <t>I 70, Silt, CO, 81652</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450535-5cd5-5807-9216-0138d48a41de</t>
   </si>
   <si>
-    <t>06/26/2026 10:51:52 AM</t>
+    <t>06/26/2026 9:51:52 AM</t>
   </si>
   <si>
     <t>24911</t>
@@ -236,19 +389,13 @@
     <t>GARCIA, FRANCISCO</t>
   </si>
   <si>
-    <t>Air Temperature, OTR</t>
-  </si>
-  <si>
     <t>I 70;US 40, El Rancho, CO, 80453</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544504a1-6199-5868-9ed0-6b81d3c5532f</t>
   </si>
   <si>
-    <t>06/25/2026 11:22:39 PM</t>
+    <t>06/25/2026 10:22:39 PM</t>
   </si>
   <si>
     <t>Congested, Night</t>
@@ -260,7 +407,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445022a-627d-5d91-bc76-f4fb85e1b796</t>
   </si>
   <si>
-    <t>06/25/2026 1:38:37 PM</t>
+    <t>06/25/2026 12:38:37 PM</t>
   </si>
   <si>
     <t>I 70, 13.5 mi SE Vail, Summit County, CO</t>
@@ -269,7 +416,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450013-ad6a-5d83-a658-ae2aa66529ba</t>
   </si>
   <si>
-    <t>06/25/2026 11:29:51 AM</t>
+    <t>06/25/2026 10:29:51 AM</t>
   </si>
   <si>
     <t>22975</t>
@@ -290,7 +437,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff9d-cbdd-5880-a2e5-2df47c0ccd42</t>
   </si>
   <si>
-    <t>06/24/2026 5:10:48 PM</t>
+    <t>06/24/2026 4:10:48 PM</t>
   </si>
   <si>
     <t>Veterans Memorial Highway, Washington, UT, 84780</t>
@@ -299,7 +446,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbaf-956b-5521-86c8-e1ad024b6b32</t>
   </si>
   <si>
-    <t>06/24/2026 4:03:42 PM</t>
+    <t>06/24/2026 3:03:42 PM</t>
   </si>
   <si>
     <t>Kansas Turnpike, 2.9 mi NW Bonner Springs, Leavenworth County, KS</t>
@@ -311,7 +458,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fb72-2783-52f2-abb8-751588740a55</t>
   </si>
   <si>
-    <t>06/24/2026 5:11:55 AM</t>
+    <t>06/24/2026 4:11:55 AM</t>
   </si>
   <si>
     <t>22024</t>
@@ -329,7 +476,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f91d-6d8c-56fe-ae71-2bda4a20d15b</t>
   </si>
   <si>
-    <t>06/23/2026 5:11:29 PM</t>
+    <t>06/23/2026 4:11:29 PM</t>
   </si>
   <si>
     <t>24630</t>
@@ -341,13 +488,10 @@
     <t>US 287;US 385;CR 26, 53.0 mi S Lamar, Baca County, CO</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f689-d886-5060-a059-d716ac401798</t>
   </si>
   <si>
-    <t>06/22/2026 4:29:35 PM</t>
+    <t>06/22/2026 3:29:35 PM</t>
   </si>
   <si>
     <t>Construction, Moderate Traffic</t>
@@ -359,7 +503,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f13d-20f8-5ec3-8c9c-422c511a22a2</t>
   </si>
   <si>
-    <t>06/22/2026 1:33:02 PM</t>
+    <t>06/22/2026 12:33:02 PM</t>
   </si>
   <si>
     <t>Ronald Reagan Memorial Tollway, Malta Township, IL, 60113</t>
@@ -371,7 +515,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f09b-7c59-5088-b251-90ee7e4b87f2</t>
   </si>
   <si>
-    <t>06/22/2026 12:51:06 PM</t>
+    <t>06/22/2026 11:51:06 AM</t>
   </si>
   <si>
     <t>24677</t>
@@ -383,13 +527,10 @@
     <t>Kansas Turnpike, 10.7 mi S Wellington, Sumner County, KS</t>
   </si>
   <si>
-    <t>68</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f075-1a4c-515b-a225-207386df00d7</t>
   </si>
   <si>
-    <t>06/21/2026 2:38:22 PM</t>
+    <t>06/21/2026 1:38:22 PM</t>
   </si>
   <si>
     <t>I 80, Gretna, NE</t>
@@ -398,7 +539,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ebb0-f15e-5d59-b9a9-f35c7dd40f0e</t>
   </si>
   <si>
-    <t>06/21/2026 1:24:01 PM</t>
+    <t>06/21/2026 12:24:01 PM</t>
   </si>
   <si>
     <t>I 80, Knox, NE</t>
@@ -407,7 +548,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445eb6c-e148-53dd-8c1e-72d7d77a9ed7</t>
   </si>
   <si>
-    <t>06/20/2026 12:26:55 PM</t>
+    <t>06/20/2026 11:26:55 AM</t>
   </si>
   <si>
     <t>23467</t>
@@ -419,13 +560,10 @@
     <t>I 35W, Alvarado, TX, 76007</t>
   </si>
   <si>
-    <t>66</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e612-3bdb-5540-a91a-7a681ddd407e</t>
   </si>
   <si>
-    <t>06/19/2026 6:06:53 PM</t>
+    <t>06/19/2026 5:06:53 PM</t>
   </si>
   <si>
     <t>World War I Veterans Memorial Highway, Ardmore, OK, 73401</t>
@@ -437,7 +575,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e223-1f6b-51c2-9f70-aa656bc9b47b</t>
   </si>
   <si>
-    <t>06/19/2026 5:32:27 PM</t>
+    <t>06/19/2026 4:32:27 PM</t>
   </si>
   <si>
     <t>24690</t>
@@ -455,7 +593,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e203-9a5a-5c9b-90ec-204789b29201</t>
   </si>
   <si>
-    <t>06/19/2026 10:12:30 AM</t>
+    <t>06/19/2026 9:12:30 AM</t>
   </si>
   <si>
     <t>Dwight D. Eisenhower Highway, Erie, CO, 80514</t>
@@ -464,7 +602,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e070-d0ae-5996-bafd-079887fbd3c9</t>
   </si>
   <si>
-    <t>06/18/2026 12:45:10 PM</t>
+    <t>06/18/2026 11:45:10 AM</t>
   </si>
   <si>
     <t>Dwight D. Eisenhower Highway, 44.6 mi E The Pinery, Elbert County, CO</t>
@@ -476,7 +614,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dbd6-3af7-524c-87f3-6e56bdb0f8b4</t>
   </si>
   <si>
-    <t>06/18/2026 11:35:17 AM</t>
+    <t>06/18/2026 10:35:17 AM</t>
   </si>
   <si>
     <t>KS 156, 30.5 mi NE Great Bend, Ellsworth County, KS</t>
@@ -485,7 +623,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445db96-3efe-5994-964b-1a1194aab183</t>
   </si>
   <si>
-    <t>06/17/2026 3:18:01 PM</t>
+    <t>06/17/2026 2:18:01 PM</t>
   </si>
   <si>
     <t>I 40, Los Pinos, NM</t>
@@ -497,7 +635,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d73b-cd21-58a1-a5c5-b4a294014f75</t>
   </si>
   <si>
-    <t>06/17/2026 1:24:24 PM</t>
+    <t>06/17/2026 12:24:24 PM</t>
   </si>
   <si>
     <t>Purple Heart Trail, 20.7 mi ENE Holbrook, Apache County, AZ</t>
@@ -506,7 +644,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d6d3-c962-50ff-9b41-3d746ff61c92</t>
   </si>
   <si>
-    <t>06/17/2026 9:51:05 AM</t>
+    <t>06/17/2026 8:51:05 AM</t>
   </si>
   <si>
     <t>North Collins Freeway, Howe, TX, 75459</t>
@@ -515,7 +653,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d610-7f77-5f72-81b1-c4694de011c7</t>
   </si>
   <si>
-    <t>06/14/2026 12:51:39 PM</t>
+    <t>06/14/2026 11:51:39 AM</t>
   </si>
   <si>
     <t>24688</t>
@@ -533,7 +671,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c742-bb80-57f3-bbb2-56768c9b226e</t>
   </si>
   <si>
-    <t>06/13/2026 12:37:03 PM</t>
+    <t>06/13/2026 11:37:03 AM</t>
   </si>
   <si>
     <t>23473</t>
@@ -545,13 +683,13 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c20f-014b-5409-87c5-e43d0cc0efd9</t>
   </si>
   <si>
-    <t>06/12/2026 6:47:19 PM</t>
+    <t>06/12/2026 5:47:19 PM</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445be3b-9f80-5fd9-a6cf-dbf18fac6d9d</t>
   </si>
   <si>
-    <t>06/12/2026 2:22:37 PM</t>
+    <t>06/12/2026 1:22:37 PM</t>
   </si>
   <si>
     <t>Heartland Expressway, Hazeltine Heights, CO, 80640</t>
@@ -560,19 +698,16 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bd49-499d-5743-adbe-6302dd74cc86</t>
   </si>
   <si>
-    <t>06/12/2026 10:50:38 AM</t>
+    <t>06/12/2026 9:50:38 AM</t>
   </si>
   <si>
     <t>I 70, Dumont, CO, 80436</t>
   </si>
   <si>
-    <t>73</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc87-36b4-5f55-82c0-3ec307c4646f</t>
   </si>
   <si>
-    <t>06/11/2026 5:29:52 PM</t>
+    <t>06/11/2026 4:29:52 PM</t>
   </si>
   <si>
     <t>Truman/Eisenhower Presidential Highway, 7.0 mi ENE Abilene, Dickinson County, KS, 67431</t>
@@ -584,7 +719,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b8ce-5cde-5f34-8fd0-70906359417e</t>
   </si>
   <si>
-    <t>06/11/2026 3:42:27 PM</t>
+    <t>06/11/2026 2:42:27 PM</t>
   </si>
   <si>
     <t>24910</t>
@@ -599,7 +734,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b86c-03c6-5709-b3fc-9e16d1d9a452</t>
   </si>
   <si>
-    <t>06/11/2026 10:57:37 AM</t>
+    <t>06/11/2026 9:57:37 AM</t>
   </si>
   <si>
     <t>Las Vegas Freeway, Moapa, NV</t>
@@ -608,10 +743,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b767-3eca-56ce-bec5-a899a8fc9176</t>
   </si>
   <si>
-    <t>06/10/2026 8:47:02 PM</t>
-  </si>
-  <si>
-    <t>Construction, Congested</t>
+    <t>06/10/2026 7:47:02 PM</t>
   </si>
   <si>
     <t>59</t>
@@ -620,7 +752,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b45c-834c-5c1d-8c85-58bf1f78108e</t>
   </si>
   <si>
-    <t>06/10/2026 2:34:29 PM</t>
+    <t>06/10/2026 1:34:29 PM</t>
   </si>
   <si>
     <t>I 80, 4.4 mi SSE Lexington, Dawson County, NE</t>
@@ -629,13 +761,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b307-6f9f-5d8d-b567-89a04243da8c</t>
   </si>
   <si>
-    <t>06/10/2026 9:58:07 AM</t>
-  </si>
-  <si>
-    <t>24634</t>
-  </si>
-  <si>
-    <t>KELLY GNEITING</t>
+    <t>06/10/2026 8:58:07 AM</t>
   </si>
   <si>
     <t>Purple Heart Trail, 22.1 mi NW Zuni Pueblo, Apache County, AZ</t>
@@ -644,7 +770,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b20a-6a3c-5987-953d-06052c8a1179</t>
   </si>
   <si>
-    <t>06/09/2026 8:49:37 PM</t>
+    <t>06/09/2026 7:49:37 PM</t>
   </si>
   <si>
     <t>24679</t>
@@ -659,7 +785,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445af38-854c-5719-9503-413e384e10a8</t>
   </si>
   <si>
-    <t>06/09/2026 5:15:37 PM</t>
+    <t>06/09/2026 4:15:37 PM</t>
   </si>
   <si>
     <t>Barstow and Mojave Freeway, 11.2 mi SW Barstow Heights, San Bernardino County, CA</t>
@@ -668,13 +794,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ae74-984f-5ea2-b3cb-4dcbc89dece1</t>
   </si>
   <si>
-    <t>06/09/2026 9:52:33 AM</t>
-  </si>
-  <si>
-    <t>23466</t>
-  </si>
-  <si>
-    <t>NUNEZ, WALLY</t>
+    <t>06/09/2026 8:52:33 AM</t>
   </si>
   <si>
     <t>I 25;US 85;US 87, Cheyenne, WY, 82005</t>
@@ -683,13 +803,13 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445acde-f735-5191-a0fd-09c6dcc5a30e</t>
   </si>
   <si>
-    <t>06/09/2026 6:09:33 AM</t>
+    <t>06/09/2026 5:09:33 AM</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ac12-c9e2-538b-b316-68bf086b39de</t>
   </si>
   <si>
-    <t>06/08/2026 10:24:03 AM</t>
+    <t>06/08/2026 9:24:03 AM</t>
   </si>
   <si>
     <t>Heartland Expressway, Brighton, CO</t>
@@ -698,7 +818,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a7d5-6f9b-5d1d-a439-54ff28a6a7b6</t>
   </si>
   <si>
-    <t>06/08/2026 6:36:45 AM</t>
+    <t>06/08/2026 5:36:45 AM</t>
   </si>
   <si>
     <t>I 40, McCartys, NM</t>
@@ -707,7 +827,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a705-5620-5e1a-94db-d10e3064fa7f</t>
   </si>
   <si>
-    <t>06/07/2026 10:34:55 PM</t>
+    <t>06/07/2026 9:34:55 PM</t>
   </si>
   <si>
     <t>22003</t>
@@ -722,7 +842,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a54c-3401-54fc-bc7f-7505d81ed801</t>
   </si>
   <si>
-    <t>06/05/2026 3:56:56 PM</t>
+    <t>06/05/2026 2:56:56 PM</t>
   </si>
   <si>
     <t>Las Vegas Freeway, North Las Vegas, NV, 89030</t>
@@ -731,13 +851,13 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459993-1faf-53df-8570-11c11b6ea9e0</t>
   </si>
   <si>
-    <t>06/03/2026 5:14:46 PM</t>
+    <t>06/03/2026 4:14:46 PM</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f8d-abd6-5146-8bb1-64bec70d67ff</t>
   </si>
   <si>
-    <t>06/03/2026 3:43:38 PM</t>
+    <t>06/03/2026 2:43:38 PM</t>
   </si>
   <si>
     <t>US Highway 287, Washburn, TX</t>
@@ -746,7 +866,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f3a-39c4-5099-b36c-20f6bb3436bb</t>
   </si>
   <si>
-    <t>06/03/2026 5:35:42 AM</t>
+    <t>06/03/2026 4:35:42 AM</t>
   </si>
   <si>
     <t>Tuskegee Airmen Memorial Highway, Denver, CO, 80238</t>
@@ -758,7 +878,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458d0d-a730-5e11-9d43-47e13c31e947</t>
   </si>
   <si>
-    <t>06/02/2026 1:11:41 PM</t>
+    <t>06/02/2026 12:11:41 PM</t>
   </si>
   <si>
     <t>Barstow and Mojave Freeway, 20.0 mi SE Fort Irwin, San Bernardino County, CA</t>
@@ -767,16 +887,13 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458988-c24f-5239-8b2f-6ed4002c3d47</t>
   </si>
   <si>
-    <t>06/01/2026 1:21:17 PM</t>
-  </si>
-  <si>
-    <t>Purple Heart Trail, Williams, AZ</t>
+    <t>06/01/2026 12:21:17 PM</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445846b-2f9b-504c-a5e2-746dc3eb184b</t>
   </si>
   <si>
-    <t>06/01/2026 1:03:09 PM</t>
+    <t>06/01/2026 12:03:09 PM</t>
   </si>
   <si>
     <t>I 70, Wheeler Junction, CO</t>
@@ -785,7 +902,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445845a-93f3-5a28-8c8f-4d792daac76a</t>
   </si>
   <si>
-    <t>06/01/2026 8:29:16 AM</t>
+    <t>06/01/2026 7:29:16 AM</t>
   </si>
   <si>
     <t>Truman/Eisenhower Presidential Highway, 12.3 mi SE Manhattan, Riley County, KS</t>
@@ -794,7 +911,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445835f-d7b4-5879-807e-486a45440275</t>
   </si>
   <si>
-    <t>05/31/2026 12:04:28 PM</t>
+    <t>05/31/2026 11:04:28 AM</t>
   </si>
   <si>
     <t>Dwight D. Eisenhower Highway, 83.4 mi N Lamar, Kit Carson County, CO</t>
@@ -806,7 +923,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457efe-7fb9-5272-9be1-1033b1429e83</t>
   </si>
   <si>
-    <t>05/30/2026 11:04:14 AM</t>
+    <t>05/30/2026 10:04:14 AM</t>
   </si>
   <si>
     <t>Las Vegas Freeway, 14.4 mi WSW Moapa Valley, Clark County, NV</t>
@@ -815,7 +932,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544579a0-ffd5-53f5-ad38-1bb699bee121</t>
   </si>
   <si>
-    <t>05/29/2026 4:52:36 PM</t>
+    <t>05/29/2026 3:52:36 PM</t>
   </si>
   <si>
     <t>I 70, 6.4 mi NNW Evergreen, Jefferson County, CO</t>
@@ -824,7 +941,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544575b9-92fc-55ef-a898-fa27588be6bb</t>
   </si>
   <si>
-    <t>05/29/2026 11:37:37 AM</t>
+    <t>05/29/2026 10:37:37 AM</t>
   </si>
   <si>
     <t>Las Vegas Freeway, 17.2 mi NE Sunrise Manor, Clark County, NV</t>
@@ -833,7 +950,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457499-31c1-5502-bd12-77ecc94be916</t>
   </si>
   <si>
-    <t>05/28/2026 12:12:12 PM</t>
+    <t>05/28/2026 11:12:12 AM</t>
   </si>
   <si>
     <t>I 215, Riverside, CA, 93507</t>
@@ -842,7 +959,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456f92-7fde-51e0-88a7-c63bcd50ad87</t>
   </si>
   <si>
-    <t>05/27/2026 4:38:39 PM</t>
+    <t>05/27/2026 3:38:39 PM</t>
   </si>
   <si>
     <t>23471</t>
@@ -854,7 +971,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b60-14f9-5a48-9d21-698da447b93c</t>
   </si>
   <si>
-    <t>05/27/2026 11:08:19 AM</t>
+    <t>05/27/2026 10:08:19 AM</t>
   </si>
   <si>
     <t>Las Vegas Freeway, North Las Vegas, NV, 89165</t>
@@ -863,16 +980,13 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a31-a5a8-5e7e-b93a-9a5ca0fa096a</t>
   </si>
   <si>
-    <t>05/26/2026 3:34:06 PM</t>
+    <t>05/26/2026 2:34:06 PM</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544565fe-a10f-5965-a302-83a8e3584b11</t>
   </si>
   <si>
-    <t>05/26/2026 3:20:19 PM</t>
-  </si>
-  <si>
-    <t>Harsh Brake</t>
+    <t>05/26/2026 2:20:19 PM</t>
   </si>
   <si>
     <t>Riverside Freeway, Anaheim, CA, 92817</t>
@@ -887,7 +1001,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544565f2-020f-5dd3-a972-2e172d1dd4b2</t>
   </si>
   <si>
-    <t>05/25/2026 5:35:28 PM</t>
+    <t>05/25/2026 4:35:28 PM</t>
   </si>
   <si>
     <t>Needles Freeway, 19.9 mi NW Lake Havasu City, San Bernardino County, CA, 92363</t>
@@ -896,7 +1010,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456147-62b9-5147-8973-5d0101640dd4</t>
   </si>
   <si>
-    <t>05/25/2026 11:15:21 AM</t>
+    <t>05/25/2026 10:15:21 AM</t>
   </si>
   <si>
     <t>Veterans Memorial Highway, 15.6 mi SSW Santa Clara, Mohave County, AZ</t>
@@ -905,7 +1019,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455feb-5f71-5eba-be9e-a36e01923dc2</t>
   </si>
   <si>
-    <t>05/24/2026 9:35:31 AM</t>
+    <t>05/24/2026 8:35:31 AM</t>
   </si>
   <si>
     <t>4490 I 70;US 6, Georgetown, CO, 80452</t>
@@ -914,7 +1028,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455a69-9c9f-597a-a394-68472b8c2b7f</t>
   </si>
   <si>
-    <t>05/22/2026 3:18:28 PM</t>
+    <t>05/22/2026 2:18:28 PM</t>
   </si>
   <si>
     <t>Gerald R. Ford Memorial Highway, Gypsum, CO, 81637</t>
@@ -923,7 +1037,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455156-dfad-56b2-9565-910122a51df4</t>
   </si>
   <si>
-    <t>05/21/2026 1:03:45 PM</t>
+    <t>05/21/2026 12:03:45 PM</t>
   </si>
   <si>
     <t>Kansas Turnpike, 1.9 mi NE Lawrence, Douglas County, KS, 66044:66046</t>
@@ -932,7 +1046,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454bb5-2fc4-5f6a-b062-ed0090cd46cf</t>
   </si>
   <si>
-    <t>05/20/2026 12:39:26 PM</t>
+    <t>05/20/2026 11:39:26 AM</t>
   </si>
   <si>
     <t>I 40, 12.9 mi ESE Grants, Cibola County, NM, 87034</t>
@@ -941,7 +1055,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454678-8fe2-5166-907f-e0171d3ee957</t>
   </si>
   <si>
-    <t>05/20/2026 12:22:51 PM</t>
+    <t>05/20/2026 11:22:51 AM</t>
   </si>
   <si>
     <t>Ronald Reagan Memorial Tollway, Rochelle, IL, 61068</t>
@@ -950,7 +1064,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454669-5ff6-5e11-9def-17d3817067d6</t>
   </si>
   <si>
-    <t>05/19/2026 5:24:24 PM</t>
+    <t>05/19/2026 4:24:24 PM</t>
   </si>
   <si>
     <t>Purple Heart Trail, Topock, AZ</t>
@@ -959,7 +1073,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454257-18f4-5d8e-bc12-4db87a4e6828</t>
   </si>
   <si>
-    <t>05/19/2026 4:15:44 PM</t>
+    <t>05/19/2026 3:15:44 PM</t>
   </si>
   <si>
     <t>I 35, Civil Bend, MO, 64689</t>
@@ -968,7 +1082,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454218-3996-5ecc-9726-38e156929605</t>
   </si>
   <si>
-    <t>05/19/2026 1:29:17 PM</t>
+    <t>05/19/2026 12:29:17 PM</t>
   </si>
   <si>
     <t>I 15, Parowan, UT, 87620</t>
@@ -977,7 +1091,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445417f-d7ec-5217-b7c9-34ad4a4a01ac</t>
   </si>
   <si>
-    <t>05/18/2026 6:17:08 PM</t>
+    <t>05/18/2026 5:17:08 PM</t>
   </si>
   <si>
     <t>I 70;US 6, Frisco, CO, 80443</t>
@@ -986,7 +1100,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453d61-015a-5d73-ac9b-53f98002fc26</t>
   </si>
   <si>
-    <t>05/18/2026 1:57:44 PM</t>
+    <t>05/18/2026 12:57:44 PM</t>
   </si>
   <si>
     <t>Purple Heart Trail, Flagstaff, AZ</t>
@@ -995,7 +1109,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453c73-853c-5119-8b53-27f347efb4ef</t>
   </si>
   <si>
-    <t>05/18/2026 11:03:11 AM</t>
+    <t>05/18/2026 10:03:11 AM</t>
   </si>
   <si>
     <t>I 80, Oxford Township, IA, 52241</t>
@@ -1004,7 +1118,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453bd3-b79c-5f26-b2a7-eaeef6583a43</t>
   </si>
   <si>
-    <t>05/17/2026 10:01:54 AM</t>
+    <t>05/17/2026 9:01:54 AM</t>
   </si>
   <si>
     <t>I 80, 10.7 mi S Harlan, Pottawattamie County, IA, 51521</t>
@@ -1013,7 +1127,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453675-3f65-5b3a-ad6e-d665322bf9df</t>
   </si>
   <si>
-    <t>05/15/2026 4:10:22 PM</t>
+    <t>05/15/2026 3:10:22 PM</t>
   </si>
   <si>
     <t>I 25, Colorado Springs, CO, 80906</t>
@@ -1022,7 +1136,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452d79-df18-50bb-b4e3-cb346e3190f8</t>
   </si>
   <si>
-    <t>05/15/2026 3:06:50 PM</t>
+    <t>05/15/2026 2:06:50 PM</t>
   </si>
   <si>
     <t>I 25, Lone Tree, CO, 80124-5644</t>
@@ -1031,10 +1145,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452d3f-b507-5257-8f90-7e0209dca3e8</t>
   </si>
   <si>
-    <t>05/14/2026 12:52:19 PM</t>
-  </si>
-  <si>
-    <t>Construction, Light Traffic</t>
+    <t>05/14/2026 11:52:19 AM</t>
   </si>
   <si>
     <t>I 70;US 40, 4.0 mi ENE Abilene, Dickinson County, KS, 67410</t>
@@ -1043,7 +1154,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445279e-33c2-5ec6-9e89-ce4902fbac77</t>
   </si>
   <si>
-    <t>05/14/2026 12:37:30 PM</t>
+    <t>05/14/2026 11:37:30 AM</t>
   </si>
   <si>
     <t>I 10, 7.9 mi W Benson, Cochise County, AZ</t>
@@ -1052,7 +1163,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452790-a126-5449-9239-ef6570957a47</t>
   </si>
   <si>
-    <t>05/13/2026 4:43:40 PM</t>
+    <t>05/13/2026 3:43:40 PM</t>
   </si>
   <si>
     <t>I 40, Vegas Junction, NM, 87070</t>
@@ -1061,7 +1172,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445234b-a412-5bb6-a4f4-fbe4e6a7330d</t>
   </si>
   <si>
-    <t>05/12/2026 4:07:28 PM</t>
+    <t>05/12/2026 3:07:28 PM</t>
   </si>
   <si>
     <t>I 40, El Rito, NM</t>
@@ -1070,7 +1181,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451e04-2587-5d71-ad6c-5da28bd73eec</t>
   </si>
   <si>
-    <t>05/08/2026 7:06:40 PM</t>
+    <t>05/08/2026 6:06:40 PM</t>
   </si>
   <si>
     <t>I 70, Aurora, CO, 80011-3316</t>
@@ -1079,7 +1190,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450a0e-c4f9-544c-8750-50b4e0cfb115</t>
   </si>
   <si>
-    <t>05/08/2026 9:30:54 AM</t>
+    <t>05/08/2026 8:30:54 AM</t>
   </si>
   <si>
     <t>I 25, Fort Collins, CO, 80525-9717</t>
@@ -1088,7 +1199,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544507ff-a179-57a1-9258-f152ca06ecd0</t>
   </si>
   <si>
-    <t>05/07/2026 4:20:38 PM</t>
+    <t>05/07/2026 3:20:38 PM</t>
   </si>
   <si>
     <t>Veterans Memorial Highway, 14.6 mi SSW Santa Clara, Mohave County, AZ</t>
@@ -1097,7 +1208,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450450-668e-501f-b53e-f7416cd8b6e4</t>
   </si>
   <si>
-    <t>05/07/2026 12:45:01 PM</t>
+    <t>05/07/2026 11:45:01 AM</t>
   </si>
   <si>
     <t>I 40, Twin Buttes, NM, 87395</t>
@@ -1106,7 +1217,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445038b-00e7-5778-93eb-88bcde2a585e</t>
   </si>
   <si>
-    <t>05/06/2026 6:42:51 PM</t>
+    <t>05/06/2026 5:42:51 PM</t>
   </si>
   <si>
     <t>I 15, 34.9 mi NE Enoch, Beaver County, UT</t>
@@ -1115,7 +1226,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ffac-3db7-5839-b640-dce43216519f</t>
   </si>
   <si>
-    <t>05/05/2026 7:41:30 PM</t>
+    <t>05/05/2026 6:41:30 PM</t>
   </si>
   <si>
     <t>I 10, Loma Linda, CA, 92408-3539</t>
@@ -1124,7 +1235,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fabb-9539-57e9-8686-c4f946e17ab4</t>
   </si>
   <si>
-    <t>05/05/2026 10:41:30 AM</t>
+    <t>05/05/2026 9:41:30 AM</t>
   </si>
   <si>
     <t>Wet Road, Light Traffic</t>
@@ -1136,7 +1247,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f8cd-32b7-528f-a054-5d6358165a0f</t>
   </si>
   <si>
-    <t>05/04/2026 7:31:45 PM</t>
+    <t>05/04/2026 6:31:45 PM</t>
   </si>
   <si>
     <t>Needles Freeway, 55.6 mi NE Twentynine Palms, San Bernardino County, CA</t>
@@ -1145,13 +1256,13 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f58c-4c3a-51a3-acab-596b803976de</t>
   </si>
   <si>
-    <t>05/04/2026 4:03:39 PM</t>
+    <t>05/04/2026 3:03:39 PM</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f4cd-c56d-52f7-a540-ad03bdd02aa1</t>
   </si>
   <si>
-    <t>05/04/2026 10:49:56 AM</t>
+    <t>05/04/2026 9:49:56 AM</t>
   </si>
   <si>
     <t>I 40, 17.5 mi WSW Gallup, McKinley County, NM, 86308</t>
@@ -1160,7 +1271,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f3ae-8ef0-529b-ab32-2f61959df938</t>
   </si>
   <si>
-    <t>05/01/2026 3:30:32 PM</t>
+    <t>05/01/2026 2:30:32 PM</t>
   </si>
   <si>
     <t>I 76;US 6, Brighton, CO, 80603</t>
@@ -1169,19 +1280,16 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e53c-60b7-52e7-86f6-6a7a256bccf4</t>
   </si>
   <si>
-    <t>04/30/2026 7:58:15 PM</t>
+    <t>04/30/2026 6:58:15 PM</t>
   </si>
   <si>
     <t>I 270, 1.2 mi WNW Commerce City, Adams County, CO, 80216-8470</t>
   </si>
   <si>
-    <t>61</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e10b-1cd3-5112-9e9d-8e8d27c598fa</t>
   </si>
   <si>
-    <t>04/29/2026 12:10:42 PM</t>
+    <t>04/29/2026 11:10:42 AM</t>
   </si>
   <si>
     <t>I 29;US 71, Platte City, MO, 64079</t>
@@ -1190,7 +1298,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445da38-b36e-5ab0-9baa-e65c7fa22c32</t>
   </si>
   <si>
-    <t>04/29/2026 12:03:52 PM</t>
+    <t>04/29/2026 11:03:52 AM</t>
   </si>
   <si>
     <t>I 29;US 71, 12.1 mi WNW Smithville, Platte County, MO, 64439</t>
@@ -1199,7 +1307,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445da32-7327-5863-82f2-e383366061d4</t>
   </si>
   <si>
-    <t>04/29/2026 8:44:21 AM</t>
+    <t>04/29/2026 7:44:21 AM</t>
   </si>
   <si>
     <t>I 55;I 72;US 36, Springfield, IL, 62723</t>
@@ -1208,7 +1316,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d97b-ca3a-50ae-8332-d1d4ea1258ee</t>
   </si>
   <si>
-    <t>04/29/2026 7:16:29 AM</t>
+    <t>04/29/2026 6:16:29 AM</t>
   </si>
   <si>
     <t>22986</t>
@@ -1223,7 +1331,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d92b-5897-570f-952f-7d2bd666df23</t>
   </si>
   <si>
-    <t>04/29/2026 6:20:37 AM</t>
+    <t>04/29/2026 5:20:37 AM</t>
   </si>
   <si>
     <t>Purple Heart Trail, 32.6 mi NNW Paulden, Yavapai County, AZ</t>
@@ -1232,7 +1340,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d8f8-320e-5681-aa04-c25c096a973b</t>
   </si>
   <si>
-    <t>04/28/2026 2:53:58 PM</t>
+    <t>04/28/2026 1:53:58 PM</t>
   </si>
   <si>
     <t>Congested</t>
@@ -1244,7 +1352,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d5a7-d00f-5d34-8310-726e6e361f4b</t>
   </si>
   <si>
-    <t>04/28/2026 2:11:26 PM</t>
+    <t>04/28/2026 1:11:26 PM</t>
   </si>
   <si>
     <t>South Valley Highway, Lone Tree, CO, 80124</t>
@@ -1253,7 +1361,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d580-e0a6-51e3-ba43-9cd5ff7c2ef7</t>
   </si>
   <si>
-    <t>04/28/2026 11:23:10 AM</t>
+    <t>04/28/2026 10:23:10 AM</t>
   </si>
   <si>
     <t>Las Vegas Freeway (Heavy Traffic Route), Jean, NV, 89026</t>
@@ -1262,13 +1370,13 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d4e6-d38c-5cb8-b153-5bd390c64204</t>
   </si>
   <si>
-    <t>04/27/2026 1:48:35 PM</t>
+    <t>04/27/2026 12:48:35 PM</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d045-9983-5475-9ca4-258c86e3f735</t>
   </si>
   <si>
-    <t>04/27/2026 12:09:18 AM</t>
+    <t>04/26/2026 11:09:18 PM</t>
   </si>
   <si>
     <t>Moderate Traffic, Night</t>
@@ -1280,7 +1388,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cd57-84f6-5e38-ae80-a22349115905</t>
   </si>
   <si>
-    <t>04/25/2026 5:57:05 PM</t>
+    <t>04/25/2026 4:57:05 PM</t>
   </si>
   <si>
     <t>I 80, North Platte, NE, 69101</t>
@@ -1289,7 +1397,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c6dc-638a-524f-b746-bf315fc11210</t>
   </si>
   <si>
-    <t>04/25/2026 1:09:23 PM</t>
+    <t>04/25/2026 12:09:23 PM</t>
   </si>
   <si>
     <t>I 70, 76.0 mi SSE Brush, Kit Carson County, CO</t>
@@ -1298,7 +1406,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c5d4-ff08-5054-abb7-05b009fa997c</t>
   </si>
   <si>
-    <t>04/24/2026 6:41:49 PM</t>
+    <t>04/24/2026 5:41:49 PM</t>
   </si>
   <si>
     <t>I 70, 24.6 mi E Aurora, Arapahoe County, CO, 80136</t>
@@ -1307,7 +1415,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c1de-fb9e-5bc6-a5b0-80b2cd385fbe</t>
   </si>
   <si>
-    <t>04/23/2026 3:01:20 PM</t>
+    <t>04/23/2026 2:01:20 PM</t>
   </si>
   <si>
     <t>I 80, 7.2 mi S Grand Island, Hamilton County, NE, 68832</t>
@@ -1316,7 +1424,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbee-c514-5121-a85c-da6b03457f61</t>
   </si>
   <si>
-    <t>04/23/2026 2:30:37 PM</t>
+    <t>04/23/2026 1:30:37 PM</t>
   </si>
   <si>
     <t>I 15, 9.4 mi SW Cedar City, Iron County, UT, 84742</t>
@@ -1325,7 +1433,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbd2-a715-5fe6-9ae9-89b567065f03</t>
   </si>
   <si>
-    <t>04/23/2026 1:00:05 PM</t>
+    <t>04/23/2026 12:00:05 PM</t>
   </si>
   <si>
     <t>20420</t>
@@ -1337,7 +1445,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bb7f-c24a-5ddd-a623-ea59ed2a3d54</t>
   </si>
   <si>
-    <t>04/21/2026 9:38:37 PM</t>
+    <t>04/21/2026 8:38:37 PM</t>
   </si>
   <si>
     <t>Needles Freeway, 18.0 mi ESE Barstow, San Bernardino County, CA</t>
@@ -1346,7 +1454,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b30d-c561-5368-aa61-41c66d664b77</t>
   </si>
   <si>
-    <t>04/21/2026 4:01:15 PM</t>
+    <t>04/21/2026 3:01:15 PM</t>
   </si>
   <si>
     <t>Mojave Freeway, 43.4 mi SSW Enterprise, San Bernardino County, CA</t>
@@ -1355,7 +1463,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b1d8-e640-5974-91c2-e547c8e09850</t>
   </si>
   <si>
-    <t>04/20/2026 5:32:39 PM</t>
+    <t>04/20/2026 4:32:39 PM</t>
   </si>
   <si>
     <t>Needles Freeway, 53.5 mi NE Twentynine Palms, San Bernardino County, CA</t>
@@ -1364,7 +1472,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ad06-38a7-50b3-b5c5-69248d4d182e</t>
   </si>
   <si>
-    <t>04/20/2026 5:06:22 PM</t>
+    <t>04/20/2026 4:06:22 PM</t>
   </si>
   <si>
     <t>I 70, Grand Junction, CO, 81505</t>
@@ -1373,7 +1481,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445acee-2a9f-5336-b268-b2e48aa3a5e0</t>
   </si>
   <si>
-    <t>04/20/2026 12:57:18 PM</t>
+    <t>04/20/2026 11:57:18 AM</t>
   </si>
   <si>
     <t>I 25, Fountain, CO, 80907</t>
@@ -1382,7 +1490,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ac0a-226d-53c8-9a69-cf0c004a78e2</t>
   </si>
   <si>
-    <t>04/18/2026 6:15:26 PM</t>
+    <t>04/18/2026 5:15:26 PM</t>
   </si>
   <si>
     <t>I 80, 7.5 mi SSW Grand Island, Hall County, NE, 68839</t>
@@ -1391,7 +1499,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a2e0-ae88-51ac-873f-dd004d77f5ba</t>
   </si>
   <si>
-    <t>04/17/2026 1:18:32 PM</t>
+    <t>04/17/2026 12:18:32 PM</t>
   </si>
   <si>
     <t>Purple Heart Trail, Allentown, AZ, 86506</t>
@@ -1400,7 +1508,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459caa-7e11-5f75-ac96-82a2e62b721a</t>
   </si>
   <si>
-    <t>04/17/2026 12:36:30 PM</t>
+    <t>04/17/2026 11:36:30 AM</t>
   </si>
   <si>
     <t>Harsh Brake, Defensive Driving</t>
@@ -1421,7 +1529,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459c84-0180-5154-8268-0357ebbcd7bd</t>
   </si>
   <si>
-    <t>04/16/2026 3:50:16 PM</t>
+    <t>04/16/2026 2:50:16 PM</t>
   </si>
   <si>
     <t>I 70, Rhone, CO, 81521</t>
@@ -1430,7 +1538,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445980f-0c29-598f-adef-d4897dc0754e</t>
   </si>
   <si>
-    <t>04/15/2026 11:28:05 PM</t>
+    <t>04/15/2026 10:28:05 PM</t>
   </si>
   <si>
     <t>Construction, Congested, Night</t>
@@ -1442,13 +1550,13 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445948b-d4e5-570d-a292-d7620cbbd82b</t>
   </si>
   <si>
-    <t>04/15/2026 4:55:37 PM</t>
+    <t>04/15/2026 3:55:37 PM</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459324-859d-598b-99dd-2fa21af4e465</t>
   </si>
   <si>
-    <t>04/15/2026 3:28:22 PM</t>
+    <t>04/15/2026 2:28:22 PM</t>
   </si>
   <si>
     <t>I 70, 5.5 mi E Aurora, Arapahoe County, CO, 80019</t>
@@ -1457,7 +1565,7 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544592d4-a52a-5c6d-879c-e7c89c2424cb</t>
   </si>
   <si>
-    <t>04/15/2026 1:30:53 PM</t>
+    <t>04/15/2026 12:30:53 PM</t>
   </si>
   <si>
     <t>I 70;US 6, Rulison, CO</t>
@@ -1466,67 +1574,13 @@
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459269-146e-52a1-9868-7e6a0f624e0b</t>
   </si>
   <si>
-    <t>04/14/2026 2:24:59 PM</t>
+    <t>04/14/2026 1:24:59 PM</t>
   </si>
   <si>
     <t>Las Vegas Freeway, Glendale, NV</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458d74-4142-5a64-9ea6-83999fbe0a60</t>
-  </si>
-  <si>
-    <t>04/09/2026 4:35:03 PM</t>
-  </si>
-  <si>
-    <t>24689</t>
-  </si>
-  <si>
-    <t>JONATHON BENNET</t>
-  </si>
-  <si>
-    <t>I 95, Pooler, GA, 31407</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445742b-89c2-5394-88dd-6f32d5d37e49</t>
-  </si>
-  <si>
-    <t>04/09/2026 1:08:52 PM</t>
-  </si>
-  <si>
-    <t>Veterans Memorial Highway, Beaver Dam, AZ, 86432</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445736e-c3d5-5be8-8125-3480e38e0d6b</t>
-  </si>
-  <si>
-    <t>04/07/2026 3:51:08 PM</t>
-  </si>
-  <si>
-    <t>Mojave Freeway, Baker, CA, 92309</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544569b6-9ab2-5ff4-8110-155771c8edb6</t>
-  </si>
-  <si>
-    <t>04/07/2026 2:58:08 PM</t>
-  </si>
-  <si>
-    <t>5822 Palmer Park Boulevard, Cimarron Hills, CO, 80915</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456986-182d-55ec-945e-86ad202f030e</t>
-  </si>
-  <si>
-    <t>04/06/2026 3:34:04 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456480-a09c-50c6-97ae-2be992fb4bac</t>
   </si>
 </sst>
 </file>
@@ -1903,7 +1957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O134"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -2014,19 +2068,19 @@
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
         <v>30</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
       </c>
       <c r="J3" t="s">
         <v>31</v>
@@ -2052,13 +2106,13 @@
         <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -2070,16 +2124,16 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L4" t="s">
         <v>25</v>
@@ -2091,21 +2145,21 @@
         <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -2117,16 +2171,16 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L5" t="s">
         <v>25</v>
@@ -2138,18 +2192,18 @@
         <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -2161,19 +2215,19 @@
         <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L6" t="s">
         <v>25</v>
@@ -2185,21 +2239,21 @@
         <v>25</v>
       </c>
       <c r="O6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -2208,19 +2262,19 @@
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L7" t="s">
         <v>25</v>
@@ -2232,24 +2286,24 @@
         <v>25</v>
       </c>
       <c r="O7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
         <v>19</v>
@@ -2258,16 +2312,16 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L8" t="s">
         <v>25</v>
@@ -2279,42 +2333,42 @@
         <v>25</v>
       </c>
       <c r="O8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>25</v>
@@ -2323,21 +2377,21 @@
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="O9" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -2349,19 +2403,19 @@
         <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
       </c>
       <c r="J10" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s">
         <v>25</v>
@@ -2373,21 +2427,21 @@
         <v>25</v>
       </c>
       <c r="O10" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -2396,19 +2450,19 @@
         <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
       </c>
       <c r="J11" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K11" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L11" t="s">
         <v>25</v>
@@ -2420,21 +2474,21 @@
         <v>25</v>
       </c>
       <c r="O11" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
@@ -2443,19 +2497,19 @@
         <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="L12" t="s">
         <v>25</v>
@@ -2467,18 +2521,18 @@
         <v>25</v>
       </c>
       <c r="O12" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -2490,19 +2544,19 @@
         <v>19</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s">
         <v>25</v>
@@ -2514,21 +2568,21 @@
         <v>25</v>
       </c>
       <c r="O13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -2540,16 +2594,16 @@
         <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L14" t="s">
         <v>25</v>
@@ -2561,21 +2615,21 @@
         <v>25</v>
       </c>
       <c r="O14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -2587,16 +2641,16 @@
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K15" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="L15" t="s">
         <v>25</v>
@@ -2608,18 +2662,18 @@
         <v>25</v>
       </c>
       <c r="O15" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -2631,19 +2685,19 @@
         <v>19</v>
       </c>
       <c r="G16" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L16" t="s">
         <v>25</v>
@@ -2655,21 +2709,21 @@
         <v>25</v>
       </c>
       <c r="O16" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
@@ -2678,19 +2732,19 @@
         <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="L17" t="s">
         <v>25</v>
@@ -2702,42 +2756,42 @@
         <v>25</v>
       </c>
       <c r="O17" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
         <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K18" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="L18" t="s">
         <v>25</v>
@@ -2749,21 +2803,21 @@
         <v>25</v>
       </c>
       <c r="O18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
@@ -2772,19 +2826,19 @@
         <v>19</v>
       </c>
       <c r="G19" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K19" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L19" t="s">
         <v>25</v>
@@ -2796,18 +2850,18 @@
         <v>25</v>
       </c>
       <c r="O19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -2819,19 +2873,19 @@
         <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K20" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="L20" t="s">
         <v>25</v>
@@ -2843,24 +2897,24 @@
         <v>25</v>
       </c>
       <c r="O20" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
         <v>19</v>
@@ -2869,16 +2923,16 @@
         <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
       </c>
       <c r="J21" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K21" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="L21" t="s">
         <v>25</v>
@@ -2890,21 +2944,21 @@
         <v>25</v>
       </c>
       <c r="O21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
@@ -2913,19 +2967,19 @@
         <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K22" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="L22" t="s">
         <v>25</v>
@@ -2937,18 +2991,18 @@
         <v>25</v>
       </c>
       <c r="O22" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -2963,16 +3017,16 @@
         <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L23" t="s">
         <v>25</v>
@@ -2984,21 +3038,21 @@
         <v>25</v>
       </c>
       <c r="O23" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="E24" t="s">
         <v>18</v>
@@ -3010,16 +3064,16 @@
         <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L24" t="s">
         <v>25</v>
@@ -3031,24 +3085,24 @@
         <v>25</v>
       </c>
       <c r="O24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -3057,16 +3111,16 @@
         <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
       </c>
       <c r="J25" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K25" t="s">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="L25" t="s">
         <v>25</v>
@@ -3078,18 +3132,18 @@
         <v>25</v>
       </c>
       <c r="O25" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -3101,10 +3155,10 @@
         <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -3113,7 +3167,7 @@
         <v>144</v>
       </c>
       <c r="K26" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="L26" t="s">
         <v>25</v>
@@ -3125,21 +3179,21 @@
         <v>25</v>
       </c>
       <c r="O26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
         <v>18</v>
@@ -3148,19 +3202,19 @@
         <v>19</v>
       </c>
       <c r="G27" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="H27" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
       </c>
       <c r="J27" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K27" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="L27" t="s">
         <v>25</v>
@@ -3172,42 +3226,42 @@
         <v>25</v>
       </c>
       <c r="O27" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
       </c>
       <c r="G28" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="K28" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="L28" t="s">
         <v>25</v>
@@ -3219,21 +3273,21 @@
         <v>25</v>
       </c>
       <c r="O28" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E29" t="s">
         <v>18</v>
@@ -3242,19 +3296,19 @@
         <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="H29" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="K29" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="L29" t="s">
         <v>25</v>
@@ -3266,18 +3320,18 @@
         <v>25</v>
       </c>
       <c r="O29" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -3292,16 +3346,16 @@
         <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="K30" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="L30" t="s">
         <v>25</v>
@@ -3313,21 +3367,21 @@
         <v>25</v>
       </c>
       <c r="O30" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E31" t="s">
         <v>25</v>
@@ -3339,16 +3393,16 @@
         <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I31" t="s">
         <v>22</v>
       </c>
       <c r="J31" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="K31" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="L31" t="s">
         <v>25</v>
@@ -3360,21 +3414,21 @@
         <v>25</v>
       </c>
       <c r="O31" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E32" t="s">
         <v>18</v>
@@ -3383,20 +3437,20 @@
         <v>19</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
       </c>
       <c r="J32" t="s">
+        <v>172</v>
+      </c>
+      <c r="K32" t="s">
         <v>164</v>
       </c>
-      <c r="K32" t="s">
-        <v>122</v>
-      </c>
       <c r="L32" t="s">
         <v>25</v>
       </c>
@@ -3407,21 +3461,21 @@
         <v>25</v>
       </c>
       <c r="O32" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
         <v>18</v>
@@ -3433,16 +3487,16 @@
         <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="K33" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="L33" t="s">
         <v>25</v>
@@ -3454,18 +3508,18 @@
         <v>25</v>
       </c>
       <c r="O33" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>179</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -3477,19 +3531,19 @@
         <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="K34" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="L34" t="s">
         <v>25</v>
@@ -3501,24 +3555,24 @@
         <v>25</v>
       </c>
       <c r="O34" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -3527,16 +3581,16 @@
         <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
       </c>
       <c r="J35" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="K35" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="L35" t="s">
         <v>25</v>
@@ -3548,18 +3602,18 @@
         <v>25</v>
       </c>
       <c r="O35" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>187</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -3571,19 +3625,19 @@
         <v>19</v>
       </c>
       <c r="G36" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I36" t="s">
         <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="K36" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="L36" t="s">
         <v>25</v>
@@ -3595,21 +3649,21 @@
         <v>25</v>
       </c>
       <c r="O36" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E37" t="s">
         <v>18</v>
@@ -3618,19 +3672,19 @@
         <v>19</v>
       </c>
       <c r="G37" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I37" t="s">
         <v>22</v>
       </c>
       <c r="J37" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K37" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="L37" t="s">
         <v>25</v>
@@ -3642,21 +3696,21 @@
         <v>25</v>
       </c>
       <c r="O37" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="E38" t="s">
         <v>18</v>
@@ -3665,19 +3719,19 @@
         <v>19</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I38" t="s">
         <v>22</v>
       </c>
       <c r="J38" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K38" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="L38" t="s">
         <v>25</v>
@@ -3689,21 +3743,21 @@
         <v>25</v>
       </c>
       <c r="O38" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
         <v>18</v>
@@ -3712,19 +3766,19 @@
         <v>19</v>
       </c>
       <c r="G39" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
       </c>
       <c r="J39" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="K39" t="s">
-        <v>187</v>
+        <v>53</v>
       </c>
       <c r="L39" t="s">
         <v>25</v>
@@ -3736,21 +3790,21 @@
         <v>25</v>
       </c>
       <c r="O39" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
         <v>18</v>
@@ -3762,16 +3816,16 @@
         <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I40" t="s">
         <v>22</v>
       </c>
       <c r="J40" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="K40" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="L40" t="s">
         <v>25</v>
@@ -3783,42 +3837,42 @@
         <v>25</v>
       </c>
       <c r="O40" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
         <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I41" t="s">
         <v>22</v>
       </c>
       <c r="J41" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="K41" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="L41" t="s">
         <v>25</v>
@@ -3830,21 +3884,21 @@
         <v>25</v>
       </c>
       <c r="O41" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B42" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="E42" t="s">
         <v>18</v>
@@ -3853,19 +3907,19 @@
         <v>19</v>
       </c>
       <c r="G42" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I42" t="s">
         <v>22</v>
       </c>
       <c r="J42" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="K42" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="L42" t="s">
         <v>25</v>
@@ -3877,42 +3931,42 @@
         <v>25</v>
       </c>
       <c r="O42" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B43" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C43" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E43" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F43" t="s">
         <v>19</v>
       </c>
       <c r="G43" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I43" t="s">
         <v>22</v>
       </c>
       <c r="J43" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="K43" t="s">
-        <v>116</v>
+        <v>216</v>
       </c>
       <c r="L43" t="s">
         <v>25</v>
@@ -3924,21 +3978,21 @@
         <v>25</v>
       </c>
       <c r="O43" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C44" t="s">
-        <v>211</v>
+        <v>57</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
         <v>18</v>
@@ -3947,19 +4001,19 @@
         <v>19</v>
       </c>
       <c r="G44" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I44" t="s">
         <v>22</v>
       </c>
       <c r="J44" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="K44" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="L44" t="s">
         <v>25</v>
@@ -3971,21 +4025,21 @@
         <v>25</v>
       </c>
       <c r="O44" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E45" t="s">
         <v>18</v>
@@ -3994,19 +4048,19 @@
         <v>19</v>
       </c>
       <c r="G45" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I45" t="s">
         <v>22</v>
       </c>
       <c r="J45" t="s">
-        <v>215</v>
+        <v>98</v>
       </c>
       <c r="K45" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="L45" t="s">
         <v>25</v>
@@ -4018,42 +4072,42 @@
         <v>25</v>
       </c>
       <c r="O45" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s">
-        <v>218</v>
+        <v>42</v>
       </c>
       <c r="C46" t="s">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F46" t="s">
         <v>19</v>
       </c>
       <c r="G46" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H46" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I46" t="s">
         <v>22</v>
       </c>
       <c r="J46" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K46" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="L46" t="s">
         <v>25</v>
@@ -4065,21 +4119,21 @@
         <v>25</v>
       </c>
       <c r="O46" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E47" t="s">
         <v>18</v>
@@ -4088,19 +4142,19 @@
         <v>19</v>
       </c>
       <c r="G47" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I47" t="s">
         <v>22</v>
       </c>
       <c r="J47" t="s">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="K47" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="L47" t="s">
         <v>25</v>
@@ -4112,21 +4166,21 @@
         <v>25</v>
       </c>
       <c r="O47" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>213</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>214</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E48" t="s">
         <v>18</v>
@@ -4138,16 +4192,16 @@
         <v>20</v>
       </c>
       <c r="H48" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I48" t="s">
         <v>22</v>
       </c>
       <c r="J48" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K48" t="s">
-        <v>116</v>
+        <v>232</v>
       </c>
       <c r="L48" t="s">
         <v>25</v>
@@ -4159,21 +4213,21 @@
         <v>25</v>
       </c>
       <c r="O48" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>235</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>236</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E49" t="s">
         <v>18</v>
@@ -4185,16 +4239,16 @@
         <v>20</v>
       </c>
       <c r="H49" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I49" t="s">
         <v>22</v>
       </c>
       <c r="J49" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="K49" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="L49" t="s">
         <v>25</v>
@@ -4206,21 +4260,21 @@
         <v>25</v>
       </c>
       <c r="O49" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B50" t="s">
-        <v>231</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="E50" t="s">
         <v>18</v>
@@ -4232,16 +4286,16 @@
         <v>20</v>
       </c>
       <c r="H50" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I50" t="s">
         <v>22</v>
       </c>
       <c r="J50" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="K50" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="L50" t="s">
         <v>25</v>
@@ -4253,21 +4307,21 @@
         <v>25</v>
       </c>
       <c r="O50" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D51" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E51" t="s">
         <v>18</v>
@@ -4276,19 +4330,19 @@
         <v>19</v>
       </c>
       <c r="G51" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H51" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I51" t="s">
         <v>22</v>
       </c>
       <c r="J51" t="s">
-        <v>236</v>
+        <v>128</v>
       </c>
       <c r="K51" t="s">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="L51" t="s">
         <v>25</v>
@@ -4300,43 +4354,43 @@
         <v>25</v>
       </c>
       <c r="O51" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>219</v>
       </c>
       <c r="C52" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H52" t="s">
+        <v>44</v>
+      </c>
+      <c r="I52" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" t="s">
+        <v>246</v>
+      </c>
+      <c r="K52" t="s">
         <v>39</v>
       </c>
-      <c r="D52" t="s">
-        <v>40</v>
-      </c>
-      <c r="E52" t="s">
-        <v>18</v>
-      </c>
-      <c r="F52" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" t="s">
-        <v>20</v>
-      </c>
-      <c r="H52" t="s">
-        <v>30</v>
-      </c>
-      <c r="I52" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" t="s">
-        <v>112</v>
-      </c>
-      <c r="K52" t="s">
-        <v>75</v>
-      </c>
       <c r="L52" t="s">
         <v>25</v>
       </c>
@@ -4347,42 +4401,42 @@
         <v>25</v>
       </c>
       <c r="O52" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B53" t="s">
-        <v>190</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>191</v>
+        <v>63</v>
       </c>
       <c r="D53" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F53" t="s">
         <v>19</v>
       </c>
       <c r="G53" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I53" t="s">
         <v>22</v>
       </c>
       <c r="J53" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="K53" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="L53" t="s">
         <v>25</v>
@@ -4394,21 +4448,21 @@
         <v>25</v>
       </c>
       <c r="O53" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B54" t="s">
-        <v>167</v>
+        <v>252</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>253</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E54" t="s">
         <v>18</v>
@@ -4417,19 +4471,19 @@
         <v>19</v>
       </c>
       <c r="G54" t="s">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I54" t="s">
         <v>22</v>
       </c>
       <c r="J54" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="K54" t="s">
-        <v>245</v>
+        <v>164</v>
       </c>
       <c r="L54" t="s">
         <v>25</v>
@@ -4441,21 +4495,21 @@
         <v>25</v>
       </c>
       <c r="O54" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="C55" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D55" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E55" t="s">
         <v>18</v>
@@ -4464,19 +4518,19 @@
         <v>19</v>
       </c>
       <c r="G55" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I55" t="s">
         <v>22</v>
       </c>
       <c r="J55" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="K55" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="L55" t="s">
         <v>25</v>
@@ -4488,42 +4542,42 @@
         <v>25</v>
       </c>
       <c r="O55" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F56" t="s">
         <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I56" t="s">
         <v>22</v>
       </c>
       <c r="J56" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="K56" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="L56" t="s">
         <v>25</v>
@@ -4535,21 +4589,21 @@
         <v>25</v>
       </c>
       <c r="O56" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B57" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E57" t="s">
         <v>18</v>
@@ -4561,16 +4615,16 @@
         <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I57" t="s">
         <v>22</v>
       </c>
       <c r="J57" t="s">
-        <v>254</v>
+        <v>111</v>
       </c>
       <c r="K57" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="L57" t="s">
         <v>25</v>
@@ -4582,42 +4636,42 @@
         <v>25</v>
       </c>
       <c r="O57" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E58" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F58" t="s">
         <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I58" t="s">
         <v>22</v>
       </c>
       <c r="J58" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="K58" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="L58" t="s">
         <v>25</v>
@@ -4629,42 +4683,42 @@
         <v>25</v>
       </c>
       <c r="O58" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="C59" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="D59" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E59" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F59" t="s">
         <v>19</v>
       </c>
       <c r="G59" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I59" t="s">
         <v>22</v>
       </c>
       <c r="J59" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="K59" t="s">
-        <v>261</v>
+        <v>24</v>
       </c>
       <c r="L59" t="s">
         <v>25</v>
@@ -4676,21 +4730,21 @@
         <v>25</v>
       </c>
       <c r="O59" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="C60" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="D60" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
@@ -4699,19 +4753,19 @@
         <v>19</v>
       </c>
       <c r="G60" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H60" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I60" t="s">
         <v>22</v>
       </c>
       <c r="J60" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="K60" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="L60" t="s">
         <v>25</v>
@@ -4723,21 +4777,21 @@
         <v>25</v>
       </c>
       <c r="O60" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B61" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
@@ -4746,19 +4800,19 @@
         <v>19</v>
       </c>
       <c r="G61" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H61" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I61" t="s">
         <v>22</v>
       </c>
       <c r="J61" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="K61" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="L61" t="s">
         <v>25</v>
@@ -4770,21 +4824,21 @@
         <v>25</v>
       </c>
       <c r="O61" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>35</v>
       </c>
       <c r="C62" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
@@ -4793,19 +4847,19 @@
         <v>19</v>
       </c>
       <c r="G62" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H62" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I62" t="s">
         <v>22</v>
       </c>
       <c r="J62" t="s">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="K62" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L62" t="s">
         <v>25</v>
@@ -4817,21 +4871,21 @@
         <v>25</v>
       </c>
       <c r="O62" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B63" t="s">
-        <v>51</v>
+        <v>235</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>236</v>
       </c>
       <c r="D63" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E63" t="s">
         <v>18</v>
@@ -4840,19 +4894,19 @@
         <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="H63" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I63" t="s">
         <v>22</v>
       </c>
       <c r="J63" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="K63" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="L63" t="s">
         <v>25</v>
@@ -4864,21 +4918,21 @@
         <v>25</v>
       </c>
       <c r="O63" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B64" t="s">
-        <v>276</v>
+        <v>213</v>
       </c>
       <c r="C64" t="s">
-        <v>277</v>
+        <v>214</v>
       </c>
       <c r="D64" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E64" t="s">
         <v>18</v>
@@ -4890,16 +4944,16 @@
         <v>20</v>
       </c>
       <c r="H64" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I64" t="s">
         <v>22</v>
       </c>
       <c r="J64" t="s">
-        <v>102</v>
+        <v>284</v>
       </c>
       <c r="K64" t="s">
-        <v>75</v>
+        <v>285</v>
       </c>
       <c r="L64" t="s">
         <v>25</v>
@@ -4911,21 +4965,21 @@
         <v>25</v>
       </c>
       <c r="O64" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B65" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D65" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
@@ -4934,19 +4988,19 @@
         <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H65" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I65" t="s">
         <v>22</v>
       </c>
       <c r="J65" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="K65" t="s">
-        <v>68</v>
+        <v>243</v>
       </c>
       <c r="L65" t="s">
         <v>25</v>
@@ -4958,21 +5012,21 @@
         <v>25</v>
       </c>
       <c r="O65" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D66" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E66" t="s">
         <v>18</v>
@@ -4981,19 +5035,19 @@
         <v>19</v>
       </c>
       <c r="G66" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I66" t="s">
         <v>22</v>
       </c>
       <c r="J66" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K66" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="L66" t="s">
         <v>25</v>
@@ -5005,42 +5059,42 @@
         <v>25</v>
       </c>
       <c r="O66" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B67" t="s">
-        <v>231</v>
+        <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="D67" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="E67" t="s">
         <v>18</v>
       </c>
       <c r="F67" t="s">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="G67" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="H67" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I67" t="s">
         <v>22</v>
       </c>
       <c r="J67" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="K67" t="s">
-        <v>287</v>
+        <v>24</v>
       </c>
       <c r="L67" t="s">
         <v>25</v>
@@ -5049,45 +5103,45 @@
         <v>25</v>
       </c>
       <c r="N67" t="s">
-        <v>288</v>
+        <v>25</v>
       </c>
       <c r="O67" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B68" t="s">
-        <v>16</v>
+        <v>167</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>168</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E68" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F68" t="s">
         <v>19</v>
       </c>
       <c r="G68" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I68" t="s">
         <v>22</v>
       </c>
       <c r="J68" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K68" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="L68" t="s">
         <v>25</v>
@@ -5099,12 +5153,12 @@
         <v>25</v>
       </c>
       <c r="O68" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B69" t="s">
         <v>167</v>
@@ -5113,28 +5167,28 @@
         <v>168</v>
       </c>
       <c r="D69" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E69" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F69" t="s">
         <v>19</v>
       </c>
       <c r="G69" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I69" t="s">
         <v>22</v>
       </c>
       <c r="J69" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K69" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="L69" t="s">
         <v>25</v>
@@ -5146,21 +5200,21 @@
         <v>25</v>
       </c>
       <c r="O69" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>252</v>
       </c>
       <c r="C70" t="s">
-        <v>168</v>
+        <v>253</v>
       </c>
       <c r="D70" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E70" t="s">
         <v>18</v>
@@ -5169,19 +5223,19 @@
         <v>19</v>
       </c>
       <c r="G70" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I70" t="s">
         <v>22</v>
       </c>
       <c r="J70" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="K70" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="L70" t="s">
         <v>25</v>
@@ -5193,21 +5247,21 @@
         <v>25</v>
       </c>
       <c r="O70" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="C71" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="D71" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="E71" t="s">
         <v>18</v>
@@ -5216,19 +5270,19 @@
         <v>19</v>
       </c>
       <c r="G71" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I71" t="s">
         <v>22</v>
       </c>
       <c r="J71" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="K71" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L71" t="s">
         <v>25</v>
@@ -5240,21 +5294,21 @@
         <v>25</v>
       </c>
       <c r="O71" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>213</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>214</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E72" t="s">
         <v>18</v>
@@ -5263,19 +5317,19 @@
         <v>19</v>
       </c>
       <c r="G72" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I72" t="s">
         <v>22</v>
       </c>
       <c r="J72" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="K72" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L72" t="s">
         <v>25</v>
@@ -5287,21 +5341,21 @@
         <v>25</v>
       </c>
       <c r="O72" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B73" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="D73" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="E73" t="s">
         <v>18</v>
@@ -5310,19 +5364,19 @@
         <v>19</v>
       </c>
       <c r="G73" t="s">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="H73" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I73" t="s">
         <v>22</v>
       </c>
       <c r="J73" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="K73" t="s">
-        <v>170</v>
+        <v>79</v>
       </c>
       <c r="L73" t="s">
         <v>25</v>
@@ -5334,42 +5388,42 @@
         <v>25</v>
       </c>
       <c r="O73" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B74" t="s">
-        <v>119</v>
+        <v>315</v>
       </c>
       <c r="C74" t="s">
-        <v>120</v>
+        <v>316</v>
       </c>
       <c r="D74" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E74" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F74" t="s">
         <v>19</v>
       </c>
       <c r="G74" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H74" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I74" t="s">
         <v>22</v>
       </c>
       <c r="J74" t="s">
-        <v>309</v>
+        <v>151</v>
       </c>
       <c r="K74" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="L74" t="s">
         <v>25</v>
@@ -5381,21 +5435,21 @@
         <v>25</v>
       </c>
       <c r="O74" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="D75" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="E75" t="s">
         <v>18</v>
@@ -5404,19 +5458,19 @@
         <v>19</v>
       </c>
       <c r="G75" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H75" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I75" t="s">
         <v>22</v>
       </c>
       <c r="J75" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="K75" t="s">
-        <v>187</v>
+        <v>46</v>
       </c>
       <c r="L75" t="s">
         <v>25</v>
@@ -5428,21 +5482,21 @@
         <v>25</v>
       </c>
       <c r="O75" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B76" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="C76" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
@@ -5451,19 +5505,19 @@
         <v>19</v>
       </c>
       <c r="G76" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H76" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I76" t="s">
         <v>22</v>
       </c>
       <c r="J76" t="s">
-        <v>315</v>
+        <v>119</v>
       </c>
       <c r="K76" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="L76" t="s">
         <v>25</v>
@@ -5475,42 +5529,42 @@
         <v>25</v>
       </c>
       <c r="O76" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B77" t="s">
-        <v>51</v>
+        <v>271</v>
       </c>
       <c r="C77" t="s">
-        <v>52</v>
+        <v>272</v>
       </c>
       <c r="D77" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E77" t="s">
         <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="G77" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="H77" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I77" t="s">
         <v>22</v>
       </c>
       <c r="J77" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="K77" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="L77" t="s">
         <v>25</v>
@@ -5519,24 +5573,24 @@
         <v>25</v>
       </c>
       <c r="N77" t="s">
-        <v>25</v>
+        <v>326</v>
       </c>
       <c r="O77" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B78" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C78" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D78" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
         <v>18</v>
@@ -5545,19 +5599,19 @@
         <v>19</v>
       </c>
       <c r="G78" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I78" t="s">
         <v>22</v>
       </c>
       <c r="J78" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="K78" t="s">
-        <v>138</v>
+        <v>204</v>
       </c>
       <c r="L78" t="s">
         <v>25</v>
@@ -5569,21 +5623,21 @@
         <v>25</v>
       </c>
       <c r="O78" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B79" t="s">
-        <v>16</v>
+        <v>213</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>214</v>
       </c>
       <c r="D79" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E79" t="s">
         <v>18</v>
@@ -5592,19 +5646,19 @@
         <v>19</v>
       </c>
       <c r="G79" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H79" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I79" t="s">
         <v>22</v>
       </c>
       <c r="J79" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="K79" t="s">
-        <v>68</v>
+        <v>204</v>
       </c>
       <c r="L79" t="s">
         <v>25</v>
@@ -5616,42 +5670,42 @@
         <v>25</v>
       </c>
       <c r="O79" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B80" t="s">
-        <v>119</v>
+        <v>213</v>
       </c>
       <c r="C80" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="D80" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E80" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F80" t="s">
         <v>19</v>
       </c>
       <c r="G80" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H80" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I80" t="s">
         <v>22</v>
       </c>
       <c r="J80" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="K80" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="L80" t="s">
         <v>25</v>
@@ -5663,21 +5717,21 @@
         <v>25</v>
       </c>
       <c r="O80" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B81" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="C81" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="D81" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E81" t="s">
         <v>18</v>
@@ -5686,19 +5740,19 @@
         <v>19</v>
       </c>
       <c r="G81" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H81" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I81" t="s">
         <v>22</v>
       </c>
       <c r="J81" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="K81" t="s">
-        <v>187</v>
+        <v>53</v>
       </c>
       <c r="L81" t="s">
         <v>25</v>
@@ -5710,21 +5764,21 @@
         <v>25</v>
       </c>
       <c r="O81" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B82" t="s">
-        <v>276</v>
+        <v>42</v>
       </c>
       <c r="C82" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
       <c r="D82" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
         <v>18</v>
@@ -5736,16 +5790,16 @@
         <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I82" t="s">
         <v>22</v>
       </c>
       <c r="J82" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="K82" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="L82" t="s">
         <v>25</v>
@@ -5757,21 +5811,21 @@
         <v>25</v>
       </c>
       <c r="O82" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B83" t="s">
-        <v>276</v>
+        <v>42</v>
       </c>
       <c r="C83" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
       <c r="D83" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E83" t="s">
         <v>18</v>
@@ -5783,16 +5837,16 @@
         <v>20</v>
       </c>
       <c r="H83" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I83" t="s">
         <v>22</v>
       </c>
       <c r="J83" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="K83" t="s">
-        <v>89</v>
+        <v>216</v>
       </c>
       <c r="L83" t="s">
         <v>25</v>
@@ -5804,42 +5858,42 @@
         <v>25</v>
       </c>
       <c r="O83" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>167</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>168</v>
       </c>
       <c r="D84" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E84" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
         <v>19</v>
       </c>
       <c r="G84" t="s">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I84" t="s">
         <v>22</v>
       </c>
       <c r="J84" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="K84" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="L84" t="s">
         <v>25</v>
@@ -5851,21 +5905,21 @@
         <v>25</v>
       </c>
       <c r="O84" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B85" t="s">
-        <v>210</v>
+        <v>42</v>
       </c>
       <c r="C85" t="s">
-        <v>211</v>
+        <v>43</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E85" t="s">
         <v>18</v>
@@ -5874,19 +5928,19 @@
         <v>19</v>
       </c>
       <c r="G85" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H85" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I85" t="s">
         <v>22</v>
       </c>
       <c r="J85" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="K85" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="L85" t="s">
         <v>25</v>
@@ -5898,21 +5952,21 @@
         <v>25</v>
       </c>
       <c r="O85" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>214</v>
       </c>
       <c r="D86" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E86" t="s">
         <v>18</v>
@@ -5921,19 +5975,19 @@
         <v>19</v>
       </c>
       <c r="G86" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I86" t="s">
         <v>22</v>
       </c>
       <c r="J86" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K86" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="L86" t="s">
         <v>25</v>
@@ -5945,42 +5999,42 @@
         <v>25</v>
       </c>
       <c r="O86" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B87" t="s">
-        <v>205</v>
+        <v>105</v>
       </c>
       <c r="C87" t="s">
-        <v>206</v>
+        <v>106</v>
       </c>
       <c r="D87" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="E87" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F87" t="s">
         <v>19</v>
       </c>
       <c r="G87" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I87" t="s">
         <v>22</v>
       </c>
       <c r="J87" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="K87" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="L87" t="s">
         <v>25</v>
@@ -5992,21 +6046,21 @@
         <v>25</v>
       </c>
       <c r="O87" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B88" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C88" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="D88" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="E88" t="s">
         <v>18</v>
@@ -6015,19 +6069,19 @@
         <v>19</v>
       </c>
       <c r="G88" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I88" t="s">
         <v>22</v>
       </c>
       <c r="J88" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K88" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="L88" t="s">
         <v>25</v>
@@ -6039,21 +6093,21 @@
         <v>25</v>
       </c>
       <c r="O88" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B89" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C89" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D89" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E89" t="s">
         <v>18</v>
@@ -6065,16 +6119,16 @@
         <v>20</v>
       </c>
       <c r="H89" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I89" t="s">
         <v>22</v>
       </c>
       <c r="J89" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="K89" t="s">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="L89" t="s">
         <v>25</v>
@@ -6086,42 +6140,42 @@
         <v>25</v>
       </c>
       <c r="O89" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B90" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C90" t="s">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E90" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
       </c>
       <c r="G90" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H90" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I90" t="s">
         <v>22</v>
       </c>
       <c r="J90" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="K90" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="L90" t="s">
         <v>25</v>
@@ -6133,21 +6187,21 @@
         <v>25</v>
       </c>
       <c r="O90" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B91" t="s">
-        <v>276</v>
+        <v>213</v>
       </c>
       <c r="C91" t="s">
-        <v>277</v>
+        <v>214</v>
       </c>
       <c r="D91" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E91" t="s">
         <v>18</v>
@@ -6156,19 +6210,19 @@
         <v>19</v>
       </c>
       <c r="G91" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I91" t="s">
         <v>22</v>
       </c>
       <c r="J91" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="K91" t="s">
-        <v>187</v>
+        <v>232</v>
       </c>
       <c r="L91" t="s">
         <v>25</v>
@@ -6180,21 +6234,21 @@
         <v>25</v>
       </c>
       <c r="O91" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B92" t="s">
-        <v>51</v>
+        <v>315</v>
       </c>
       <c r="C92" t="s">
-        <v>52</v>
+        <v>316</v>
       </c>
       <c r="D92" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E92" t="s">
         <v>18</v>
@@ -6203,19 +6257,19 @@
         <v>19</v>
       </c>
       <c r="G92" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H92" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I92" t="s">
         <v>22</v>
       </c>
       <c r="J92" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="K92" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="L92" t="s">
         <v>25</v>
@@ -6227,21 +6281,21 @@
         <v>25</v>
       </c>
       <c r="O92" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B93" t="s">
-        <v>51</v>
+        <v>315</v>
       </c>
       <c r="C93" t="s">
-        <v>52</v>
+        <v>316</v>
       </c>
       <c r="D93" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E93" t="s">
         <v>18</v>
@@ -6253,16 +6307,16 @@
         <v>20</v>
       </c>
       <c r="H93" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I93" t="s">
         <v>22</v>
       </c>
       <c r="J93" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="K93" t="s">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="L93" t="s">
         <v>25</v>
@@ -6274,21 +6328,21 @@
         <v>25</v>
       </c>
       <c r="O93" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B94" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C94" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="D94" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E94" t="s">
         <v>18</v>
@@ -6297,19 +6351,19 @@
         <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>370</v>
+        <v>51</v>
       </c>
       <c r="H94" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I94" t="s">
         <v>22</v>
       </c>
       <c r="J94" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="K94" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="L94" t="s">
         <v>25</v>
@@ -6321,21 +6375,21 @@
         <v>25</v>
       </c>
       <c r="O94" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B95" t="s">
-        <v>85</v>
+        <v>252</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>253</v>
       </c>
       <c r="D95" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E95" t="s">
         <v>18</v>
@@ -6344,19 +6398,19 @@
         <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H95" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I95" t="s">
         <v>22</v>
       </c>
       <c r="J95" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="K95" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L95" t="s">
         <v>25</v>
@@ -6368,21 +6422,21 @@
         <v>25</v>
       </c>
       <c r="O95" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B96" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="C96" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D96" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E96" t="s">
         <v>18</v>
@@ -6391,19 +6445,19 @@
         <v>19</v>
       </c>
       <c r="G96" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H96" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I96" t="s">
         <v>22</v>
       </c>
       <c r="J96" t="s">
-        <v>67</v>
+        <v>383</v>
       </c>
       <c r="K96" t="s">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="L96" t="s">
         <v>25</v>
@@ -6415,18 +6469,18 @@
         <v>25</v>
       </c>
       <c r="O96" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B97" t="s">
-        <v>218</v>
+        <v>62</v>
       </c>
       <c r="C97" t="s">
-        <v>219</v>
+        <v>63</v>
       </c>
       <c r="D97" t="s">
         <v>18</v>
@@ -6438,19 +6492,19 @@
         <v>19</v>
       </c>
       <c r="G97" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I97" t="s">
         <v>22</v>
       </c>
       <c r="J97" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="K97" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="L97" t="s">
         <v>25</v>
@@ -6462,18 +6516,18 @@
         <v>25</v>
       </c>
       <c r="O97" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B98" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -6485,19 +6539,19 @@
         <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H98" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I98" t="s">
         <v>22</v>
       </c>
       <c r="J98" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="K98" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="L98" t="s">
         <v>25</v>
@@ -6509,21 +6563,21 @@
         <v>25</v>
       </c>
       <c r="O98" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B99" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="E99" t="s">
         <v>18</v>
@@ -6535,16 +6589,16 @@
         <v>20</v>
       </c>
       <c r="H99" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I99" t="s">
         <v>22</v>
       </c>
       <c r="J99" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="K99" t="s">
-        <v>386</v>
+        <v>24</v>
       </c>
       <c r="L99" t="s">
         <v>25</v>
@@ -6556,18 +6610,18 @@
         <v>25</v>
       </c>
       <c r="O99" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B100" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="C100" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -6579,19 +6633,19 @@
         <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H100" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I100" t="s">
         <v>22</v>
       </c>
       <c r="J100" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="K100" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="L100" t="s">
         <v>25</v>
@@ -6603,21 +6657,21 @@
         <v>25</v>
       </c>
       <c r="O100" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B101" t="s">
-        <v>173</v>
+        <v>315</v>
       </c>
       <c r="C101" t="s">
-        <v>46</v>
+        <v>316</v>
       </c>
       <c r="D101" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E101" t="s">
         <v>18</v>
@@ -6626,19 +6680,19 @@
         <v>19</v>
       </c>
       <c r="G101" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I101" t="s">
         <v>22</v>
       </c>
       <c r="J101" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K101" t="s">
-        <v>24</v>
+        <v>232</v>
       </c>
       <c r="L101" t="s">
         <v>25</v>
@@ -6650,21 +6704,21 @@
         <v>25</v>
       </c>
       <c r="O101" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B102" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="C102" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="D102" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="E102" t="s">
         <v>18</v>
@@ -6673,19 +6727,19 @@
         <v>19</v>
       </c>
       <c r="G102" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I102" t="s">
         <v>22</v>
       </c>
       <c r="J102" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="K102" t="s">
-        <v>386</v>
+        <v>216</v>
       </c>
       <c r="L102" t="s">
         <v>25</v>
@@ -6697,21 +6751,21 @@
         <v>25</v>
       </c>
       <c r="O102" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B103" t="s">
-        <v>398</v>
+        <v>105</v>
       </c>
       <c r="C103" t="s">
-        <v>399</v>
+        <v>106</v>
       </c>
       <c r="D103" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E103" t="s">
         <v>18</v>
@@ -6723,16 +6777,16 @@
         <v>20</v>
       </c>
       <c r="H103" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I103" t="s">
         <v>22</v>
       </c>
       <c r="J103" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="K103" t="s">
-        <v>75</v>
+        <v>285</v>
       </c>
       <c r="L103" t="s">
         <v>25</v>
@@ -6744,21 +6798,21 @@
         <v>25</v>
       </c>
       <c r="O103" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B104" t="s">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>214</v>
       </c>
       <c r="D104" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E104" t="s">
         <v>18</v>
@@ -6767,19 +6821,19 @@
         <v>19</v>
       </c>
       <c r="G104" t="s">
-        <v>101</v>
+        <v>407</v>
       </c>
       <c r="H104" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I104" t="s">
         <v>22</v>
       </c>
       <c r="J104" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K104" t="s">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="L104" t="s">
         <v>25</v>
@@ -6791,21 +6845,21 @@
         <v>25</v>
       </c>
       <c r="O104" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E105" t="s">
         <v>18</v>
@@ -6814,19 +6868,19 @@
         <v>19</v>
       </c>
       <c r="G105" t="s">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I105" t="s">
         <v>22</v>
       </c>
       <c r="J105" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="K105" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="L105" t="s">
         <v>25</v>
@@ -6838,21 +6892,21 @@
         <v>25</v>
       </c>
       <c r="O105" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B106" t="s">
-        <v>398</v>
+        <v>105</v>
       </c>
       <c r="C106" t="s">
-        <v>399</v>
+        <v>106</v>
       </c>
       <c r="D106" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E106" t="s">
         <v>18</v>
@@ -6861,19 +6915,19 @@
         <v>19</v>
       </c>
       <c r="G106" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I106" t="s">
         <v>22</v>
       </c>
       <c r="J106" t="s">
-        <v>410</v>
+        <v>119</v>
       </c>
       <c r="K106" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L106" t="s">
         <v>25</v>
@@ -6885,42 +6939,42 @@
         <v>25</v>
       </c>
       <c r="O106" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B107" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C107" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D107" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E107" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F107" t="s">
         <v>19</v>
       </c>
       <c r="G107" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H107" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I107" t="s">
         <v>22</v>
       </c>
       <c r="J107" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="K107" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="L107" t="s">
         <v>25</v>
@@ -6932,21 +6986,21 @@
         <v>25</v>
       </c>
       <c r="O107" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B108" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C108" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D108" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
         <v>18</v>
@@ -6955,19 +7009,19 @@
         <v>19</v>
       </c>
       <c r="G108" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H108" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I108" t="s">
         <v>22</v>
       </c>
       <c r="J108" t="s">
-        <v>300</v>
+        <v>419</v>
       </c>
       <c r="K108" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="L108" t="s">
         <v>25</v>
@@ -6979,21 +7033,21 @@
         <v>25</v>
       </c>
       <c r="O108" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B109" t="s">
-        <v>276</v>
+        <v>49</v>
       </c>
       <c r="C109" t="s">
-        <v>277</v>
+        <v>50</v>
       </c>
       <c r="D109" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E109" t="s">
         <v>18</v>
@@ -7002,19 +7056,19 @@
         <v>19</v>
       </c>
       <c r="G109" t="s">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="H109" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I109" t="s">
         <v>22</v>
       </c>
       <c r="J109" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K109" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L109" t="s">
         <v>25</v>
@@ -7026,18 +7080,18 @@
         <v>25</v>
       </c>
       <c r="O109" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B110" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="C110" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
@@ -7049,19 +7103,19 @@
         <v>19</v>
       </c>
       <c r="G110" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H110" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I110" t="s">
         <v>22</v>
       </c>
       <c r="J110" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K110" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="L110" t="s">
         <v>25</v>
@@ -7073,21 +7127,21 @@
         <v>25</v>
       </c>
       <c r="O110" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="C111" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D111" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E111" t="s">
         <v>18</v>
@@ -7096,19 +7150,19 @@
         <v>19</v>
       </c>
       <c r="G111" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H111" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I111" t="s">
         <v>22</v>
       </c>
       <c r="J111" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="K111" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="L111" t="s">
         <v>25</v>
@@ -7120,21 +7174,21 @@
         <v>25</v>
       </c>
       <c r="O111" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>213</v>
       </c>
       <c r="C112" t="s">
-        <v>17</v>
+        <v>214</v>
       </c>
       <c r="D112" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E112" t="s">
         <v>18</v>
@@ -7143,19 +7197,19 @@
         <v>19</v>
       </c>
       <c r="G112" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H112" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I112" t="s">
         <v>22</v>
       </c>
       <c r="J112" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K112" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="L112" t="s">
         <v>25</v>
@@ -7167,42 +7221,42 @@
         <v>25</v>
       </c>
       <c r="O112" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B113" t="s">
-        <v>105</v>
+        <v>434</v>
       </c>
       <c r="C113" t="s">
-        <v>106</v>
+        <v>435</v>
       </c>
       <c r="D113" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="E113" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F113" t="s">
         <v>19</v>
       </c>
       <c r="G113" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H113" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I113" t="s">
         <v>22</v>
       </c>
       <c r="J113" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="K113" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L113" t="s">
         <v>25</v>
@@ -7214,42 +7268,42 @@
         <v>25</v>
       </c>
       <c r="O113" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B114" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="C114" t="s">
-        <v>219</v>
+        <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E114" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F114" t="s">
         <v>19</v>
       </c>
       <c r="G114" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="H114" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I114" t="s">
         <v>22</v>
       </c>
       <c r="J114" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K114" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="L114" t="s">
         <v>25</v>
@@ -7261,21 +7315,21 @@
         <v>25</v>
       </c>
       <c r="O114" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B115" t="s">
-        <v>437</v>
+        <v>49</v>
       </c>
       <c r="C115" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="D115" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="E115" t="s">
         <v>18</v>
@@ -7284,19 +7338,19 @@
         <v>19</v>
       </c>
       <c r="G115" t="s">
-        <v>54</v>
+        <v>442</v>
       </c>
       <c r="H115" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I115" t="s">
         <v>22</v>
       </c>
       <c r="J115" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K115" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="L115" t="s">
         <v>25</v>
@@ -7308,42 +7362,42 @@
         <v>25</v>
       </c>
       <c r="O115" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B116" t="s">
-        <v>218</v>
+        <v>434</v>
       </c>
       <c r="C116" t="s">
-        <v>219</v>
+        <v>435</v>
       </c>
       <c r="D116" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="E116" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F116" t="s">
         <v>19</v>
       </c>
       <c r="G116" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H116" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I116" t="s">
         <v>22</v>
       </c>
       <c r="J116" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="K116" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="L116" t="s">
         <v>25</v>
@@ -7355,21 +7409,21 @@
         <v>25</v>
       </c>
       <c r="O116" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B117" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="C117" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D117" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E117" t="s">
         <v>18</v>
@@ -7378,19 +7432,19 @@
         <v>19</v>
       </c>
       <c r="G117" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H117" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I117" t="s">
         <v>22</v>
       </c>
       <c r="J117" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K117" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="L117" t="s">
         <v>25</v>
@@ -7402,21 +7456,21 @@
         <v>25</v>
       </c>
       <c r="O117" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="C118" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="D118" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="E118" t="s">
         <v>18</v>
@@ -7425,19 +7479,19 @@
         <v>19</v>
       </c>
       <c r="G118" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H118" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I118" t="s">
         <v>22</v>
       </c>
       <c r="J118" t="s">
-        <v>447</v>
+        <v>338</v>
       </c>
       <c r="K118" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="L118" t="s">
         <v>25</v>
@@ -7449,43 +7503,43 @@
         <v>25</v>
       </c>
       <c r="O118" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B119" t="s">
-        <v>51</v>
+        <v>315</v>
       </c>
       <c r="C119" t="s">
-        <v>52</v>
+        <v>316</v>
       </c>
       <c r="D119" t="s">
+        <v>70</v>
+      </c>
+      <c r="E119" t="s">
+        <v>18</v>
+      </c>
+      <c r="F119" t="s">
+        <v>19</v>
+      </c>
+      <c r="G119" t="s">
+        <v>454</v>
+      </c>
+      <c r="H119" t="s">
+        <v>44</v>
+      </c>
+      <c r="I119" t="s">
+        <v>22</v>
+      </c>
+      <c r="J119" t="s">
+        <v>455</v>
+      </c>
+      <c r="K119" t="s">
         <v>53</v>
       </c>
-      <c r="E119" t="s">
-        <v>18</v>
-      </c>
-      <c r="F119" t="s">
-        <v>19</v>
-      </c>
-      <c r="G119" t="s">
-        <v>54</v>
-      </c>
-      <c r="H119" t="s">
-        <v>30</v>
-      </c>
-      <c r="I119" t="s">
-        <v>22</v>
-      </c>
-      <c r="J119" t="s">
-        <v>450</v>
-      </c>
-      <c r="K119" t="s">
-        <v>183</v>
-      </c>
       <c r="L119" t="s">
         <v>25</v>
       </c>
@@ -7496,24 +7550,24 @@
         <v>25</v>
       </c>
       <c r="O119" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B120" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C120" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="D120" t="s">
         <v>18</v>
       </c>
       <c r="E120" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F120" t="s">
         <v>19</v>
@@ -7522,16 +7576,16 @@
         <v>20</v>
       </c>
       <c r="H120" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I120" t="s">
         <v>22</v>
       </c>
       <c r="J120" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K120" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="L120" t="s">
         <v>25</v>
@@ -7543,21 +7597,21 @@
         <v>25</v>
       </c>
       <c r="O120" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B121" t="s">
-        <v>276</v>
+        <v>122</v>
       </c>
       <c r="C121" t="s">
-        <v>277</v>
+        <v>123</v>
       </c>
       <c r="D121" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E121" t="s">
         <v>18</v>
@@ -7566,19 +7620,19 @@
         <v>19</v>
       </c>
       <c r="G121" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H121" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I121" t="s">
         <v>22</v>
       </c>
       <c r="J121" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K121" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="L121" t="s">
         <v>25</v>
@@ -7590,21 +7644,21 @@
         <v>25</v>
       </c>
       <c r="O121" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B122" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
       <c r="C122" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="D122" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E122" t="s">
         <v>18</v>
@@ -7613,19 +7667,19 @@
         <v>19</v>
       </c>
       <c r="G122" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H122" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I122" t="s">
         <v>22</v>
       </c>
       <c r="J122" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="K122" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="L122" t="s">
         <v>25</v>
@@ -7637,42 +7691,42 @@
         <v>25</v>
       </c>
       <c r="O122" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B123" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="C123" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="D123" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E123" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F123" t="s">
-        <v>462</v>
+        <v>19</v>
       </c>
       <c r="G123" t="s">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="H123" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I123" t="s">
         <v>22</v>
       </c>
       <c r="J123" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K123" t="s">
-        <v>465</v>
+        <v>88</v>
       </c>
       <c r="L123" t="s">
         <v>25</v>
@@ -7681,45 +7735,45 @@
         <v>25</v>
       </c>
       <c r="N123" t="s">
-        <v>466</v>
+        <v>25</v>
       </c>
       <c r="O123" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B124" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C124" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D124" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E124" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
         <v>19</v>
       </c>
       <c r="G124" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="H124" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I124" t="s">
         <v>22</v>
       </c>
       <c r="J124" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K124" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="L124" t="s">
         <v>25</v>
@@ -7731,21 +7785,21 @@
         <v>25</v>
       </c>
       <c r="O124" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B125" t="s">
-        <v>51</v>
+        <v>473</v>
       </c>
       <c r="C125" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="D125" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E125" t="s">
         <v>18</v>
@@ -7754,19 +7808,19 @@
         <v>19</v>
       </c>
       <c r="G125" t="s">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="H125" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I125" t="s">
         <v>22</v>
       </c>
       <c r="J125" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K125" t="s">
-        <v>261</v>
+        <v>46</v>
       </c>
       <c r="L125" t="s">
         <v>25</v>
@@ -7778,12 +7832,12 @@
         <v>25</v>
       </c>
       <c r="O125" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B126" t="s">
         <v>28</v>
@@ -7795,25 +7849,25 @@
         <v>18</v>
       </c>
       <c r="E126" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F126" t="s">
         <v>19</v>
       </c>
       <c r="G126" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H126" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I126" t="s">
         <v>22</v>
       </c>
       <c r="J126" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="K126" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="L126" t="s">
         <v>25</v>
@@ -7825,21 +7879,21 @@
         <v>25</v>
       </c>
       <c r="O126" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B127" t="s">
-        <v>210</v>
+        <v>105</v>
       </c>
       <c r="C127" t="s">
-        <v>211</v>
+        <v>106</v>
       </c>
       <c r="D127" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="E127" t="s">
         <v>18</v>
@@ -7848,19 +7902,19 @@
         <v>19</v>
       </c>
       <c r="G127" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H127" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I127" t="s">
         <v>22</v>
       </c>
       <c r="J127" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K127" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="L127" t="s">
         <v>25</v>
@@ -7872,21 +7926,21 @@
         <v>25</v>
       </c>
       <c r="O127" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B128" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C128" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D128" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E128" t="s">
         <v>18</v>
@@ -7895,19 +7949,19 @@
         <v>19</v>
       </c>
       <c r="G128" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H128" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I128" t="s">
         <v>22</v>
       </c>
       <c r="J128" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K128" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="L128" t="s">
         <v>25</v>
@@ -7919,21 +7973,21 @@
         <v>25</v>
       </c>
       <c r="O128" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B129" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="C129" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D129" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E129" t="s">
         <v>18</v>
@@ -7942,19 +7996,19 @@
         <v>19</v>
       </c>
       <c r="G129" t="s">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="H129" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I129" t="s">
         <v>22</v>
       </c>
       <c r="J129" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K129" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="L129" t="s">
         <v>25</v>
@@ -7966,24 +8020,24 @@
         <v>25</v>
       </c>
       <c r="O129" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B130" t="s">
-        <v>487</v>
+        <v>28</v>
       </c>
       <c r="C130" t="s">
-        <v>488</v>
+        <v>29</v>
       </c>
       <c r="D130" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E130" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F130" t="s">
         <v>19</v>
@@ -7992,7 +8046,7 @@
         <v>20</v>
       </c>
       <c r="H130" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I130" t="s">
         <v>22</v>
@@ -8001,7 +8055,7 @@
         <v>489</v>
       </c>
       <c r="K130" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L130" t="s">
         <v>25</v>
@@ -8021,13 +8075,13 @@
         <v>491</v>
       </c>
       <c r="B131" t="s">
-        <v>51</v>
+        <v>315</v>
       </c>
       <c r="C131" t="s">
-        <v>52</v>
+        <v>316</v>
       </c>
       <c r="D131" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E131" t="s">
         <v>18</v>
@@ -8036,10 +8090,10 @@
         <v>19</v>
       </c>
       <c r="G131" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H131" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I131" t="s">
         <v>22</v>
@@ -8048,7 +8102,7 @@
         <v>492</v>
       </c>
       <c r="K131" t="s">
-        <v>108</v>
+        <v>184</v>
       </c>
       <c r="L131" t="s">
         <v>25</v>
@@ -8068,13 +8122,13 @@
         <v>494</v>
       </c>
       <c r="B132" t="s">
-        <v>51</v>
+        <v>213</v>
       </c>
       <c r="C132" t="s">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="D132" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E132" t="s">
         <v>18</v>
@@ -8083,10 +8137,10 @@
         <v>19</v>
       </c>
       <c r="G132" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H132" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I132" t="s">
         <v>22</v>
@@ -8095,7 +8149,7 @@
         <v>495</v>
       </c>
       <c r="K132" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="L132" t="s">
         <v>25</v>
@@ -8115,34 +8169,34 @@
         <v>497</v>
       </c>
       <c r="B133" t="s">
-        <v>437</v>
+        <v>35</v>
       </c>
       <c r="C133" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="D133" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="E133" t="s">
         <v>18</v>
       </c>
       <c r="F133" t="s">
-        <v>285</v>
+        <v>498</v>
       </c>
       <c r="G133" t="s">
-        <v>20</v>
+        <v>499</v>
       </c>
       <c r="H133" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I133" t="s">
         <v>22</v>
       </c>
       <c r="J133" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K133" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L133" t="s">
         <v>25</v>
@@ -8151,57 +8205,292 @@
         <v>25</v>
       </c>
       <c r="N133" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O133" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B134" t="s">
+        <v>105</v>
+      </c>
+      <c r="C134" t="s">
+        <v>106</v>
+      </c>
+      <c r="D134" t="s">
+        <v>107</v>
+      </c>
+      <c r="E134" t="s">
+        <v>18</v>
+      </c>
+      <c r="F134" t="s">
+        <v>19</v>
+      </c>
+      <c r="G134" t="s">
+        <v>82</v>
+      </c>
+      <c r="H134" t="s">
+        <v>44</v>
+      </c>
+      <c r="I134" t="s">
+        <v>22</v>
+      </c>
+      <c r="J134" t="s">
+        <v>505</v>
+      </c>
+      <c r="K134" t="s">
+        <v>24</v>
+      </c>
+      <c r="L134" t="s">
+        <v>25</v>
+      </c>
+      <c r="M134" t="s">
+        <v>25</v>
+      </c>
+      <c r="N134" t="s">
+        <v>25</v>
+      </c>
+      <c r="O134" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>507</v>
+      </c>
+      <c r="B135" t="s">
+        <v>105</v>
+      </c>
+      <c r="C135" t="s">
+        <v>106</v>
+      </c>
+      <c r="D135" t="s">
+        <v>107</v>
+      </c>
+      <c r="E135" t="s">
+        <v>18</v>
+      </c>
+      <c r="F135" t="s">
+        <v>19</v>
+      </c>
+      <c r="G135" t="s">
+        <v>508</v>
+      </c>
+      <c r="H135" t="s">
+        <v>44</v>
+      </c>
+      <c r="I135" t="s">
+        <v>22</v>
+      </c>
+      <c r="J135" t="s">
+        <v>509</v>
+      </c>
+      <c r="K135" t="s">
+        <v>300</v>
+      </c>
+      <c r="L135" t="s">
+        <v>25</v>
+      </c>
+      <c r="M135" t="s">
+        <v>25</v>
+      </c>
+      <c r="N135" t="s">
+        <v>25</v>
+      </c>
+      <c r="O135" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>511</v>
+      </c>
+      <c r="B136" t="s">
+        <v>49</v>
+      </c>
+      <c r="C136" t="s">
+        <v>50</v>
+      </c>
+      <c r="D136" t="s">
+        <v>18</v>
+      </c>
+      <c r="E136" t="s">
+        <v>18</v>
+      </c>
+      <c r="F136" t="s">
+        <v>19</v>
+      </c>
+      <c r="G136" t="s">
+        <v>82</v>
+      </c>
+      <c r="H136" t="s">
+        <v>44</v>
+      </c>
+      <c r="I136" t="s">
+        <v>22</v>
+      </c>
+      <c r="J136" t="s">
+        <v>443</v>
+      </c>
+      <c r="K136" t="s">
+        <v>164</v>
+      </c>
+      <c r="L136" t="s">
+        <v>25</v>
+      </c>
+      <c r="M136" t="s">
+        <v>25</v>
+      </c>
+      <c r="N136" t="s">
+        <v>25</v>
+      </c>
+      <c r="O136" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>513</v>
+      </c>
+      <c r="B137" t="s">
+        <v>252</v>
+      </c>
+      <c r="C137" t="s">
+        <v>253</v>
+      </c>
+      <c r="D137" t="s">
+        <v>70</v>
+      </c>
+      <c r="E137" t="s">
+        <v>18</v>
+      </c>
+      <c r="F137" t="s">
+        <v>19</v>
+      </c>
+      <c r="G137" t="s">
+        <v>82</v>
+      </c>
+      <c r="H137" t="s">
+        <v>44</v>
+      </c>
+      <c r="I137" t="s">
+        <v>22</v>
+      </c>
+      <c r="J137" t="s">
+        <v>514</v>
+      </c>
+      <c r="K137" t="s">
+        <v>39</v>
+      </c>
+      <c r="L137" t="s">
+        <v>25</v>
+      </c>
+      <c r="M137" t="s">
+        <v>25</v>
+      </c>
+      <c r="N137" t="s">
+        <v>25</v>
+      </c>
+      <c r="O137" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>516</v>
+      </c>
+      <c r="B138" t="s">
+        <v>122</v>
+      </c>
+      <c r="C138" t="s">
+        <v>123</v>
+      </c>
+      <c r="D138" t="s">
+        <v>70</v>
+      </c>
+      <c r="E138" t="s">
+        <v>18</v>
+      </c>
+      <c r="F138" t="s">
+        <v>19</v>
+      </c>
+      <c r="G138" t="s">
+        <v>82</v>
+      </c>
+      <c r="H138" t="s">
+        <v>44</v>
+      </c>
+      <c r="I138" t="s">
+        <v>22</v>
+      </c>
+      <c r="J138" t="s">
+        <v>517</v>
+      </c>
+      <c r="K138" t="s">
+        <v>79</v>
+      </c>
+      <c r="L138" t="s">
+        <v>25</v>
+      </c>
+      <c r="M138" t="s">
+        <v>25</v>
+      </c>
+      <c r="N138" t="s">
+        <v>25</v>
+      </c>
+      <c r="O138" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>519</v>
+      </c>
+      <c r="B139" t="s">
+        <v>105</v>
+      </c>
+      <c r="C139" t="s">
+        <v>106</v>
+      </c>
+      <c r="D139" t="s">
+        <v>107</v>
+      </c>
+      <c r="E139" t="s">
+        <v>18</v>
+      </c>
+      <c r="F139" t="s">
+        <v>19</v>
+      </c>
+      <c r="G139" t="s">
         <v>51</v>
       </c>
-      <c r="C134" t="s">
-        <v>52</v>
-      </c>
-      <c r="D134" t="s">
-        <v>53</v>
-      </c>
-      <c r="E134" t="s">
-        <v>18</v>
-      </c>
-      <c r="F134" t="s">
-        <v>19</v>
-      </c>
-      <c r="G134" t="s">
-        <v>54</v>
-      </c>
-      <c r="H134" t="s">
-        <v>30</v>
-      </c>
-      <c r="I134" t="s">
-        <v>22</v>
-      </c>
-      <c r="J134" t="s">
-        <v>481</v>
-      </c>
-      <c r="K134" t="s">
-        <v>170</v>
-      </c>
-      <c r="L134" t="s">
-        <v>25</v>
-      </c>
-      <c r="M134" t="s">
-        <v>25</v>
-      </c>
-      <c r="N134" t="s">
-        <v>25</v>
-      </c>
-      <c r="O134" t="s">
-        <v>503</v>
+      <c r="H139" t="s">
+        <v>44</v>
+      </c>
+      <c r="I139" t="s">
+        <v>22</v>
+      </c>
+      <c r="J139" t="s">
+        <v>520</v>
+      </c>
+      <c r="K139" t="s">
+        <v>65</v>
+      </c>
+      <c r="L139" t="s">
+        <v>25</v>
+      </c>
+      <c r="M139" t="s">
+        <v>25</v>
+      </c>
+      <c r="N139" t="s">
+        <v>25</v>
+      </c>
+      <c r="O139" t="s">
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99F7B820-0492-487E-903B-9295C36E08F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7621B21C-B6AF-4A8B-9CD0-6FCF9D0451C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="537">
   <si>
     <t>Time</t>
   </si>
@@ -62,54 +62,261 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>07/15/2026 6:54:31 PM</t>
+  </si>
+  <si>
+    <t>23466</t>
+  </si>
+  <si>
+    <t>NUNEZ, WALLY</t>
+  </si>
+  <si>
+    <t>OTR</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanya Smith </t>
+  </si>
+  <si>
+    <t>Barstow Freeway;Mojave Freeway, 11.9 mi SW Barstow Heights, San Bernardino County, CA</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445686b-022c-59fd-b15e-94b387010cfb</t>
+  </si>
+  <si>
+    <t>07/15/2026 1:59:24 PM</t>
+  </si>
+  <si>
+    <t>24632</t>
+  </si>
+  <si>
+    <t>EMERY.SHANE</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>I 40, 51.1 mi SSE Las Vegas, Guadalupe County, NM</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445675c-d388-5dca-827d-fdd256fd9a22</t>
+  </si>
+  <si>
+    <t>07/15/2026 12:48:31 PM</t>
+  </si>
+  <si>
+    <t>22996</t>
+  </si>
+  <si>
+    <t>FOFANA, MAMADOU</t>
+  </si>
+  <si>
+    <t>Purple Heart Trail, 26.5 mi NNW Paulden, Yavapai County, AZ</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445671b-ed66-59a6-b8e5-6ffd8afa4e43</t>
+  </si>
+  <si>
+    <t>07/14/2026 5:43:29 PM</t>
+  </si>
+  <si>
+    <t>Purple Heart Trail, 13.5 mi SSW Kingman, Mohave County, AZ, 86414</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456303-9e8f-5b5e-8c64-92e8c776dc57</t>
+  </si>
+  <si>
+    <t>07/14/2026 2:47:33 PM</t>
+  </si>
+  <si>
+    <t>24688</t>
+  </si>
+  <si>
+    <t>WADE,ADAM</t>
+  </si>
+  <si>
+    <t>Air Temperature, OTR</t>
+  </si>
+  <si>
+    <t>I 80, Bettendorf, IA, 52807</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456262-8bbb-56a0-aa06-7e67f17ad1b6</t>
+  </si>
+  <si>
+    <t>07/14/2026 2:11:57 PM</t>
+  </si>
+  <si>
+    <t>22970</t>
+  </si>
+  <si>
+    <t>MEYERS, DAVID</t>
+  </si>
+  <si>
+    <t>Air Temperature, Local</t>
+  </si>
+  <si>
+    <t>Heartland Expressway, 1.2 mi SW Welby, Adams County, CO, 80229</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456241-f4ff-5ff1-ad05-662b7ab9cf1c</t>
+  </si>
+  <si>
+    <t>07/14/2026 4:21:23 AM</t>
+  </si>
+  <si>
+    <t>24690</t>
+  </si>
+  <si>
+    <t>MOORE, ROYCE</t>
+  </si>
+  <si>
+    <t>Crash</t>
+  </si>
+  <si>
+    <t>Sensitive Media, Light Traffic</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, Abilene, KS</t>
+  </si>
+  <si>
+    <t>2.78</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456025-4528-508a-ae61-f198b0b6aa7e</t>
+  </si>
+  <si>
+    <t>07/13/2026 4:16:14 PM</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needles Freeway, 37.2 mi SW Bullhead City, San Bernardino County, CA</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455d8d-611d-5334-8176-a22e3da72974</t>
+  </si>
+  <si>
+    <t>07/13/2026 3:57:54 PM</t>
+  </si>
+  <si>
+    <t>Heartland Expressway, Arvada, CO, 80033</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455d7c-9a1a-5599-b3aa-1238cf18bc3d</t>
+  </si>
+  <si>
+    <t>07/13/2026 2:56:13 PM</t>
+  </si>
+  <si>
+    <t>22024</t>
+  </si>
+  <si>
+    <t>KENNEDY LINNETTE</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Sensitive Media</t>
+  </si>
+  <si>
+    <t>East Colfax Avenue, Aurora, CO, 80249</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3.77</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455d44-2016-5f81-9551-963ae672abb1</t>
+  </si>
+  <si>
+    <t>07/13/2026 1:42:02 PM</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Kansas Turnpike, Lawrence, KS, 66049</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455d00-34bc-5cd1-a200-90b4a673d99e</t>
+  </si>
+  <si>
+    <t>07/11/2026 12:18:11 PM</t>
+  </si>
+  <si>
+    <t>22022</t>
+  </si>
+  <si>
+    <t>TREVIZO, ESTABAN I.</t>
+  </si>
+  <si>
+    <t>Veterans Memorial Highway, 35.5 mi NE Enoch, Beaver County, UT</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455266-b723-5726-9da5-943dd1f75eb3</t>
+  </si>
+  <si>
+    <t>07/10/2026 8:53:41 AM</t>
+  </si>
+  <si>
+    <t>24634</t>
+  </si>
+  <si>
+    <t>KELLY GNEITING</t>
+  </si>
+  <si>
+    <t>I 40, Grants, NM, 87020</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454c85-21f8-51ae-80f2-f04f7c5dbfd4</t>
+  </si>
+  <si>
     <t>07/09/2026 9:54:42 AM</t>
   </si>
   <si>
-    <t>22996</t>
-  </si>
-  <si>
-    <t>FOFANA, MAMADOU</t>
-  </si>
-  <si>
-    <t>OTR</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
     <t>Pearl Harbor Memorial Highway, 14.5 mi WSW Las Cruces, Doña Ana County, NM</t>
   </si>
   <si>
     <t>66</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454796-a48a-508d-b3bf-cc18834d612c</t>
   </si>
   <si>
     <t>07/09/2026 8:49:26 AM</t>
   </si>
   <si>
-    <t>23466</t>
-  </si>
-  <si>
-    <t>NUNEZ, WALLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanya Smith </t>
-  </si>
-  <si>
     <t>Veterans Memorial Highway, 12.8 mi SSW Santa Clara, Mohave County, AZ</t>
   </si>
   <si>
@@ -122,33 +329,15 @@
     <t>07/07/2026 4:35:06 PM</t>
   </si>
   <si>
-    <t>22970</t>
-  </si>
-  <si>
-    <t>MEYERS, DAVID</t>
-  </si>
-  <si>
-    <t>Air Temperature, Local</t>
-  </si>
-  <si>
     <t>Dwight D. Eisenhower Highway, Aurora, CO, 80249</t>
   </si>
   <si>
-    <t>68</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453eb8-7e69-5014-bdb1-0ed5f2065eef</t>
   </si>
   <si>
     <t>07/06/2026 5:07:40 PM</t>
   </si>
   <si>
-    <t>24632</t>
-  </si>
-  <si>
-    <t>EMERY.SHANE</t>
-  </si>
-  <si>
     <t>Coached</t>
   </si>
   <si>
@@ -203,12 +392,6 @@
     <t>07/05/2026 5:34:14 PM</t>
   </si>
   <si>
-    <t>24634</t>
-  </si>
-  <si>
-    <t>KELLY GNEITING</t>
-  </si>
-  <si>
     <t>Purple Heart Trail, Williams, AZ</t>
   </si>
   <si>
@@ -227,9 +410,6 @@
     <t>FOUNTAIN, RODNEY</t>
   </si>
   <si>
-    <t>Air Temperature, OTR</t>
-  </si>
-  <si>
     <t>Harsh Brake</t>
   </si>
   <si>
@@ -254,18 +434,12 @@
     <t>Dwight D. Eisenhower Highway, Del Camino, CO, 80542</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445292d-0052-54c8-87db-4a5b25b78cdd</t>
   </si>
   <si>
     <t>07/03/2026 10:57:21 AM</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>I 35, Sanger, TX, 76266</t>
   </si>
   <si>
@@ -281,9 +455,6 @@
     <t>Kansas Turnpike, Kanwaka Township, KS, 66050</t>
   </si>
   <si>
-    <t>69</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523ec-334c-59c8-a435-37794192dcb9</t>
   </si>
   <si>
@@ -425,9 +596,6 @@
     <t>ROBERT REVELES</t>
   </si>
   <si>
-    <t>Local</t>
-  </si>
-  <si>
     <t>Dwight D. Eisenhower Highway, Dacono, CO, 80514</t>
   </si>
   <si>
@@ -461,12 +629,6 @@
     <t>06/24/2026 4:11:55 AM</t>
   </si>
   <si>
-    <t>22024</t>
-  </si>
-  <si>
-    <t>KENNEDY LINNETTE</t>
-  </si>
-  <si>
     <t>Light Traffic, Night</t>
   </si>
   <si>
@@ -509,9 +671,6 @@
     <t>Ronald Reagan Memorial Tollway, Malta Township, IL, 60113</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f09b-7c59-5088-b251-90ee7e4b87f2</t>
   </si>
   <si>
@@ -578,12 +737,6 @@
     <t>06/19/2026 4:32:27 PM</t>
   </si>
   <si>
-    <t>24690</t>
-  </si>
-  <si>
-    <t>MOORE, ROYCE</t>
-  </si>
-  <si>
     <t>Wet Road, Moderate Traffic</t>
   </si>
   <si>
@@ -656,18 +809,9 @@
     <t>06/14/2026 11:51:39 AM</t>
   </si>
   <si>
-    <t>24688</t>
-  </si>
-  <si>
-    <t>WADE,ADAM</t>
-  </si>
-  <si>
     <t>Gerald R. Ford Memorial Highway, Dotsero, CO</t>
   </si>
   <si>
-    <t>71</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c742-bb80-57f3-bbb2-56768c9b226e</t>
   </si>
   <si>
@@ -746,9 +890,6 @@
     <t>06/10/2026 7:47:02 PM</t>
   </si>
   <si>
-    <t>59</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b45c-834c-5c1d-8c85-58bf1f78108e</t>
   </si>
   <si>
@@ -965,9 +1106,6 @@
     <t>23471</t>
   </si>
   <si>
-    <t>TREVIZO, ESTABAN I.</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b60-14f9-5a48-9d21-698da447b93c</t>
   </si>
   <si>
@@ -1488,99 +1626,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ac0a-226d-53c8-9a69-cf0c004a78e2</t>
-  </si>
-  <si>
-    <t>04/18/2026 5:15:26 PM</t>
-  </si>
-  <si>
-    <t>I 80, 7.5 mi SSW Grand Island, Hall County, NE, 68839</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a2e0-ae88-51ac-873f-dd004d77f5ba</t>
-  </si>
-  <si>
-    <t>04/17/2026 12:18:32 PM</t>
-  </si>
-  <si>
-    <t>Purple Heart Trail, Allentown, AZ, 86506</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459caa-7e11-5f75-ac96-82a2e62b721a</t>
-  </si>
-  <si>
-    <t>04/17/2026 11:36:30 AM</t>
-  </si>
-  <si>
-    <t>Harsh Brake, Defensive Driving</t>
-  </si>
-  <si>
-    <t>Defensive, Wet Road, Light Traffic, Snowing</t>
-  </si>
-  <si>
-    <t>6400 Franklin Street, 1.7 mi SSW Welby, Adams County, CO, 80229</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459c84-0180-5154-8268-0357ebbcd7bd</t>
-  </si>
-  <si>
-    <t>04/16/2026 2:50:16 PM</t>
-  </si>
-  <si>
-    <t>I 70, Rhone, CO, 81521</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445980f-0c29-598f-adef-d4897dc0754e</t>
-  </si>
-  <si>
-    <t>04/15/2026 10:28:05 PM</t>
-  </si>
-  <si>
-    <t>Construction, Congested, Night</t>
-  </si>
-  <si>
-    <t>Veterans Memorial Highway, St. George, UT</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445948b-d4e5-570d-a292-d7620cbbd82b</t>
-  </si>
-  <si>
-    <t>04/15/2026 3:55:37 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459324-859d-598b-99dd-2fa21af4e465</t>
-  </si>
-  <si>
-    <t>04/15/2026 2:28:22 PM</t>
-  </si>
-  <si>
-    <t>I 70, 5.5 mi E Aurora, Arapahoe County, CO, 80019</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544592d4-a52a-5c6d-879c-e7c89c2424cb</t>
-  </si>
-  <si>
-    <t>04/15/2026 12:30:53 PM</t>
-  </si>
-  <si>
-    <t>I 70;US 6, Rulison, CO</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459269-146e-52a1-9868-7e6a0f624e0b</t>
-  </si>
-  <si>
-    <t>04/14/2026 1:24:59 PM</t>
-  </si>
-  <si>
-    <t>Las Vegas Freeway, Glendale, NV</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/30314/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458d74-4142-5a64-9ea6-83999fbe0a60</t>
   </si>
 </sst>
 </file>
@@ -1957,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -2021,13 +2066,13 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -2042,780 +2087,780 @@
         <v>24</v>
       </c>
       <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" t="s">
         <v>25</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
         <v>21</v>
       </c>
       <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
         <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" t="s">
         <v>38</v>
-      </c>
-      <c r="K4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" t="s">
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" t="s">
         <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" t="s">
         <v>48</v>
-      </c>
-      <c r="B6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="O8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" t="s">
         <v>67</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K9" t="s">
-        <v>74</v>
-      </c>
-      <c r="L9" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" t="s">
-        <v>75</v>
-      </c>
-      <c r="O9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="L10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O10" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="O11" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O12" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
         <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" t="s">
+        <v>93</v>
+      </c>
+      <c r="K14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14" t="s">
         <v>94</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" t="s">
-        <v>95</v>
-      </c>
-      <c r="K14" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" t="s">
+        <v>96</v>
+      </c>
+      <c r="K15" t="s">
         <v>97</v>
       </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15" t="s">
         <v>98</v>
-      </c>
-      <c r="K15" t="s">
-        <v>99</v>
-      </c>
-      <c r="L15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
+        <v>100</v>
+      </c>
+      <c r="K16" t="s">
+        <v>101</v>
+      </c>
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" t="s">
+        <v>19</v>
+      </c>
+      <c r="N16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16" t="s">
         <v>102</v>
-      </c>
-      <c r="K16" t="s">
-        <v>84</v>
-      </c>
-      <c r="L16" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" t="s">
-        <v>25</v>
-      </c>
-      <c r="O16" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" t="s">
         <v>104</v>
       </c>
-      <c r="B17" t="s">
+      <c r="K17" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O17" t="s">
         <v>105</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" t="s">
-        <v>108</v>
-      </c>
-      <c r="K17" t="s">
-        <v>88</v>
-      </c>
-      <c r="L17" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" t="s">
-        <v>25</v>
-      </c>
-      <c r="N17" t="s">
-        <v>25</v>
-      </c>
-      <c r="O17" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" t="s">
+        <v>19</v>
+      </c>
+      <c r="O18" t="s">
         <v>110</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" t="s">
-        <v>111</v>
-      </c>
-      <c r="K18" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" t="s">
-        <v>25</v>
-      </c>
-      <c r="N18" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s">
         <v>113</v>
       </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>43</v>
-      </c>
       <c r="D19" t="s">
         <v>18</v>
       </c>
@@ -2823,45 +2868,45 @@
         <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="H19" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I19" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K19" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="L19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -2870,139 +2915,139 @@
         <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I20" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K20" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I21" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K21" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="L21" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N21" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="G22" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I22" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J22" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K22" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N22" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="O22" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -3011,92 +3056,92 @@
         <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J23" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K23" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="L23" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N23" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O23" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B24" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
         <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I24" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M24" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N24" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O24" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -3105,45 +3150,45 @@
         <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I25" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J25" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="K25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L25" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M25" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N25" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O25" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -3152,125 +3197,125 @@
         <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I26" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J26" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K26" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L26" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M26" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N26" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O26" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" t="s">
+        <v>107</v>
+      </c>
+      <c r="I27" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" t="s">
+        <v>152</v>
+      </c>
+      <c r="K27" t="s">
         <v>149</v>
       </c>
-      <c r="D27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" t="s">
-        <v>151</v>
-      </c>
-      <c r="K27" t="s">
-        <v>92</v>
-      </c>
       <c r="L27" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M27" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N27" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" t="s">
         <v>155</v>
       </c>
-      <c r="D28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" t="s">
-        <v>44</v>
-      </c>
-      <c r="I28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>156</v>
       </c>
-      <c r="K28" t="s">
-        <v>79</v>
-      </c>
       <c r="L28" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M28" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N28" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O28" t="s">
         <v>157</v>
@@ -3281,198 +3326,198 @@
         <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
         <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" t="s">
         <v>159</v>
       </c>
-      <c r="H29" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L29" t="s">
+        <v>19</v>
+      </c>
+      <c r="M29" t="s">
+        <v>19</v>
+      </c>
+      <c r="N29" t="s">
+        <v>19</v>
+      </c>
+      <c r="O29" t="s">
         <v>160</v>
-      </c>
-      <c r="K29" t="s">
-        <v>53</v>
-      </c>
-      <c r="L29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N29" t="s">
-        <v>25</v>
-      </c>
-      <c r="O29" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" t="s">
         <v>162</v>
       </c>
-      <c r="B30" t="s">
-        <v>49</v>
-      </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="E30" t="s">
         <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H30" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I30" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K30" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="L30" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N30" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" t="s">
         <v>168</v>
       </c>
-      <c r="D31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
+        <v>101</v>
+      </c>
+      <c r="L31" t="s">
+        <v>19</v>
+      </c>
+      <c r="M31" t="s">
+        <v>19</v>
+      </c>
+      <c r="N31" t="s">
+        <v>19</v>
+      </c>
+      <c r="O31" t="s">
         <v>169</v>
-      </c>
-      <c r="K31" t="s">
-        <v>39</v>
-      </c>
-      <c r="L31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M31" t="s">
-        <v>25</v>
-      </c>
-      <c r="N31" t="s">
-        <v>25</v>
-      </c>
-      <c r="O31" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" t="s">
+        <v>107</v>
+      </c>
+      <c r="I32" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" t="s">
         <v>171</v>
       </c>
-      <c r="B32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" t="s">
-        <v>82</v>
-      </c>
-      <c r="H32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
+        <v>41</v>
+      </c>
+      <c r="L32" t="s">
+        <v>19</v>
+      </c>
+      <c r="M32" t="s">
+        <v>19</v>
+      </c>
+      <c r="N32" t="s">
+        <v>19</v>
+      </c>
+      <c r="O32" t="s">
         <v>172</v>
-      </c>
-      <c r="K32" t="s">
-        <v>164</v>
-      </c>
-      <c r="L32" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" t="s">
-        <v>25</v>
-      </c>
-      <c r="N32" t="s">
-        <v>25</v>
-      </c>
-      <c r="O32" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B33" t="s">
         <v>174</v>
       </c>
-      <c r="B33" t="s">
-        <v>56</v>
-      </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -3481,266 +3526,266 @@
         <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I33" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K33" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="L33" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M33" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N33" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
         <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I34" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K34" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L34" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M34" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N34" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="H35" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I35" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K35" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="L35" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M35" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N35" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" t="s">
+        <v>29</v>
+      </c>
+      <c r="J36" t="s">
         <v>188</v>
       </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" t="s">
-        <v>18</v>
-      </c>
-      <c r="F36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="K36" t="s">
+        <v>149</v>
+      </c>
+      <c r="L36" t="s">
+        <v>19</v>
+      </c>
+      <c r="M36" t="s">
+        <v>19</v>
+      </c>
+      <c r="N36" t="s">
+        <v>19</v>
+      </c>
+      <c r="O36" t="s">
         <v>189</v>
-      </c>
-      <c r="H36" t="s">
-        <v>44</v>
-      </c>
-      <c r="I36" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" t="s">
-        <v>190</v>
-      </c>
-      <c r="K36" t="s">
-        <v>39</v>
-      </c>
-      <c r="L36" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" t="s">
-        <v>25</v>
-      </c>
-      <c r="N36" t="s">
-        <v>25</v>
-      </c>
-      <c r="O36" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" t="s">
+        <v>191</v>
+      </c>
+      <c r="C37" t="s">
         <v>192</v>
       </c>
-      <c r="B37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" t="s">
-        <v>36</v>
-      </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E37" t="s">
         <v>18</v>
       </c>
       <c r="F37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I37" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J37" t="s">
         <v>193</v>
       </c>
       <c r="K37" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="L37" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M37" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N37" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O37" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="E38" t="s">
         <v>18</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I38" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J38" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K38" t="s">
-        <v>197</v>
+        <v>109</v>
       </c>
       <c r="L38" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M38" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N38" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O38" t="s">
         <v>198</v>
@@ -3751,10 +3796,10 @@
         <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -3763,327 +3808,327 @@
         <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G39" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H39" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I39" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J39" t="s">
         <v>200</v>
       </c>
       <c r="K39" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="L39" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M39" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N39" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="E40" t="s">
         <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="H40" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J40" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K40" t="s">
-        <v>204</v>
+        <v>149</v>
       </c>
       <c r="L40" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M40" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N40" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="C41" t="s">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H41" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I41" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J41" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K41" t="s">
-        <v>184</v>
+        <v>24</v>
       </c>
       <c r="L41" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M41" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N41" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O41" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="E42" t="s">
         <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G42" t="s">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="H42" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I42" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J42" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K42" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="L42" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M42" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N42" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O42" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I43" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J43" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K43" t="s">
-        <v>216</v>
+        <v>37</v>
       </c>
       <c r="L43" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M43" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N43" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O43" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I44" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J44" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K44" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L44" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M44" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N44" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O44" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B45" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" t="s">
+        <v>107</v>
+      </c>
+      <c r="I45" t="s">
+        <v>29</v>
+      </c>
+      <c r="J45" t="s">
+        <v>225</v>
+      </c>
+      <c r="K45" t="s">
         <v>37</v>
       </c>
-      <c r="E45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" t="s">
-        <v>44</v>
-      </c>
-      <c r="I45" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" t="s">
-        <v>98</v>
-      </c>
-      <c r="K45" t="s">
-        <v>164</v>
-      </c>
       <c r="L45" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M45" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N45" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O45" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -4092,280 +4137,280 @@
         <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I46" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J46" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K46" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="L46" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M46" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N46" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O46" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>231</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
         <v>18</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I47" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J47" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K47" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="L47" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M47" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N47" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O47" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C48" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D48" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I48" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J48" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K48" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L48" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M48" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N48" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="D49" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E49" t="s">
         <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="H49" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I49" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J49" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K49" t="s">
-        <v>232</v>
+        <v>31</v>
       </c>
       <c r="L49" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M49" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N49" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O49" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="E50" t="s">
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H50" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I50" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J50" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K50" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="L50" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M50" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N50" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O50" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="D51" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="E51" t="s">
         <v>18</v>
       </c>
       <c r="F51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G51" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H51" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I51" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J51" t="s">
-        <v>128</v>
+        <v>247</v>
       </c>
       <c r="K51" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="L51" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M51" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N51" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O51" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B52" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -4374,327 +4419,327 @@
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H52" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I52" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J52" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K52" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="L52" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M52" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N52" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O52" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I53" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J53" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K53" t="s">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="L53" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M53" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N53" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O53" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B54" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="C54" t="s">
-        <v>253</v>
+        <v>209</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I54" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J54" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K54" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="L54" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M54" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N54" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O54" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="D55" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="E55" t="s">
         <v>18</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I55" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J55" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K55" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="L55" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M55" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N55" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O55" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E56" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I56" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J56" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K56" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="L56" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M56" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N56" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O56" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="E57" t="s">
         <v>18</v>
       </c>
       <c r="F57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H57" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I57" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J57" t="s">
-        <v>111</v>
+        <v>268</v>
       </c>
       <c r="K57" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="L57" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M57" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N57" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O57" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D58" t="s">
+        <v>52</v>
+      </c>
+      <c r="E58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s">
+        <v>107</v>
+      </c>
+      <c r="I58" t="s">
+        <v>29</v>
+      </c>
+      <c r="J58" t="s">
+        <v>155</v>
+      </c>
+      <c r="K58" t="s">
         <v>37</v>
       </c>
-      <c r="E58" t="s">
-        <v>18</v>
-      </c>
-      <c r="F58" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" t="s">
-        <v>44</v>
-      </c>
-      <c r="I58" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" t="s">
-        <v>265</v>
-      </c>
-      <c r="K58" t="s">
-        <v>164</v>
-      </c>
       <c r="L58" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M58" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N58" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O58" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B59" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -4703,1737 +4748,1737 @@
         <v>18</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I59" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J59" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K59" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L59" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M59" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N59" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O59" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B60" t="s">
-        <v>271</v>
+        <v>162</v>
       </c>
       <c r="C60" t="s">
-        <v>272</v>
+        <v>163</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H60" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I60" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J60" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K60" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="L60" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M60" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N60" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O60" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="D61" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I61" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J61" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K61" t="s">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="L61" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M61" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N61" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O61" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>283</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>284</v>
       </c>
       <c r="D62" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I62" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J62" t="s">
-        <v>160</v>
+        <v>285</v>
       </c>
       <c r="K62" t="s">
-        <v>53</v>
+        <v>280</v>
       </c>
       <c r="L62" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M62" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N62" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O62" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B63" t="s">
-        <v>235</v>
+        <v>162</v>
       </c>
       <c r="C63" t="s">
-        <v>236</v>
+        <v>163</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E63" t="s">
         <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I63" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J63" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="K63" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="L63" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M63" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N63" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B64" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C64" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E64" t="s">
         <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="H64" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I64" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J64" t="s">
-        <v>284</v>
+        <v>185</v>
       </c>
       <c r="K64" t="s">
-        <v>285</v>
+        <v>66</v>
       </c>
       <c r="L64" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M64" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N64" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O64" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B65" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D65" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G65" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H65" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I65" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J65" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K65" t="s">
-        <v>243</v>
+        <v>31</v>
       </c>
       <c r="L65" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M65" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N65" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O65" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B66" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C66" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H66" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I66" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J66" t="s">
-        <v>64</v>
+        <v>296</v>
       </c>
       <c r="K66" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L66" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M66" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N66" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O66" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B67" t="s">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="C67" t="s">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E67" t="s">
         <v>18</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="H67" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I67" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J67" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="K67" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L67" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M67" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N67" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O67" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B68" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C68" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D68" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E68" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F68" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H68" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I68" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J68" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="K68" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="L68" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M68" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N68" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O68" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B69" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G69" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H69" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I69" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J69" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="K69" t="s">
-        <v>300</v>
+        <v>24</v>
       </c>
       <c r="L69" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M69" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N69" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O69" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B70" t="s">
-        <v>252</v>
+        <v>191</v>
       </c>
       <c r="C70" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D70" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E70" t="s">
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I70" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J70" t="s">
-        <v>303</v>
+        <v>168</v>
       </c>
       <c r="K70" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="L70" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M70" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N70" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O70" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B71" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="D71" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="E71" t="s">
         <v>18</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I71" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J71" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="K71" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="L71" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M71" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N71" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O71" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B72" t="s">
-        <v>213</v>
+        <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>214</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E72" t="s">
         <v>18</v>
       </c>
       <c r="F72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G72" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I72" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J72" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="K72" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L72" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M72" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N72" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O72" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B73" t="s">
-        <v>105</v>
+        <v>318</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>319</v>
       </c>
       <c r="D73" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E73" t="s">
         <v>18</v>
       </c>
       <c r="F73" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G73" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I73" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J73" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="K73" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="L73" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M73" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N73" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O73" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B74" t="s">
-        <v>315</v>
+        <v>162</v>
       </c>
       <c r="C74" t="s">
-        <v>316</v>
+        <v>163</v>
       </c>
       <c r="D74" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
       </c>
       <c r="F74" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I74" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J74" t="s">
-        <v>151</v>
+        <v>323</v>
       </c>
       <c r="K74" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="L74" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M74" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N74" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O74" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="D75" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="E75" t="s">
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I75" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J75" t="s">
-        <v>319</v>
+        <v>214</v>
       </c>
       <c r="K75" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="L75" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M75" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N75" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O75" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B76" t="s">
-        <v>105</v>
+        <v>283</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>284</v>
       </c>
       <c r="D76" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
       </c>
       <c r="F76" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H76" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I76" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J76" t="s">
-        <v>119</v>
+        <v>328</v>
       </c>
       <c r="K76" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="L76" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M76" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N76" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O76" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B77" t="s">
-        <v>271</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>272</v>
+        <v>45</v>
       </c>
       <c r="D77" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E77" t="s">
         <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I77" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J77" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="K77" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="L77" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M77" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N77" t="s">
-        <v>326</v>
+        <v>19</v>
       </c>
       <c r="O77" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B78" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="C78" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="E78" t="s">
         <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I78" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J78" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="K78" t="s">
-        <v>204</v>
+        <v>66</v>
       </c>
       <c r="L78" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M78" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N78" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B79" t="s">
-        <v>213</v>
+        <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>214</v>
+        <v>28</v>
       </c>
       <c r="D79" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
         <v>18</v>
       </c>
       <c r="F79" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H79" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I79" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J79" t="s">
-        <v>332</v>
+        <v>125</v>
       </c>
       <c r="K79" t="s">
-        <v>204</v>
+        <v>31</v>
       </c>
       <c r="L79" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M79" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N79" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O79" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B80" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C80" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
         <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I80" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J80" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K80" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="L80" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M80" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N80" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O80" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B81" t="s">
-        <v>122</v>
+        <v>220</v>
       </c>
       <c r="C81" t="s">
-        <v>123</v>
+        <v>221</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E81" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G81" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H81" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I81" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J81" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K81" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="L81" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M81" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N81" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O81" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B82" t="s">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="C82" t="s">
-        <v>43</v>
+        <v>221</v>
       </c>
       <c r="D82" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E82" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H82" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I82" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J82" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K82" t="s">
-        <v>88</v>
+        <v>347</v>
       </c>
       <c r="L82" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M82" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N82" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O82" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B83" t="s">
-        <v>42</v>
+        <v>299</v>
       </c>
       <c r="C83" t="s">
-        <v>43</v>
+        <v>300</v>
       </c>
       <c r="D83" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E83" t="s">
         <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H83" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I83" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J83" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="K83" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="L83" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M83" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N83" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O83" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C84" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D84" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E84" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F84" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H84" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I84" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J84" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="K84" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="L84" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M84" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N84" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O84" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B85" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D85" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E85" t="s">
         <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H85" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I85" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J85" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="K85" t="s">
-        <v>232</v>
+        <v>41</v>
       </c>
       <c r="L85" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M85" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N85" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O85" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B86" t="s">
+        <v>162</v>
+      </c>
+      <c r="C86" t="s">
+        <v>163</v>
+      </c>
+      <c r="D86" t="s">
+        <v>164</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" t="s">
         <v>213</v>
       </c>
-      <c r="C86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D86" t="s">
-        <v>70</v>
-      </c>
-      <c r="E86" t="s">
-        <v>18</v>
-      </c>
-      <c r="F86" t="s">
-        <v>19</v>
-      </c>
-      <c r="G86" t="s">
-        <v>82</v>
-      </c>
       <c r="H86" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I86" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J86" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="K86" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="L86" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M86" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N86" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O86" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B87" t="s">
-        <v>105</v>
+        <v>362</v>
       </c>
       <c r="C87" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D87" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I87" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J87" t="s">
-        <v>356</v>
+        <v>205</v>
       </c>
       <c r="K87" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="L87" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M87" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N87" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O87" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B88" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="C88" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="D88" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="E88" t="s">
         <v>18</v>
       </c>
       <c r="F88" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H88" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I88" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J88" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="K88" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="L88" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M88" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N88" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O88" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B89" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="C89" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="D89" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="E89" t="s">
         <v>18</v>
       </c>
       <c r="F89" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G89" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I89" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J89" t="s">
-        <v>362</v>
+        <v>176</v>
       </c>
       <c r="K89" t="s">
-        <v>46</v>
+        <v>237</v>
       </c>
       <c r="L89" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M89" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N89" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O89" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B90" t="s">
-        <v>167</v>
+        <v>318</v>
       </c>
       <c r="C90" t="s">
-        <v>168</v>
+        <v>319</v>
       </c>
       <c r="D90" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E90" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F90" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="G90" t="s">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="H90" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I90" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J90" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="K90" t="s">
-        <v>164</v>
+        <v>371</v>
       </c>
       <c r="L90" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M90" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N90" t="s">
-        <v>25</v>
+        <v>372</v>
       </c>
       <c r="O90" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B91" t="s">
-        <v>213</v>
+        <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>214</v>
+        <v>28</v>
       </c>
       <c r="D91" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E91" t="s">
         <v>18</v>
       </c>
       <c r="F91" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G91" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H91" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I91" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J91" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="K91" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="L91" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M91" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N91" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O91" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B92" t="s">
-        <v>315</v>
+        <v>44</v>
       </c>
       <c r="C92" t="s">
-        <v>316</v>
+        <v>45</v>
       </c>
       <c r="D92" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E92" t="s">
         <v>18</v>
       </c>
       <c r="F92" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G92" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H92" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I92" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J92" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="K92" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="L92" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M92" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N92" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O92" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B93" t="s">
-        <v>315</v>
+        <v>44</v>
       </c>
       <c r="C93" t="s">
-        <v>316</v>
+        <v>45</v>
       </c>
       <c r="D93" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E93" t="s">
         <v>18</v>
       </c>
       <c r="F93" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G93" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H93" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I93" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J93" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="K93" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="L93" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M93" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N93" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O93" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B94" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="C94" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="D94" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E94" t="s">
         <v>18</v>
       </c>
       <c r="F94" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G94" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H94" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I94" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J94" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="K94" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="L94" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M94" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N94" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O94" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B95" t="s">
-        <v>252</v>
+        <v>27</v>
       </c>
       <c r="C95" t="s">
-        <v>253</v>
+        <v>28</v>
       </c>
       <c r="D95" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E95" t="s">
         <v>18</v>
       </c>
       <c r="F95" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G95" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I95" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J95" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="K95" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L95" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M95" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N95" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O95" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B96" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="C96" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D96" t="s">
         <v>18</v>
@@ -6442,92 +6487,92 @@
         <v>18</v>
       </c>
       <c r="F96" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G96" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I96" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J96" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="K96" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L96" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M96" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N96" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O96" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B97" t="s">
-        <v>62</v>
+        <v>220</v>
       </c>
       <c r="C97" t="s">
-        <v>63</v>
+        <v>221</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E97" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G97" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H97" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I97" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J97" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="K97" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="L97" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M97" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N97" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O97" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B98" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="C98" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -6536,515 +6581,515 @@
         <v>18</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G98" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H98" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I98" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J98" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="K98" t="s">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="L98" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M98" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N98" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O98" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C99" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="D99" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E99" t="s">
         <v>18</v>
       </c>
       <c r="F99" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H99" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I99" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J99" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="K99" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L99" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M99" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N99" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O99" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B100" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="C100" t="s">
-        <v>57</v>
+        <v>163</v>
       </c>
       <c r="D100" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="E100" t="s">
         <v>18</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G100" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H100" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I100" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J100" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="K100" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="L100" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M100" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N100" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O100" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B101" t="s">
-        <v>315</v>
+        <v>162</v>
       </c>
       <c r="C101" t="s">
-        <v>316</v>
+        <v>163</v>
       </c>
       <c r="D101" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E101" t="s">
         <v>18</v>
       </c>
       <c r="F101" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G101" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H101" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I101" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J101" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="K101" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L101" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M101" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N101" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O101" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="C102" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="E102" t="s">
         <v>18</v>
       </c>
       <c r="F102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G102" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I102" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J102" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="K102" t="s">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="L102" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M102" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N102" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O102" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
       <c r="C103" t="s">
-        <v>106</v>
+        <v>221</v>
       </c>
       <c r="D103" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G103" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I103" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J103" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="K103" t="s">
-        <v>285</v>
+        <v>37</v>
       </c>
       <c r="L103" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M103" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N103" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O103" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B104" t="s">
-        <v>213</v>
+        <v>44</v>
       </c>
       <c r="C104" t="s">
-        <v>214</v>
+        <v>45</v>
       </c>
       <c r="D104" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E104" t="s">
         <v>18</v>
       </c>
       <c r="F104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G104" t="s">
-        <v>407</v>
+        <v>64</v>
       </c>
       <c r="H104" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I104" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J104" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="K104" t="s">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="L104" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M104" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N104" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O104" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B105" t="s">
-        <v>134</v>
+        <v>362</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="D105" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E105" t="s">
         <v>18</v>
       </c>
       <c r="F105" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G105" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I105" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J105" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="K105" t="s">
-        <v>99</v>
+        <v>255</v>
       </c>
       <c r="L105" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M105" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N105" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O105" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>362</v>
       </c>
       <c r="C106" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D106" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E106" t="s">
         <v>18</v>
       </c>
       <c r="F106" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G106" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I106" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J106" t="s">
-        <v>119</v>
+        <v>420</v>
       </c>
       <c r="K106" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="L106" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M106" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N106" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O106" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B107" t="s">
+        <v>191</v>
+      </c>
+      <c r="C107" t="s">
         <v>28</v>
       </c>
-      <c r="C107" t="s">
-        <v>29</v>
-      </c>
       <c r="D107" t="s">
         <v>18</v>
       </c>
       <c r="E107" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F107" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G107" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="H107" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I107" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J107" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="K107" t="s">
-        <v>39</v>
+        <v>255</v>
       </c>
       <c r="L107" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M107" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N107" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O107" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B108" t="s">
-        <v>49</v>
+        <v>299</v>
       </c>
       <c r="C108" t="s">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="D108" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E108" t="s">
         <v>18</v>
       </c>
       <c r="F108" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G108" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H108" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I108" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J108" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="K108" t="s">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="L108" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M108" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N108" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O108" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B109" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="C109" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D109" t="s">
         <v>18</v>
@@ -7053,92 +7098,92 @@
         <v>18</v>
       </c>
       <c r="F109" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G109" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I109" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J109" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="K109" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="L109" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M109" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N109" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O109" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B110" t="s">
-        <v>219</v>
+        <v>91</v>
       </c>
       <c r="C110" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
       </c>
       <c r="E110" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F110" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G110" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H110" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I110" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J110" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="K110" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="L110" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M110" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N110" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O110" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B111" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="C111" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
@@ -7147,515 +7192,515 @@
         <v>18</v>
       </c>
       <c r="F111" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H111" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I111" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J111" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="K111" t="s">
-        <v>88</v>
+        <v>255</v>
       </c>
       <c r="L111" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M111" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N111" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O111" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B112" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C112" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="D112" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E112" t="s">
         <v>18</v>
       </c>
       <c r="F112" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G112" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I112" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J112" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="K112" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="L112" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M112" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N112" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O112" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B113" t="s">
-        <v>434</v>
+        <v>267</v>
       </c>
       <c r="C113" t="s">
-        <v>435</v>
+        <v>120</v>
       </c>
       <c r="D113" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="E113" t="s">
         <v>18</v>
       </c>
       <c r="F113" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G113" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H113" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I113" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J113" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K113" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="L113" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M113" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N113" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O113" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B114" t="s">
-        <v>134</v>
+        <v>362</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="D114" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E114" t="s">
         <v>18</v>
       </c>
       <c r="F114" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G114" t="s">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="H114" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I114" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J114" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="K114" t="s">
-        <v>184</v>
+        <v>280</v>
       </c>
       <c r="L114" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M114" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N114" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O114" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B115" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="C115" t="s">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="D115" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="E115" t="s">
         <v>18</v>
       </c>
       <c r="F115" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>442</v>
+        <v>64</v>
       </c>
       <c r="H115" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I115" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J115" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="K115" t="s">
-        <v>164</v>
+        <v>88</v>
       </c>
       <c r="L115" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M115" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N115" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O115" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B116" t="s">
-        <v>434</v>
+        <v>162</v>
       </c>
       <c r="C116" t="s">
-        <v>435</v>
+        <v>163</v>
       </c>
       <c r="D116" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="E116" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G116" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I116" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J116" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="K116" t="s">
-        <v>32</v>
+        <v>332</v>
       </c>
       <c r="L116" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M116" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N116" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O116" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B117" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="D117" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E117" t="s">
         <v>18</v>
       </c>
       <c r="F117" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="H117" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I117" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J117" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="K117" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="L117" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M117" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N117" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O117" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B118" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="C118" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E118" t="s">
         <v>18</v>
       </c>
       <c r="F118" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H118" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I118" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J118" t="s">
-        <v>338</v>
+        <v>457</v>
       </c>
       <c r="K118" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="L118" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M118" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N118" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O118" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B119" t="s">
-        <v>315</v>
+        <v>162</v>
       </c>
       <c r="C119" t="s">
-        <v>316</v>
+        <v>163</v>
       </c>
       <c r="D119" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E119" t="s">
         <v>18</v>
       </c>
       <c r="F119" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G119" t="s">
-        <v>454</v>
+        <v>64</v>
       </c>
       <c r="H119" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I119" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J119" t="s">
-        <v>455</v>
+        <v>176</v>
       </c>
       <c r="K119" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="L119" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M119" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N119" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O119" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B120" t="s">
-        <v>219</v>
+        <v>16</v>
       </c>
       <c r="C120" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="D120" t="s">
         <v>18</v>
       </c>
       <c r="E120" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F120" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G120" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H120" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I120" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J120" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="K120" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
       <c r="L120" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M120" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N120" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O120" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B121" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C121" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D121" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E121" t="s">
         <v>18</v>
       </c>
       <c r="F121" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G121" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H121" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I121" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J121" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="K121" t="s">
-        <v>39</v>
+        <v>255</v>
       </c>
       <c r="L121" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M121" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N121" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O121" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B122" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="C122" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="D122" t="s">
         <v>18</v>
@@ -7664,280 +7709,280 @@
         <v>18</v>
       </c>
       <c r="F122" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G122" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I122" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J122" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="K122" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="L122" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M122" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N122" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O122" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B123" t="s">
-        <v>154</v>
+        <v>267</v>
       </c>
       <c r="C123" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="D123" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E123" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F123" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G123" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H123" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I123" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J123" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="K123" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="L123" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M123" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N123" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O123" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>267</v>
       </c>
       <c r="C124" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
       </c>
       <c r="E124" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F124" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G124" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I124" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J124" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="K124" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L124" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M124" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N124" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O124" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B125" t="s">
-        <v>473</v>
+        <v>44</v>
       </c>
       <c r="C125" t="s">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="D125" t="s">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="E125" t="s">
         <v>18</v>
       </c>
       <c r="F125" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G125" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I125" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J125" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K125" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="L125" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M125" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N125" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O125" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>480</v>
       </c>
       <c r="C126" t="s">
-        <v>29</v>
+        <v>481</v>
       </c>
       <c r="D126" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="E126" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F126" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G126" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H126" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I126" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J126" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="K126" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="L126" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M126" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N126" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O126" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B127" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="C127" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="D127" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E127" t="s">
         <v>18</v>
       </c>
       <c r="F127" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G127" t="s">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="H127" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I127" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J127" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="K127" t="s">
-        <v>24</v>
+        <v>237</v>
       </c>
       <c r="L127" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M127" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N127" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O127" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B128" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="C128" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="D128" t="s">
         <v>18</v>
@@ -7946,551 +7991,739 @@
         <v>18</v>
       </c>
       <c r="F128" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G128" t="s">
-        <v>20</v>
+        <v>488</v>
       </c>
       <c r="H128" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I128" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J128" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="K128" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="L128" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M128" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N128" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O128" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B129" t="s">
-        <v>105</v>
+        <v>480</v>
       </c>
       <c r="C129" t="s">
-        <v>106</v>
+        <v>481</v>
       </c>
       <c r="D129" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="E129" t="s">
         <v>18</v>
       </c>
       <c r="F129" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G129" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H129" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I129" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J129" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="K129" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="L129" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M129" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N129" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O129" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B130" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="C130" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="D130" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="E130" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G130" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H130" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I130" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J130" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="K130" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="L130" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M130" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N130" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O130" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B131" t="s">
-        <v>315</v>
+        <v>162</v>
       </c>
       <c r="C131" t="s">
-        <v>316</v>
+        <v>163</v>
       </c>
       <c r="D131" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E131" t="s">
         <v>18</v>
       </c>
       <c r="F131" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G131" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H131" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I131" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J131" t="s">
-        <v>492</v>
+        <v>384</v>
       </c>
       <c r="K131" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="L131" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M131" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N131" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O131" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B132" t="s">
-        <v>213</v>
+        <v>362</v>
       </c>
       <c r="C132" t="s">
-        <v>214</v>
+        <v>86</v>
       </c>
       <c r="D132" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E132" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G132" t="s">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="H132" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I132" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J132" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="K132" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L132" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M132" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N132" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O132" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>267</v>
       </c>
       <c r="C133" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="D133" t="s">
+        <v>18</v>
+      </c>
+      <c r="E133" t="s">
+        <v>18</v>
+      </c>
+      <c r="F133" t="s">
+        <v>20</v>
+      </c>
+      <c r="G133" t="s">
+        <v>81</v>
+      </c>
+      <c r="H133" t="s">
+        <v>107</v>
+      </c>
+      <c r="I133" t="s">
+        <v>29</v>
+      </c>
+      <c r="J133" t="s">
+        <v>504</v>
+      </c>
+      <c r="K133" t="s">
         <v>37</v>
       </c>
-      <c r="E133" t="s">
-        <v>18</v>
-      </c>
-      <c r="F133" t="s">
-        <v>498</v>
-      </c>
-      <c r="G133" t="s">
-        <v>499</v>
-      </c>
-      <c r="H133" t="s">
-        <v>44</v>
-      </c>
-      <c r="I133" t="s">
-        <v>22</v>
-      </c>
-      <c r="J133" t="s">
-        <v>500</v>
-      </c>
-      <c r="K133" t="s">
-        <v>501</v>
-      </c>
       <c r="L133" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M133" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N133" t="s">
-        <v>502</v>
+        <v>19</v>
       </c>
       <c r="O133" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B134" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="C134" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="D134" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E134" t="s">
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G134" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H134" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I134" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J134" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K134" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L134" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M134" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N134" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O134" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B135" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="C135" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="D135" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="E135" t="s">
         <v>18</v>
       </c>
       <c r="F135" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G135" t="s">
-        <v>508</v>
+        <v>64</v>
       </c>
       <c r="H135" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I135" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J135" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K135" t="s">
-        <v>300</v>
+        <v>149</v>
       </c>
       <c r="L135" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M135" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N135" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O135" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B136" t="s">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="C136" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="D136" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E136" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F136" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G136" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H136" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I136" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J136" t="s">
-        <v>443</v>
+        <v>513</v>
       </c>
       <c r="K136" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="L136" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M136" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N136" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O136" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B137" t="s">
-        <v>252</v>
+        <v>16</v>
       </c>
       <c r="C137" t="s">
-        <v>253</v>
+        <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E137" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F137" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G137" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="H137" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I137" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J137" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K137" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L137" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M137" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N137" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O137" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B138" t="s">
-        <v>122</v>
+        <v>519</v>
       </c>
       <c r="C138" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="D138" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E138" t="s">
         <v>18</v>
       </c>
       <c r="F138" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G138" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H138" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I138" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J138" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="K138" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L138" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M138" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N138" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O138" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B139" t="s">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="C139" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="E139" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F139" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G139" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="H139" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="I139" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J139" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K139" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="L139" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M139" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N139" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O139" t="s">
-        <v>521</v>
+        <v>524</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>525</v>
+      </c>
+      <c r="B140" t="s">
+        <v>162</v>
+      </c>
+      <c r="C140" t="s">
+        <v>163</v>
+      </c>
+      <c r="D140" t="s">
+        <v>164</v>
+      </c>
+      <c r="E140" t="s">
+        <v>18</v>
+      </c>
+      <c r="F140" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" t="s">
+        <v>81</v>
+      </c>
+      <c r="H140" t="s">
+        <v>107</v>
+      </c>
+      <c r="I140" t="s">
+        <v>29</v>
+      </c>
+      <c r="J140" t="s">
+        <v>526</v>
+      </c>
+      <c r="K140" t="s">
+        <v>97</v>
+      </c>
+      <c r="L140" t="s">
+        <v>19</v>
+      </c>
+      <c r="M140" t="s">
+        <v>19</v>
+      </c>
+      <c r="N140" t="s">
+        <v>19</v>
+      </c>
+      <c r="O140" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>528</v>
+      </c>
+      <c r="B141" t="s">
+        <v>27</v>
+      </c>
+      <c r="C141" t="s">
+        <v>28</v>
+      </c>
+      <c r="D141" t="s">
+        <v>18</v>
+      </c>
+      <c r="E141" t="s">
+        <v>18</v>
+      </c>
+      <c r="F141" t="s">
+        <v>20</v>
+      </c>
+      <c r="G141" t="s">
+        <v>81</v>
+      </c>
+      <c r="H141" t="s">
+        <v>107</v>
+      </c>
+      <c r="I141" t="s">
+        <v>29</v>
+      </c>
+      <c r="J141" t="s">
+        <v>529</v>
+      </c>
+      <c r="K141" t="s">
+        <v>24</v>
+      </c>
+      <c r="L141" t="s">
+        <v>19</v>
+      </c>
+      <c r="M141" t="s">
+        <v>19</v>
+      </c>
+      <c r="N141" t="s">
+        <v>19</v>
+      </c>
+      <c r="O141" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>531</v>
+      </c>
+      <c r="B142" t="s">
+        <v>162</v>
+      </c>
+      <c r="C142" t="s">
+        <v>163</v>
+      </c>
+      <c r="D142" t="s">
+        <v>164</v>
+      </c>
+      <c r="E142" t="s">
+        <v>18</v>
+      </c>
+      <c r="F142" t="s">
+        <v>20</v>
+      </c>
+      <c r="G142" t="s">
+        <v>64</v>
+      </c>
+      <c r="H142" t="s">
+        <v>107</v>
+      </c>
+      <c r="I142" t="s">
+        <v>29</v>
+      </c>
+      <c r="J142" t="s">
+        <v>532</v>
+      </c>
+      <c r="K142" t="s">
+        <v>126</v>
+      </c>
+      <c r="L142" t="s">
+        <v>19</v>
+      </c>
+      <c r="M142" t="s">
+        <v>19</v>
+      </c>
+      <c r="N142" t="s">
+        <v>19</v>
+      </c>
+      <c r="O142" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>534</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" t="s">
+        <v>18</v>
+      </c>
+      <c r="E143" t="s">
+        <v>19</v>
+      </c>
+      <c r="F143" t="s">
+        <v>20</v>
+      </c>
+      <c r="G143" t="s">
+        <v>81</v>
+      </c>
+      <c r="H143" t="s">
+        <v>107</v>
+      </c>
+      <c r="I143" t="s">
+        <v>29</v>
+      </c>
+      <c r="J143" t="s">
+        <v>535</v>
+      </c>
+      <c r="K143" t="s">
+        <v>237</v>
+      </c>
+      <c r="L143" t="s">
+        <v>19</v>
+      </c>
+      <c r="M143" t="s">
+        <v>19</v>
+      </c>
+      <c r="N143" t="s">
+        <v>19</v>
+      </c>
+      <c r="O143" t="s">
+        <v>536</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O138"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,7 +527,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -576,7 +576,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -625,7 +625,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -674,7 +674,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -7121,55 +7121,6 @@
       </c>
       <c r="O137" t="inlineStr"/>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>05/05/2026 10:41:30 AM</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>24688</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>WADE,ADAM</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/31/2026 6:26:45 PM</t>
+          <t>08/06/2026 3:20:23 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -527,7 +527,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -545,22 +545,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/31/2026 5:30:17 PM</t>
+          <t>08/06/2026 10:05:54 AM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -576,7 +576,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -594,7 +594,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/31/2026 9:34:25 AM</t>
+          <t>08/06/2026 9:26:56 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -625,7 +625,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -643,22 +643,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/30/2026 11:38:58 AM</t>
+          <t>08/05/2026 6:03:04 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -674,7 +674,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -692,27 +692,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/29/2026 4:01:22 PM</t>
+          <t>08/05/2026 6:38:38 AM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -723,7 +723,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -741,27 +741,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/28/2026 2:44:19 PM</t>
+          <t>08/03/2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -772,7 +772,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -790,22 +790,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/28/2026 11:43:00 AM</t>
+          <t>08/03/2026 10:34:02 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -821,7 +821,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -839,17 +839,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/26/2026 12:37:34 PM</t>
+          <t>07/31/2026 6:26:45 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -888,17 +888,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/25/2026 5:25:51 PM</t>
+          <t>07/31/2026 5:30:17 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/25/2026 10:23:49 AM</t>
+          <t>07/31/2026 9:34:25 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -986,22 +986,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/24/2026 9:42:30 AM</t>
+          <t>07/30/2026 11:38:58 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/23/2026 11:13:22 AM</t>
+          <t>07/29/2026 4:01:22 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/23/2026 9:14:39 AM</t>
+          <t>07/28/2026 2:44:19 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/22/2026 3:17:16 PM</t>
+          <t>07/28/2026 11:43:00 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1182,22 +1182,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/22/2026 1:14:58 PM</t>
+          <t>07/26/2026 12:37:34 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1231,17 +1231,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/21/2026 4:12:57 AM</t>
+          <t>07/25/2026 5:25:51 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,22 +1280,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/20/2026 6:32:21 PM</t>
+          <t>07/25/2026 10:23:49 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1329,22 +1329,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/20/2026 5:14:06 PM</t>
+          <t>07/24/2026 9:42:30 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1378,22 +1378,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/20/2026 11:21:24 AM</t>
+          <t>07/23/2026 11:13:22 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1427,17 +1427,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/18/2026 5:40:41 PM</t>
+          <t>07/23/2026 9:14:39 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1476,22 +1476,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/18/2026 4:24:58 PM</t>
+          <t>07/22/2026 3:17:16 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/18/2026 7:28:02 AM</t>
+          <t>07/22/2026 1:14:58 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1574,17 +1574,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/17/2026 8:53:39 AM</t>
+          <t>07/21/2026 4:12:57 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1623,27 +1623,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15/2026 7:54:31 PM</t>
+          <t>07/20/2026 6:32:21 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1672,7 +1672,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/15/2026 2:59:24 PM</t>
+          <t>07/20/2026 5:14:06 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1721,22 +1721,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/15/2026 1:48:31 PM</t>
+          <t>07/20/2026 11:21:24 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1770,22 +1770,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/14/2026 6:43:29 PM</t>
+          <t>07/18/2026 5:40:41 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/14/2026 3:47:33 PM</t>
+          <t>07/18/2026 4:24:58 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1868,22 +1868,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/14/2026 3:11:57 PM</t>
+          <t>07/18/2026 7:28:02 AM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1917,27 +1917,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/13/2026 5:16:14 PM</t>
+          <t>07/17/2026 8:53:39 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1966,27 +1966,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/13/2026 4:57:54 PM</t>
+          <t>07/15/2026 7:54:31 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2015,17 +2015,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/13/2026 2:42:02 PM</t>
+          <t>07/15/2026 2:59:24 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2064,22 +2064,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/11/2026 1:18:11 PM</t>
+          <t>07/15/2026 1:48:31 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2095,7 +2095,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2113,17 +2113,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/10/2026 9:53:41 AM</t>
+          <t>07/14/2026 6:43:29 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2144,7 +2144,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2162,22 +2162,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/09/2026 10:54:42 AM</t>
+          <t>07/14/2026 3:47:33 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2193,7 +2193,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -2211,27 +2211,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/09/2026 9:49:26 AM</t>
+          <t>07/14/2026 3:11:57 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2242,7 +2242,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2260,22 +2260,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/07/2026 5:35:06 PM</t>
+          <t>07/13/2026 5:16:14 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2291,7 +2291,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2309,22 +2309,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/06/2026 6:07:40 PM</t>
+          <t>07/13/2026 4:57:54 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2358,17 +2358,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/06/2026 4:04:58 PM</t>
+          <t>07/13/2026 2:42:02 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2407,20 +2407,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/06/2026 12:54:43 PM</t>
+          <t>07/11/2026 1:18:11 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>TREVIZO, ESTABAN I.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -2452,7 +2456,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/05/2026 6:34:14 PM</t>
+          <t>07/10/2026 9:53:41 AM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2501,22 +2505,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/05/2026 10:38:36 AM</t>
+          <t>07/09/2026 10:54:42 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2526,7 +2530,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2540,25 +2544,27 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="n">
-        <v>0.714</v>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/03/2026 1:10:42 PM</t>
+          <t>07/09/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2568,7 +2574,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2597,20 +2603,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/03/2026 11:57:21 AM</t>
+          <t>07/07/2026 5:35:06 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -2642,7 +2652,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/02/2026 12:41:50 PM</t>
+          <t>07/06/2026 6:07:40 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2691,7 +2701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30/2026 3:08:17 PM</t>
+          <t>07/06/2026 4:04:58 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2740,24 +2750,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/29/2026 5:02:30 PM</t>
+          <t>07/06/2026 12:54:43 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -2789,27 +2795,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/29/2026 4:46:11 PM</t>
+          <t>07/05/2026 6:34:14 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2838,20 +2844,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/27/2026 11:52:56 AM</t>
+          <t>07/05/2026 10:38:36 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>FOUNTAIN, RODNEY</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -2859,7 +2869,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2873,32 +2883,30 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N50" t="n">
+        <v>0.714</v>
       </c>
       <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/27/2026 11:42:51 AM</t>
+          <t>07/03/2026 1:10:42 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2932,24 +2940,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/26/2026 2:42:28 PM</t>
+          <t>07/03/2026 11:57:21 AM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -2981,7 +2985,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/26/2026 2:10:46 PM</t>
+          <t>07/02/2026 12:41:50 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3030,17 +3034,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/26/2026 1:33:31 PM</t>
+          <t>06/30/2026 3:08:17 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SCOTT, GRANT</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3079,22 +3083,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/26/2026 10:51:52 AM</t>
+          <t>06/29/2026 5:02:30 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3128,22 +3132,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/25/2026 11:22:39 PM</t>
+          <t>06/29/2026 4:46:11 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3177,24 +3181,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/25/2026 1:38:37 PM</t>
+          <t>06/27/2026 11:52:56 AM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3226,22 +3226,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/25/2026 11:29:51 AM</t>
+          <t>06/27/2026 11:42:51 AM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3275,22 +3275,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/24/2026 5:10:48 PM</t>
+          <t>06/26/2026 2:42:28 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3324,20 +3324,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/24/2026 4:03:42 PM</t>
+          <t>06/26/2026 2:10:46 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>EMERY.SHANE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3369,22 +3373,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/24/2026 5:11:55 AM</t>
+          <t>06/26/2026 1:33:31 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
+          <t>SCOTT, GRANT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3418,17 +3422,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/23/2026 5:11:29 PM</t>
+          <t>06/26/2026 10:51:52 AM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3438,7 +3442,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3467,22 +3471,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/22/2026 4:29:35 PM</t>
+          <t>06/25/2026 11:22:39 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3516,17 +3520,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/22/2026 1:33:02 PM</t>
+          <t>06/25/2026 1:38:37 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3565,27 +3569,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/22/2026 12:51:06 PM</t>
+          <t>06/25/2026 11:29:51 AM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3614,17 +3618,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/21/2026 2:38:22 PM</t>
+          <t>06/24/2026 5:10:48 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3663,7 +3667,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/21/2026 1:24:01 PM</t>
+          <t>06/24/2026 4:03:42 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3708,22 +3712,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/20/2026 12:26:55 PM</t>
+          <t>06/24/2026 5:11:55 AM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KREUTZER, DON</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3757,7 +3761,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/19/2026 6:06:53 PM</t>
+          <t>06/23/2026 5:11:29 PM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3806,22 +3810,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/19/2026 5:32:27 PM</t>
+          <t>06/22/2026 4:29:35 PM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MOORE, ROYCE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3855,22 +3859,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/19/2026 10:12:30 AM</t>
+          <t>06/22/2026 1:33:02 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3904,27 +3908,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/18/2026 12:45:10 PM</t>
+          <t>06/22/2026 12:51:06 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3953,17 +3957,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/18/2026 11:35:17 AM</t>
+          <t>06/21/2026 2:38:22 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4002,24 +4006,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/17/2026 3:18:01 PM</t>
+          <t>06/21/2026 1:24:01 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4051,27 +4051,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/17/2026 1:24:24 PM</t>
+          <t>06/20/2026 12:26:55 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>KREUTZER, DON</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4100,27 +4100,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/17/2026 9:51:05 AM</t>
+          <t>06/19/2026 6:06:53 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4149,22 +4149,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/14/2026 12:51:39 PM</t>
+          <t>06/19/2026 5:32:27 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MOORE, ROYCE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4198,20 +4198,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/13/2026 12:37:03 PM</t>
+          <t>06/19/2026 10:12:30 AM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4243,22 +4247,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/12/2026 6:47:19 PM</t>
+          <t>06/18/2026 12:45:10 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4292,7 +4296,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/12/2026 2:22:37 PM</t>
+          <t>06/18/2026 11:35:17 AM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4341,22 +4345,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/12/2026 10:50:38 AM</t>
+          <t>06/17/2026 3:18:01 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4390,17 +4394,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/11/2026 5:29:52 PM</t>
+          <t>06/17/2026 1:24:24 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4410,7 +4414,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4439,22 +4443,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/11/2026 3:42:27 PM</t>
+          <t>06/17/2026 9:51:05 AM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4488,22 +4492,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/11/2026 10:57:37 AM</t>
+          <t>06/14/2026 12:51:39 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4537,24 +4541,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/10/2026 8:47:02 PM</t>
+          <t>06/13/2026 12:37:03 PM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4586,20 +4586,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/10/2026 2:34:29 PM</t>
+          <t>06/12/2026 6:47:19 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4631,17 +4635,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/10/2026 9:58:07 AM</t>
+          <t>06/12/2026 2:22:37 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4651,7 +4655,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4680,22 +4684,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/09/2026 8:49:37 PM</t>
+          <t>06/12/2026 10:50:38 AM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4729,22 +4733,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/09/2026 5:15:37 PM</t>
+          <t>06/11/2026 5:29:52 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4778,27 +4782,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/09/2026 9:52:33 AM</t>
+          <t>06/11/2026 3:42:27 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4827,22 +4831,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/09/2026 6:09:33 AM</t>
+          <t>06/11/2026 10:57:37 AM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4876,22 +4880,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/08/2026 10:24:03 AM</t>
+          <t>06/10/2026 8:47:02 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4925,24 +4929,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/08/2026 6:36:45 AM</t>
+          <t>06/10/2026 2:34:29 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4974,27 +4974,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/07/2026 10:34:55 PM</t>
+          <t>06/10/2026 9:58:07 AM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5023,22 +5023,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/05/2026 3:56:56 PM</t>
+          <t>06/09/2026 8:49:37 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5072,22 +5072,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/03/2026 5:14:46 PM</t>
+          <t>06/09/2026 5:15:37 PM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5121,27 +5121,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/03/2026 3:43:38 PM</t>
+          <t>06/09/2026 9:52:33 AM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5170,22 +5170,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/03/2026 5:35:42 AM</t>
+          <t>06/09/2026 6:09:33 AM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5219,22 +5219,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/02/2026 1:11:41 PM</t>
+          <t>06/08/2026 10:24:03 AM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5268,7 +5268,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/01/2026 1:21:17 PM</t>
+          <t>06/08/2026 6:36:45 AM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5317,22 +5317,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/01/2026 1:03:09 PM</t>
+          <t>06/07/2026 10:34:55 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5366,27 +5366,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/01/2026 8:29:16 AM</t>
+          <t>06/05/2026 3:56:56 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5415,27 +5415,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>05/31/2026 12:04:28 PM</t>
+          <t>06/03/2026 5:14:46 PM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5464,17 +5464,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>05/30/2026 11:04:14 AM</t>
+          <t>06/03/2026 3:43:38 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5513,22 +5513,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>05/29/2026 4:52:36 PM</t>
+          <t>06/03/2026 5:35:42 AM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5562,22 +5562,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>05/29/2026 11:37:37 AM</t>
+          <t>06/02/2026 1:11:41 PM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5611,22 +5611,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>05/28/2026 12:12:12 PM</t>
+          <t>06/01/2026 1:21:17 PM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5660,22 +5660,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>05/27/2026 4:38:39 PM</t>
+          <t>06/01/2026 1:03:09 PM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5709,27 +5709,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>05/27/2026 11:08:19 AM</t>
+          <t>06/01/2026 8:29:16 AM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5758,27 +5758,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>05/26/2026 3:34:06 PM</t>
+          <t>05/31/2026 12:04:28 PM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5807,17 +5807,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>05/26/2026 3:20:19 PM</t>
+          <t>05/30/2026 11:04:14 AM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -5846,30 +5846,32 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="n">
-        <v>0.586</v>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>05/25/2026 5:35:28 PM</t>
+          <t>05/29/2026 4:52:36 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5903,7 +5905,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>05/25/2026 11:15:21 AM</t>
+          <t>05/29/2026 11:37:37 AM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5952,22 +5954,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>05/24/2026 9:35:31 AM</t>
+          <t>05/28/2026 12:12:12 PM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6001,17 +6003,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>05/22/2026 3:18:28 PM</t>
+          <t>05/27/2026 4:38:39 PM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6050,22 +6052,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>05/21/2026 1:03:45 PM</t>
+          <t>05/27/2026 11:08:19 AM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6099,22 +6101,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>05/20/2026 12:39:26 PM</t>
+          <t>05/26/2026 3:34:06 PM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6148,17 +6150,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>05/20/2026 12:22:51 PM</t>
+          <t>05/26/2026 3:20:19 PM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6168,12 +6170,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -6187,17 +6189,15 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N118" t="n">
+        <v>0.586</v>
       </c>
       <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>05/19/2026 5:24:24 PM</t>
+          <t>05/25/2026 5:35:28 PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>05/19/2026 4:15:44 PM</t>
+          <t>05/25/2026 11:15:21 AM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6295,22 +6295,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>05/19/2026 1:29:17 PM</t>
+          <t>05/24/2026 9:35:31 AM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6344,22 +6344,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>05/18/2026 6:17:08 PM</t>
+          <t>05/22/2026 3:18:28 PM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6393,7 +6393,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>05/18/2026 1:57:44 PM</t>
+          <t>05/21/2026 1:03:45 PM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6442,27 +6442,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>05/18/2026 11:03:11 AM</t>
+          <t>05/20/2026 12:39:26 PM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6491,17 +6491,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>05/17/2026 10:01:54 AM</t>
+          <t>05/20/2026 12:22:51 PM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6540,22 +6540,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>05/15/2026 4:10:22 PM</t>
+          <t>05/19/2026 5:24:24 PM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6589,17 +6589,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>05/15/2026 3:06:50 PM</t>
+          <t>05/19/2026 4:15:44 PM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6638,22 +6638,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>05/14/2026 12:52:19 PM</t>
+          <t>05/19/2026 1:29:17 PM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6687,22 +6687,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>05/14/2026 12:37:30 PM</t>
+          <t>05/18/2026 6:17:08 PM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6736,12 +6736,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>05/13/2026 4:43:40 PM</t>
+          <t>05/18/2026 1:57:44 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6785,22 +6785,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>05/12/2026 4:07:28 PM</t>
+          <t>05/18/2026 11:03:11 AM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6834,22 +6834,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>05/08/2026 7:06:40 PM</t>
+          <t>05/17/2026 10:01:54 AM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6883,22 +6883,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>05/08/2026 9:30:54 AM</t>
+          <t>05/15/2026 4:10:22 PM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6932,20 +6932,24 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>05/07/2026 4:20:38 PM</t>
+          <t>05/15/2026 3:06:50 PM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>TREVIZO, ESTABAN I.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -6977,22 +6981,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>05/07/2026 12:45:01 PM</t>
+          <t>05/14/2026 12:52:19 PM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7026,22 +7030,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>05/06/2026 6:42:51 PM</t>
+          <t>05/14/2026 12:37:30 PM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7075,22 +7079,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>05/05/2026 7:41:30 PM</t>
+          <t>05/13/2026 4:43:40 PM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7121,6 +7125,55 @@
       </c>
       <c r="O137" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>05/12/2026 4:07:28 PM</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>24634</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>KELLY GNEITING</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Following Distance</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O138"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,22 +496,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/06/2026 3:20:23 PM</t>
+          <t>08/14/2026 11:58:42 AM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/06/2026 10:05:54 AM</t>
+          <t>08/14/2026 10:19:19 AM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/06/2026 9:26:56 AM</t>
+          <t>08/13/2026 3:35:07 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -643,32 +643,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/05/2026 6:03:04 PM</t>
+          <t>08/12/2026 6:11:01 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>BRANSCOME, JULIAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -682,37 +682,35 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N5" t="n">
+        <v>0.621</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/05/2026 6:38:38 AM</t>
+          <t>08/11/2026 4:40:14 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -723,7 +721,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -741,22 +739,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/03/2026 12:58:44 PM</t>
+          <t>08/11/2026 1:10:19 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -772,7 +770,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -790,22 +788,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/03/2026 10:34:02 AM</t>
+          <t>08/11/2026 12:08:45 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -821,7 +819,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -839,7 +837,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/31/2026 6:26:45 PM</t>
+          <t>08/10/2026 5:25:42 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -888,22 +886,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/31/2026 5:30:17 PM</t>
+          <t>08/10/2026 12:55:13 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -913,7 +911,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -937,22 +935,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/31/2026 9:34:25 AM</t>
+          <t>08/10/2026 12:42:11 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -986,22 +984,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/30/2026 11:38:58 AM</t>
+          <t>08/09/2026 4:41:43 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1011,7 +1009,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1025,32 +1023,30 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N12" t="n">
+        <v>0.512</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/29/2026 4:01:22 PM</t>
+          <t>08/07/2026 3:48:46 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1084,17 +1080,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/28/2026 2:44:19 PM</t>
+          <t>08/06/2026 3:20:23 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1104,7 +1100,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1133,22 +1129,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/28/2026 11:43:00 AM</t>
+          <t>08/06/2026 10:05:54 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1182,22 +1178,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/26/2026 12:37:34 PM</t>
+          <t>08/06/2026 9:26:56 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1231,17 +1227,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/25/2026 5:25:51 PM</t>
+          <t>08/05/2026 6:03:04 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,22 +1276,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/25/2026 10:23:49 AM</t>
+          <t>08/03/2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1329,22 +1325,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/24/2026 9:42:30 AM</t>
+          <t>08/03/2026 10:34:02 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1378,22 +1374,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/23/2026 11:13:22 AM</t>
+          <t>07/31/2026 6:26:45 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1427,17 +1423,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/23/2026 9:14:39 AM</t>
+          <t>07/31/2026 5:30:17 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1447,7 +1443,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1476,7 +1472,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/22/2026 3:17:16 PM</t>
+          <t>07/31/2026 9:34:25 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1525,17 +1521,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22/2026 1:14:58 PM</t>
+          <t>07/30/2026 11:38:58 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1574,22 +1570,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/21/2026 4:12:57 AM</t>
+          <t>07/29/2026 4:01:22 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1623,17 +1619,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/20/2026 6:32:21 PM</t>
+          <t>07/28/2026 2:44:19 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1643,7 +1639,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1672,22 +1668,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/20/2026 5:14:06 PM</t>
+          <t>07/28/2026 11:43:00 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1721,17 +1717,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/20/2026 11:21:24 AM</t>
+          <t>07/26/2026 12:37:34 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1770,17 +1766,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/18/2026 5:40:41 PM</t>
+          <t>07/25/2026 5:25:51 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1819,22 +1815,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/18/2026 4:24:58 PM</t>
+          <t>07/25/2026 10:23:49 AM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1868,22 +1864,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/18/2026 7:28:02 AM</t>
+          <t>07/24/2026 9:42:30 AM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1917,27 +1913,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/17/2026 8:53:39 AM</t>
+          <t>07/23/2026 11:13:22 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1966,22 +1962,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/15/2026 7:54:31 PM</t>
+          <t>07/23/2026 9:14:39 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2015,7 +2011,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15/2026 2:59:24 PM</t>
+          <t>07/22/2026 3:17:16 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2064,17 +2060,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/15/2026 1:48:31 PM</t>
+          <t>07/22/2026 1:14:58 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2113,22 +2109,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/14/2026 6:43:29 PM</t>
+          <t>07/21/2026 4:12:57 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2162,17 +2158,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/14/2026 3:47:33 PM</t>
+          <t>07/20/2026 6:32:21 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2211,22 +2207,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/14/2026 3:11:57 PM</t>
+          <t>07/20/2026 5:14:06 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2260,22 +2256,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/13/2026 5:16:14 PM</t>
+          <t>07/20/2026 11:21:24 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2309,22 +2305,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/13/2026 4:57:54 PM</t>
+          <t>07/18/2026 5:40:41 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2358,27 +2354,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/13/2026 2:42:02 PM</t>
+          <t>07/18/2026 4:24:58 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2407,22 +2403,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/11/2026 1:18:11 PM</t>
+          <t>07/18/2026 7:28:02 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2456,22 +2452,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/10/2026 9:53:41 AM</t>
+          <t>07/17/2026 8:53:39 AM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2505,17 +2501,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/09/2026 10:54:42 AM</t>
+          <t>07/15/2026 7:54:31 PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2525,7 +2521,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2554,17 +2550,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/09/2026 9:49:26 AM</t>
+          <t>07/15/2026 2:59:24 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2574,7 +2570,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2603,22 +2599,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/07/2026 5:35:06 PM</t>
+          <t>07/15/2026 1:48:31 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2652,7 +2648,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/06/2026 6:07:40 PM</t>
+          <t>07/14/2026 6:43:29 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2701,22 +2697,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/06/2026 4:04:58 PM</t>
+          <t>07/14/2026 3:47:33 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2750,20 +2746,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/06/2026 12:54:43 PM</t>
+          <t>07/14/2026 3:11:57 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -2795,17 +2795,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/05/2026 6:34:14 PM</t>
+          <t>07/13/2026 5:16:14 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2844,22 +2844,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/05/2026 10:38:36 AM</t>
+          <t>07/13/2026 4:57:54 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2883,25 +2883,27 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="n">
-        <v>0.714</v>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/03/2026 1:10:42 PM</t>
+          <t>07/13/2026 2:42:02 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2911,7 +2913,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2940,20 +2942,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/03/2026 11:57:21 AM</t>
+          <t>07/11/2026 1:18:11 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>TREVIZO, ESTABAN I.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -2985,17 +2991,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/02/2026 12:41:50 PM</t>
+          <t>07/10/2026 9:53:41 AM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3005,7 +3011,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3034,17 +3040,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30/2026 3:08:17 PM</t>
+          <t>07/09/2026 10:54:42 AM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,17 +3089,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/29/2026 5:02:30 PM</t>
+          <t>07/09/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3103,7 +3109,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3132,7 +3138,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/29/2026 4:46:11 PM</t>
+          <t>07/07/2026 5:35:06 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3181,20 +3187,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/27/2026 11:52:56 AM</t>
+          <t>07/06/2026 6:07:40 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>EMERY.SHANE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3226,22 +3236,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/27/2026 11:42:51 AM</t>
+          <t>07/06/2026 4:04:58 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3275,24 +3285,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/26/2026 2:42:28 PM</t>
+          <t>07/06/2026 12:54:43 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3324,17 +3330,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/26/2026 2:10:46 PM</t>
+          <t>07/05/2026 6:34:14 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3344,7 +3350,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3373,22 +3379,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/26/2026 1:33:31 PM</t>
+          <t>07/05/2026 10:38:36 AM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SCOTT, GRANT</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3398,7 +3404,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3412,32 +3418,30 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N61" t="n">
+        <v>0.714</v>
       </c>
       <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/26/2026 10:51:52 AM</t>
+          <t>07/03/2026 1:10:42 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3471,24 +3475,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/25/2026 11:22:39 PM</t>
+          <t>07/03/2026 11:57:21 AM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3520,7 +3520,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/25/2026 1:38:37 PM</t>
+          <t>07/02/2026 12:41:50 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3569,22 +3569,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/25/2026 11:29:51 AM</t>
+          <t>06/30/2026 3:08:17 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3618,17 +3618,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/24/2026 5:10:48 PM</t>
+          <t>06/29/2026 5:02:30 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3667,20 +3667,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/24/2026 4:03:42 PM</t>
+          <t>06/29/2026 4:46:11 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3712,24 +3716,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/24/2026 5:11:55 AM</t>
+          <t>06/27/2026 11:52:56 AM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3761,27 +3761,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/23/2026 5:11:29 PM</t>
+          <t>06/27/2026 11:42:51 AM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3810,7 +3810,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/22/2026 4:29:35 PM</t>
+          <t>06/26/2026 2:42:28 PM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3859,17 +3859,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/22/2026 1:33:02 PM</t>
+          <t>06/26/2026 2:10:46 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3908,27 +3908,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/22/2026 12:51:06 PM</t>
+          <t>06/26/2026 1:33:31 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>SCOTT, GRANT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3957,22 +3957,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/21/2026 2:38:22 PM</t>
+          <t>06/26/2026 10:51:52 AM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4006,20 +4006,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/21/2026 1:24:01 PM</t>
+          <t>06/25/2026 11:22:39 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>JELTOV, VLADIMIR K.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>OTR, Safety Pro Test</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4051,17 +4055,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/20/2026 12:26:55 PM</t>
+          <t>06/25/2026 1:38:37 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KREUTZER, DON</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4100,27 +4104,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/19/2026 6:06:53 PM</t>
+          <t>06/25/2026 11:29:51 AM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4149,17 +4153,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/19/2026 5:32:27 PM</t>
+          <t>06/24/2026 5:10:48 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MOORE, ROYCE</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4198,24 +4202,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/19/2026 10:12:30 AM</t>
+          <t>06/24/2026 4:03:42 PM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4247,22 +4247,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/18/2026 12:45:10 PM</t>
+          <t>06/24/2026 5:11:55 AM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4296,27 +4296,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/18/2026 11:35:17 AM</t>
+          <t>06/23/2026 5:11:29 PM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4345,22 +4345,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/17/2026 3:18:01 PM</t>
+          <t>06/22/2026 4:29:35 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4394,27 +4394,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/17/2026 1:24:24 PM</t>
+          <t>06/22/2026 1:33:02 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4443,27 +4443,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/17/2026 9:51:05 AM</t>
+          <t>06/22/2026 12:51:06 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4492,22 +4492,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/14/2026 12:51:39 PM</t>
+          <t>06/21/2026 2:38:22 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4541,12 +4541,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/13/2026 12:37:03 PM</t>
+          <t>06/21/2026 1:24:01 PM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4586,22 +4586,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/12/2026 6:47:19 PM</t>
+          <t>06/20/2026 12:26:55 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>KREUTZER, DON</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4635,27 +4635,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/12/2026 2:22:37 PM</t>
+          <t>06/19/2026 6:06:53 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4684,22 +4684,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/12/2026 10:50:38 AM</t>
+          <t>06/19/2026 5:32:27 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MOORE, ROYCE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4733,22 +4733,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/11/2026 5:29:52 PM</t>
+          <t>06/19/2026 10:12:30 AM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4782,22 +4782,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/11/2026 3:42:27 PM</t>
+          <t>06/18/2026 12:45:10 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4831,22 +4831,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/11/2026 10:57:37 AM</t>
+          <t>06/18/2026 11:35:17 AM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4880,22 +4880,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/10/2026 8:47:02 PM</t>
+          <t>06/17/2026 3:18:01 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4929,23 +4929,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/10/2026 2:34:29 PM</t>
+          <t>06/17/2026 1:24:24 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>MAGEE LONDON, TRESSEL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4974,27 +4978,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/10/2026 9:58:07 AM</t>
+          <t>06/17/2026 9:51:05 AM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5023,17 +5027,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/09/2026 8:49:37 PM</t>
+          <t>06/14/2026 12:51:39 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5072,24 +5076,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/09/2026 5:15:37 PM</t>
+          <t>06/13/2026 12:37:03 PM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5121,27 +5121,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/09/2026 9:52:33 AM</t>
+          <t>06/12/2026 6:47:19 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5170,22 +5170,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/09/2026 6:09:33 AM</t>
+          <t>06/12/2026 2:22:37 PM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5219,22 +5219,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/08/2026 10:24:03 AM</t>
+          <t>06/12/2026 10:50:38 AM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5268,22 +5268,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/08/2026 6:36:45 AM</t>
+          <t>06/11/2026 5:29:52 PM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5317,17 +5317,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/07/2026 10:34:55 PM</t>
+          <t>06/11/2026 3:42:27 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/05/2026 3:56:56 PM</t>
+          <t>06/11/2026 10:57:37 AM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5415,22 +5415,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/03/2026 5:14:46 PM</t>
+          <t>06/10/2026 8:47:02 PM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5464,24 +5464,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06/03/2026 3:43:38 PM</t>
+          <t>06/10/2026 2:34:29 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5513,27 +5509,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>06/03/2026 5:35:42 AM</t>
+          <t>06/10/2026 9:58:07 AM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5562,22 +5558,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>06/02/2026 1:11:41 PM</t>
+          <t>06/09/2026 8:49:37 PM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5611,22 +5607,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>06/01/2026 1:21:17 PM</t>
+          <t>06/09/2026 5:15:37 PM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5660,27 +5656,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06/01/2026 1:03:09 PM</t>
+          <t>06/09/2026 9:52:33 AM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5709,27 +5705,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>06/01/2026 8:29:16 AM</t>
+          <t>06/09/2026 6:09:33 AM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5758,27 +5754,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>05/31/2026 12:04:28 PM</t>
+          <t>06/08/2026 10:24:03 AM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5807,22 +5803,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>05/30/2026 11:04:14 AM</t>
+          <t>06/08/2026 6:36:45 AM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5856,22 +5852,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>05/29/2026 4:52:36 PM</t>
+          <t>06/07/2026 10:34:55 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5905,22 +5901,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>05/29/2026 11:37:37 AM</t>
+          <t>06/05/2026 3:56:56 PM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5954,22 +5950,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>05/28/2026 12:12:12 PM</t>
+          <t>06/03/2026 5:14:46 PM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6003,17 +5999,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>05/27/2026 4:38:39 PM</t>
+          <t>06/03/2026 3:43:38 PM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6052,22 +6048,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>05/27/2026 11:08:19 AM</t>
+          <t>06/03/2026 5:35:42 AM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6101,7 +6097,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>05/26/2026 3:34:06 PM</t>
+          <t>06/02/2026 1:11:41 PM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6150,22 +6146,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>05/26/2026 3:20:19 PM</t>
+          <t>06/01/2026 1:21:17 PM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6175,7 +6171,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -6189,30 +6185,32 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="n">
-        <v>0.586</v>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>05/25/2026 5:35:28 PM</t>
+          <t>06/01/2026 1:03:09 PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6246,17 +6244,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>05/25/2026 11:15:21 AM</t>
+          <t>06/01/2026 8:29:16 AM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6266,7 +6264,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6295,17 +6293,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>05/24/2026 9:35:31 AM</t>
+          <t>05/31/2026 12:04:28 PM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6315,7 +6313,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6344,17 +6342,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>05/22/2026 3:18:28 PM</t>
+          <t>05/30/2026 11:04:14 AM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6393,22 +6391,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>05/21/2026 1:03:45 PM</t>
+          <t>05/29/2026 4:52:36 PM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6442,22 +6440,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>05/20/2026 12:39:26 PM</t>
+          <t>05/29/2026 11:37:37 AM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6491,27 +6489,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>05/20/2026 12:22:51 PM</t>
+          <t>05/28/2026 12:12:12 PM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6540,22 +6538,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>05/19/2026 5:24:24 PM</t>
+          <t>05/27/2026 4:38:39 PM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6589,22 +6587,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>05/19/2026 4:15:44 PM</t>
+          <t>05/27/2026 11:08:19 AM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6638,7 +6636,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>05/19/2026 1:29:17 PM</t>
+          <t>05/26/2026 3:34:06 PM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6687,22 +6685,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>05/18/2026 6:17:08 PM</t>
+          <t>05/26/2026 3:20:19 PM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6712,7 +6710,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -6726,17 +6724,15 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N129" t="n">
+        <v>0.586</v>
       </c>
       <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>05/18/2026 1:57:44 PM</t>
+          <t>05/25/2026 5:35:28 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6785,17 +6781,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>05/18/2026 11:03:11 AM</t>
+          <t>05/25/2026 11:15:21 AM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6805,7 +6801,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6834,7 +6830,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>05/17/2026 10:01:54 AM</t>
+          <t>05/24/2026 9:35:31 AM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6883,17 +6879,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>05/15/2026 4:10:22 PM</t>
+          <t>05/22/2026 3:18:28 PM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6932,22 +6928,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>05/15/2026 3:06:50 PM</t>
+          <t>05/21/2026 1:03:45 PM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6981,12 +6977,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>05/14/2026 12:52:19 PM</t>
+          <t>05/20/2026 12:39:26 PM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7030,17 +7026,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>05/14/2026 12:37:30 PM</t>
+          <t>05/20/2026 12:22:51 PM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7050,7 +7046,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7079,12 +7075,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>05/13/2026 4:43:40 PM</t>
+          <t>05/19/2026 5:24:24 PM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7128,27 +7124,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>05/12/2026 4:07:28 PM</t>
+          <t>05/19/2026 4:15:44 PM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7174,6 +7170,55 @@
       </c>
       <c r="O138" t="inlineStr"/>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>05/19/2026 1:29:17 PM</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>23470</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JELTOV, VLADIMIR K.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>OTR, Safety Pro Test</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Following Distance</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,22 +496,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/14/2026 11:58:42 AM</t>
+          <t>08/20/2026 5:30:05 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -545,22 +545,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/14/2026 10:19:19 AM</t>
+          <t>08/20/2026 2:15:19 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -594,17 +594,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/13/2026 3:35:07 PM</t>
+          <t>08/20/2026 5:42:43 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -643,32 +643,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/12/2026 6:11:01 PM</t>
+          <t>08/19/2026 6:50:12 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BRANSCOME, JULIAN</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -682,25 +682,27 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>0.621</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/11/2026 4:40:14 PM</t>
+          <t>08/18/2026 5:49:15 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -710,18 +712,18 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -729,32 +731,30 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N6" t="n">
+        <v>0.515</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/11/2026 1:10:19 PM</t>
+          <t>08/18/2026 7:13:51 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -764,13 +764,13 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -788,27 +788,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/11/2026 12:08:45 PM</t>
+          <t>08/17/2026 10:04:29 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -819,7 +819,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -837,22 +837,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/10/2026 5:25:42 PM</t>
+          <t>08/16/2026 2:27:54 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -862,13 +862,13 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -876,17 +876,15 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N9" t="n">
+        <v>0.515</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/10/2026 12:55:13 PM</t>
+          <t>08/14/2026 11:58:42 AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -911,13 +909,13 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -935,7 +933,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/10/2026 12:42:11 PM</t>
+          <t>08/14/2026 10:19:19 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -966,7 +964,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -984,22 +982,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/09/2026 4:41:43 PM</t>
+          <t>08/13/2026 3:35:07 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1009,13 +1007,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1023,46 +1021,48 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>0.512</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/07/2026 3:48:46 PM</t>
+          <t>08/12/2026 6:11:01 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>BRANSCOME, JULIAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1070,32 +1070,30 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N13" t="n">
+        <v>0.621</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/06/2026 3:20:23 PM</t>
+          <t>08/11/2026 4:40:14 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1129,22 +1127,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/06/2026 10:05:54 AM</t>
+          <t>08/11/2026 1:10:19 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1178,22 +1176,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/06/2026 9:26:56 AM</t>
+          <t>08/11/2026 12:08:45 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1227,7 +1225,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/05/2026 6:03:04 PM</t>
+          <t>08/10/2026 5:25:42 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1276,17 +1274,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/03/2026 12:58:44 PM</t>
+          <t>08/10/2026 12:55:13 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1301,7 +1299,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1325,22 +1323,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/03/2026 10:34:02 AM</t>
+          <t>08/10/2026 12:42:11 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1374,17 +1372,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/31/2026 6:26:45 PM</t>
+          <t>08/09/2026 4:41:43 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1399,7 +1397,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1413,27 +1411,25 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N20" t="n">
+        <v>0.512</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/31/2026 5:30:17 PM</t>
+          <t>08/07/2026 3:48:46 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1472,22 +1468,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/31/2026 9:34:25 AM</t>
+          <t>08/06/2026 3:20:23 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1521,22 +1517,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/30/2026 11:38:58 AM</t>
+          <t>08/06/2026 10:05:54 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1570,7 +1566,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/29/2026 4:01:22 PM</t>
+          <t>08/06/2026 9:26:56 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1619,17 +1615,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/28/2026 2:44:19 PM</t>
+          <t>08/05/2026 6:03:04 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1639,7 +1635,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1668,7 +1664,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/28/2026 11:43:00 AM</t>
+          <t>08/03/2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1717,22 +1713,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/26/2026 12:37:34 PM</t>
+          <t>08/03/2026 10:34:02 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1766,17 +1762,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/25/2026 5:25:51 PM</t>
+          <t>07/31/2026 6:26:45 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1815,22 +1811,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/25/2026 10:23:49 AM</t>
+          <t>07/31/2026 5:30:17 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1864,22 +1860,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/24/2026 9:42:30 AM</t>
+          <t>07/31/2026 9:34:25 AM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1913,17 +1909,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/23/2026 11:13:22 AM</t>
+          <t>07/30/2026 11:38:58 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1962,27 +1958,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/23/2026 9:14:39 AM</t>
+          <t>07/29/2026 4:01:22 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2011,27 +2007,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/22/2026 3:17:16 PM</t>
+          <t>07/28/2026 2:44:19 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2060,22 +2056,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/22/2026 1:14:58 PM</t>
+          <t>07/28/2026 11:43:00 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2109,17 +2105,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/21/2026 4:12:57 AM</t>
+          <t>07/26/2026 12:37:34 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2158,17 +2154,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/20/2026 6:32:21 PM</t>
+          <t>07/25/2026 5:25:51 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2207,7 +2203,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/20/2026 5:14:06 PM</t>
+          <t>07/25/2026 10:23:49 AM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2256,22 +2252,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/20/2026 11:21:24 AM</t>
+          <t>07/24/2026 9:42:30 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2305,22 +2301,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/18/2026 5:40:41 PM</t>
+          <t>07/23/2026 11:13:22 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2354,17 +2350,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/18/2026 4:24:58 PM</t>
+          <t>07/23/2026 9:14:39 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2374,7 +2370,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2403,17 +2399,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/18/2026 7:28:02 AM</t>
+          <t>07/22/2026 3:17:16 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2452,27 +2448,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/17/2026 8:53:39 AM</t>
+          <t>07/22/2026 1:14:58 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2501,27 +2497,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/15/2026 7:54:31 PM</t>
+          <t>07/21/2026 4:12:57 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2550,22 +2546,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/15/2026 2:59:24 PM</t>
+          <t>07/20/2026 6:32:21 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2599,17 +2595,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/15/2026 1:48:31 PM</t>
+          <t>07/20/2026 5:14:06 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2648,22 +2644,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/14/2026 6:43:29 PM</t>
+          <t>07/20/2026 11:21:24 AM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2697,17 +2693,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/14/2026 3:47:33 PM</t>
+          <t>07/18/2026 5:40:41 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2746,22 +2742,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/14/2026 3:11:57 PM</t>
+          <t>07/18/2026 4:24:58 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2795,17 +2791,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/13/2026 5:16:14 PM</t>
+          <t>07/18/2026 7:28:02 AM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2844,27 +2840,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/13/2026 4:57:54 PM</t>
+          <t>07/17/2026 8:53:39 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2893,7 +2889,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/13/2026 2:42:02 PM</t>
+          <t>07/15/2026 7:54:31 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2942,22 +2938,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/11/2026 1:18:11 PM</t>
+          <t>07/15/2026 2:59:24 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2991,17 +2987,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/10/2026 9:53:41 AM</t>
+          <t>07/15/2026 1:48:31 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3011,7 +3007,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3040,17 +3036,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/09/2026 10:54:42 AM</t>
+          <t>07/14/2026 6:43:29 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3089,27 +3085,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/09/2026 9:49:26 AM</t>
+          <t>07/14/2026 3:47:33 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3138,7 +3134,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/07/2026 5:35:06 PM</t>
+          <t>07/14/2026 3:11:57 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3187,7 +3183,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/06/2026 6:07:40 PM</t>
+          <t>07/13/2026 5:16:14 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3236,22 +3232,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/06/2026 4:04:58 PM</t>
+          <t>07/13/2026 4:57:54 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3285,23 +3281,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/06/2026 12:54:43 PM</t>
+          <t>07/13/2026 2:42:02 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>NUNEZ, WALLY</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3330,27 +3330,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/05/2026 6:34:14 PM</t>
+          <t>07/11/2026 1:18:11 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3379,32 +3379,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/05/2026 10:38:36 AM</t>
+          <t>07/10/2026 9:53:41 AM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3418,25 +3418,27 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
-        <v>0.714</v>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/03/2026 1:10:42 PM</t>
+          <t>07/09/2026 10:54:42 AM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,23 +3477,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/03/2026 11:57:21 AM</t>
+          <t>07/09/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>NUNEZ, WALLY</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3520,22 +3526,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/02/2026 12:41:50 PM</t>
+          <t>07/07/2026 5:35:06 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3569,17 +3575,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/30/2026 3:08:17 PM</t>
+          <t>07/06/2026 6:07:40 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3618,7 +3624,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/29/2026 5:02:30 PM</t>
+          <t>07/06/2026 4:04:58 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3667,24 +3673,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/29/2026 4:46:11 PM</t>
+          <t>07/06/2026 12:54:43 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3716,23 +3718,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/27/2026 11:52:56 AM</t>
+          <t>07/05/2026 6:34:14 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>KELLY GNEITING</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3761,22 +3767,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/27/2026 11:42:51 AM</t>
+          <t>07/05/2026 10:38:36 AM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3786,7 +3792,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3800,32 +3806,30 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N69" t="n">
+        <v>0.714</v>
       </c>
       <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/26/2026 2:42:28 PM</t>
+          <t>07/03/2026 1:10:42 PM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3859,24 +3863,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/26/2026 2:10:46 PM</t>
+          <t>07/03/2026 11:57:21 AM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3908,17 +3908,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/26/2026 1:33:31 PM</t>
+          <t>07/02/2026 12:41:50 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SCOTT, GRANT</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3957,22 +3957,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/26/2026 10:51:52 AM</t>
+          <t>06/30/2026 3:08:17 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4006,22 +4006,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/25/2026 11:22:39 PM</t>
+          <t>06/29/2026 5:02:30 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4055,22 +4055,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/25/2026 1:38:37 PM</t>
+          <t>06/29/2026 4:46:11 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4104,24 +4104,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/25/2026 11:29:51 AM</t>
+          <t>06/27/2026 11:52:56 AM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4153,22 +4149,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/24/2026 5:10:48 PM</t>
+          <t>06/27/2026 11:42:51 AM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4202,20 +4198,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/24/2026 4:03:42 PM</t>
+          <t>06/26/2026 2:42:28 PM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4247,22 +4247,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/24/2026 5:11:55 AM</t>
+          <t>06/26/2026 2:10:46 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4296,27 +4296,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/23/2026 5:11:29 PM</t>
+          <t>06/26/2026 1:33:31 PM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>SCOTT, GRANT</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4345,22 +4345,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/22/2026 4:29:35 PM</t>
+          <t>06/26/2026 10:51:52 AM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4394,22 +4394,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/22/2026 1:33:02 PM</t>
+          <t>06/25/2026 11:22:39 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4443,27 +4443,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/22/2026 12:51:06 PM</t>
+          <t>06/25/2026 1:38:37 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4492,22 +4492,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/21/2026 2:38:22 PM</t>
+          <t>06/25/2026 11:29:51 AM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4541,20 +4541,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/21/2026 1:24:01 PM</t>
+          <t>06/24/2026 5:10:48 PM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>EMERY.SHANE</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4586,24 +4590,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/20/2026 12:26:55 PM</t>
+          <t>06/24/2026 4:03:42 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KREUTZER, DON</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4635,27 +4635,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/19/2026 6:06:53 PM</t>
+          <t>06/24/2026 5:11:55 AM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4684,27 +4684,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/19/2026 5:32:27 PM</t>
+          <t>06/23/2026 5:11:29 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MOORE, ROYCE</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4733,7 +4733,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/19/2026 10:12:30 AM</t>
+          <t>06/22/2026 4:29:35 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4782,22 +4782,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/18/2026 12:45:10 PM</t>
+          <t>06/22/2026 1:33:02 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4831,27 +4831,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/18/2026 11:35:17 AM</t>
+          <t>06/22/2026 12:51:06 PM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4880,17 +4880,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/17/2026 3:18:01 PM</t>
+          <t>06/21/2026 2:38:22 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4929,27 +4929,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/17/2026 1:24:24 PM</t>
+          <t>06/21/2026 1:24:01 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4978,22 +4974,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/17/2026 9:51:05 AM</t>
+          <t>06/20/2026 12:26:55 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>KREUTZER, DON</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5027,17 +5023,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/14/2026 12:51:39 PM</t>
+          <t>06/19/2026 6:06:53 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5047,7 +5043,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5076,20 +5072,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/13/2026 12:37:03 PM</t>
+          <t>06/19/2026 5:32:27 PM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>MOORE, ROYCE</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5121,7 +5121,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/12/2026 6:47:19 PM</t>
+          <t>06/19/2026 10:12:30 AM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5170,22 +5170,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/12/2026 2:22:37 PM</t>
+          <t>06/18/2026 12:45:10 PM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5219,22 +5219,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/12/2026 10:50:38 AM</t>
+          <t>06/18/2026 11:35:17 AM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5268,22 +5268,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/11/2026 5:29:52 PM</t>
+          <t>06/17/2026 3:18:01 PM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5317,17 +5317,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/11/2026 3:42:27 PM</t>
+          <t>06/17/2026 1:24:24 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/11/2026 10:57:37 AM</t>
+          <t>06/17/2026 9:51:05 AM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5415,22 +5415,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/10/2026 8:47:02 PM</t>
+          <t>06/14/2026 12:51:39 PM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5464,7 +5464,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06/10/2026 2:34:29 PM</t>
+          <t>06/13/2026 12:37:03 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5509,27 +5509,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>06/10/2026 9:58:07 AM</t>
+          <t>06/12/2026 6:47:19 PM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5558,22 +5558,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>06/09/2026 8:49:37 PM</t>
+          <t>06/12/2026 2:22:37 PM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5607,7 +5607,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>06/09/2026 5:15:37 PM</t>
+          <t>06/12/2026 10:50:38 AM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5656,27 +5656,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06/09/2026 9:52:33 AM</t>
+          <t>06/11/2026 5:29:52 PM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5705,22 +5705,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>06/09/2026 6:09:33 AM</t>
+          <t>06/11/2026 3:42:27 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5754,22 +5754,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>06/08/2026 10:24:03 AM</t>
+          <t>06/11/2026 10:57:37 AM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5803,22 +5803,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>06/08/2026 6:36:45 AM</t>
+          <t>06/10/2026 8:47:02 PM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5852,24 +5852,20 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>06/07/2026 10:34:55 PM</t>
+          <t>06/10/2026 2:34:29 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5901,27 +5897,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>06/05/2026 3:56:56 PM</t>
+          <t>06/10/2026 9:58:07 AM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5950,22 +5946,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>06/03/2026 5:14:46 PM</t>
+          <t>06/09/2026 8:49:37 PM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5999,22 +5995,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>06/03/2026 3:43:38 PM</t>
+          <t>06/09/2026 5:15:37 PM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6048,27 +6044,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>06/03/2026 5:35:42 AM</t>
+          <t>06/09/2026 9:52:33 AM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6097,22 +6093,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06/02/2026 1:11:41 PM</t>
+          <t>06/09/2026 6:09:33 AM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6146,22 +6142,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>06/01/2026 1:21:17 PM</t>
+          <t>06/08/2026 10:24:03 AM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6195,22 +6191,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>06/01/2026 1:03:09 PM</t>
+          <t>06/08/2026 6:36:45 AM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6244,17 +6240,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>06/01/2026 8:29:16 AM</t>
+          <t>06/07/2026 10:34:55 PM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6264,7 +6260,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6293,27 +6289,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>05/31/2026 12:04:28 PM</t>
+          <t>06/05/2026 3:56:56 PM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6342,22 +6338,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>05/30/2026 11:04:14 AM</t>
+          <t>06/03/2026 5:14:46 PM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6391,22 +6387,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>05/29/2026 4:52:36 PM</t>
+          <t>06/03/2026 3:43:38 PM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6440,7 +6436,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>05/29/2026 11:37:37 AM</t>
+          <t>06/03/2026 5:35:42 AM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6489,7 +6485,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>05/28/2026 12:12:12 PM</t>
+          <t>06/02/2026 1:11:41 PM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6538,22 +6534,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>05/27/2026 4:38:39 PM</t>
+          <t>06/01/2026 1:21:17 PM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6587,7 +6583,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>05/27/2026 11:08:19 AM</t>
+          <t>06/01/2026 1:03:09 PM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6636,27 +6632,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>05/26/2026 3:34:06 PM</t>
+          <t>06/01/2026 8:29:16 AM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6685,17 +6681,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>05/26/2026 3:20:19 PM</t>
+          <t>05/31/2026 12:04:28 PM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6705,12 +6701,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -6724,30 +6720,32 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="n">
-        <v>0.586</v>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>05/25/2026 5:35:28 PM</t>
+          <t>05/30/2026 11:04:14 AM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6781,22 +6779,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>05/25/2026 11:15:21 AM</t>
+          <t>05/29/2026 4:52:36 PM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6830,7 +6828,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>05/24/2026 9:35:31 AM</t>
+          <t>05/29/2026 11:37:37 AM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6879,22 +6877,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>05/22/2026 3:18:28 PM</t>
+          <t>05/28/2026 12:12:12 PM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6928,22 +6926,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>05/21/2026 1:03:45 PM</t>
+          <t>05/27/2026 4:38:39 PM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6977,22 +6975,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>05/20/2026 12:39:26 PM</t>
+          <t>05/27/2026 11:08:19 AM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7026,27 +7024,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>05/20/2026 12:22:51 PM</t>
+          <t>05/26/2026 3:34:06 PM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7075,22 +7073,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>05/19/2026 5:24:24 PM</t>
+          <t>05/26/2026 3:20:19 PM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7100,7 +7098,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -7114,110 +7112,10 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N137" t="n">
+        <v>0.586</v>
       </c>
       <c r="O137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>05/19/2026 4:15:44 PM</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>24688</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>WADE,ADAM</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>05/19/2026 1:29:17 PM</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>23470</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/20/2026 5:30:05 PM</t>
+          <t>08/21/2026 7:22:26 AM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -545,22 +545,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/20/2026 2:15:19 PM</t>
+          <t>08/20/2026 5:30:05 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -594,17 +594,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/20/2026 5:42:43 AM</t>
+          <t>08/20/2026 2:15:19 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -643,22 +643,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/19/2026 6:50:12 PM</t>
+          <t>08/20/2026 5:42:43 AM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,32 +692,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/18/2026 5:49:15 PM</t>
+          <t>08/19/2026 6:50:12 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -731,40 +731,42 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>0.515</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/18/2026 7:13:51 AM</t>
+          <t>08/18/2026 5:49:15 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -778,42 +780,40 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N7" t="n">
+        <v>0.515</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/17/2026 10:04:29 AM</t>
+          <t>08/18/2026 7:13:51 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -837,32 +837,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/16/2026 2:27:54 PM</t>
+          <t>08/17/2026 10:04:29 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -876,25 +876,27 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>0.515</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/14/2026 11:58:42 AM</t>
+          <t>08/16/2026 2:27:54 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -909,7 +911,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -923,32 +925,30 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N10" t="n">
+        <v>0.515</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/14/2026 10:19:19 AM</t>
+          <t>08/14/2026 11:58:42 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -982,22 +982,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/13/2026 3:35:07 PM</t>
+          <t>08/14/2026 10:19:19 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1031,17 +1031,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/12/2026 6:11:01 PM</t>
+          <t>08/13/2026 3:35:07 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BRANSCOME, JULIAN</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1070,25 +1070,27 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>0.621</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/11/2026 4:40:14 PM</t>
+          <t>08/12/2026 6:11:01 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>BRANSCOME, JULIAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1098,18 +1100,18 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1117,27 +1119,25 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N14" t="n">
+        <v>0.621</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/11/2026 1:10:19 PM</t>
+          <t>08/11/2026 4:40:14 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,22 +1176,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/11/2026 12:08:45 PM</t>
+          <t>08/11/2026 1:10:19 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1225,22 +1225,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/10/2026 5:25:42 PM</t>
+          <t>08/11/2026 12:08:45 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1274,22 +1274,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/10/2026 12:55:13 PM</t>
+          <t>08/10/2026 5:25:42 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1323,22 +1323,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/10/2026 12:42:11 PM</t>
+          <t>08/10/2026 12:55:13 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/09/2026 4:41:43 PM</t>
+          <t>08/10/2026 12:42:11 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1411,25 +1411,27 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>0.512</v>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/07/2026 3:48:46 PM</t>
+          <t>08/09/2026 4:41:43 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1444,7 +1446,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1458,17 +1460,15 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N21" t="n">
+        <v>0.512</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/06/2026 3:20:23 PM</t>
+          <t>08/07/2026 3:48:46 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1517,22 +1517,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/06/2026 10:05:54 AM</t>
+          <t>08/06/2026 3:20:23 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1566,22 +1566,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/06/2026 9:26:56 AM</t>
+          <t>08/06/2026 10:05:54 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1615,22 +1615,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/05/2026 6:03:04 PM</t>
+          <t>08/06/2026 9:26:56 AM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1664,22 +1664,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/03/2026 12:58:44 PM</t>
+          <t>08/05/2026 6:03:04 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1713,22 +1713,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/03/2026 10:34:02 AM</t>
+          <t>08/03/2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1762,22 +1762,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/31/2026 6:26:45 PM</t>
+          <t>08/03/2026 10:34:02 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/31/2026 5:30:17 PM</t>
+          <t>07/31/2026 6:26:45 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1860,22 +1860,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/31/2026 9:34:25 AM</t>
+          <t>07/31/2026 5:30:17 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/30/2026 11:38:58 AM</t>
+          <t>07/31/2026 9:34:25 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1958,17 +1958,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/29/2026 4:01:22 PM</t>
+          <t>07/30/2026 11:38:58 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2007,27 +2007,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/28/2026 2:44:19 PM</t>
+          <t>07/29/2026 4:01:22 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2056,27 +2056,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/28/2026 11:43:00 AM</t>
+          <t>07/28/2026 2:44:19 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2105,22 +2105,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/26/2026 12:37:34 PM</t>
+          <t>07/28/2026 11:43:00 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2154,17 +2154,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/25/2026 5:25:51 PM</t>
+          <t>07/26/2026 12:37:34 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2203,22 +2203,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/25/2026 10:23:49 AM</t>
+          <t>07/25/2026 5:25:51 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2252,22 +2252,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/24/2026 9:42:30 AM</t>
+          <t>07/25/2026 10:23:49 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2301,22 +2301,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/23/2026 11:13:22 AM</t>
+          <t>07/24/2026 9:42:30 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2350,27 +2350,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/23/2026 9:14:39 AM</t>
+          <t>07/23/2026 11:13:22 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2399,27 +2399,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/22/2026 3:17:16 PM</t>
+          <t>07/23/2026 9:14:39 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2448,17 +2448,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/22/2026 1:14:58 PM</t>
+          <t>07/22/2026 3:17:16 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2497,22 +2497,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/21/2026 4:12:57 AM</t>
+          <t>07/22/2026 1:14:58 PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2546,17 +2546,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/20/2026 6:32:21 PM</t>
+          <t>07/21/2026 4:12:57 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2595,22 +2595,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/20/2026 5:14:06 PM</t>
+          <t>07/20/2026 6:32:21 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2644,22 +2644,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/20/2026 11:21:24 AM</t>
+          <t>07/20/2026 5:14:06 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2693,17 +2693,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/18/2026 5:40:41 PM</t>
+          <t>07/20/2026 11:21:24 AM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2742,17 +2742,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/18/2026 4:24:58 PM</t>
+          <t>07/18/2026 5:40:41 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2791,22 +2791,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/18/2026 7:28:02 AM</t>
+          <t>07/18/2026 4:24:58 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2840,27 +2840,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/17/2026 8:53:39 AM</t>
+          <t>07/18/2026 7:28:02 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2889,22 +2889,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/15/2026 7:54:31 PM</t>
+          <t>07/17/2026 8:53:39 AM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2938,17 +2938,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/15/2026 2:59:24 PM</t>
+          <t>07/15/2026 7:54:31 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2987,17 +2987,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/15/2026 1:48:31 PM</t>
+          <t>07/15/2026 2:59:24 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3036,17 +3036,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/14/2026 6:43:29 PM</t>
+          <t>07/15/2026 1:48:31 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3085,22 +3085,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/14/2026 3:47:33 PM</t>
+          <t>07/14/2026 6:43:29 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3134,22 +3134,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/14/2026 3:11:57 PM</t>
+          <t>07/14/2026 3:47:33 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3183,22 +3183,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/13/2026 5:16:14 PM</t>
+          <t>07/14/2026 3:11:57 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3232,22 +3232,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/13/2026 4:57:54 PM</t>
+          <t>07/13/2026 5:16:14 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3281,27 +3281,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/13/2026 2:42:02 PM</t>
+          <t>07/13/2026 4:57:54 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3330,27 +3330,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/11/2026 1:18:11 PM</t>
+          <t>07/13/2026 2:42:02 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3379,27 +3379,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/10/2026 9:53:41 AM</t>
+          <t>07/11/2026 1:18:11 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3428,17 +3428,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/09/2026 10:54:42 AM</t>
+          <t>07/10/2026 9:53:41 AM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3477,17 +3477,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/09/2026 9:49:26 AM</t>
+          <t>07/09/2026 10:54:42 AM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3526,27 +3526,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/07/2026 5:35:06 PM</t>
+          <t>07/09/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3575,22 +3575,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/06/2026 6:07:40 PM</t>
+          <t>07/07/2026 5:35:06 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3624,17 +3624,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/06/2026 4:04:58 PM</t>
+          <t>07/06/2026 6:07:40 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3673,20 +3673,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/06/2026 12:54:43 PM</t>
+          <t>07/06/2026 4:04:58 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>CLARK, KC</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3718,27 +3722,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/05/2026 6:34:14 PM</t>
+          <t>07/06/2026 12:54:43 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3767,32 +3767,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/05/2026 10:38:36 AM</t>
+          <t>07/05/2026 6:34:14 PM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3806,30 +3806,32 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
-        <v>0.714</v>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/03/2026 1:10:42 PM</t>
+          <t>07/05/2026 10:38:36 AM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3839,7 +3841,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3853,30 +3855,32 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N70" t="n">
+        <v>0.714</v>
       </c>
       <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/03/2026 11:57:21 AM</t>
+          <t>07/03/2026 1:10:42 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>EMERY.SHANE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3908,24 +3912,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/02/2026 12:41:50 PM</t>
+          <t>07/03/2026 11:57:21 AM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3957,17 +3957,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/30/2026 3:08:17 PM</t>
+          <t>07/02/2026 12:41:50 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/29/2026 5:02:30 PM</t>
+          <t>06/30/2026 3:08:17 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4055,22 +4055,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/29/2026 4:46:11 PM</t>
+          <t>06/29/2026 5:02:30 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4104,20 +4104,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/27/2026 11:52:56 AM</t>
+          <t>06/29/2026 4:46:11 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4149,24 +4153,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/27/2026 11:42:51 AM</t>
+          <t>06/27/2026 11:52:56 AM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4198,22 +4198,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/26/2026 2:42:28 PM</t>
+          <t>06/27/2026 11:42:51 AM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4247,22 +4247,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/26/2026 2:10:46 PM</t>
+          <t>06/26/2026 2:42:28 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4296,17 +4296,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/26/2026 1:33:31 PM</t>
+          <t>06/26/2026 2:10:46 PM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SCOTT, GRANT</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4345,22 +4345,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/26/2026 10:51:52 AM</t>
+          <t>06/26/2026 1:33:31 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>SCOTT, GRANT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4394,22 +4394,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/25/2026 11:22:39 PM</t>
+          <t>06/26/2026 10:51:52 AM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4443,22 +4443,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/25/2026 1:38:37 PM</t>
+          <t>06/25/2026 11:22:39 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4492,22 +4492,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/25/2026 11:29:51 AM</t>
+          <t>06/25/2026 1:38:37 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4541,22 +4541,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/24/2026 5:10:48 PM</t>
+          <t>06/25/2026 11:29:51 AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4590,20 +4590,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/24/2026 4:03:42 PM</t>
+          <t>06/24/2026 5:10:48 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>EMERY.SHANE</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4635,24 +4639,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/24/2026 5:11:55 AM</t>
+          <t>06/24/2026 4:03:42 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4684,27 +4684,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/23/2026 5:11:29 PM</t>
+          <t>06/24/2026 5:11:55 AM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4733,27 +4733,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/22/2026 4:29:35 PM</t>
+          <t>06/23/2026 5:11:29 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4782,22 +4782,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/22/2026 1:33:02 PM</t>
+          <t>06/22/2026 4:29:35 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4831,27 +4831,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/22/2026 12:51:06 PM</t>
+          <t>06/22/2026 1:33:02 PM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4880,27 +4880,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/21/2026 2:38:22 PM</t>
+          <t>06/22/2026 12:51:06 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4929,20 +4929,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/21/2026 1:24:01 PM</t>
+          <t>06/21/2026 2:38:22 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>CLARK, KC</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4974,24 +4978,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/20/2026 12:26:55 PM</t>
+          <t>06/21/2026 1:24:01 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KREUTZER, DON</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5023,27 +5023,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/19/2026 6:06:53 PM</t>
+          <t>06/20/2026 12:26:55 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>KREUTZER, DON</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5072,27 +5072,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/19/2026 5:32:27 PM</t>
+          <t>06/19/2026 6:06:53 PM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MOORE, ROYCE</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5121,22 +5121,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/19/2026 10:12:30 AM</t>
+          <t>06/19/2026 5:32:27 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>MOORE, ROYCE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5170,22 +5170,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/18/2026 12:45:10 PM</t>
+          <t>06/19/2026 10:12:30 AM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5219,22 +5219,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/18/2026 11:35:17 AM</t>
+          <t>06/18/2026 12:45:10 PM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5268,7 +5268,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/17/2026 3:18:01 PM</t>
+          <t>06/18/2026 11:35:17 AM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5317,27 +5317,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/17/2026 1:24:24 PM</t>
+          <t>06/17/2026 3:18:01 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5366,27 +5366,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/17/2026 9:51:05 AM</t>
+          <t>06/17/2026 1:24:24 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5415,22 +5415,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/14/2026 12:51:39 PM</t>
+          <t>06/17/2026 9:51:05 AM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5464,20 +5464,24 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06/13/2026 12:37:03 PM</t>
+          <t>06/14/2026 12:51:39 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>WADE,ADAM</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5509,24 +5513,20 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>06/12/2026 6:47:19 PM</t>
+          <t>06/13/2026 12:37:03 PM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5558,22 +5558,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>06/12/2026 2:22:37 PM</t>
+          <t>06/12/2026 6:47:19 PM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5607,22 +5607,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>06/12/2026 10:50:38 AM</t>
+          <t>06/12/2026 2:22:37 PM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5656,22 +5656,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06/11/2026 5:29:52 PM</t>
+          <t>06/12/2026 10:50:38 AM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5705,17 +5705,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>06/11/2026 3:42:27 PM</t>
+          <t>06/11/2026 5:29:52 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5754,22 +5754,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>06/11/2026 10:57:37 AM</t>
+          <t>06/11/2026 3:42:27 PM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5803,7 +5803,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>06/10/2026 8:47:02 PM</t>
+          <t>06/11/2026 10:57:37 AM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5852,20 +5852,24 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>06/10/2026 2:34:29 PM</t>
+          <t>06/10/2026 8:47:02 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>JELTOV, VLADIMIR K.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>OTR, Safety Pro Test</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5897,27 +5901,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>06/10/2026 9:58:07 AM</t>
+          <t>06/10/2026 2:34:29 PM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5946,27 +5946,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>06/09/2026 8:49:37 PM</t>
+          <t>06/10/2026 9:58:07 AM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5995,22 +5995,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>06/09/2026 5:15:37 PM</t>
+          <t>06/09/2026 8:49:37 PM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6044,27 +6044,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>06/09/2026 9:52:33 AM</t>
+          <t>06/09/2026 5:15:37 PM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6093,27 +6093,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06/09/2026 6:09:33 AM</t>
+          <t>06/09/2026 9:52:33 AM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6142,22 +6142,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>06/08/2026 10:24:03 AM</t>
+          <t>06/09/2026 6:09:33 AM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6191,22 +6191,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>06/08/2026 6:36:45 AM</t>
+          <t>06/08/2026 10:24:03 AM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6240,22 +6240,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>06/07/2026 10:34:55 PM</t>
+          <t>06/08/2026 6:36:45 AM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6289,22 +6289,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>06/05/2026 3:56:56 PM</t>
+          <t>06/07/2026 10:34:55 PM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6338,22 +6338,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>06/03/2026 5:14:46 PM</t>
+          <t>06/05/2026 3:56:56 PM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6387,22 +6387,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>06/03/2026 3:43:38 PM</t>
+          <t>06/03/2026 5:14:46 PM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6436,17 +6436,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>06/03/2026 5:35:42 AM</t>
+          <t>06/03/2026 3:43:38 PM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6485,22 +6485,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>06/02/2026 1:11:41 PM</t>
+          <t>06/03/2026 5:35:42 AM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>06/01/2026 1:21:17 PM</t>
+          <t>06/02/2026 1:11:41 PM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6583,22 +6583,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>06/01/2026 1:03:09 PM</t>
+          <t>06/01/2026 1:21:17 PM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6632,27 +6632,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>06/01/2026 8:29:16 AM</t>
+          <t>06/01/2026 1:03:09 PM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6681,7 +6681,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>05/31/2026 12:04:28 PM</t>
+          <t>06/01/2026 8:29:16 AM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6730,17 +6730,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>05/30/2026 11:04:14 AM</t>
+          <t>05/31/2026 12:04:28 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6779,22 +6779,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>05/29/2026 4:52:36 PM</t>
+          <t>05/30/2026 11:04:14 AM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6828,22 +6828,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>05/29/2026 11:37:37 AM</t>
+          <t>05/29/2026 4:52:36 PM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6877,22 +6877,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>05/28/2026 12:12:12 PM</t>
+          <t>05/29/2026 11:37:37 AM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6926,22 +6926,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>05/27/2026 4:38:39 PM</t>
+          <t>05/28/2026 12:12:12 PM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>05/27/2026 11:08:19 AM</t>
+          <t>05/27/2026 4:38:39 PM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7024,7 +7024,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>05/26/2026 3:34:06 PM</t>
+          <t>05/27/2026 11:08:19 AM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7073,22 +7073,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>05/26/2026 3:20:19 PM</t>
+          <t>05/26/2026 3:34:06 PM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -7112,10 +7112,59 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="n">
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>05/26/2026 3:20:19 PM</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>22003</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ACKERMAN, JASON B.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="n">
         <v>0.586</v>
       </c>
-      <c r="O137" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O138"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,22 +496,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/21/2026 7:22:26 AM</t>
+          <t>08/23/2026 7:41:04 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>TORRES, VIVIAN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -545,22 +545,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/20/2026 5:30:05 PM</t>
+          <t>08/22/2026 12:06:51 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>HARRELL, JOHN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Lane Departure</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -594,22 +594,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/20/2026 2:15:19 PM</t>
+          <t>08/22/2026 10:17:03 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -643,22 +643,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/20/2026 5:42:43 AM</t>
+          <t>08/21/2026 7:22:26 AM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/19/2026 6:50:12 PM</t>
+          <t>08/20/2026 5:30:05 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -741,17 +741,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/18/2026 5:49:15 PM</t>
+          <t>08/20/2026 2:15:19 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -780,30 +780,32 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>0.515</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/18/2026 7:13:51 AM</t>
+          <t>08/20/2026 5:42:43 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -813,7 +815,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -837,27 +839,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/17/2026 10:04:29 AM</t>
+          <t>08/19/2026 6:50:12 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -886,27 +888,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/16/2026 2:27:54 PM</t>
+          <t>08/18/2026 5:49:15 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -933,17 +935,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/14/2026 11:58:42 AM</t>
+          <t>08/18/2026 7:13:51 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -958,7 +960,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -982,27 +984,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/14/2026 10:19:19 AM</t>
+          <t>08/17/2026 10:04:29 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1031,22 +1033,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/13/2026 3:35:07 PM</t>
+          <t>08/16/2026 2:27:54 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1056,7 +1058,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1070,42 +1072,40 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N13" t="n">
+        <v>0.515</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/12/2026 6:11:01 PM</t>
+          <t>08/14/2026 11:58:42 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BRANSCOME, JULIAN</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1119,30 +1119,32 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>0.621</v>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/11/2026 4:40:14 PM</t>
+          <t>08/14/2026 10:19:19 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1158,7 +1160,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1176,17 +1178,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/11/2026 1:10:19 PM</t>
+          <t>08/13/2026 3:35:07 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1207,7 +1209,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1225,38 +1227,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/11/2026 12:08:45 PM</t>
+          <t>08/12/2026 6:11:01 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>BRANSCOME, JULIAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1264,32 +1266,30 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N17" t="n">
+        <v>0.621</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/10/2026 5:25:42 PM</t>
+          <t>08/11/2026 4:40:14 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1323,22 +1323,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/10/2026 12:55:13 PM</t>
+          <t>08/11/2026 1:10:19 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/10/2026 12:42:11 PM</t>
+          <t>08/11/2026 12:08:45 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1421,17 +1421,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/09/2026 4:41:43 PM</t>
+          <t>08/10/2026 5:25:42 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1460,30 +1460,32 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>0.512</v>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/07/2026 3:48:46 PM</t>
+          <t>08/10/2026 12:55:13 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1493,7 +1495,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1517,22 +1519,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/06/2026 3:20:23 PM</t>
+          <t>08/10/2026 12:42:11 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1566,22 +1568,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/06/2026 10:05:54 AM</t>
+          <t>08/09/2026 4:41:43 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1591,7 +1593,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1605,32 +1607,30 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N24" t="n">
+        <v>0.512</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/06/2026 9:26:56 AM</t>
+          <t>08/07/2026 3:48:46 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/05/2026 6:03:04 PM</t>
+          <t>08/06/2026 3:20:23 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1713,22 +1713,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/03/2026 12:58:44 PM</t>
+          <t>08/06/2026 10:05:54 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1762,7 +1762,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/03/2026 10:34:02 AM</t>
+          <t>08/06/2026 9:26:56 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/31/2026 6:26:45 PM</t>
+          <t>08/05/2026 6:03:04 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1860,22 +1860,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/31/2026 5:30:17 PM</t>
+          <t>08/03/2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/31/2026 9:34:25 AM</t>
+          <t>08/03/2026 10:34:02 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1958,22 +1958,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/30/2026 11:38:58 AM</t>
+          <t>07/31/2026 6:26:45 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2007,22 +2007,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/29/2026 4:01:22 PM</t>
+          <t>07/31/2026 5:30:17 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2056,27 +2056,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/28/2026 2:44:19 PM</t>
+          <t>07/31/2026 9:34:25 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2105,22 +2105,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/28/2026 11:43:00 AM</t>
+          <t>07/30/2026 11:38:58 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2154,22 +2154,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/26/2026 12:37:34 PM</t>
+          <t>07/29/2026 4:01:22 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2203,17 +2203,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/25/2026 5:25:51 PM</t>
+          <t>07/28/2026 2:44:19 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2252,22 +2252,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/25/2026 10:23:49 AM</t>
+          <t>07/28/2026 11:43:00 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2301,22 +2301,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/24/2026 9:42:30 AM</t>
+          <t>07/26/2026 12:37:34 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2350,22 +2350,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/23/2026 11:13:22 AM</t>
+          <t>07/25/2026 5:25:51 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2399,27 +2399,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/23/2026 9:14:39 AM</t>
+          <t>07/25/2026 10:23:49 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2448,22 +2448,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/22/2026 3:17:16 PM</t>
+          <t>07/24/2026 9:42:30 AM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2497,17 +2497,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/22/2026 1:14:58 PM</t>
+          <t>07/23/2026 11:13:22 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2546,17 +2546,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/21/2026 4:12:57 AM</t>
+          <t>07/23/2026 9:14:39 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2595,22 +2595,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/20/2026 6:32:21 PM</t>
+          <t>07/22/2026 3:17:16 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2644,17 +2644,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/20/2026 5:14:06 PM</t>
+          <t>07/22/2026 1:14:58 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2693,7 +2693,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/20/2026 11:21:24 AM</t>
+          <t>07/21/2026 4:12:57 AM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2742,17 +2742,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/18/2026 5:40:41 PM</t>
+          <t>07/20/2026 6:32:21 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2791,22 +2791,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/18/2026 4:24:58 PM</t>
+          <t>07/20/2026 5:14:06 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2840,22 +2840,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/18/2026 7:28:02 AM</t>
+          <t>07/20/2026 11:21:24 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2889,17 +2889,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/17/2026 8:53:39 AM</t>
+          <t>07/18/2026 5:40:41 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2938,27 +2938,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/15/2026 7:54:31 PM</t>
+          <t>07/18/2026 4:24:58 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2987,17 +2987,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/15/2026 2:59:24 PM</t>
+          <t>07/18/2026 7:28:02 AM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3036,27 +3036,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/15/2026 1:48:31 PM</t>
+          <t>07/17/2026 8:53:39 AM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3085,17 +3085,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/14/2026 6:43:29 PM</t>
+          <t>07/15/2026 7:54:31 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3134,22 +3134,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/14/2026 3:47:33 PM</t>
+          <t>07/15/2026 2:59:24 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3183,22 +3183,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/14/2026 3:11:57 PM</t>
+          <t>07/15/2026 1:48:31 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3232,7 +3232,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/13/2026 5:16:14 PM</t>
+          <t>07/14/2026 6:43:29 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3281,22 +3281,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/13/2026 4:57:54 PM</t>
+          <t>07/14/2026 3:47:33 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3330,27 +3330,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/13/2026 2:42:02 PM</t>
+          <t>07/14/2026 3:11:57 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3379,22 +3379,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/11/2026 1:18:11 PM</t>
+          <t>07/13/2026 5:16:14 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3428,27 +3428,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/10/2026 9:53:41 AM</t>
+          <t>07/13/2026 4:57:54 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3477,17 +3477,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/09/2026 10:54:42 AM</t>
+          <t>07/13/2026 2:42:02 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3526,27 +3526,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/09/2026 9:49:26 AM</t>
+          <t>07/11/2026 1:18:11 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3575,27 +3575,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/07/2026 5:35:06 PM</t>
+          <t>07/10/2026 9:53:41 AM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3624,17 +3624,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/06/2026 6:07:40 PM</t>
+          <t>07/09/2026 10:54:42 AM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3673,17 +3673,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/06/2026 4:04:58 PM</t>
+          <t>07/09/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3722,20 +3722,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/06/2026 12:54:43 PM</t>
+          <t>07/07/2026 5:35:06 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3767,17 +3771,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/05/2026 6:34:14 PM</t>
+          <t>07/06/2026 6:07:40 PM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3787,7 +3791,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3816,22 +3820,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/05/2026 10:38:36 AM</t>
+          <t>07/06/2026 4:04:58 PM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3841,7 +3845,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3855,32 +3859,30 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="n">
-        <v>0.714</v>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/03/2026 1:10:42 PM</t>
+          <t>07/06/2026 12:54:43 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3912,23 +3914,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/03/2026 11:57:21 AM</t>
+          <t>07/05/2026 6:34:14 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>KELLY GNEITING</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3957,22 +3963,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/02/2026 12:41:50 PM</t>
+          <t>07/05/2026 10:38:36 AM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3982,7 +3988,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -3996,27 +4002,25 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N73" t="n">
+        <v>0.714</v>
       </c>
       <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/30/2026 3:08:17 PM</t>
+          <t>07/03/2026 1:10:42 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4055,24 +4059,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/29/2026 5:02:30 PM</t>
+          <t>07/03/2026 11:57:21 AM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4104,22 +4104,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/29/2026 4:46:11 PM</t>
+          <t>07/02/2026 12:41:50 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4153,20 +4153,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/27/2026 11:52:56 AM</t>
+          <t>06/30/2026 3:08:17 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>CLARK, KC</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4198,22 +4202,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/27/2026 11:42:51 AM</t>
+          <t>06/29/2026 5:02:30 PM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4247,7 +4251,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/26/2026 2:42:28 PM</t>
+          <t>06/29/2026 4:46:11 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4296,24 +4300,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/26/2026 2:10:46 PM</t>
+          <t>06/27/2026 11:52:56 AM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4345,22 +4345,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/26/2026 1:33:31 PM</t>
+          <t>06/27/2026 11:42:51 AM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SCOTT, GRANT</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4394,22 +4394,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/26/2026 10:51:52 AM</t>
+          <t>06/26/2026 2:42:28 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4443,22 +4443,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/25/2026 11:22:39 PM</t>
+          <t>06/26/2026 2:10:46 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4492,17 +4492,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/25/2026 1:38:37 PM</t>
+          <t>06/26/2026 1:33:31 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>SCOTT, GRANT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4541,22 +4541,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/25/2026 11:29:51 AM</t>
+          <t>06/26/2026 10:51:52 AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4590,22 +4590,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/24/2026 5:10:48 PM</t>
+          <t>06/25/2026 11:22:39 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4639,20 +4639,24 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/24/2026 4:03:42 PM</t>
+          <t>06/25/2026 1:38:37 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>EMERY.SHANE</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4684,17 +4688,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/24/2026 5:11:55 AM</t>
+          <t>06/25/2026 11:29:51 AM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4733,27 +4737,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/23/2026 5:11:29 PM</t>
+          <t>06/24/2026 5:10:48 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4782,24 +4786,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/22/2026 4:29:35 PM</t>
+          <t>06/24/2026 4:03:42 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4831,22 +4831,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/22/2026 1:33:02 PM</t>
+          <t>06/24/2026 5:11:55 AM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4880,17 +4880,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/22/2026 12:51:06 PM</t>
+          <t>06/23/2026 5:11:29 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4929,22 +4929,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/21/2026 2:38:22 PM</t>
+          <t>06/22/2026 4:29:35 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4978,20 +4978,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/21/2026 1:24:01 PM</t>
+          <t>06/22/2026 1:33:02 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>CLARK, KC</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5023,27 +5027,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/20/2026 12:26:55 PM</t>
+          <t>06/22/2026 12:51:06 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KREUTZER, DON</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5072,27 +5076,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/19/2026 6:06:53 PM</t>
+          <t>06/21/2026 2:38:22 PM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5121,24 +5125,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/19/2026 5:32:27 PM</t>
+          <t>06/21/2026 1:24:01 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MOORE, ROYCE</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5170,22 +5170,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/19/2026 10:12:30 AM</t>
+          <t>06/20/2026 12:26:55 PM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>KREUTZER, DON</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5219,27 +5219,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/18/2026 12:45:10 PM</t>
+          <t>06/19/2026 6:06:53 PM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5268,17 +5268,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/18/2026 11:35:17 AM</t>
+          <t>06/19/2026 5:32:27 PM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MOORE, ROYCE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5317,22 +5317,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/17/2026 3:18:01 PM</t>
+          <t>06/19/2026 10:12:30 AM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5366,27 +5366,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/17/2026 1:24:24 PM</t>
+          <t>06/18/2026 12:45:10 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5415,22 +5415,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/17/2026 9:51:05 AM</t>
+          <t>06/18/2026 11:35:17 AM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5464,22 +5464,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06/14/2026 12:51:39 PM</t>
+          <t>06/17/2026 3:18:01 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5513,23 +5513,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>06/13/2026 12:37:03 PM</t>
+          <t>06/17/2026 1:24:24 PM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>MAGEE LONDON, TRESSEL</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5558,22 +5562,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>06/12/2026 6:47:19 PM</t>
+          <t>06/17/2026 9:51:05 AM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5607,22 +5611,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>06/12/2026 2:22:37 PM</t>
+          <t>06/14/2026 12:51:39 PM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5656,24 +5660,20 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06/12/2026 10:50:38 AM</t>
+          <t>06/13/2026 12:37:03 PM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5705,22 +5705,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>06/11/2026 5:29:52 PM</t>
+          <t>06/12/2026 6:47:19 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5754,22 +5754,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>06/11/2026 3:42:27 PM</t>
+          <t>06/12/2026 2:22:37 PM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5803,7 +5803,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>06/11/2026 10:57:37 AM</t>
+          <t>06/12/2026 10:50:38 AM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5852,22 +5852,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>06/10/2026 8:47:02 PM</t>
+          <t>06/11/2026 5:29:52 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5901,20 +5901,24 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>06/10/2026 2:34:29 PM</t>
+          <t>06/11/2026 3:42:27 PM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>BROUSSEAU, SALLY</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5946,27 +5950,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>06/10/2026 9:58:07 AM</t>
+          <t>06/11/2026 10:57:37 AM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5995,22 +5999,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>06/09/2026 8:49:37 PM</t>
+          <t>06/10/2026 8:47:02 PM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6044,24 +6048,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>06/09/2026 5:15:37 PM</t>
+          <t>06/10/2026 2:34:29 PM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -6093,17 +6093,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06/09/2026 9:52:33 AM</t>
+          <t>06/10/2026 9:58:07 AM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6142,22 +6142,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>06/09/2026 6:09:33 AM</t>
+          <t>06/09/2026 8:49:37 PM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6191,22 +6191,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>06/08/2026 10:24:03 AM</t>
+          <t>06/09/2026 5:15:37 PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6240,17 +6240,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>06/08/2026 6:36:45 AM</t>
+          <t>06/09/2026 9:52:33 AM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6289,22 +6289,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>06/07/2026 10:34:55 PM</t>
+          <t>06/09/2026 6:09:33 AM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6338,22 +6338,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>06/05/2026 3:56:56 PM</t>
+          <t>06/08/2026 10:24:03 AM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6387,22 +6387,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>06/03/2026 5:14:46 PM</t>
+          <t>06/08/2026 6:36:45 AM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6436,17 +6436,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>06/03/2026 3:43:38 PM</t>
+          <t>06/07/2026 10:34:55 PM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6485,22 +6485,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>06/03/2026 5:35:42 AM</t>
+          <t>06/05/2026 3:56:56 PM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>06/02/2026 1:11:41 PM</t>
+          <t>06/03/2026 5:14:46 PM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6583,22 +6583,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>06/01/2026 1:21:17 PM</t>
+          <t>06/03/2026 3:43:38 PM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6632,22 +6632,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>06/01/2026 1:03:09 PM</t>
+          <t>06/03/2026 5:35:42 AM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6681,27 +6681,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>06/01/2026 8:29:16 AM</t>
+          <t>06/02/2026 1:11:41 PM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6730,27 +6730,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>05/31/2026 12:04:28 PM</t>
+          <t>06/01/2026 1:21:17 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6779,22 +6779,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>05/30/2026 11:04:14 AM</t>
+          <t>06/01/2026 1:03:09 PM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6828,27 +6828,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>05/29/2026 4:52:36 PM</t>
+          <t>06/01/2026 8:29:16 AM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6877,17 +6877,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>05/29/2026 11:37:37 AM</t>
+          <t>05/31/2026 12:04:28 PM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6926,22 +6926,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>05/28/2026 12:12:12 PM</t>
+          <t>05/30/2026 11:04:14 AM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>05/27/2026 4:38:39 PM</t>
+          <t>05/29/2026 4:52:36 PM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7024,22 +7024,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>05/27/2026 11:08:19 AM</t>
+          <t>05/29/2026 11:37:37 AM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7073,7 +7073,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>05/26/2026 3:34:06 PM</t>
+          <t>05/28/2026 12:12:12 PM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7122,17 +7122,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>05/26/2026 3:20:19 PM</t>
+          <t>05/27/2026 4:38:39 PM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -7161,10 +7161,157 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="n">
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>05/27/2026 11:08:19 AM</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>23470</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JELTOV, VLADIMIR K.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>OTR, Safety Pro Test</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Following Distance</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>05/26/2026 3:34:06 PM</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>23470</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>JELTOV, VLADIMIR K.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OTR, Safety Pro Test</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Following Distance</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>05/26/2026 3:20:19 PM</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>22003</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ACKERMAN, JASON B.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="n">
         <v>0.586</v>
       </c>
-      <c r="O138" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O141"/>
+  <dimension ref="A1:O134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,27 +496,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/23/2026 7:41:04 PM</t>
+          <t>08/29/2026 5:17:06 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TORRES, VIVIAN</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/22/2026 12:06:51 PM</t>
+          <t>08/26/2026 2:16:48 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22013</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HARRELL, JOHN</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lane Departure</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -594,22 +594,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/22/2026 10:17:03 AM</t>
+          <t>08/26/2026 7:52:29 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -643,22 +643,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/21/2026 7:22:26 AM</t>
+          <t>08/26/2026 6:03:53 AM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -692,22 +692,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/20/2026 5:30:05 PM</t>
+          <t>08/25/2026 7:50:34 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>HARRELL, JOHN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -741,22 +741,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/20/2026 2:15:19 PM</t>
+          <t>08/24/2026 12:05:53 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -772,7 +772,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -790,22 +790,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/20/2026 5:42:43 AM</t>
+          <t>08/24/2026 11:26:42 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -815,13 +815,13 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Lane Departure</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -839,22 +839,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/19/2026 6:50:12 PM</t>
+          <t>08/23/2026 7:41:04 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>TORRES, VIVIAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -870,7 +870,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -888,38 +888,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/18/2026 5:49:15 PM</t>
+          <t>08/22/2026 10:17:03 AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -927,30 +927,32 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>0.515</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/18/2026 7:13:51 AM</t>
+          <t>08/21/2026 7:22:26 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -960,13 +962,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -984,27 +986,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/17/2026 10:04:29 AM</t>
+          <t>08/20/2026 5:30:05 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1015,7 +1017,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1033,22 +1035,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/16/2026 2:27:54 PM</t>
+          <t>08/20/2026 2:15:19 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1058,13 +1060,13 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1072,30 +1074,32 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>0.515</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/14/2026 11:58:42 AM</t>
+          <t>08/19/2026 6:50:12 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1111,7 +1115,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1129,38 +1133,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/14/2026 10:19:19 AM</t>
+          <t>08/18/2026 5:49:15 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1168,32 +1172,30 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N15" t="n">
+        <v>0.515</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/13/2026 3:35:07 PM</t>
+          <t>08/18/2026 7:13:51 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1203,13 +1205,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1227,17 +1229,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/12/2026 6:11:01 PM</t>
+          <t>08/17/2026 10:04:29 AM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BRANSCOME, JULIAN</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1252,13 +1254,13 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1266,30 +1268,32 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0.621</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/11/2026 4:40:14 PM</t>
+          <t>08/16/2026 2:27:54 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1299,7 +1303,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1313,32 +1317,30 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N18" t="n">
+        <v>0.515</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/11/2026 1:10:19 PM</t>
+          <t>08/14/2026 11:58:42 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1372,7 +1374,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/11/2026 12:08:45 PM</t>
+          <t>08/14/2026 10:19:19 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1421,22 +1423,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/10/2026 5:25:42 PM</t>
+          <t>08/13/2026 3:35:07 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1470,32 +1472,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/10/2026 12:55:13 PM</t>
+          <t>08/12/2026 6:11:01 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>BRANSCOME, JULIAN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1509,32 +1511,30 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N22" t="n">
+        <v>0.621</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/10/2026 12:42:11 PM</t>
+          <t>08/11/2026 4:40:14 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1568,22 +1568,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/09/2026 4:41:43 PM</t>
+          <t>08/11/2026 1:10:19 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1607,30 +1607,32 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
-        <v>0.512</v>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/07/2026 3:48:46 PM</t>
+          <t>08/11/2026 12:08:45 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1664,7 +1666,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/06/2026 3:20:23 PM</t>
+          <t>08/10/2026 5:25:42 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1713,22 +1715,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/06/2026 10:05:54 AM</t>
+          <t>08/10/2026 12:55:13 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1738,7 +1740,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1762,22 +1764,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/06/2026 9:26:56 AM</t>
+          <t>08/10/2026 12:42:11 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1811,17 +1813,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/05/2026 6:03:04 PM</t>
+          <t>08/09/2026 4:41:43 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1836,7 +1838,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1850,32 +1852,30 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N29" t="n">
+        <v>0.512</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/03/2026 12:58:44 PM</t>
+          <t>08/07/2026 3:48:46 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1909,22 +1909,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/03/2026 10:34:02 AM</t>
+          <t>08/06/2026 3:20:23 PM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1958,22 +1958,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/31/2026 6:26:45 PM</t>
+          <t>08/06/2026 10:05:54 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2007,22 +2007,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/31/2026 5:30:17 PM</t>
+          <t>08/06/2026 9:26:56 AM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2056,22 +2056,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/31/2026 9:34:25 AM</t>
+          <t>08/05/2026 6:03:04 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2105,22 +2105,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/30/2026 11:38:58 AM</t>
+          <t>08/03/2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/29/2026 4:01:22 PM</t>
+          <t>08/03/2026 10:34:02 AM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2203,17 +2203,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/28/2026 2:44:19 PM</t>
+          <t>07/31/2026 6:26:45 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2252,22 +2252,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/28/2026 11:43:00 AM</t>
+          <t>07/31/2026 5:30:17 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2301,22 +2301,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/26/2026 12:37:34 PM</t>
+          <t>07/31/2026 9:34:25 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2350,22 +2350,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/25/2026 5:25:51 PM</t>
+          <t>07/30/2026 11:38:58 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/25/2026 10:23:49 AM</t>
+          <t>07/29/2026 4:01:22 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2448,27 +2448,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/24/2026 9:42:30 AM</t>
+          <t>07/28/2026 2:44:19 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2497,22 +2497,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/23/2026 11:13:22 AM</t>
+          <t>07/28/2026 11:43:00 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>LOPER, WILLIAM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2546,17 +2546,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/23/2026 9:14:39 AM</t>
+          <t>07/26/2026 12:37:34 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2595,22 +2595,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/22/2026 3:17:16 PM</t>
+          <t>07/25/2026 5:25:51 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2644,17 +2644,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/22/2026 1:14:58 PM</t>
+          <t>07/25/2026 10:23:49 AM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2693,22 +2693,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/21/2026 4:12:57 AM</t>
+          <t>07/24/2026 9:42:30 AM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2742,22 +2742,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/20/2026 6:32:21 PM</t>
+          <t>07/23/2026 11:13:22 AM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2791,27 +2791,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/20/2026 5:14:06 PM</t>
+          <t>07/23/2026 9:14:39 AM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2840,22 +2840,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/20/2026 11:21:24 AM</t>
+          <t>07/22/2026 3:17:16 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2889,22 +2889,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/18/2026 5:40:41 PM</t>
+          <t>07/22/2026 1:14:58 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2938,7 +2938,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/18/2026 4:24:58 PM</t>
+          <t>07/21/2026 4:12:57 AM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2987,22 +2987,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/18/2026 7:28:02 AM</t>
+          <t>07/20/2026 6:32:21 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3036,27 +3036,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/17/2026 8:53:39 AM</t>
+          <t>07/20/2026 5:14:06 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3085,27 +3085,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/15/2026 7:54:31 PM</t>
+          <t>07/20/2026 11:21:24 AM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3134,22 +3134,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/15/2026 2:59:24 PM</t>
+          <t>07/18/2026 5:40:41 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3183,22 +3183,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/15/2026 1:48:31 PM</t>
+          <t>07/18/2026 4:24:58 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3232,17 +3232,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/14/2026 6:43:29 PM</t>
+          <t>07/18/2026 7:28:02 AM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3281,17 +3281,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/14/2026 3:47:33 PM</t>
+          <t>07/17/2026 8:53:39 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3330,27 +3330,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/14/2026 3:11:57 PM</t>
+          <t>07/15/2026 7:54:31 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/13/2026 5:16:14 PM</t>
+          <t>07/15/2026 2:59:24 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3428,22 +3428,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/13/2026 4:57:54 PM</t>
+          <t>07/15/2026 1:48:31 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3477,17 +3477,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/13/2026 2:42:02 PM</t>
+          <t>07/14/2026 6:43:29 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3526,17 +3526,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/11/2026 1:18:11 PM</t>
+          <t>07/14/2026 3:47:33 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3575,27 +3575,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/10/2026 9:53:41 AM</t>
+          <t>07/14/2026 3:11:57 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3624,17 +3624,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/09/2026 10:54:42 AM</t>
+          <t>07/13/2026 5:16:14 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3673,27 +3673,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/09/2026 9:49:26 AM</t>
+          <t>07/13/2026 4:57:54 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3722,27 +3722,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/07/2026 5:35:06 PM</t>
+          <t>07/13/2026 2:42:02 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3771,22 +3771,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/06/2026 6:07:40 PM</t>
+          <t>07/11/2026 1:18:11 PM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3820,17 +3820,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/06/2026 4:04:58 PM</t>
+          <t>07/10/2026 9:53:41 AM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3869,20 +3869,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/06/2026 12:54:43 PM</t>
+          <t>07/09/2026 10:54:42 AM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>FOFANA, MAMADOU</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -3914,17 +3918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/05/2026 6:34:14 PM</t>
+          <t>07/09/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3963,22 +3967,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/05/2026 10:38:36 AM</t>
+          <t>07/07/2026 5:35:06 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3988,7 +3992,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -4002,15 +4006,17 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="n">
-        <v>0.714</v>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/03/2026 1:10:42 PM</t>
+          <t>07/06/2026 6:07:40 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4059,20 +4065,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/03/2026 11:57:21 AM</t>
+          <t>07/06/2026 4:04:58 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>CLARK, KC</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4104,24 +4114,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/02/2026 12:41:50 PM</t>
+          <t>07/06/2026 12:54:43 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4153,17 +4159,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/30/2026 3:08:17 PM</t>
+          <t>07/05/2026 6:34:14 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4173,7 +4179,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4202,22 +4208,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/29/2026 5:02:30 PM</t>
+          <t>07/05/2026 10:38:36 AM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4227,7 +4233,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -4241,32 +4247,30 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N78" t="n">
+        <v>0.714</v>
       </c>
       <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/29/2026 4:46:11 PM</t>
+          <t>07/03/2026 1:10:42 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4300,7 +4304,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/27/2026 11:52:56 AM</t>
+          <t>07/03/2026 11:57:21 AM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4345,22 +4349,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/27/2026 11:42:51 AM</t>
+          <t>07/02/2026 12:41:50 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4394,22 +4398,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/26/2026 2:42:28 PM</t>
+          <t>06/30/2026 3:08:17 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4443,17 +4447,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/26/2026 2:10:46 PM</t>
+          <t>06/29/2026 5:02:30 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4492,22 +4496,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/26/2026 1:33:31 PM</t>
+          <t>06/29/2026 4:46:11 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SCOTT, GRANT</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4541,24 +4545,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/26/2026 10:51:52 AM</t>
+          <t>06/27/2026 11:52:56 AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4590,7 +4590,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/25/2026 11:22:39 PM</t>
+          <t>06/27/2026 11:42:51 AM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/25/2026 1:38:37 PM</t>
+          <t>06/26/2026 2:42:28 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4688,22 +4688,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/25/2026 11:29:51 AM</t>
+          <t>06/26/2026 2:10:46 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4737,17 +4737,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/24/2026 5:10:48 PM</t>
+          <t>06/26/2026 1:33:31 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>SCOTT, GRANT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4786,20 +4786,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/24/2026 4:03:42 PM</t>
+          <t>06/26/2026 10:51:52 AM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>GARCIA, FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4831,22 +4835,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/24/2026 5:11:55 AM</t>
+          <t>06/25/2026 11:22:39 PM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4880,27 +4884,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/23/2026 5:11:29 PM</t>
+          <t>06/25/2026 1:38:37 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4929,22 +4933,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/22/2026 4:29:35 PM</t>
+          <t>06/25/2026 11:29:51 AM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4978,17 +4982,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/22/2026 1:33:02 PM</t>
+          <t>06/24/2026 5:10:48 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5027,27 +5031,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/22/2026 12:51:06 PM</t>
+          <t>06/24/2026 4:03:42 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5076,22 +5076,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/21/2026 2:38:22 PM</t>
+          <t>06/24/2026 5:11:55 AM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5125,23 +5125,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/21/2026 1:24:01 PM</t>
+          <t>06/23/2026 5:11:29 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>MAGEE LONDON, TRESSEL</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5170,22 +5174,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/20/2026 12:26:55 PM</t>
+          <t>06/22/2026 4:29:35 PM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KREUTZER, DON</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5219,27 +5223,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/19/2026 6:06:53 PM</t>
+          <t>06/22/2026 1:33:02 PM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5268,27 +5272,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/19/2026 5:32:27 PM</t>
+          <t>06/22/2026 12:51:06 PM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MOORE, ROYCE</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5317,22 +5321,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/19/2026 10:12:30 AM</t>
+          <t>06/21/2026 2:38:22 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5366,24 +5370,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/18/2026 12:45:10 PM</t>
+          <t>06/21/2026 1:24:01 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5415,17 +5415,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/18/2026 11:35:17 AM</t>
+          <t>06/20/2026 12:26:55 PM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>KREUTZER, DON</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5464,27 +5464,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06/17/2026 3:18:01 PM</t>
+          <t>06/19/2026 6:06:53 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5513,27 +5513,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>06/17/2026 1:24:24 PM</t>
+          <t>06/19/2026 5:32:27 PM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>MOORE, ROYCE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5562,22 +5562,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>06/17/2026 9:51:05 AM</t>
+          <t>06/19/2026 10:12:30 AM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5611,22 +5611,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>06/14/2026 12:51:39 PM</t>
+          <t>06/18/2026 12:45:10 PM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5660,20 +5660,24 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06/13/2026 12:37:03 PM</t>
+          <t>06/18/2026 11:35:17 AM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>EMERY.SHANE</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5705,22 +5709,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>06/12/2026 6:47:19 PM</t>
+          <t>06/17/2026 3:18:01 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5754,27 +5758,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>06/12/2026 2:22:37 PM</t>
+          <t>06/17/2026 1:24:24 PM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5803,7 +5807,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>06/12/2026 10:50:38 AM</t>
+          <t>06/17/2026 9:51:05 AM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5852,7 +5856,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>06/11/2026 5:29:52 PM</t>
+          <t>06/14/2026 12:51:39 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5901,24 +5905,20 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>06/11/2026 3:42:27 PM</t>
+          <t>06/13/2026 12:37:03 PM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5950,22 +5950,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>06/11/2026 10:57:37 AM</t>
+          <t>06/12/2026 6:47:19 PM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5999,22 +5999,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>06/10/2026 8:47:02 PM</t>
+          <t>06/12/2026 2:22:37 PM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6048,20 +6048,24 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>06/10/2026 2:34:29 PM</t>
+          <t>06/12/2026 10:50:38 AM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>JELTOV, VLADIMIR K.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OTR, Safety Pro Test</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -6093,27 +6097,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06/10/2026 9:58:07 AM</t>
+          <t>06/11/2026 5:29:52 PM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6142,17 +6146,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>06/09/2026 8:49:37 PM</t>
+          <t>06/11/2026 3:42:27 PM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6191,7 +6195,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>06/09/2026 5:15:37 PM</t>
+          <t>06/11/2026 10:57:37 AM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6240,27 +6244,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>06/09/2026 9:52:33 AM</t>
+          <t>06/10/2026 8:47:02 PM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6289,24 +6293,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>06/09/2026 6:09:33 AM</t>
+          <t>06/10/2026 2:34:29 PM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -6338,27 +6338,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>06/08/2026 10:24:03 AM</t>
+          <t>06/10/2026 9:58:07 AM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6387,22 +6387,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>06/08/2026 6:36:45 AM</t>
+          <t>06/09/2026 8:49:37 PM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6436,22 +6436,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>06/07/2026 10:34:55 PM</t>
+          <t>06/09/2026 5:15:37 PM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6485,27 +6485,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>06/05/2026 3:56:56 PM</t>
+          <t>06/09/2026 9:52:33 AM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>06/03/2026 5:14:46 PM</t>
+          <t>06/09/2026 6:09:33 AM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6583,22 +6583,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>06/03/2026 3:43:38 PM</t>
+          <t>06/08/2026 10:24:03 AM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6632,22 +6632,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>06/03/2026 5:35:42 AM</t>
+          <t>06/08/2026 6:36:45 AM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6681,22 +6681,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>06/02/2026 1:11:41 PM</t>
+          <t>06/07/2026 10:34:55 PM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6730,22 +6730,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>06/01/2026 1:21:17 PM</t>
+          <t>06/05/2026 3:56:56 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6779,22 +6779,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>06/01/2026 1:03:09 PM</t>
+          <t>06/03/2026 5:14:46 PM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6828,17 +6828,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>06/01/2026 8:29:16 AM</t>
+          <t>06/03/2026 3:43:38 PM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6877,17 +6877,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>05/31/2026 12:04:28 PM</t>
+          <t>06/03/2026 5:35:42 AM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6926,22 +6926,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>05/30/2026 11:04:14 AM</t>
+          <t>06/02/2026 1:11:41 PM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6972,347 +6972,6 @@
       </c>
       <c r="O134" t="inlineStr"/>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>05/29/2026 4:52:36 PM</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>23470</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>05/29/2026 11:37:37 AM</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>24688</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>WADE,ADAM</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>05/28/2026 12:12:12 PM</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>23470</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>05/27/2026 4:38:39 PM</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>23471</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>TREVIZO, ESTABAN I.</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>05/27/2026 11:08:19 AM</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>23470</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>05/26/2026 3:34:06 PM</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>23470</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>05/26/2026 3:20:19 PM</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>22003</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>ACKERMAN, JASON B.</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Harsh Brake</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="O141" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O134"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,17 +496,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/29/2026 5:17:06 PM</t>
+          <t>09/03/2026 7:58:09 AM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/26/2026 2:16:48 PM</t>
+          <t>09/02/2026 7:09:38 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -594,22 +594,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/26/2026 7:52:29 AM</t>
+          <t>09/02/2026 6:16:41 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -643,22 +643,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/26/2026 6:03:53 AM</t>
+          <t>09/02/2026 1:32:51 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>ACKERMAN, JASON B.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -682,32 +682,30 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N5" t="n">
+        <v>0.634</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/25/2026 7:50:34 PM</t>
+          <t>09/02/2026 5:17:16 AM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22013</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HARRELL, JOHN</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -741,24 +739,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/24/2026 12:05:53 PM</t>
+          <t>08/31/2026 4:20:37 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22986</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LOPER, WILLIAM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
+          <t>23473</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -766,13 +756,13 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -790,22 +780,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/24/2026 11:26:42 AM</t>
+          <t>08/30/2026 7:56:43 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -815,13 +805,13 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lane Departure</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -839,27 +829,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/23/2026 7:41:04 PM</t>
+          <t>08/29/2026 5:17:06 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TORRES, VIVIAN</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -870,7 +860,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -888,7 +878,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/22/2026 10:17:03 AM</t>
+          <t>08/26/2026 2:16:48 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -919,7 +909,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -937,24 +927,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/21/2026 7:22:26 AM</t>
+          <t>08/26/2026 7:52:29 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>LOPER, WILLIAM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -968,7 +954,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -986,22 +972,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/20/2026 5:30:05 PM</t>
+          <t>08/26/2026 6:03:53 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1011,13 +997,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1035,22 +1021,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/20/2026 2:15:19 PM</t>
+          <t>08/25/2026 7:50:34 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>HARRELL, JOHN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1060,13 +1046,13 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1084,24 +1070,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/19/2026 6:50:12 PM</t>
+          <t>08/24/2026 12:05:53 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>LOPER, WILLIAM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -1133,32 +1115,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/18/2026 5:49:15 PM</t>
+          <t>08/24/2026 11:26:42 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Lane Departure</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1172,30 +1154,32 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>0.515</v>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/18/2026 7:13:51 AM</t>
+          <t>08/23/2026 7:41:04 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
+          <t>TORRES, VIVIAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1205,7 +1189,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1229,27 +1213,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/17/2026 10:04:29 AM</t>
+          <t>08/22/2026 10:17:03 AM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1278,22 +1262,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/16/2026 2:27:54 PM</t>
+          <t>08/21/2026 7:22:26 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1303,7 +1287,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1317,30 +1301,32 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>0.515</v>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/14/2026 11:58:42 AM</t>
+          <t>08/20/2026 5:30:05 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1374,22 +1360,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/14/2026 10:19:19 AM</t>
+          <t>08/20/2026 2:15:19 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1423,22 +1409,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/13/2026 3:35:07 PM</t>
+          <t>08/19/2026 6:50:12 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1472,17 +1458,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/12/2026 6:11:01 PM</t>
+          <t>08/18/2026 5:49:15 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BRANSCOME, JULIAN</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1512,29 +1498,29 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>0.621</v>
+        <v>0.515</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/11/2026 4:40:14 PM</t>
+          <t>08/18/2026 7:13:51 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1544,7 +1530,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1568,17 +1554,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/11/2026 1:10:19 PM</t>
+          <t>08/17/2026 10:04:29 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1588,7 +1574,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1617,24 +1603,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/11/2026 12:08:45 PM</t>
+          <t>08/16/2026 2:27:54 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>LOPER, WILLIAM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -1642,7 +1624,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1656,32 +1638,30 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N25" t="n">
+        <v>0.515</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/10/2026 5:25:42 PM</t>
+          <t>08/14/2026 11:58:42 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1715,22 +1695,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/10/2026 12:55:13 PM</t>
+          <t>08/14/2026 10:19:19 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1740,7 +1720,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1764,22 +1744,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/10/2026 12:42:11 PM</t>
+          <t>08/13/2026 3:35:07 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1813,32 +1793,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/09/2026 4:41:43 PM</t>
+          <t>08/12/2026 6:11:01 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>BRANSCOME, JULIAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1853,29 +1833,29 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>0.512</v>
+        <v>0.621</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/07/2026 3:48:46 PM</t>
+          <t>08/11/2026 4:40:14 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1909,22 +1889,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/06/2026 3:20:23 PM</t>
+          <t>08/11/2026 1:10:19 PM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1958,7 +1938,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/06/2026 10:05:54 AM</t>
+          <t>08/11/2026 12:08:45 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2007,22 +1987,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/06/2026 9:26:56 AM</t>
+          <t>08/10/2026 5:25:42 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2056,22 +2036,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/05/2026 6:03:04 PM</t>
+          <t>08/10/2026 12:55:13 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2081,7 +2061,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2105,22 +2085,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/03/2026 12:58:44 PM</t>
+          <t>08/10/2026 12:42:11 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2154,22 +2134,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/03/2026 10:34:02 AM</t>
+          <t>08/09/2026 4:41:43 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2179,7 +2159,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2193,17 +2173,15 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N36" t="n">
+        <v>0.512</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/31/2026 6:26:45 PM</t>
+          <t>08/07/2026 3:48:46 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2252,17 +2230,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/31/2026 5:30:17 PM</t>
+          <t>08/06/2026 3:20:23 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2301,22 +2279,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/31/2026 9:34:25 AM</t>
+          <t>08/06/2026 10:05:54 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2350,17 +2328,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/30/2026 11:38:58 AM</t>
+          <t>08/06/2026 9:26:56 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2399,22 +2377,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/29/2026 4:01:22 PM</t>
+          <t>08/05/2026 6:03:04 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2448,27 +2426,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/28/2026 2:44:19 PM</t>
+          <t>08/03/2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
+          <t>LOPER, WILLIAM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2497,22 +2471,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/28/2026 11:43:00 AM</t>
+          <t>08/03/2026 10:34:02 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LOPER, WILLIAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2546,17 +2520,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/26/2026 12:37:34 PM</t>
+          <t>07/31/2026 6:26:45 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2595,17 +2569,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/25/2026 5:25:51 PM</t>
+          <t>07/31/2026 5:30:17 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2644,7 +2618,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/25/2026 10:23:49 AM</t>
+          <t>07/31/2026 9:34:25 AM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2693,22 +2667,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/24/2026 9:42:30 AM</t>
+          <t>07/30/2026 11:38:58 AM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2742,7 +2716,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/23/2026 11:13:22 AM</t>
+          <t>07/29/2026 4:01:22 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2791,7 +2765,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/23/2026 9:14:39 AM</t>
+          <t>07/28/2026 2:44:19 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2840,24 +2814,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/22/2026 3:17:16 PM</t>
+          <t>07/28/2026 11:43:00 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>LOPER, WILLIAM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -2889,22 +2859,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/22/2026 1:14:58 PM</t>
+          <t>07/26/2026 12:37:34 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MARTINEZ, FERNANDEZ</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2938,17 +2908,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/21/2026 4:12:57 AM</t>
+          <t>07/25/2026 5:25:51 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>FOUNTAIN, RODNEY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2987,22 +2957,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/20/2026 6:32:21 PM</t>
+          <t>07/25/2026 10:23:49 AM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3036,22 +3006,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/20/2026 5:14:06 PM</t>
+          <t>07/24/2026 9:42:30 AM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3085,22 +3055,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/20/2026 11:21:24 AM</t>
+          <t>07/23/2026 11:13:22 AM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3134,17 +3104,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/18/2026 5:40:41 PM</t>
+          <t>07/23/2026 9:14:39 AM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3154,7 +3124,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3183,22 +3153,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/18/2026 4:24:58 PM</t>
+          <t>07/22/2026 3:17:16 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3232,17 +3202,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/18/2026 7:28:02 AM</t>
+          <t>07/22/2026 1:14:58 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>MARTINEZ, FERNANDEZ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3281,17 +3251,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/17/2026 8:53:39 AM</t>
+          <t>07/21/2026 4:12:57 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3301,7 +3271,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3330,27 +3300,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/15/2026 7:54:31 PM</t>
+          <t>07/20/2026 6:32:21 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3379,7 +3349,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/15/2026 2:59:24 PM</t>
+          <t>07/20/2026 5:14:06 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3428,22 +3398,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/15/2026 1:48:31 PM</t>
+          <t>07/20/2026 11:21:24 AM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3477,22 +3447,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/14/2026 6:43:29 PM</t>
+          <t>07/18/2026 5:40:41 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>TREVIZO, ESTABAN I.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3526,7 +3496,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/14/2026 3:47:33 PM</t>
+          <t>07/18/2026 4:24:58 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3575,22 +3545,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/14/2026 3:11:57 PM</t>
+          <t>07/18/2026 7:28:02 AM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3624,27 +3594,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/13/2026 5:16:14 PM</t>
+          <t>07/17/2026 8:53:39 AM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3673,27 +3643,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/13/2026 4:57:54 PM</t>
+          <t>07/15/2026 7:54:31 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3722,17 +3692,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/13/2026 2:42:02 PM</t>
+          <t>07/15/2026 2:59:24 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3742,7 +3712,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3771,22 +3741,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/11/2026 1:18:11 PM</t>
+          <t>07/15/2026 1:48:31 PM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TREVIZO, ESTABAN I.</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3820,17 +3790,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/10/2026 9:53:41 AM</t>
+          <t>07/14/2026 6:43:29 PM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3840,7 +3810,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3869,22 +3839,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/09/2026 10:54:42 AM</t>
+          <t>07/14/2026 3:47:33 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FOFANA, MAMADOU</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3918,27 +3888,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/09/2026 9:49:26 AM</t>
+          <t>07/14/2026 3:11:57 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3967,22 +3937,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/07/2026 5:35:06 PM</t>
+          <t>07/13/2026 5:16:14 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4016,22 +3986,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/06/2026 6:07:40 PM</t>
+          <t>07/13/2026 4:57:54 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4065,17 +4035,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/06/2026 4:04:58 PM</t>
+          <t>07/13/2026 2:42:02 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4085,7 +4055,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4114,20 +4084,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/06/2026 12:54:43 PM</t>
+          <t>07/11/2026 1:18:11 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>TREVIZO, ESTABAN I.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4159,7 +4133,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/05/2026 6:34:14 PM</t>
+          <t>07/10/2026 9:53:41 AM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4208,22 +4182,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/05/2026 10:38:36 AM</t>
+          <t>07/09/2026 10:54:42 AM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FOUNTAIN, RODNEY</t>
+          <t>FOFANA, MAMADOU</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4233,7 +4207,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -4247,25 +4221,27 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
-        <v>0.714</v>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/03/2026 1:10:42 PM</t>
+          <t>07/09/2026 9:49:26 AM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4275,7 +4251,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4304,20 +4280,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/03/2026 11:57:21 AM</t>
+          <t>07/07/2026 5:35:06 PM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4349,7 +4329,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/02/2026 12:41:50 PM</t>
+          <t>07/06/2026 6:07:40 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4398,7 +4378,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/30/2026 3:08:17 PM</t>
+          <t>07/06/2026 4:04:58 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4447,24 +4427,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/29/2026 5:02:30 PM</t>
+          <t>07/06/2026 12:54:43 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4496,27 +4472,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/29/2026 4:46:11 PM</t>
+          <t>07/05/2026 6:34:14 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4545,20 +4521,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/27/2026 11:52:56 AM</t>
+          <t>07/05/2026 10:38:36 AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>FOUNTAIN, RODNEY</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Air Temperature, OTR</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4566,7 +4546,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -4580,32 +4560,30 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N85" t="n">
+        <v>0.714</v>
       </c>
       <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/27/2026 11:42:51 AM</t>
+          <t>07/03/2026 1:10:42 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4639,24 +4617,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/26/2026 2:42:28 PM</t>
+          <t>07/03/2026 11:57:21 AM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Air Temperature, Local</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4688,7 +4662,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/26/2026 2:10:46 PM</t>
+          <t>07/02/2026 12:41:50 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4737,17 +4711,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/26/2026 1:33:31 PM</t>
+          <t>06/30/2026 3:08:17 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SCOTT, GRANT</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4786,22 +4760,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/26/2026 10:51:52 AM</t>
+          <t>06/29/2026 5:02:30 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GARCIA, FRANCISCO</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4835,22 +4809,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/25/2026 11:22:39 PM</t>
+          <t>06/29/2026 4:46:11 PM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4884,24 +4858,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/25/2026 1:38:37 PM</t>
+          <t>06/27/2026 11:52:56 AM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -4933,22 +4903,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/25/2026 11:29:51 AM</t>
+          <t>06/27/2026 11:42:51 AM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4982,22 +4952,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/24/2026 5:10:48 PM</t>
+          <t>06/26/2026 2:42:28 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5031,20 +5001,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/24/2026 4:03:42 PM</t>
+          <t>06/26/2026 2:10:46 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>EMERY.SHANE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5076,22 +5050,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/24/2026 5:11:55 AM</t>
+          <t>06/26/2026 1:33:31 PM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KENNEDY LINNETTE</t>
+          <t>SCOTT, GRANT</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5125,17 +5099,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/23/2026 5:11:29 PM</t>
+          <t>06/26/2026 10:51:52 AM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>GARCIA, FRANCISCO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5145,7 +5119,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5174,22 +5148,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/22/2026 4:29:35 PM</t>
+          <t>06/25/2026 11:22:39 PM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5223,17 +5197,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/22/2026 1:33:02 PM</t>
+          <t>06/25/2026 1:38:37 PM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5272,27 +5246,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/22/2026 12:51:06 PM</t>
+          <t>06/25/2026 11:29:51 AM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>WALLACE, ANDREW</t>
+          <t>ROBERT REVELES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5321,17 +5295,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/21/2026 2:38:22 PM</t>
+          <t>06/24/2026 5:10:48 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CLARK, KC</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5370,7 +5344,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/21/2026 1:24:01 PM</t>
+          <t>06/24/2026 4:03:42 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5415,22 +5389,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/20/2026 12:26:55 PM</t>
+          <t>06/24/2026 5:11:55 AM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KREUTZER, DON</t>
+          <t>KENNEDY LINNETTE</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5464,7 +5438,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06/19/2026 6:06:53 PM</t>
+          <t>06/23/2026 5:11:29 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5513,22 +5487,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>06/19/2026 5:32:27 PM</t>
+          <t>06/22/2026 4:29:35 PM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MOORE, ROYCE</t>
+          <t>MEYERS, DAVID</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, Local</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5562,22 +5536,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>06/19/2026 10:12:30 AM</t>
+          <t>06/22/2026 1:33:02 PM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5611,27 +5585,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>06/18/2026 12:45:10 PM</t>
+          <t>06/22/2026 12:51:06 PM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WALLACE, ANDREW</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5660,17 +5634,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06/18/2026 11:35:17 AM</t>
+          <t>06/21/2026 2:38:22 PM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
+          <t>CLARK, KC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5709,24 +5683,20 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>06/17/2026 3:18:01 PM</t>
+          <t>06/21/2026 1:24:01 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5758,27 +5728,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>06/17/2026 1:24:24 PM</t>
+          <t>06/20/2026 12:26:55 PM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MAGEE LONDON, TRESSEL</t>
+          <t>KREUTZER, DON</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5807,27 +5777,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>06/17/2026 9:51:05 AM</t>
+          <t>06/19/2026 6:06:53 PM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5856,22 +5826,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>06/14/2026 12:51:39 PM</t>
+          <t>06/19/2026 5:32:27 PM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MOORE, ROYCE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5905,20 +5875,24 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>06/13/2026 12:37:03 PM</t>
+          <t>06/19/2026 10:12:30 AM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -5950,22 +5924,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>06/12/2026 6:47:19 PM</t>
+          <t>06/18/2026 12:45:10 PM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5999,7 +5973,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>06/12/2026 2:22:37 PM</t>
+          <t>06/18/2026 11:35:17 AM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6048,22 +6022,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>06/12/2026 10:50:38 AM</t>
+          <t>06/17/2026 3:18:01 PM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6097,17 +6071,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06/11/2026 5:29:52 PM</t>
+          <t>06/17/2026 1:24:24 PM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>WADE,ADAM</t>
+          <t>MAGEE LONDON, TRESSEL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6117,7 +6091,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6146,22 +6120,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>06/11/2026 3:42:27 PM</t>
+          <t>06/17/2026 9:51:05 AM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6195,22 +6169,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>06/11/2026 10:57:37 AM</t>
+          <t>06/14/2026 12:51:39 PM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6244,24 +6218,20 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>06/10/2026 8:47:02 PM</t>
+          <t>06/13/2026 12:37:03 PM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -6293,20 +6263,24 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>06/10/2026 2:34:29 PM</t>
+          <t>06/12/2026 6:47:19 PM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>WELCH, GREGORY</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>MEYERS, DAVID</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Air Temperature, Local</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -6338,17 +6312,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>06/10/2026 9:58:07 AM</t>
+          <t>06/12/2026 2:22:37 PM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KELLY GNEITING</t>
+          <t>EMERY.SHANE</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6358,7 +6332,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6387,22 +6361,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>06/09/2026 8:49:37 PM</t>
+          <t>06/12/2026 10:50:38 AM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GERVACIO, ARNOLD</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6436,22 +6410,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>06/09/2026 5:15:37 PM</t>
+          <t>06/11/2026 5:29:52 PM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>WADE,ADAM</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6485,27 +6459,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>06/09/2026 9:52:33 AM</t>
+          <t>06/11/2026 3:42:27 PM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NUNEZ, WALLY</t>
+          <t>BROUSSEAU, SALLY</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6534,22 +6508,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>06/09/2026 6:09:33 AM</t>
+          <t>06/11/2026 10:57:37 AM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ROBERT REVELES</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6583,22 +6557,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>06/08/2026 10:24:03 AM</t>
+          <t>06/10/2026 8:47:02 PM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6632,24 +6606,20 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>06/08/2026 6:36:45 AM</t>
+          <t>06/10/2026 2:34:29 PM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EMERY.SHANE</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
+          <t>WELCH, GREGORY</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>OTR</t>
@@ -6681,27 +6651,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>06/07/2026 10:34:55 PM</t>
+          <t>06/10/2026 9:58:07 AM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ACKERMAN, JASON B.</t>
+          <t>KELLY GNEITING</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6730,22 +6700,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>06/05/2026 3:56:56 PM</t>
+          <t>06/09/2026 8:49:37 PM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>JELTOV, VLADIMIR K.</t>
+          <t>GERVACIO, ARNOLD</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>OTR, Safety Pro Test</t>
+          <t>Air Temperature, OTR</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6779,22 +6749,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>06/03/2026 5:14:46 PM</t>
+          <t>06/09/2026 5:15:37 PM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MEYERS, DAVID</t>
+          <t>JELTOV, VLADIMIR K.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Air Temperature, Local</t>
+          <t>OTR, Safety Pro Test</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6828,27 +6798,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>06/03/2026 3:43:38 PM</t>
+          <t>06/09/2026 9:52:33 AM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BROUSSEAU, SALLY</t>
+          <t>NUNEZ, WALLY</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Air Temperature, OTR</t>
+          <t>OTR</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6874,104 +6844,6 @@
       </c>
       <c r="O132" t="inlineStr"/>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>06/03/2026 5:35:42 AM</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>24688</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>WADE,ADAM</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Air Temperature, OTR</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>06/02/2026 1:11:41 PM</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>23470</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>JELTOV, VLADIMIR K.</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>OTR, Safety Pro Test</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>OTR</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
